--- a/data/50001524 - ATACAMA KOZAN.xlsx
+++ b/data/50001524 - ATACAMA KOZAN.xlsx
@@ -1498,13 +1498,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46080.61161974537</v>
+        <v>46080.77828641204</v>
       </c>
       <c r="C4" s="5">
-        <v>46097.66998934028</v>
+        <v>46097.83665600694</v>
       </c>
       <c r="D4" s="5">
-        <v>46097.67008267361</v>
+        <v>46097.83674934028</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1547,13 +1547,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46080.611620138894</v>
+        <v>46080.77828680555</v>
       </c>
       <c r="C5" s="8">
-        <v>46097.669548425925</v>
+        <v>46097.8362150926</v>
       </c>
       <c r="D5" s="8">
-        <v>46097.66956912037</v>
+        <v>46097.836235787036</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1610,13 +1610,13 @@
         <v>33</v>
       </c>
       <c r="B6" s="5">
-        <v>46080.61162043981</v>
+        <v>46080.778287106485</v>
       </c>
       <c r="C6" s="5">
-        <v>46097.66955386574</v>
+        <v>46097.83622053241</v>
       </c>
       <c r="D6" s="5">
-        <v>46097.66956886574</v>
+        <v>46097.836235532406</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>34</v>
@@ -1673,13 +1673,13 @@
         <v>37</v>
       </c>
       <c r="B7" s="8">
-        <v>46080.61162074074</v>
+        <v>46080.778287407404</v>
       </c>
       <c r="C7" s="8">
-        <v>46097.66956028935</v>
+        <v>46097.83622695602</v>
       </c>
       <c r="D7" s="8">
-        <v>46097.669575266205</v>
+        <v>46097.83624193287</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>38</v>
@@ -1736,13 +1736,13 @@
         <v>39</v>
       </c>
       <c r="B8" s="5">
-        <v>46080.61162106482</v>
+        <v>46080.77828773148</v>
       </c>
       <c r="C8" s="5">
-        <v>46093.47637546297</v>
+        <v>46093.643042129625</v>
       </c>
       <c r="D8" s="5">
-        <v>46100.62501127315</v>
+        <v>46100.791677939815</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>40</v>
@@ -1799,13 +1799,13 @@
         <v>42</v>
       </c>
       <c r="B9" s="8">
-        <v>46080.61162134259</v>
+        <v>46080.778288009256</v>
       </c>
       <c r="C9" s="8">
-        <v>46097.66957738426</v>
+        <v>46097.83624405092</v>
       </c>
       <c r="D9" s="8">
-        <v>46097.669591805556</v>
+        <v>46097.83625847222</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>43</v>
@@ -1862,13 +1862,13 @@
         <v>44</v>
       </c>
       <c r="B10" s="5">
-        <v>46080.61691350694</v>
+        <v>46080.78358017361</v>
       </c>
       <c r="C10" s="5">
-        <v>46141.54493447917</v>
+        <v>46141.711601145835</v>
       </c>
       <c r="D10" s="5">
-        <v>46141.54493556713</v>
+        <v>46141.7116022338</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>45</v>
@@ -1911,13 +1911,13 @@
         <v>47</v>
       </c>
       <c r="B11" s="8">
-        <v>46080.617096863425</v>
+        <v>46080.7837635301</v>
       </c>
       <c r="C11" s="8">
-        <v>46114.345154421295</v>
+        <v>46114.51182108796</v>
       </c>
       <c r="D11" s="8">
-        <v>46114.34517267361</v>
+        <v>46114.51183934028</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>48</v>
@@ -1976,13 +1976,13 @@
         <v>52</v>
       </c>
       <c r="B12" s="5">
-        <v>46080.61714857639</v>
+        <v>46080.783815243056</v>
       </c>
       <c r="C12" s="5">
-        <v>46141.54484769676</v>
+        <v>46141.71151436343</v>
       </c>
       <c r="D12" s="5">
-        <v>46141.60557300926</v>
+        <v>46141.77223967593</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>53</v>
@@ -2041,13 +2041,13 @@
         <v>58</v>
       </c>
       <c r="B13" s="8">
-        <v>46080.61162163195</v>
+        <v>46080.77828829861</v>
       </c>
       <c r="C13" s="8">
-        <v>46114.34593138889</v>
+        <v>46114.51259805556</v>
       </c>
       <c r="D13" s="8">
-        <v>46114.59239144676</v>
+        <v>46114.75905811343</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>59</v>
@@ -2092,13 +2092,13 @@
         <v>61</v>
       </c>
       <c r="B14" s="5">
-        <v>46080.6116219213</v>
+        <v>46080.778288587964</v>
       </c>
       <c r="C14" s="5">
-        <v>46114.34528306713</v>
+        <v>46114.511949733795</v>
       </c>
       <c r="D14" s="5">
-        <v>46114.34529875</v>
+        <v>46114.51196541666</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>62</v>
@@ -2157,13 +2157,13 @@
         <v>64</v>
       </c>
       <c r="B15" s="8">
-        <v>46080.61162287037</v>
+        <v>46080.77828953703</v>
       </c>
       <c r="C15" s="8">
-        <v>46114.34543883102</v>
+        <v>46114.512105497684</v>
       </c>
       <c r="D15" s="8">
-        <v>46114.345454849536</v>
+        <v>46114.51212151621</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>65</v>
@@ -2222,13 +2222,13 @@
         <v>67</v>
       </c>
       <c r="B16" s="5">
-        <v>46080.61161952546</v>
+        <v>46080.77828619213</v>
       </c>
       <c r="C16" s="5">
-        <v>46114.345740000004</v>
+        <v>46114.51240666666</v>
       </c>
       <c r="D16" s="5">
-        <v>46114.34575462963</v>
+        <v>46114.5124212963</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>68</v>
@@ -2287,13 +2287,13 @@
         <v>70</v>
       </c>
       <c r="B17" s="8">
-        <v>46080.61161986111</v>
+        <v>46080.77828652778</v>
       </c>
       <c r="C17" s="8">
-        <v>46114.34591538194</v>
+        <v>46114.512582048614</v>
       </c>
       <c r="D17" s="8">
-        <v>46114.34593252315</v>
+        <v>46114.51259918981</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>71</v>
@@ -2352,13 +2352,13 @@
         <v>74</v>
       </c>
       <c r="B18" s="5">
-        <v>46080.611620208336</v>
+        <v>46080.778286875</v>
       </c>
       <c r="C18" s="5">
-        <v>46126.68891861111</v>
+        <v>46126.85558527778</v>
       </c>
       <c r="D18" s="5">
-        <v>46126.6889318287</v>
+        <v>46126.85559849537</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>75</v>
@@ -2405,13 +2405,13 @@
         <v>77</v>
       </c>
       <c r="B19" s="8">
-        <v>46080.61162048611</v>
+        <v>46080.778287152774</v>
       </c>
       <c r="C19" s="8">
-        <v>46114.345347615745</v>
+        <v>46114.51201428241</v>
       </c>
       <c r="D19" s="8">
-        <v>46114.345363518514</v>
+        <v>46114.512030185186</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>78</v>
@@ -2470,13 +2470,13 @@
         <v>80</v>
       </c>
       <c r="B20" s="5">
-        <v>46080.61162085648</v>
+        <v>46080.77828752315</v>
       </c>
       <c r="C20" s="5">
-        <v>46114.34608914352</v>
+        <v>46114.51275581018</v>
       </c>
       <c r="D20" s="5">
-        <v>46114.34610408565</v>
+        <v>46114.51277075231</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>81</v>
@@ -2535,13 +2535,13 @@
         <v>83</v>
       </c>
       <c r="B21" s="8">
-        <v>46080.61162113426</v>
+        <v>46080.77828780093</v>
       </c>
       <c r="C21" s="8">
-        <v>46126.68889943287</v>
+        <v>46126.85556609953</v>
       </c>
       <c r="D21" s="8">
-        <v>46126.6889155324</v>
+        <v>46126.855582199074</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>84</v>
@@ -2600,13 +2600,13 @@
         <v>87</v>
       </c>
       <c r="B22" s="5">
-        <v>46080.61739265046</v>
+        <v>46080.78405931713</v>
       </c>
       <c r="C22" s="5">
-        <v>46114.34641268519</v>
+        <v>46114.51307935185</v>
       </c>
       <c r="D22" s="5">
-        <v>46114.34642909722</v>
+        <v>46114.51309576389</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>88</v>
@@ -2665,13 +2665,13 @@
         <v>90</v>
       </c>
       <c r="B23" s="8">
-        <v>46080.61162144676</v>
+        <v>46080.778288113426</v>
       </c>
       <c r="C23" s="8">
-        <v>46114.34650914352</v>
+        <v>46114.513175810185</v>
       </c>
       <c r="D23" s="8">
-        <v>46114.34660958333</v>
+        <v>46114.51327625</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>91</v>
@@ -2730,13 +2730,13 @@
         <v>93</v>
       </c>
       <c r="B24" s="5">
-        <v>46080.61162173611</v>
+        <v>46080.77828840278</v>
       </c>
       <c r="C24" s="5">
-        <v>46114.593050069445</v>
+        <v>46114.75971673611</v>
       </c>
       <c r="D24" s="5">
-        <v>46114.593065532405</v>
+        <v>46114.759732199076</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>94</v>
@@ -2795,13 +2795,13 @@
         <v>98</v>
       </c>
       <c r="B25" s="8">
-        <v>46080.61162202546</v>
+        <v>46080.778288692134</v>
       </c>
       <c r="C25" s="8">
-        <v>46140.67228493055</v>
+        <v>46140.83895159722</v>
       </c>
       <c r="D25" s="8">
-        <v>46140.67228600694</v>
+        <v>46140.838952673614</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>99</v>
@@ -2844,13 +2844,13 @@
         <v>101</v>
       </c>
       <c r="B26" s="5">
-        <v>46080.61162231481</v>
+        <v>46080.778288981484</v>
       </c>
       <c r="C26" s="5">
-        <v>46139.61452841436</v>
+        <v>46139.781195081014</v>
       </c>
       <c r="D26" s="5">
-        <v>46139.614539560185</v>
+        <v>46139.78120622685</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>102</v>
@@ -2909,13 +2909,13 @@
         <v>106</v>
       </c>
       <c r="B27" s="8">
-        <v>46080.611619351854</v>
+        <v>46080.77828601852</v>
       </c>
       <c r="C27" s="8">
-        <v>46139.61441649306</v>
+        <v>46139.78108315972</v>
       </c>
       <c r="D27" s="8">
-        <v>46139.61441783565</v>
+        <v>46139.78108450232</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>107</v>
@@ -2970,13 +2970,13 @@
         <v>110</v>
       </c>
       <c r="B28" s="5">
-        <v>46080.61161972222</v>
+        <v>46080.778286388886</v>
       </c>
       <c r="C28" s="5">
-        <v>46139.6145152199</v>
+        <v>46139.781181886574</v>
       </c>
       <c r="D28" s="5">
-        <v>46139.61451663195</v>
+        <v>46139.78118329861</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>111</v>
@@ -3031,13 +3031,13 @@
         <v>112</v>
       </c>
       <c r="B29" s="8">
-        <v>46080.617547939815</v>
+        <v>46080.78421460648</v>
       </c>
       <c r="C29" s="8">
-        <v>46140.64236803241</v>
+        <v>46140.80903469908</v>
       </c>
       <c r="D29" s="8">
-        <v>46140.642443206016</v>
+        <v>46140.80910987269</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>113</v>
@@ -3096,13 +3096,13 @@
         <v>115</v>
       </c>
       <c r="B30" s="5">
-        <v>46080.61797731482</v>
+        <v>46080.78464398148</v>
       </c>
       <c r="C30" s="5">
-        <v>46114.59513332176</v>
+        <v>46114.761799988424</v>
       </c>
       <c r="D30" s="5">
-        <v>46114.595134641204</v>
+        <v>46114.761801307875</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>116</v>
@@ -3151,13 +3151,13 @@
         <v>118</v>
       </c>
       <c r="B31" s="8">
-        <v>46080.61805363426</v>
+        <v>46080.78472030093</v>
       </c>
       <c r="C31" s="8">
-        <v>46140.64228364584</v>
+        <v>46140.8089503125</v>
       </c>
       <c r="D31" s="8">
-        <v>46140.642285671296</v>
+        <v>46140.80895233796</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>119</v>
@@ -3206,13 +3206,13 @@
         <v>121</v>
       </c>
       <c r="B32" s="5">
-        <v>46080.61161998843</v>
+        <v>46080.77828665509</v>
       </c>
       <c r="C32" s="5">
-        <v>46133.45426238426</v>
+        <v>46133.62092905093</v>
       </c>
       <c r="D32" s="5">
-        <v>46154.02539614584</v>
+        <v>46154.1920628125</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>122</v>
@@ -3271,13 +3271,13 @@
         <v>124</v>
       </c>
       <c r="B33" s="8">
-        <v>46080.611620254625</v>
+        <v>46080.7782869213</v>
       </c>
       <c r="C33" s="8">
-        <v>46133.45419553241</v>
+        <v>46133.62086219907</v>
       </c>
       <c r="D33" s="8">
-        <v>46133.454196597224</v>
+        <v>46133.62086326389</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>125</v>
@@ -3332,13 +3332,13 @@
         <v>127</v>
       </c>
       <c r="B34" s="5">
-        <v>46080.61162052084</v>
+        <v>46080.778287187495</v>
       </c>
       <c r="C34" s="5">
-        <v>46133.45423341435</v>
+        <v>46133.62090008102</v>
       </c>
       <c r="D34" s="5">
-        <v>46133.45423459491</v>
+        <v>46133.62090126157</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>128</v>
@@ -3393,13 +3393,13 @@
         <v>130</v>
       </c>
       <c r="B35" s="8">
-        <v>46080.61162079861</v>
+        <v>46080.77828746528</v>
       </c>
       <c r="C35" s="8">
-        <v>46114.59660967592</v>
+        <v>46114.76327634259</v>
       </c>
       <c r="D35" s="8">
-        <v>46114.59662506945</v>
+        <v>46114.76329173611</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>131</v>
@@ -3458,13 +3458,13 @@
         <v>133</v>
       </c>
       <c r="B36" s="5">
-        <v>46080.61162106482</v>
+        <v>46080.77828773148</v>
       </c>
       <c r="C36" s="5">
-        <v>46114.59652575231</v>
+        <v>46114.76319241898</v>
       </c>
       <c r="D36" s="5">
-        <v>46114.596526875</v>
+        <v>46114.76319354167</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>134</v>
@@ -3519,13 +3519,13 @@
         <v>136</v>
       </c>
       <c r="B37" s="8">
-        <v>46080.611621331016</v>
+        <v>46080.77828799769</v>
       </c>
       <c r="C37" s="8">
-        <v>46114.59658092592</v>
+        <v>46114.76324759259</v>
       </c>
       <c r="D37" s="8">
-        <v>46114.59658221065</v>
+        <v>46114.763248877316</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>137</v>
@@ -3580,13 +3580,13 @@
         <v>139</v>
       </c>
       <c r="B38" s="5">
-        <v>46080.611621585645</v>
+        <v>46080.77828825232</v>
       </c>
       <c r="C38" s="5">
-        <v>46114.596591678244</v>
+        <v>46114.76325834491</v>
       </c>
       <c r="D38" s="5">
-        <v>46114.59659328704</v>
+        <v>46114.7632599537</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>140</v>
@@ -3641,13 +3641,13 @@
         <v>142</v>
       </c>
       <c r="B39" s="8">
-        <v>46080.61162185185</v>
+        <v>46080.778288518515</v>
       </c>
       <c r="C39" s="8">
-        <v>46121.69341248843</v>
+        <v>46121.86007915509</v>
       </c>
       <c r="D39" s="8">
-        <v>46149.030915219904</v>
+        <v>46149.197581886576</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>143</v>
@@ -3706,13 +3706,13 @@
         <v>147</v>
       </c>
       <c r="B40" s="5">
-        <v>46080.611620069445</v>
+        <v>46080.77828673611</v>
       </c>
       <c r="C40" s="5">
-        <v>46114.5931810301</v>
+        <v>46114.759847696754</v>
       </c>
       <c r="D40" s="5">
-        <v>46121.693403067125</v>
+        <v>46121.8600697338</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>148</v>
@@ -3767,13 +3767,13 @@
         <v>150</v>
       </c>
       <c r="B41" s="8">
-        <v>46080.611620358795</v>
+        <v>46080.77828702546</v>
       </c>
       <c r="C41" s="8">
-        <v>46121.69339813657</v>
+        <v>46121.860064803244</v>
       </c>
       <c r="D41" s="8">
-        <v>46121.69339930556</v>
+        <v>46121.86006597222</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>149</v>
@@ -3828,13 +3828,13 @@
         <v>152</v>
       </c>
       <c r="B42" s="5">
-        <v>46080.611620578704</v>
+        <v>46080.77828724537</v>
       </c>
       <c r="C42" s="5">
-        <v>46114.59384487268</v>
+        <v>46114.76051153935</v>
       </c>
       <c r="D42" s="5">
-        <v>46114.593975717595</v>
+        <v>46114.76064238426</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>153</v>
@@ -3893,13 +3893,13 @@
         <v>155</v>
       </c>
       <c r="B43" s="8">
-        <v>46080.61162082176</v>
+        <v>46080.77828748843</v>
       </c>
       <c r="C43" s="8">
-        <v>46114.59378298611</v>
+        <v>46114.76044965278</v>
       </c>
       <c r="D43" s="8">
-        <v>46114.593784282406</v>
+        <v>46114.76045094908</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>156</v>
@@ -3954,13 +3954,13 @@
         <v>158</v>
       </c>
       <c r="B44" s="5">
-        <v>46080.611621041666</v>
+        <v>46080.77828770834</v>
       </c>
       <c r="C44" s="5">
-        <v>46114.593829687496</v>
+        <v>46114.76049635417</v>
       </c>
       <c r="D44" s="5">
-        <v>46114.59383114583</v>
+        <v>46114.7604978125</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>159</v>
@@ -4015,13 +4015,13 @@
         <v>161</v>
       </c>
       <c r="B45" s="8">
-        <v>46080.61162127314</v>
+        <v>46080.778287939815</v>
       </c>
       <c r="C45" s="8">
-        <v>46140.672237499995</v>
+        <v>46140.83890416667</v>
       </c>
       <c r="D45" s="8">
-        <v>46141.60567505787</v>
+        <v>46141.772341724536</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>162</v>
@@ -4064,13 +4064,13 @@
         <v>164</v>
       </c>
       <c r="B46" s="5">
-        <v>46080.611621516204</v>
+        <v>46080.778288182875</v>
       </c>
       <c r="C46" s="5">
-        <v>46127.511413229164</v>
+        <v>46127.678079895835</v>
       </c>
       <c r="D46" s="5">
-        <v>46127.51143438657</v>
+        <v>46127.67810105324</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>165</v>
@@ -4129,13 +4129,13 @@
         <v>169</v>
       </c>
       <c r="B47" s="8">
-        <v>46080.611621759264</v>
+        <v>46080.77828842592</v>
       </c>
       <c r="C47" s="8">
-        <v>46127.511464745374</v>
+        <v>46127.67813141204</v>
       </c>
       <c r="D47" s="8">
-        <v>46158.00329228009</v>
+        <v>46158.16995894676</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>170</v>
@@ -4194,13 +4194,13 @@
         <v>175</v>
       </c>
       <c r="B48" s="5">
-        <v>46087.36977493056</v>
+        <v>46087.53644159722</v>
       </c>
       <c r="C48" s="5">
-        <v>46127.51151408565</v>
+        <v>46127.678180752315</v>
       </c>
       <c r="D48" s="5">
-        <v>46161.04121914352</v>
+        <v>46161.20788581019</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>176</v>
@@ -4257,13 +4257,13 @@
         <v>178</v>
       </c>
       <c r="B49" s="8">
-        <v>46087.36985466436</v>
+        <v>46087.536521331014</v>
       </c>
       <c r="C49" s="8">
-        <v>46140.67220598379</v>
+        <v>46140.83887265046</v>
       </c>
       <c r="D49" s="8">
-        <v>46141.60512039352</v>
+        <v>46141.771787060185</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>179</v>
@@ -4322,13 +4322,13 @@
         <v>182</v>
       </c>
       <c r="B50" s="5">
-        <v>46080.61162200231</v>
+        <v>46080.77828866898</v>
       </c>
       <c r="C50" s="5">
-        <v>46133.453843993055</v>
+        <v>46133.62051065972</v>
       </c>
       <c r="D50" s="5">
-        <v>46141.60591856482</v>
+        <v>46141.772585231476</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>183</v>
@@ -4371,13 +4371,13 @@
         <v>185</v>
       </c>
       <c r="B51" s="8">
-        <v>46080.61162225694</v>
+        <v>46080.77828892361</v>
       </c>
       <c r="C51" s="8">
-        <v>46133.45377119213</v>
+        <v>46133.6204378588</v>
       </c>
       <c r="D51" s="8">
-        <v>46151.01806096065</v>
+        <v>46151.18472762732</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>186</v>
@@ -4436,13 +4436,13 @@
         <v>190</v>
       </c>
       <c r="B52" s="5">
-        <v>46080.6116209375</v>
+        <v>46080.77828760417</v>
       </c>
       <c r="C52" s="5">
-        <v>46133.45382759259</v>
+        <v>46133.62049425926</v>
       </c>
       <c r="D52" s="5">
-        <v>46155.03748122686</v>
+        <v>46155.20414789351</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>191</v>
@@ -4501,13 +4501,13 @@
         <v>195</v>
       </c>
       <c r="B53" s="8">
-        <v>46080.61162134259</v>
+        <v>46080.778288009256</v>
       </c>
       <c r="C53" s="8">
-        <v>46132.6010328125</v>
+        <v>46132.76769947917</v>
       </c>
       <c r="D53" s="8">
-        <v>46141.60519509259</v>
+        <v>46141.77186175926</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>196</v>
@@ -4550,13 +4550,13 @@
         <v>198</v>
       </c>
       <c r="B54" s="5">
-        <v>46080.61162165509</v>
+        <v>46080.77828832176</v>
       </c>
       <c r="C54" s="5">
-        <v>46128.32315582176</v>
+        <v>46128.489822488424</v>
       </c>
       <c r="D54" s="5">
-        <v>46165.01464451389</v>
+        <v>46165.18131118055</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>199</v>
@@ -4615,13 +4615,13 @@
         <v>203</v>
       </c>
       <c r="B55" s="8">
-        <v>46080.611621944445</v>
+        <v>46080.77828861111</v>
       </c>
       <c r="C55" s="8">
-        <v>46128.323210532406</v>
+        <v>46128.48987719907</v>
       </c>
       <c r="D55" s="8">
-        <v>46170.01854524306</v>
+        <v>46170.185211909724</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>204</v>
@@ -4680,13 +4680,13 @@
         <v>207</v>
       </c>
       <c r="B56" s="5">
-        <v>46080.61162224537</v>
+        <v>46080.778288912035</v>
       </c>
       <c r="C56" s="5">
-        <v>46132.601014907406</v>
+        <v>46132.76768157407</v>
       </c>
       <c r="D56" s="5">
-        <v>46172.03607802083</v>
+        <v>46172.2027446875</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>208</v>
@@ -4745,13 +4745,13 @@
         <v>211</v>
       </c>
       <c r="B57" s="8">
-        <v>46080.6116225463</v>
+        <v>46080.77828921296</v>
       </c>
       <c r="C57" s="8">
-        <v>46141.54462414352</v>
+        <v>46141.711290810184</v>
       </c>
       <c r="D57" s="8">
-        <v>46141.60565009259</v>
+        <v>46141.77231675926</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>183</v>
@@ -4794,13 +4794,13 @@
         <v>213</v>
       </c>
       <c r="B58" s="5">
-        <v>46080.6116229051</v>
+        <v>46080.77828957176</v>
       </c>
       <c r="C58" s="5">
-        <v>46133.45436618055</v>
+        <v>46133.62103284722</v>
       </c>
       <c r="D58" s="5">
-        <v>46156.00241715278</v>
+        <v>46156.16908381945</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>214</v>
@@ -4859,13 +4859,13 @@
         <v>216</v>
       </c>
       <c r="B59" s="8">
-        <v>46080.61162319445</v>
+        <v>46080.77828986111</v>
       </c>
       <c r="C59" s="8">
-        <v>46133.454379965275</v>
+        <v>46133.621046631946</v>
       </c>
       <c r="D59" s="8">
-        <v>46133.45523274306</v>
+        <v>46133.62189940972</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>217</v>
@@ -4924,13 +4924,13 @@
         <v>219</v>
       </c>
       <c r="B60" s="5">
-        <v>46080.61162347222</v>
+        <v>46080.778290138885</v>
       </c>
       <c r="C60" s="5">
-        <v>46121.70129114583</v>
+        <v>46121.8679578125</v>
       </c>
       <c r="D60" s="5">
-        <v>46121.70131851852</v>
+        <v>46121.867985185185</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>220</v>
@@ -4989,13 +4989,13 @@
         <v>222</v>
       </c>
       <c r="B61" s="8">
-        <v>46080.61162372685</v>
+        <v>46080.778290393515</v>
       </c>
       <c r="C61" s="8">
-        <v>46121.70122795139</v>
+        <v>46121.86789461806</v>
       </c>
       <c r="D61" s="8">
-        <v>46121.701245069446</v>
+        <v>46121.86791173611</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>223</v>
@@ -5054,13 +5054,13 @@
         <v>225</v>
       </c>
       <c r="B62" s="5">
-        <v>46080.61881302083</v>
+        <v>46080.7854796875</v>
       </c>
       <c r="C62" s="5">
-        <v>46141.60555273148</v>
+        <v>46141.772219398146</v>
       </c>
       <c r="D62" s="5">
-        <v>46141.60557478009</v>
+        <v>46141.77224144676</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>54</v>
@@ -5119,13 +5119,13 @@
         <v>227</v>
       </c>
       <c r="B63" s="8">
-        <v>46080.61161995371</v>
+        <v>46080.77828662037</v>
       </c>
       <c r="C63" s="8">
-        <v>46141.54460908565</v>
+        <v>46141.711275752314</v>
       </c>
       <c r="D63" s="8">
-        <v>46141.544611226855</v>
+        <v>46141.71127789352</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>228</v>
@@ -5168,13 +5168,13 @@
         <v>230</v>
       </c>
       <c r="B64" s="5">
-        <v>46080.61162027778</v>
+        <v>46080.77828694445</v>
       </c>
       <c r="C64" s="5">
-        <v>46133.454125856486</v>
+        <v>46133.62079252314</v>
       </c>
       <c r="D64" s="5">
-        <v>46184.00832508102</v>
+        <v>46184.174991747685</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>231</v>
@@ -5233,13 +5233,13 @@
         <v>234</v>
       </c>
       <c r="B65" s="8">
-        <v>46080.61162052084</v>
+        <v>46080.778287187495</v>
       </c>
       <c r="C65" s="8">
-        <v>46133.45420378472</v>
+        <v>46133.620870451385</v>
       </c>
       <c r="D65" s="8">
-        <v>46133.454246608795</v>
+        <v>46133.62091327546</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>235</v>
@@ -5298,13 +5298,13 @@
         <v>238</v>
       </c>
       <c r="B66" s="5">
-        <v>46080.61162079861</v>
+        <v>46080.77828746528</v>
       </c>
       <c r="C66" s="5">
-        <v>46133.45511944444</v>
+        <v>46133.62178611111</v>
       </c>
       <c r="D66" s="5">
-        <v>46133.455135324075</v>
+        <v>46133.62180199074</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>239</v>
@@ -5363,13 +5363,13 @@
         <v>241</v>
       </c>
       <c r="B67" s="8">
-        <v>46080.611621041666</v>
+        <v>46080.77828770834</v>
       </c>
       <c r="C67" s="8">
-        <v>46133.45513137731</v>
+        <v>46133.62179804398</v>
       </c>
       <c r="D67" s="8">
-        <v>46133.45514824074</v>
+        <v>46133.62181490741</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>242</v>
@@ -5428,13 +5428,13 @@
         <v>244</v>
       </c>
       <c r="B68" s="5">
-        <v>46080.611621296295</v>
+        <v>46080.77828796297</v>
       </c>
       <c r="C68" s="5">
-        <v>46133.45515101852</v>
+        <v>46133.62181768518</v>
       </c>
       <c r="D68" s="5">
-        <v>46133.455167175925</v>
+        <v>46133.6218338426</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>245</v>
@@ -5493,13 +5493,13 @@
         <v>247</v>
       </c>
       <c r="B69" s="8">
-        <v>46080.611621550925</v>
+        <v>46080.778288217596</v>
       </c>
       <c r="C69" s="8">
-        <v>46133.455206886574</v>
+        <v>46133.621873553246</v>
       </c>
       <c r="D69" s="8">
-        <v>46133.45522304398</v>
+        <v>46133.621889710645</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>180</v>
@@ -5558,13 +5558,13 @@
         <v>250</v>
       </c>
       <c r="B70" s="5">
-        <v>46080.611621793985</v>
+        <v>46080.77828846065</v>
       </c>
       <c r="C70" s="5">
-        <v>46140.67233574074</v>
+        <v>46140.8390024074</v>
       </c>
       <c r="D70" s="5">
-        <v>46141.54510638889</v>
+        <v>46141.711773055555</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>181</v>
@@ -5623,13 +5623,13 @@
         <v>252</v>
       </c>
       <c r="B71" s="8">
-        <v>46080.61162203704</v>
+        <v>46080.7782887037</v>
       </c>
       <c r="C71" s="8">
-        <v>46141.5453846875</v>
+        <v>46141.71205135417</v>
       </c>
       <c r="D71" s="8">
-        <v>46141.54538606481</v>
+        <v>46141.712052731484</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>253</v>
@@ -5672,13 +5672,13 @@
         <v>255</v>
       </c>
       <c r="B72" s="5">
-        <v>46080.61162229167</v>
+        <v>46080.77828895833</v>
       </c>
       <c r="C72" s="5">
-        <v>46140.67238</v>
+        <v>46140.83904666667</v>
       </c>
       <c r="D72" s="5">
-        <v>46141.54513895833</v>
+        <v>46141.711805625004</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>256</v>
@@ -5737,13 +5737,13 @@
         <v>260</v>
       </c>
       <c r="B73" s="8">
-        <v>46080.61162048611</v>
+        <v>46080.778287152774</v>
       </c>
       <c r="C73" s="8">
-        <v>46141.54505951389</v>
+        <v>46141.711726180554</v>
       </c>
       <c r="D73" s="8">
-        <v>46141.54516234953</v>
+        <v>46141.7118290162</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>261</v>
@@ -5802,13 +5802,13 @@
         <v>264</v>
       </c>
       <c r="B74" s="5">
-        <v>46080.61162084491</v>
+        <v>46080.77828751157</v>
       </c>
       <c r="C74" s="5">
-        <v>46141.54524869213</v>
+        <v>46141.7119153588</v>
       </c>
       <c r="D74" s="5">
-        <v>46141.54525033565</v>
+        <v>46141.711917002314</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>265</v>
@@ -5867,13 +5867,13 @@
         <v>267</v>
       </c>
       <c r="B75" s="8">
-        <v>46080.61162115741</v>
+        <v>46080.77828782407</v>
       </c>
       <c r="C75" s="8">
-        <v>46141.545294236115</v>
+        <v>46141.71196090278</v>
       </c>
       <c r="D75" s="8">
-        <v>46141.54529546296</v>
+        <v>46141.71196212963</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>268</v>
@@ -5932,11 +5932,11 @@
         <v>270</v>
       </c>
       <c r="B76" s="5">
-        <v>46080.61162142361</v>
+        <v>46080.77828809028</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46090.44426309028</v>
+        <v>46090.61092975695</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>271</v>
@@ -5979,11 +5979,11 @@
         <v>273</v>
       </c>
       <c r="B77" s="8">
-        <v>46080.611622013894</v>
+        <v>46080.77828868055</v>
       </c>
       <c r="C77" s="9"/>
       <c r="D77" s="8">
-        <v>46141.54530271991</v>
+        <v>46141.711969386575</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>73</v>
@@ -6042,11 +6042,11 @@
         <v>277</v>
       </c>
       <c r="B78" s="5">
-        <v>46080.611621689815</v>
+        <v>46080.77828835648</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46141.54530398148</v>
+        <v>46141.711970648146</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>278</v>
@@ -6105,11 +6105,11 @@
         <v>279</v>
       </c>
       <c r="B79" s="8">
-        <v>46090.44504910879</v>
+        <v>46090.61171577546</v>
       </c>
       <c r="C79" s="9"/>
       <c r="D79" s="8">
-        <v>46090.44786366898</v>
+        <v>46090.614530335646</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>280</v>
@@ -6158,11 +6158,11 @@
         <v>282</v>
       </c>
       <c r="B80" s="5">
-        <v>46090.44533261574</v>
+        <v>46090.61199928241</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46141.545305277774</v>
+        <v>46141.711971944445</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>283</v>
@@ -6221,11 +6221,11 @@
         <v>285</v>
       </c>
       <c r="B81" s="8">
-        <v>46090.4454134375</v>
+        <v>46090.61208010417</v>
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="8">
-        <v>46090.45203153935</v>
+        <v>46090.61869820602</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>286</v>

--- a/data/50001524 - ATACAMA KOZAN.xlsx
+++ b/data/50001524 - ATACAMA KOZAN.xlsx
@@ -358,6 +358,9 @@
     <t xml:space="preserve">Generacion oc Tableros ,Fabricacion Tableros </t>
   </si>
   <si>
+    <t>Media</t>
+  </si>
+  <si>
     <t>1213458788103571</t>
   </si>
   <si>
@@ -710,9 +713,6 @@
   </si>
   <si>
     <t>Montaje motor,Montaje Alabe,Montaje Rodete,Montaje Sensor,Montaje:</t>
-  </si>
-  <si>
-    <t>Media</t>
   </si>
   <si>
     <t>1213470416901286</t>
@@ -3037,7 +3037,7 @@
         <v>46140.80903469908</v>
       </c>
       <c r="D29" s="8">
-        <v>46140.80910987269</v>
+        <v>46191.20398373842</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>113</v>
@@ -3075,8 +3075,8 @@
       <c r="P29" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="Q29" s="11" t="s">
-        <v>56</v>
+      <c r="Q29" s="12" t="s">
+        <v>115</v>
       </c>
       <c r="R29" s="9">
         <v>1</v>
@@ -3093,7 +3093,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B30" s="5">
         <v>46080.78464398148</v>
@@ -3105,7 +3105,7 @@
         <v>46114.761801307875</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
@@ -3138,7 +3138,7 @@
         <v>88</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
@@ -3148,7 +3148,7 @@
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B31" s="8">
         <v>46080.78472030093</v>
@@ -3160,7 +3160,7 @@
         <v>46140.80895233796</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>26</v>
@@ -3190,10 +3190,10 @@
         <v>113</v>
       </c>
       <c r="O31" s="9" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="P31" s="9" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="Q31" s="9"/>
       <c r="R31" s="9"/>
@@ -3203,7 +3203,7 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B32" s="5">
         <v>46080.77828665509</v>
@@ -3215,7 +3215,7 @@
         <v>46154.1920628125</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
@@ -3245,7 +3245,7 @@
         <v>99</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="P32" s="6" t="s">
         <v>99</v>
@@ -3268,7 +3268,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B33" s="8">
         <v>46080.7782869213</v>
@@ -3280,7 +3280,7 @@
         <v>46133.62086326389</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>26</v>
@@ -3307,13 +3307,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="O33" s="9" t="s">
         <v>84</v>
       </c>
       <c r="P33" s="9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="Q33" s="11" t="s">
         <v>56</v>
@@ -3329,7 +3329,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B34" s="5">
         <v>46080.778287187495</v>
@@ -3341,7 +3341,7 @@
         <v>46133.62090126157</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
@@ -3368,13 +3368,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="Q34" s="11" t="s">
         <v>56</v>
@@ -3390,7 +3390,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B35" s="8">
         <v>46080.77828746528</v>
@@ -3402,7 +3402,7 @@
         <v>46114.76329173611</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>26</v>
@@ -3432,7 +3432,7 @@
         <v>99</v>
       </c>
       <c r="O35" s="9" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="P35" s="9" t="s">
         <v>99</v>
@@ -3455,7 +3455,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B36" s="5">
         <v>46080.77828773148</v>
@@ -3467,7 +3467,7 @@
         <v>46114.76319354167</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
@@ -3494,13 +3494,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="O36" s="6" t="s">
         <v>78</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="Q36" s="11" t="s">
         <v>56</v>
@@ -3516,7 +3516,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B37" s="8">
         <v>46080.77828799769</v>
@@ -3528,7 +3528,7 @@
         <v>46114.763248877316</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>26</v>
@@ -3555,13 +3555,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="9" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="O37" s="9" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="P37" s="9" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="Q37" s="11" t="s">
         <v>56</v>
@@ -3577,7 +3577,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B38" s="5">
         <v>46080.77828825232</v>
@@ -3589,7 +3589,7 @@
         <v>46114.7632599537</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
@@ -3616,13 +3616,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="Q38" s="11" t="s">
         <v>56</v>
@@ -3638,7 +3638,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B39" s="8">
         <v>46080.778288518515</v>
@@ -3650,16 +3650,16 @@
         <v>46149.197581886576</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="I39" s="8">
         <v>46100</v>
@@ -3680,7 +3680,7 @@
         <v>99</v>
       </c>
       <c r="O39" s="9" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="P39" s="9" t="s">
         <v>99</v>
@@ -3703,7 +3703,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B40" s="5">
         <v>46080.77828673611</v>
@@ -3715,16 +3715,16 @@
         <v>46121.8600697338</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="I40" s="5">
         <v>46100</v>
@@ -3742,13 +3742,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="Q40" s="11" t="s">
         <v>56</v>
@@ -3764,7 +3764,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B41" s="8">
         <v>46080.77828702546</v>
@@ -3776,16 +3776,16 @@
         <v>46121.86006597222</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="I41" s="8">
         <v>46120</v>
@@ -3803,13 +3803,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="9" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O41" s="9" t="s">
         <v>94</v>
       </c>
       <c r="P41" s="9" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Q41" s="11" t="s">
         <v>56</v>
@@ -3825,7 +3825,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B42" s="5">
         <v>46080.77828724537</v>
@@ -3837,16 +3837,16 @@
         <v>46114.76064238426</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="I42" s="5">
         <v>46100</v>
@@ -3867,7 +3867,7 @@
         <v>99</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>99</v>
@@ -3890,7 +3890,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B43" s="8">
         <v>46080.77828748843</v>
@@ -3902,16 +3902,16 @@
         <v>46114.76045094908</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="I43" s="8">
         <v>46100</v>
@@ -3929,13 +3929,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="O43" s="9" t="s">
         <v>91</v>
       </c>
       <c r="P43" s="9" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Q43" s="11" t="s">
         <v>56</v>
@@ -3951,7 +3951,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B44" s="5">
         <v>46080.77828770834</v>
@@ -3963,16 +3963,16 @@
         <v>46114.7604978125</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="I44" s="5">
         <v>46129</v>
@@ -3990,13 +3990,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q44" s="11" t="s">
         <v>56</v>
@@ -4012,7 +4012,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B45" s="8">
         <v>46080.778287939815</v>
@@ -4024,7 +4024,7 @@
         <v>46141.772341724536</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>25</v>
@@ -4048,7 +4048,7 @@
         <v>26</v>
       </c>
       <c r="O45" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="P45" s="9" t="s">
         <v>26</v>
@@ -4061,7 +4061,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B46" s="5">
         <v>46080.778288182875</v>
@@ -4073,16 +4073,16 @@
         <v>46127.67810105324</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="I46" s="5">
         <v>46098</v>
@@ -4100,13 +4100,13 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="O46" s="6" t="s">
         <v>68</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q46" s="10" t="s">
         <v>31</v>
@@ -4126,7 +4126,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B47" s="8">
         <v>46080.77828842592</v>
@@ -4138,16 +4138,16 @@
         <v>46158.16995894676</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="I47" s="8">
         <v>46140</v>
@@ -4165,13 +4165,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="O47" s="9" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="P47" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q47" s="10" t="s">
         <v>31</v>
@@ -4191,7 +4191,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B48" s="5">
         <v>46087.53644159722</v>
@@ -4203,16 +4203,16 @@
         <v>46161.20788581019</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="I48" s="6"/>
       <c r="J48" s="5">
@@ -4228,13 +4228,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q48" s="10" t="s">
         <v>31</v>
@@ -4254,7 +4254,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B49" s="8">
         <v>46087.536521331014</v>
@@ -4266,16 +4266,16 @@
         <v>46141.771787060185</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="I49" s="8">
         <v>46233</v>
@@ -4293,13 +4293,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="9" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P49" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q49" s="11" t="s">
         <v>56</v>
@@ -4319,7 +4319,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B50" s="5">
         <v>46080.77828866898</v>
@@ -4331,7 +4331,7 @@
         <v>46141.772585231476</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>25</v>
@@ -4355,7 +4355,7 @@
         <v>26</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>26</v>
@@ -4368,7 +4368,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B51" s="8">
         <v>46080.77828892361</v>
@@ -4380,16 +4380,16 @@
         <v>46151.18472762732</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="I51" s="8">
         <v>46149</v>
@@ -4407,13 +4407,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="O51" s="9" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q51" s="10" t="s">
         <v>31</v>
@@ -4433,7 +4433,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B52" s="5">
         <v>46080.77828760417</v>
@@ -4445,16 +4445,16 @@
         <v>46155.20414789351</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I52" s="5">
         <v>46153</v>
@@ -4472,13 +4472,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q52" s="10" t="s">
         <v>31</v>
@@ -4498,7 +4498,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B53" s="8">
         <v>46080.778288009256</v>
@@ -4510,7 +4510,7 @@
         <v>46141.77186175926</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>25</v>
@@ -4534,7 +4534,7 @@
         <v>26</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P53" s="9" t="s">
         <v>26</v>
@@ -4547,7 +4547,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B54" s="5">
         <v>46080.77828832176</v>
@@ -4559,16 +4559,16 @@
         <v>46165.18131118055</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="I54" s="5">
         <v>46155</v>
@@ -4586,13 +4586,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q54" s="10" t="s">
         <v>31</v>
@@ -4612,7 +4612,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B55" s="8">
         <v>46080.77828861111</v>
@@ -4624,16 +4624,16 @@
         <v>46170.185211909724</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H55" s="9" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="I55" s="8">
         <v>46167</v>
@@ -4651,13 +4651,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="9" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="P55" s="9" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q55" s="10" t="s">
         <v>31</v>
@@ -4677,7 +4677,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B56" s="5">
         <v>46080.778288912035</v>
@@ -4689,16 +4689,16 @@
         <v>46172.2027446875</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I56" s="5">
         <v>46170</v>
@@ -4716,13 +4716,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q56" s="10" t="s">
         <v>31</v>
@@ -4742,7 +4742,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B57" s="8">
         <v>46080.77828921296</v>
@@ -4754,7 +4754,7 @@
         <v>46141.77231675926</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>25</v>
@@ -4778,7 +4778,7 @@
         <v>26</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P57" s="9" t="s">
         <v>26</v>
@@ -4791,7 +4791,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B58" s="5">
         <v>46080.77828957176</v>
@@ -4803,16 +4803,16 @@
         <v>46156.16908381945</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="I58" s="5">
         <v>46154</v>
@@ -4830,13 +4830,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q58" s="10" t="s">
         <v>31</v>
@@ -4856,7 +4856,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B59" s="8">
         <v>46080.77828986111</v>
@@ -4868,16 +4868,16 @@
         <v>46133.62189940972</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="I59" s="8">
         <v>46216</v>
@@ -4895,13 +4895,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="P59" s="9" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q59" s="11" t="s">
         <v>56</v>
@@ -4921,7 +4921,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B60" s="5">
         <v>46080.778290138885</v>
@@ -4933,16 +4933,16 @@
         <v>46121.867985185185</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="I60" s="5">
         <v>46226</v>
@@ -4960,13 +4960,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q60" s="11" t="s">
         <v>56</v>
@@ -4986,7 +4986,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B61" s="8">
         <v>46080.778290393515</v>
@@ -4998,16 +4998,16 @@
         <v>46121.86791173611</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H61" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="I61" s="8">
         <v>46210</v>
@@ -5025,13 +5025,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="P61" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q61" s="11" t="s">
         <v>56</v>
@@ -5051,7 +5051,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B62" s="5">
         <v>46080.7854796875</v>
@@ -5069,10 +5069,10 @@
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="I62" s="5">
         <v>46199</v>
@@ -5090,13 +5090,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q62" s="11" t="s">
         <v>56</v>
@@ -5116,7 +5116,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B63" s="8">
         <v>46080.77828662037</v>
@@ -5128,7 +5128,7 @@
         <v>46141.71127789352</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>25</v>
@@ -5152,7 +5152,7 @@
         <v>26</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="P63" s="9" t="s">
         <v>26</v>
@@ -5165,7 +5165,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B64" s="5">
         <v>46080.77828694445</v>
@@ -5177,7 +5177,7 @@
         <v>46184.174991747685</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
@@ -5204,16 +5204,16 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q64" s="12" t="s">
-        <v>233</v>
+        <v>115</v>
       </c>
       <c r="R64" s="6">
         <v>1</v>
@@ -5269,7 +5269,7 @@
         <v>26</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="O65" s="9" t="s">
         <v>236</v>
@@ -5334,7 +5334,7 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="O66" s="6" t="s">
         <v>240</v>
@@ -5399,7 +5399,7 @@
         <v>26</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="O67" s="9" t="s">
         <v>243</v>
@@ -5464,7 +5464,7 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="O68" s="6" t="s">
         <v>246</v>
@@ -5502,7 +5502,7 @@
         <v>46133.621889710645</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>26</v>
@@ -5529,7 +5529,7 @@
         <v>26</v>
       </c>
       <c r="N69" s="9" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="O69" s="9" t="s">
         <v>248</v>
@@ -5567,7 +5567,7 @@
         <v>46141.711773055555</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
@@ -5594,10 +5594,10 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="P70" s="6" t="s">
         <v>251</v>
@@ -5711,7 +5711,7 @@
         <v>253</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="P72" s="6" t="s">
         <v>259</v>
@@ -5817,10 +5817,10 @@
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="I74" s="5">
         <v>46239</v>
@@ -5882,10 +5882,10 @@
         <v>26</v>
       </c>
       <c r="G75" s="9" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H75" s="9" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="I75" s="8">
         <v>46240</v>

--- a/data/50001524 - ATACAMA KOZAN.xlsx
+++ b/data/50001524 - ATACAMA KOZAN.xlsx
@@ -5174,7 +5174,7 @@
         <v>46133.62079252314</v>
       </c>
       <c r="D64" s="5">
-        <v>46184.174991747685</v>
+        <v>46192.18706700232</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>232</v>
@@ -5212,8 +5212,8 @@
       <c r="P64" s="6" t="s">
         <v>233</v>
       </c>
-      <c r="Q64" s="12" t="s">
-        <v>115</v>
+      <c r="Q64" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="R64" s="6">
         <v>1</v>

--- a/data/50001524 - ATACAMA KOZAN.xlsx
+++ b/data/50001524 - ATACAMA KOZAN.xlsx
@@ -5060,7 +5060,7 @@
         <v>46141.772219398146</v>
       </c>
       <c r="D62" s="5">
-        <v>46141.77224144676</v>
+        <v>46195.17883668981</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>54</v>
@@ -5098,8 +5098,8 @@
       <c r="P62" s="6" t="s">
         <v>227</v>
       </c>
-      <c r="Q62" s="11" t="s">
-        <v>56</v>
+      <c r="Q62" s="12" t="s">
+        <v>115</v>
       </c>
       <c r="R62" s="6">
         <v>1</v>

--- a/data/50001524 - ATACAMA KOZAN.xlsx
+++ b/data/50001524 - ATACAMA KOZAN.xlsx
@@ -181,156 +181,159 @@
     <t>Embalaje,Ingenieria Servicios</t>
   </si>
   <si>
+    <t>Media</t>
+  </si>
+  <si>
+    <t>Tarea en curso</t>
+  </si>
+  <si>
+    <t>1213412709779748</t>
+  </si>
+  <si>
+    <t>Ingenieria Jefe de proyecto:</t>
+  </si>
+  <si>
+    <t>Ingenieria Detalle,Ingenieria Basica Motor,Ingenieria basica Rodete</t>
+  </si>
+  <si>
+    <t>1213412709779749</t>
+  </si>
+  <si>
+    <t>Ingenieria Basica Motor</t>
+  </si>
+  <si>
+    <t>Analisis de costeo,Ingenieria Jefe de proyecto:,propuesta motor</t>
+  </si>
+  <si>
+    <t>1213412709779751</t>
+  </si>
+  <si>
+    <t>Ingenieria basica Rodete</t>
+  </si>
+  <si>
+    <t>Analisis de costeo,Ingenieria Jefe de proyecto:,propuesta nucleo rodete,propuesta alabes</t>
+  </si>
+  <si>
+    <t>1213412709779752</t>
+  </si>
+  <si>
+    <t>Ingenieria Detalle</t>
+  </si>
+  <si>
+    <t>Analisis de costeo,Ingenieria Jefe de proyecto:,Propuesta Sensores y accesorios,propuesta compras a codigo // aprovisionamiento,Planos Preliminar</t>
+  </si>
+  <si>
+    <t>1213412709779753</t>
+  </si>
+  <si>
+    <t>Analisis de costeo</t>
+  </si>
+  <si>
+    <t>Ingenieria Basica Motor,Ingenieria Detalle,Ingenieria basica Rodete</t>
+  </si>
+  <si>
+    <t>Costos</t>
+  </si>
+  <si>
+    <t>1213412709779754</t>
+  </si>
+  <si>
+    <t>Propuesta compras:</t>
+  </si>
+  <si>
+    <t>propuesta motor,propuesta alabes,propuesta nucleo rodete,Propuesta Tablero,Propuesta Sensores y accesorios,propuesta compras a codigo // aprovisionamiento</t>
+  </si>
+  <si>
+    <t>1213412709779755</t>
+  </si>
+  <si>
+    <t>propuesta motor</t>
+  </si>
+  <si>
+    <t>Propuesta compras:,Generación OC motor</t>
+  </si>
+  <si>
+    <t>1213412709779756</t>
+  </si>
+  <si>
+    <t>propuesta alabes</t>
+  </si>
+  <si>
+    <t>Propuesta compras:,Generación OC Alabe</t>
+  </si>
+  <si>
+    <t>1213412709779757</t>
+  </si>
+  <si>
+    <t>propuesta nucleo rodete</t>
+  </si>
+  <si>
+    <t>benjamin.bustos@zitron.com</t>
+  </si>
+  <si>
+    <t>Propuesta compras:,Generación OC Rodete</t>
+  </si>
+  <si>
+    <t>1213458788103568</t>
+  </si>
+  <si>
+    <t>Propuesta Tablero</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Propuesta compras:,Generacion oc Tableros </t>
+  </si>
+  <si>
+    <t>1213412709779758</t>
+  </si>
+  <si>
+    <t>Propuesta Sensores y accesorios</t>
+  </si>
+  <si>
+    <t>Propuesta compras:,Generación Oc sensores</t>
+  </si>
+  <si>
+    <t>1213412709779759</t>
+  </si>
+  <si>
+    <t>propuesta compras a codigo // aprovisionamiento</t>
+  </si>
+  <si>
+    <t>hugo isla martinez</t>
+  </si>
+  <si>
+    <t>hugo.isla@zitron.com</t>
+  </si>
+  <si>
+    <t>Propuesta compras:,Fabricacion a codigo y compras locales</t>
+  </si>
+  <si>
+    <t>1213412709779760</t>
+  </si>
+  <si>
+    <t>Compras:</t>
+  </si>
+  <si>
+    <t>Alabe,Tableros,rodete,Motor,Materiales a codigo // compras locales aprovisionamientomiento:,Sensores</t>
+  </si>
+  <si>
+    <t>1213412709779761</t>
+  </si>
+  <si>
+    <t>Alabe</t>
+  </si>
+  <si>
+    <t>Eliana</t>
+  </si>
+  <si>
+    <t>ecarico@zitron.com</t>
+  </si>
+  <si>
+    <t>Generación OC Alabe,Fabricación Alabe</t>
+  </si>
+  <si>
     <t>Baja</t>
   </si>
   <si>
-    <t>Tarea en curso</t>
-  </si>
-  <si>
-    <t>1213412709779748</t>
-  </si>
-  <si>
-    <t>Ingenieria Jefe de proyecto:</t>
-  </si>
-  <si>
-    <t>Ingenieria Detalle,Ingenieria Basica Motor,Ingenieria basica Rodete</t>
-  </si>
-  <si>
-    <t>1213412709779749</t>
-  </si>
-  <si>
-    <t>Ingenieria Basica Motor</t>
-  </si>
-  <si>
-    <t>Analisis de costeo,Ingenieria Jefe de proyecto:,propuesta motor</t>
-  </si>
-  <si>
-    <t>1213412709779751</t>
-  </si>
-  <si>
-    <t>Ingenieria basica Rodete</t>
-  </si>
-  <si>
-    <t>Analisis de costeo,Ingenieria Jefe de proyecto:,propuesta nucleo rodete,propuesta alabes</t>
-  </si>
-  <si>
-    <t>1213412709779752</t>
-  </si>
-  <si>
-    <t>Ingenieria Detalle</t>
-  </si>
-  <si>
-    <t>Analisis de costeo,Ingenieria Jefe de proyecto:,Propuesta Sensores y accesorios,propuesta compras a codigo // aprovisionamiento,Planos Preliminar</t>
-  </si>
-  <si>
-    <t>1213412709779753</t>
-  </si>
-  <si>
-    <t>Analisis de costeo</t>
-  </si>
-  <si>
-    <t>Ingenieria Basica Motor,Ingenieria Detalle,Ingenieria basica Rodete</t>
-  </si>
-  <si>
-    <t>Costos</t>
-  </si>
-  <si>
-    <t>1213412709779754</t>
-  </si>
-  <si>
-    <t>Propuesta compras:</t>
-  </si>
-  <si>
-    <t>propuesta motor,propuesta alabes,propuesta nucleo rodete,Propuesta Tablero,Propuesta Sensores y accesorios,propuesta compras a codigo // aprovisionamiento</t>
-  </si>
-  <si>
-    <t>1213412709779755</t>
-  </si>
-  <si>
-    <t>propuesta motor</t>
-  </si>
-  <si>
-    <t>Propuesta compras:,Generación OC motor</t>
-  </si>
-  <si>
-    <t>1213412709779756</t>
-  </si>
-  <si>
-    <t>propuesta alabes</t>
-  </si>
-  <si>
-    <t>Propuesta compras:,Generación OC Alabe</t>
-  </si>
-  <si>
-    <t>1213412709779757</t>
-  </si>
-  <si>
-    <t>propuesta nucleo rodete</t>
-  </si>
-  <si>
-    <t>benjamin.bustos@zitron.com</t>
-  </si>
-  <si>
-    <t>Propuesta compras:,Generación OC Rodete</t>
-  </si>
-  <si>
-    <t>1213458788103568</t>
-  </si>
-  <si>
-    <t>Propuesta Tablero</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Propuesta compras:,Generacion oc Tableros </t>
-  </si>
-  <si>
-    <t>1213412709779758</t>
-  </si>
-  <si>
-    <t>Propuesta Sensores y accesorios</t>
-  </si>
-  <si>
-    <t>Propuesta compras:,Generación Oc sensores</t>
-  </si>
-  <si>
-    <t>1213412709779759</t>
-  </si>
-  <si>
-    <t>propuesta compras a codigo // aprovisionamiento</t>
-  </si>
-  <si>
-    <t>hugo isla martinez</t>
-  </si>
-  <si>
-    <t>hugo.isla@zitron.com</t>
-  </si>
-  <si>
-    <t>Propuesta compras:,Fabricacion a codigo y compras locales</t>
-  </si>
-  <si>
-    <t>1213412709779760</t>
-  </si>
-  <si>
-    <t>Compras:</t>
-  </si>
-  <si>
-    <t>Alabe,Tableros,rodete,Motor,Materiales a codigo // compras locales aprovisionamientomiento:,Sensores</t>
-  </si>
-  <si>
-    <t>1213412709779761</t>
-  </si>
-  <si>
-    <t>Alabe</t>
-  </si>
-  <si>
-    <t>Eliana</t>
-  </si>
-  <si>
-    <t>ecarico@zitron.com</t>
-  </si>
-  <si>
-    <t>Generación OC Alabe,Fabricación Alabe</t>
-  </si>
-  <si>
     <t>1213412709779762</t>
   </si>
   <si>
@@ -356,9 +359,6 @@
   </si>
   <si>
     <t xml:space="preserve">Generacion oc Tableros ,Fabricacion Tableros </t>
-  </si>
-  <si>
-    <t>Media</t>
   </si>
   <si>
     <t>1213458788103571</t>
@@ -1982,7 +1982,7 @@
         <v>46141.71151436343</v>
       </c>
       <c r="D12" s="5">
-        <v>46141.77223967593</v>
+        <v>46197.18632274306</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>53</v>
@@ -2020,7 +2020,7 @@
       <c r="P12" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="Q12" s="11" t="s">
+      <c r="Q12" s="12" t="s">
         <v>56</v>
       </c>
       <c r="R12" s="6">
@@ -2889,7 +2889,7 @@
         <v>99</v>
       </c>
       <c r="Q26" s="11" t="s">
-        <v>56</v>
+        <v>106</v>
       </c>
       <c r="R26" s="6">
         <v>1</v>
@@ -2906,7 +2906,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B27" s="8">
         <v>46080.77828601852</v>
@@ -2918,7 +2918,7 @@
         <v>46139.78108450232</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>26</v>
@@ -2951,23 +2951,23 @@
         <v>81</v>
       </c>
       <c r="P27" s="9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="Q27" s="11" t="s">
-        <v>56</v>
+        <v>106</v>
       </c>
       <c r="R27" s="9">
         <v>0</v>
       </c>
       <c r="S27" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="T27" s="9"/>
       <c r="U27" s="9"/>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B28" s="5">
         <v>46080.778286388886</v>
@@ -2979,7 +2979,7 @@
         <v>46139.78118329861</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
@@ -3009,26 +3009,26 @@
         <v>102</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="P28" s="6" t="s">
         <v>102</v>
       </c>
       <c r="Q28" s="11" t="s">
-        <v>56</v>
+        <v>106</v>
       </c>
       <c r="R28" s="6">
         <v>0</v>
       </c>
       <c r="S28" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="T28" s="6"/>
       <c r="U28" s="6"/>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B29" s="8">
         <v>46080.78421460648</v>
@@ -3040,7 +3040,7 @@
         <v>46191.20398373842</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>26</v>
@@ -3070,19 +3070,19 @@
         <v>99</v>
       </c>
       <c r="O29" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="P29" s="9" t="s">
         <v>99</v>
       </c>
       <c r="Q29" s="12" t="s">
-        <v>115</v>
+        <v>56</v>
       </c>
       <c r="R29" s="9">
         <v>1</v>
       </c>
       <c r="S29" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="T29" s="8">
         <v>46092</v>
@@ -3132,7 +3132,7 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="O30" s="6" t="s">
         <v>88</v>
@@ -3187,7 +3187,7 @@
         <v>26</v>
       </c>
       <c r="N31" s="9" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="O31" s="9" t="s">
         <v>117</v>
@@ -3316,13 +3316,13 @@
         <v>127</v>
       </c>
       <c r="Q33" s="11" t="s">
-        <v>56</v>
+        <v>106</v>
       </c>
       <c r="R33" s="9">
         <v>0</v>
       </c>
       <c r="S33" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="T33" s="9"/>
       <c r="U33" s="9"/>
@@ -3377,13 +3377,13 @@
         <v>130</v>
       </c>
       <c r="Q34" s="11" t="s">
-        <v>56</v>
+        <v>106</v>
       </c>
       <c r="R34" s="6">
         <v>0</v>
       </c>
       <c r="S34" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="T34" s="6"/>
       <c r="U34" s="6"/>
@@ -3438,7 +3438,7 @@
         <v>99</v>
       </c>
       <c r="Q35" s="11" t="s">
-        <v>56</v>
+        <v>106</v>
       </c>
       <c r="R35" s="9">
         <v>1</v>
@@ -3503,13 +3503,13 @@
         <v>136</v>
       </c>
       <c r="Q36" s="11" t="s">
-        <v>56</v>
+        <v>106</v>
       </c>
       <c r="R36" s="6">
         <v>0</v>
       </c>
       <c r="S36" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="T36" s="6"/>
       <c r="U36" s="6"/>
@@ -3564,13 +3564,13 @@
         <v>139</v>
       </c>
       <c r="Q37" s="11" t="s">
-        <v>56</v>
+        <v>106</v>
       </c>
       <c r="R37" s="9">
         <v>0</v>
       </c>
       <c r="S37" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="T37" s="9"/>
       <c r="U37" s="9"/>
@@ -3625,13 +3625,13 @@
         <v>142</v>
       </c>
       <c r="Q38" s="11" t="s">
-        <v>56</v>
+        <v>106</v>
       </c>
       <c r="R38" s="6">
         <v>0</v>
       </c>
       <c r="S38" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="T38" s="6"/>
       <c r="U38" s="6"/>
@@ -3751,13 +3751,13 @@
         <v>144</v>
       </c>
       <c r="Q40" s="11" t="s">
-        <v>56</v>
+        <v>106</v>
       </c>
       <c r="R40" s="6">
         <v>0</v>
       </c>
       <c r="S40" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="T40" s="6"/>
       <c r="U40" s="6"/>
@@ -3812,13 +3812,13 @@
         <v>152</v>
       </c>
       <c r="Q41" s="11" t="s">
-        <v>56</v>
+        <v>106</v>
       </c>
       <c r="R41" s="9">
         <v>0</v>
       </c>
       <c r="S41" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="T41" s="9"/>
       <c r="U41" s="9"/>
@@ -3873,7 +3873,7 @@
         <v>99</v>
       </c>
       <c r="Q42" s="11" t="s">
-        <v>56</v>
+        <v>106</v>
       </c>
       <c r="R42" s="6">
         <v>1</v>
@@ -3938,13 +3938,13 @@
         <v>158</v>
       </c>
       <c r="Q43" s="11" t="s">
-        <v>56</v>
+        <v>106</v>
       </c>
       <c r="R43" s="9">
         <v>0</v>
       </c>
       <c r="S43" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="T43" s="9"/>
       <c r="U43" s="9"/>
@@ -3999,13 +3999,13 @@
         <v>161</v>
       </c>
       <c r="Q44" s="11" t="s">
-        <v>56</v>
+        <v>106</v>
       </c>
       <c r="R44" s="6">
         <v>0</v>
       </c>
       <c r="S44" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="T44" s="6"/>
       <c r="U44" s="6"/>
@@ -4302,7 +4302,7 @@
         <v>182</v>
       </c>
       <c r="Q49" s="11" t="s">
-        <v>56</v>
+        <v>106</v>
       </c>
       <c r="R49" s="9">
         <v>1</v>
@@ -4904,7 +4904,7 @@
         <v>219</v>
       </c>
       <c r="Q59" s="11" t="s">
-        <v>56</v>
+        <v>106</v>
       </c>
       <c r="R59" s="9">
         <v>1</v>
@@ -4969,7 +4969,7 @@
         <v>222</v>
       </c>
       <c r="Q60" s="11" t="s">
-        <v>56</v>
+        <v>106</v>
       </c>
       <c r="R60" s="6">
         <v>1</v>
@@ -5034,7 +5034,7 @@
         <v>225</v>
       </c>
       <c r="Q61" s="11" t="s">
-        <v>56</v>
+        <v>106</v>
       </c>
       <c r="R61" s="9">
         <v>1</v>
@@ -5099,7 +5099,7 @@
         <v>227</v>
       </c>
       <c r="Q62" s="12" t="s">
-        <v>115</v>
+        <v>56</v>
       </c>
       <c r="R62" s="6">
         <v>1</v>
@@ -5278,7 +5278,7 @@
         <v>237</v>
       </c>
       <c r="Q65" s="11" t="s">
-        <v>56</v>
+        <v>106</v>
       </c>
       <c r="R65" s="9">
         <v>1</v>
@@ -5343,7 +5343,7 @@
         <v>237</v>
       </c>
       <c r="Q66" s="11" t="s">
-        <v>56</v>
+        <v>106</v>
       </c>
       <c r="R66" s="6">
         <v>1</v>
@@ -5408,7 +5408,7 @@
         <v>237</v>
       </c>
       <c r="Q67" s="11" t="s">
-        <v>56</v>
+        <v>106</v>
       </c>
       <c r="R67" s="9">
         <v>1</v>
@@ -5473,7 +5473,7 @@
         <v>237</v>
       </c>
       <c r="Q68" s="11" t="s">
-        <v>56</v>
+        <v>106</v>
       </c>
       <c r="R68" s="6">
         <v>1</v>
@@ -5538,7 +5538,7 @@
         <v>249</v>
       </c>
       <c r="Q69" s="11" t="s">
-        <v>56</v>
+        <v>106</v>
       </c>
       <c r="R69" s="9">
         <v>1</v>
@@ -5603,13 +5603,13 @@
         <v>251</v>
       </c>
       <c r="Q70" s="11" t="s">
-        <v>56</v>
+        <v>106</v>
       </c>
       <c r="R70" s="6">
         <v>1</v>
       </c>
       <c r="S70" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="T70" s="5">
         <v>46234</v>
@@ -5717,13 +5717,13 @@
         <v>259</v>
       </c>
       <c r="Q72" s="11" t="s">
-        <v>56</v>
+        <v>106</v>
       </c>
       <c r="R72" s="6">
         <v>1</v>
       </c>
       <c r="S72" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="T72" s="5">
         <v>46237</v>
@@ -5782,13 +5782,13 @@
         <v>263</v>
       </c>
       <c r="Q73" s="11" t="s">
-        <v>56</v>
+        <v>106</v>
       </c>
       <c r="R73" s="9">
         <v>1</v>
       </c>
       <c r="S73" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="T73" s="8">
         <v>46238</v>
@@ -5847,13 +5847,13 @@
         <v>266</v>
       </c>
       <c r="Q74" s="11" t="s">
-        <v>56</v>
+        <v>106</v>
       </c>
       <c r="R74" s="6">
         <v>1</v>
       </c>
       <c r="S74" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="T74" s="5">
         <v>46239</v>
@@ -5912,13 +5912,13 @@
         <v>269</v>
       </c>
       <c r="Q75" s="11" t="s">
-        <v>56</v>
+        <v>106</v>
       </c>
       <c r="R75" s="9">
         <v>1</v>
       </c>
       <c r="S75" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="T75" s="8">
         <v>46240</v>
@@ -6022,13 +6022,13 @@
         <v>271</v>
       </c>
       <c r="Q77" s="11" t="s">
-        <v>56</v>
+        <v>106</v>
       </c>
       <c r="R77" s="9">
         <v>0</v>
       </c>
       <c r="S77" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="T77" s="8">
         <v>46241</v>
@@ -6085,13 +6085,13 @@
         <v>271</v>
       </c>
       <c r="Q78" s="11" t="s">
-        <v>56</v>
+        <v>106</v>
       </c>
       <c r="R78" s="6">
         <v>0</v>
       </c>
       <c r="S78" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="T78" s="5">
         <v>46241</v>
@@ -6142,13 +6142,13 @@
         <v>26</v>
       </c>
       <c r="Q79" s="11" t="s">
-        <v>56</v>
+        <v>106</v>
       </c>
       <c r="R79" s="9">
         <v>0</v>
       </c>
       <c r="S79" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="T79" s="9"/>
       <c r="U79" s="9"/>
@@ -6201,13 +6201,13 @@
         <v>284</v>
       </c>
       <c r="Q80" s="11" t="s">
-        <v>56</v>
+        <v>106</v>
       </c>
       <c r="R80" s="6">
         <v>0</v>
       </c>
       <c r="S80" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="T80" s="5">
         <v>46241</v>
@@ -6264,13 +6264,13 @@
         <v>280</v>
       </c>
       <c r="Q81" s="11" t="s">
-        <v>56</v>
+        <v>106</v>
       </c>
       <c r="R81" s="9">
         <v>0</v>
       </c>
       <c r="S81" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="T81" s="8">
         <v>46252</v>

--- a/data/50001524 - ATACAMA KOZAN.xlsx
+++ b/data/50001524 - ATACAMA KOZAN.xlsx
@@ -1498,13 +1498,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46080.77828641204</v>
+        <v>46080.61161974537</v>
       </c>
       <c r="C4" s="5">
-        <v>46097.83665600694</v>
+        <v>46097.66998934028</v>
       </c>
       <c r="D4" s="5">
-        <v>46097.83674934028</v>
+        <v>46097.67008267361</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1547,13 +1547,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46080.77828680555</v>
+        <v>46080.611620138894</v>
       </c>
       <c r="C5" s="8">
-        <v>46097.8362150926</v>
+        <v>46097.669548425925</v>
       </c>
       <c r="D5" s="8">
-        <v>46097.836235787036</v>
+        <v>46097.66956912037</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1610,13 +1610,13 @@
         <v>33</v>
       </c>
       <c r="B6" s="5">
-        <v>46080.778287106485</v>
+        <v>46080.61162043981</v>
       </c>
       <c r="C6" s="5">
-        <v>46097.83622053241</v>
+        <v>46097.66955386574</v>
       </c>
       <c r="D6" s="5">
-        <v>46097.836235532406</v>
+        <v>46097.66956886574</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>34</v>
@@ -1673,13 +1673,13 @@
         <v>37</v>
       </c>
       <c r="B7" s="8">
-        <v>46080.778287407404</v>
+        <v>46080.61162074074</v>
       </c>
       <c r="C7" s="8">
-        <v>46097.83622695602</v>
+        <v>46097.66956028935</v>
       </c>
       <c r="D7" s="8">
-        <v>46097.83624193287</v>
+        <v>46097.669575266205</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>38</v>
@@ -1736,13 +1736,13 @@
         <v>39</v>
       </c>
       <c r="B8" s="5">
-        <v>46080.77828773148</v>
+        <v>46080.61162106482</v>
       </c>
       <c r="C8" s="5">
-        <v>46093.643042129625</v>
+        <v>46093.47637546297</v>
       </c>
       <c r="D8" s="5">
-        <v>46100.791677939815</v>
+        <v>46100.62501127315</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>40</v>
@@ -1799,13 +1799,13 @@
         <v>42</v>
       </c>
       <c r="B9" s="8">
-        <v>46080.778288009256</v>
+        <v>46080.61162134259</v>
       </c>
       <c r="C9" s="8">
-        <v>46097.83624405092</v>
+        <v>46097.66957738426</v>
       </c>
       <c r="D9" s="8">
-        <v>46097.83625847222</v>
+        <v>46097.669591805556</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>43</v>
@@ -1862,13 +1862,13 @@
         <v>44</v>
       </c>
       <c r="B10" s="5">
-        <v>46080.78358017361</v>
+        <v>46080.61691350694</v>
       </c>
       <c r="C10" s="5">
-        <v>46141.711601145835</v>
+        <v>46141.54493447917</v>
       </c>
       <c r="D10" s="5">
-        <v>46141.7116022338</v>
+        <v>46141.54493556713</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>45</v>
@@ -1911,13 +1911,13 @@
         <v>47</v>
       </c>
       <c r="B11" s="8">
-        <v>46080.7837635301</v>
+        <v>46080.617096863425</v>
       </c>
       <c r="C11" s="8">
-        <v>46114.51182108796</v>
+        <v>46114.345154421295</v>
       </c>
       <c r="D11" s="8">
-        <v>46114.51183934028</v>
+        <v>46114.34517267361</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>48</v>
@@ -1976,13 +1976,13 @@
         <v>52</v>
       </c>
       <c r="B12" s="5">
-        <v>46080.783815243056</v>
+        <v>46080.61714857639</v>
       </c>
       <c r="C12" s="5">
-        <v>46141.71151436343</v>
+        <v>46141.54484769676</v>
       </c>
       <c r="D12" s="5">
-        <v>46197.18632274306</v>
+        <v>46197.01965607639</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>53</v>
@@ -2041,13 +2041,13 @@
         <v>58</v>
       </c>
       <c r="B13" s="8">
-        <v>46080.77828829861</v>
+        <v>46080.61162163195</v>
       </c>
       <c r="C13" s="8">
-        <v>46114.51259805556</v>
+        <v>46114.34593138889</v>
       </c>
       <c r="D13" s="8">
-        <v>46114.75905811343</v>
+        <v>46114.59239144676</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>59</v>
@@ -2092,13 +2092,13 @@
         <v>61</v>
       </c>
       <c r="B14" s="5">
-        <v>46080.778288587964</v>
+        <v>46080.6116219213</v>
       </c>
       <c r="C14" s="5">
-        <v>46114.511949733795</v>
+        <v>46114.34528306713</v>
       </c>
       <c r="D14" s="5">
-        <v>46114.51196541666</v>
+        <v>46114.34529875</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>62</v>
@@ -2157,13 +2157,13 @@
         <v>64</v>
       </c>
       <c r="B15" s="8">
-        <v>46080.77828953703</v>
+        <v>46080.61162287037</v>
       </c>
       <c r="C15" s="8">
-        <v>46114.512105497684</v>
+        <v>46114.34543883102</v>
       </c>
       <c r="D15" s="8">
-        <v>46114.51212151621</v>
+        <v>46114.345454849536</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>65</v>
@@ -2222,13 +2222,13 @@
         <v>67</v>
       </c>
       <c r="B16" s="5">
-        <v>46080.77828619213</v>
+        <v>46080.61161952546</v>
       </c>
       <c r="C16" s="5">
-        <v>46114.51240666666</v>
+        <v>46114.345740000004</v>
       </c>
       <c r="D16" s="5">
-        <v>46114.5124212963</v>
+        <v>46114.34575462963</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>68</v>
@@ -2287,13 +2287,13 @@
         <v>70</v>
       </c>
       <c r="B17" s="8">
-        <v>46080.77828652778</v>
+        <v>46080.61161986111</v>
       </c>
       <c r="C17" s="8">
-        <v>46114.512582048614</v>
+        <v>46114.34591538194</v>
       </c>
       <c r="D17" s="8">
-        <v>46114.51259918981</v>
+        <v>46114.34593252315</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>71</v>
@@ -2352,13 +2352,13 @@
         <v>74</v>
       </c>
       <c r="B18" s="5">
-        <v>46080.778286875</v>
+        <v>46080.611620208336</v>
       </c>
       <c r="C18" s="5">
-        <v>46126.85558527778</v>
+        <v>46126.68891861111</v>
       </c>
       <c r="D18" s="5">
-        <v>46126.85559849537</v>
+        <v>46126.6889318287</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>75</v>
@@ -2405,13 +2405,13 @@
         <v>77</v>
       </c>
       <c r="B19" s="8">
-        <v>46080.778287152774</v>
+        <v>46080.61162048611</v>
       </c>
       <c r="C19" s="8">
-        <v>46114.51201428241</v>
+        <v>46114.345347615745</v>
       </c>
       <c r="D19" s="8">
-        <v>46114.512030185186</v>
+        <v>46114.345363518514</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>78</v>
@@ -2470,13 +2470,13 @@
         <v>80</v>
       </c>
       <c r="B20" s="5">
-        <v>46080.77828752315</v>
+        <v>46080.61162085648</v>
       </c>
       <c r="C20" s="5">
-        <v>46114.51275581018</v>
+        <v>46114.34608914352</v>
       </c>
       <c r="D20" s="5">
-        <v>46114.51277075231</v>
+        <v>46114.34610408565</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>81</v>
@@ -2535,13 +2535,13 @@
         <v>83</v>
       </c>
       <c r="B21" s="8">
-        <v>46080.77828780093</v>
+        <v>46080.61162113426</v>
       </c>
       <c r="C21" s="8">
-        <v>46126.85556609953</v>
+        <v>46126.68889943287</v>
       </c>
       <c r="D21" s="8">
-        <v>46126.855582199074</v>
+        <v>46126.6889155324</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>84</v>
@@ -2600,13 +2600,13 @@
         <v>87</v>
       </c>
       <c r="B22" s="5">
-        <v>46080.78405931713</v>
+        <v>46080.61739265046</v>
       </c>
       <c r="C22" s="5">
-        <v>46114.51307935185</v>
+        <v>46114.34641268519</v>
       </c>
       <c r="D22" s="5">
-        <v>46114.51309576389</v>
+        <v>46114.34642909722</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>88</v>
@@ -2665,13 +2665,13 @@
         <v>90</v>
       </c>
       <c r="B23" s="8">
-        <v>46080.778288113426</v>
+        <v>46080.61162144676</v>
       </c>
       <c r="C23" s="8">
-        <v>46114.513175810185</v>
+        <v>46114.34650914352</v>
       </c>
       <c r="D23" s="8">
-        <v>46114.51327625</v>
+        <v>46114.34660958333</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>91</v>
@@ -2730,13 +2730,13 @@
         <v>93</v>
       </c>
       <c r="B24" s="5">
-        <v>46080.77828840278</v>
+        <v>46080.61162173611</v>
       </c>
       <c r="C24" s="5">
-        <v>46114.75971673611</v>
+        <v>46114.593050069445</v>
       </c>
       <c r="D24" s="5">
-        <v>46114.759732199076</v>
+        <v>46114.593065532405</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>94</v>
@@ -2795,13 +2795,13 @@
         <v>98</v>
       </c>
       <c r="B25" s="8">
-        <v>46080.778288692134</v>
+        <v>46080.61162202546</v>
       </c>
       <c r="C25" s="8">
-        <v>46140.83895159722</v>
+        <v>46140.67228493055</v>
       </c>
       <c r="D25" s="8">
-        <v>46140.838952673614</v>
+        <v>46140.67228600694</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>99</v>
@@ -2844,13 +2844,13 @@
         <v>101</v>
       </c>
       <c r="B26" s="5">
-        <v>46080.778288981484</v>
+        <v>46080.61162231481</v>
       </c>
       <c r="C26" s="5">
-        <v>46139.781195081014</v>
+        <v>46139.61452841436</v>
       </c>
       <c r="D26" s="5">
-        <v>46139.78120622685</v>
+        <v>46139.614539560185</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>102</v>
@@ -2909,13 +2909,13 @@
         <v>107</v>
       </c>
       <c r="B27" s="8">
-        <v>46080.77828601852</v>
+        <v>46080.611619351854</v>
       </c>
       <c r="C27" s="8">
-        <v>46139.78108315972</v>
+        <v>46139.61441649306</v>
       </c>
       <c r="D27" s="8">
-        <v>46139.78108450232</v>
+        <v>46139.61441783565</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>108</v>
@@ -2970,13 +2970,13 @@
         <v>111</v>
       </c>
       <c r="B28" s="5">
-        <v>46080.778286388886</v>
+        <v>46080.61161972222</v>
       </c>
       <c r="C28" s="5">
-        <v>46139.781181886574</v>
+        <v>46139.6145152199</v>
       </c>
       <c r="D28" s="5">
-        <v>46139.78118329861</v>
+        <v>46139.61451663195</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>112</v>
@@ -3031,13 +3031,13 @@
         <v>113</v>
       </c>
       <c r="B29" s="8">
-        <v>46080.78421460648</v>
+        <v>46080.617547939815</v>
       </c>
       <c r="C29" s="8">
-        <v>46140.80903469908</v>
+        <v>46140.64236803241</v>
       </c>
       <c r="D29" s="8">
-        <v>46191.20398373842</v>
+        <v>46191.03731707176</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>114</v>
@@ -3096,13 +3096,13 @@
         <v>116</v>
       </c>
       <c r="B30" s="5">
-        <v>46080.78464398148</v>
+        <v>46080.61797731482</v>
       </c>
       <c r="C30" s="5">
-        <v>46114.761799988424</v>
+        <v>46114.59513332176</v>
       </c>
       <c r="D30" s="5">
-        <v>46114.761801307875</v>
+        <v>46114.595134641204</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>117</v>
@@ -3151,13 +3151,13 @@
         <v>119</v>
       </c>
       <c r="B31" s="8">
-        <v>46080.78472030093</v>
+        <v>46080.61805363426</v>
       </c>
       <c r="C31" s="8">
-        <v>46140.8089503125</v>
+        <v>46140.64228364584</v>
       </c>
       <c r="D31" s="8">
-        <v>46140.80895233796</v>
+        <v>46140.642285671296</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>120</v>
@@ -3206,13 +3206,13 @@
         <v>122</v>
       </c>
       <c r="B32" s="5">
-        <v>46080.77828665509</v>
+        <v>46080.61161998843</v>
       </c>
       <c r="C32" s="5">
-        <v>46133.62092905093</v>
+        <v>46133.45426238426</v>
       </c>
       <c r="D32" s="5">
-        <v>46154.1920628125</v>
+        <v>46154.02539614584</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>123</v>
@@ -3271,13 +3271,13 @@
         <v>125</v>
       </c>
       <c r="B33" s="8">
-        <v>46080.7782869213</v>
+        <v>46080.611620254625</v>
       </c>
       <c r="C33" s="8">
-        <v>46133.62086219907</v>
+        <v>46133.45419553241</v>
       </c>
       <c r="D33" s="8">
-        <v>46133.62086326389</v>
+        <v>46133.454196597224</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>126</v>
@@ -3332,13 +3332,13 @@
         <v>128</v>
       </c>
       <c r="B34" s="5">
-        <v>46080.778287187495</v>
+        <v>46080.61162052084</v>
       </c>
       <c r="C34" s="5">
-        <v>46133.62090008102</v>
+        <v>46133.45423341435</v>
       </c>
       <c r="D34" s="5">
-        <v>46133.62090126157</v>
+        <v>46133.45423459491</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>129</v>
@@ -3393,13 +3393,13 @@
         <v>131</v>
       </c>
       <c r="B35" s="8">
-        <v>46080.77828746528</v>
+        <v>46080.61162079861</v>
       </c>
       <c r="C35" s="8">
-        <v>46114.76327634259</v>
+        <v>46114.59660967592</v>
       </c>
       <c r="D35" s="8">
-        <v>46114.76329173611</v>
+        <v>46114.59662506945</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>132</v>
@@ -3458,13 +3458,13 @@
         <v>134</v>
       </c>
       <c r="B36" s="5">
-        <v>46080.77828773148</v>
+        <v>46080.61162106482</v>
       </c>
       <c r="C36" s="5">
-        <v>46114.76319241898</v>
+        <v>46114.59652575231</v>
       </c>
       <c r="D36" s="5">
-        <v>46114.76319354167</v>
+        <v>46114.596526875</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>135</v>
@@ -3519,13 +3519,13 @@
         <v>137</v>
       </c>
       <c r="B37" s="8">
-        <v>46080.77828799769</v>
+        <v>46080.611621331016</v>
       </c>
       <c r="C37" s="8">
-        <v>46114.76324759259</v>
+        <v>46114.59658092592</v>
       </c>
       <c r="D37" s="8">
-        <v>46114.763248877316</v>
+        <v>46114.59658221065</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>138</v>
@@ -3580,13 +3580,13 @@
         <v>140</v>
       </c>
       <c r="B38" s="5">
-        <v>46080.77828825232</v>
+        <v>46080.611621585645</v>
       </c>
       <c r="C38" s="5">
-        <v>46114.76325834491</v>
+        <v>46114.596591678244</v>
       </c>
       <c r="D38" s="5">
-        <v>46114.7632599537</v>
+        <v>46114.59659328704</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>141</v>
@@ -3641,13 +3641,13 @@
         <v>143</v>
       </c>
       <c r="B39" s="8">
-        <v>46080.778288518515</v>
+        <v>46080.61162185185</v>
       </c>
       <c r="C39" s="8">
-        <v>46121.86007915509</v>
+        <v>46121.69341248843</v>
       </c>
       <c r="D39" s="8">
-        <v>46149.197581886576</v>
+        <v>46149.030915219904</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>144</v>
@@ -3706,13 +3706,13 @@
         <v>148</v>
       </c>
       <c r="B40" s="5">
-        <v>46080.77828673611</v>
+        <v>46080.611620069445</v>
       </c>
       <c r="C40" s="5">
-        <v>46114.759847696754</v>
+        <v>46114.5931810301</v>
       </c>
       <c r="D40" s="5">
-        <v>46121.8600697338</v>
+        <v>46121.693403067125</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>149</v>
@@ -3767,13 +3767,13 @@
         <v>151</v>
       </c>
       <c r="B41" s="8">
-        <v>46080.77828702546</v>
+        <v>46080.611620358795</v>
       </c>
       <c r="C41" s="8">
-        <v>46121.860064803244</v>
+        <v>46121.69339813657</v>
       </c>
       <c r="D41" s="8">
-        <v>46121.86006597222</v>
+        <v>46121.69339930556</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>150</v>
@@ -3828,13 +3828,13 @@
         <v>153</v>
       </c>
       <c r="B42" s="5">
-        <v>46080.77828724537</v>
+        <v>46080.611620578704</v>
       </c>
       <c r="C42" s="5">
-        <v>46114.76051153935</v>
+        <v>46114.59384487268</v>
       </c>
       <c r="D42" s="5">
-        <v>46114.76064238426</v>
+        <v>46114.593975717595</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>154</v>
@@ -3893,13 +3893,13 @@
         <v>156</v>
       </c>
       <c r="B43" s="8">
-        <v>46080.77828748843</v>
+        <v>46080.61162082176</v>
       </c>
       <c r="C43" s="8">
-        <v>46114.76044965278</v>
+        <v>46114.59378298611</v>
       </c>
       <c r="D43" s="8">
-        <v>46114.76045094908</v>
+        <v>46114.593784282406</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>157</v>
@@ -3954,13 +3954,13 @@
         <v>159</v>
       </c>
       <c r="B44" s="5">
-        <v>46080.77828770834</v>
+        <v>46080.611621041666</v>
       </c>
       <c r="C44" s="5">
-        <v>46114.76049635417</v>
+        <v>46114.593829687496</v>
       </c>
       <c r="D44" s="5">
-        <v>46114.7604978125</v>
+        <v>46114.59383114583</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>160</v>
@@ -4015,13 +4015,13 @@
         <v>162</v>
       </c>
       <c r="B45" s="8">
-        <v>46080.778287939815</v>
+        <v>46080.61162127314</v>
       </c>
       <c r="C45" s="8">
-        <v>46140.83890416667</v>
+        <v>46140.672237499995</v>
       </c>
       <c r="D45" s="8">
-        <v>46141.772341724536</v>
+        <v>46141.60567505787</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>163</v>
@@ -4064,13 +4064,13 @@
         <v>165</v>
       </c>
       <c r="B46" s="5">
-        <v>46080.778288182875</v>
+        <v>46080.611621516204</v>
       </c>
       <c r="C46" s="5">
-        <v>46127.678079895835</v>
+        <v>46127.511413229164</v>
       </c>
       <c r="D46" s="5">
-        <v>46127.67810105324</v>
+        <v>46127.51143438657</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>166</v>
@@ -4129,13 +4129,13 @@
         <v>170</v>
       </c>
       <c r="B47" s="8">
-        <v>46080.77828842592</v>
+        <v>46080.611621759264</v>
       </c>
       <c r="C47" s="8">
-        <v>46127.67813141204</v>
+        <v>46127.511464745374</v>
       </c>
       <c r="D47" s="8">
-        <v>46158.16995894676</v>
+        <v>46158.00329228009</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>171</v>
@@ -4194,13 +4194,13 @@
         <v>176</v>
       </c>
       <c r="B48" s="5">
-        <v>46087.53644159722</v>
+        <v>46087.36977493056</v>
       </c>
       <c r="C48" s="5">
-        <v>46127.678180752315</v>
+        <v>46127.51151408565</v>
       </c>
       <c r="D48" s="5">
-        <v>46161.20788581019</v>
+        <v>46161.04121914352</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>177</v>
@@ -4257,13 +4257,13 @@
         <v>179</v>
       </c>
       <c r="B49" s="8">
-        <v>46087.536521331014</v>
+        <v>46087.36985466436</v>
       </c>
       <c r="C49" s="8">
-        <v>46140.83887265046</v>
+        <v>46140.67220598379</v>
       </c>
       <c r="D49" s="8">
-        <v>46141.771787060185</v>
+        <v>46141.60512039352</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>180</v>
@@ -4322,13 +4322,13 @@
         <v>183</v>
       </c>
       <c r="B50" s="5">
-        <v>46080.77828866898</v>
+        <v>46080.61162200231</v>
       </c>
       <c r="C50" s="5">
-        <v>46133.62051065972</v>
+        <v>46133.453843993055</v>
       </c>
       <c r="D50" s="5">
-        <v>46141.772585231476</v>
+        <v>46141.60591856482</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>184</v>
@@ -4371,13 +4371,13 @@
         <v>186</v>
       </c>
       <c r="B51" s="8">
-        <v>46080.77828892361</v>
+        <v>46080.61162225694</v>
       </c>
       <c r="C51" s="8">
-        <v>46133.6204378588</v>
+        <v>46133.45377119213</v>
       </c>
       <c r="D51" s="8">
-        <v>46151.18472762732</v>
+        <v>46151.01806096065</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>187</v>
@@ -4436,13 +4436,13 @@
         <v>191</v>
       </c>
       <c r="B52" s="5">
-        <v>46080.77828760417</v>
+        <v>46080.6116209375</v>
       </c>
       <c r="C52" s="5">
-        <v>46133.62049425926</v>
+        <v>46133.45382759259</v>
       </c>
       <c r="D52" s="5">
-        <v>46155.20414789351</v>
+        <v>46155.03748122686</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>192</v>
@@ -4501,13 +4501,13 @@
         <v>196</v>
       </c>
       <c r="B53" s="8">
-        <v>46080.778288009256</v>
+        <v>46080.61162134259</v>
       </c>
       <c r="C53" s="8">
-        <v>46132.76769947917</v>
+        <v>46132.6010328125</v>
       </c>
       <c r="D53" s="8">
-        <v>46141.77186175926</v>
+        <v>46141.60519509259</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>197</v>
@@ -4550,13 +4550,13 @@
         <v>199</v>
       </c>
       <c r="B54" s="5">
-        <v>46080.77828832176</v>
+        <v>46080.61162165509</v>
       </c>
       <c r="C54" s="5">
-        <v>46128.489822488424</v>
+        <v>46128.32315582176</v>
       </c>
       <c r="D54" s="5">
-        <v>46165.18131118055</v>
+        <v>46165.01464451389</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>200</v>
@@ -4615,13 +4615,13 @@
         <v>204</v>
       </c>
       <c r="B55" s="8">
-        <v>46080.77828861111</v>
+        <v>46080.611621944445</v>
       </c>
       <c r="C55" s="8">
-        <v>46128.48987719907</v>
+        <v>46128.323210532406</v>
       </c>
       <c r="D55" s="8">
-        <v>46170.185211909724</v>
+        <v>46170.01854524306</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>205</v>
@@ -4680,13 +4680,13 @@
         <v>208</v>
       </c>
       <c r="B56" s="5">
-        <v>46080.778288912035</v>
+        <v>46080.61162224537</v>
       </c>
       <c r="C56" s="5">
-        <v>46132.76768157407</v>
+        <v>46132.601014907406</v>
       </c>
       <c r="D56" s="5">
-        <v>46172.2027446875</v>
+        <v>46172.03607802083</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>209</v>
@@ -4745,13 +4745,13 @@
         <v>212</v>
       </c>
       <c r="B57" s="8">
-        <v>46080.77828921296</v>
+        <v>46080.6116225463</v>
       </c>
       <c r="C57" s="8">
-        <v>46141.711290810184</v>
+        <v>46141.54462414352</v>
       </c>
       <c r="D57" s="8">
-        <v>46141.77231675926</v>
+        <v>46141.60565009259</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>184</v>
@@ -4794,13 +4794,13 @@
         <v>214</v>
       </c>
       <c r="B58" s="5">
-        <v>46080.77828957176</v>
+        <v>46080.6116229051</v>
       </c>
       <c r="C58" s="5">
-        <v>46133.62103284722</v>
+        <v>46133.45436618055</v>
       </c>
       <c r="D58" s="5">
-        <v>46156.16908381945</v>
+        <v>46156.00241715278</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>215</v>
@@ -4859,13 +4859,13 @@
         <v>217</v>
       </c>
       <c r="B59" s="8">
-        <v>46080.77828986111</v>
+        <v>46080.61162319445</v>
       </c>
       <c r="C59" s="8">
-        <v>46133.621046631946</v>
+        <v>46133.454379965275</v>
       </c>
       <c r="D59" s="8">
-        <v>46133.62189940972</v>
+        <v>46133.45523274306</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>218</v>
@@ -4924,13 +4924,13 @@
         <v>220</v>
       </c>
       <c r="B60" s="5">
-        <v>46080.778290138885</v>
+        <v>46080.61162347222</v>
       </c>
       <c r="C60" s="5">
-        <v>46121.8679578125</v>
+        <v>46121.70129114583</v>
       </c>
       <c r="D60" s="5">
-        <v>46121.867985185185</v>
+        <v>46121.70131851852</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>221</v>
@@ -4989,13 +4989,13 @@
         <v>223</v>
       </c>
       <c r="B61" s="8">
-        <v>46080.778290393515</v>
+        <v>46080.61162372685</v>
       </c>
       <c r="C61" s="8">
-        <v>46121.86789461806</v>
+        <v>46121.70122795139</v>
       </c>
       <c r="D61" s="8">
-        <v>46121.86791173611</v>
+        <v>46121.701245069446</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>224</v>
@@ -5054,13 +5054,13 @@
         <v>226</v>
       </c>
       <c r="B62" s="5">
-        <v>46080.7854796875</v>
+        <v>46080.61881302083</v>
       </c>
       <c r="C62" s="5">
-        <v>46141.772219398146</v>
+        <v>46141.60555273148</v>
       </c>
       <c r="D62" s="5">
-        <v>46195.17883668981</v>
+        <v>46195.01217002315</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>54</v>
@@ -5119,13 +5119,13 @@
         <v>228</v>
       </c>
       <c r="B63" s="8">
-        <v>46080.77828662037</v>
+        <v>46080.61161995371</v>
       </c>
       <c r="C63" s="8">
-        <v>46141.711275752314</v>
+        <v>46141.54460908565</v>
       </c>
       <c r="D63" s="8">
-        <v>46141.71127789352</v>
+        <v>46141.544611226855</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>229</v>
@@ -5168,13 +5168,13 @@
         <v>231</v>
       </c>
       <c r="B64" s="5">
-        <v>46080.77828694445</v>
+        <v>46080.61162027778</v>
       </c>
       <c r="C64" s="5">
-        <v>46133.62079252314</v>
+        <v>46133.454125856486</v>
       </c>
       <c r="D64" s="5">
-        <v>46192.18706700232</v>
+        <v>46192.02040033565</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>232</v>
@@ -5233,13 +5233,13 @@
         <v>234</v>
       </c>
       <c r="B65" s="8">
-        <v>46080.778287187495</v>
+        <v>46080.61162052084</v>
       </c>
       <c r="C65" s="8">
-        <v>46133.620870451385</v>
+        <v>46133.45420378472</v>
       </c>
       <c r="D65" s="8">
-        <v>46133.62091327546</v>
+        <v>46133.454246608795</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>235</v>
@@ -5298,13 +5298,13 @@
         <v>238</v>
       </c>
       <c r="B66" s="5">
-        <v>46080.77828746528</v>
+        <v>46080.61162079861</v>
       </c>
       <c r="C66" s="5">
-        <v>46133.62178611111</v>
+        <v>46133.45511944444</v>
       </c>
       <c r="D66" s="5">
-        <v>46133.62180199074</v>
+        <v>46133.455135324075</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>239</v>
@@ -5363,13 +5363,13 @@
         <v>241</v>
       </c>
       <c r="B67" s="8">
-        <v>46080.77828770834</v>
+        <v>46080.611621041666</v>
       </c>
       <c r="C67" s="8">
-        <v>46133.62179804398</v>
+        <v>46133.45513137731</v>
       </c>
       <c r="D67" s="8">
-        <v>46133.62181490741</v>
+        <v>46133.45514824074</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>242</v>
@@ -5428,13 +5428,13 @@
         <v>244</v>
       </c>
       <c r="B68" s="5">
-        <v>46080.77828796297</v>
+        <v>46080.611621296295</v>
       </c>
       <c r="C68" s="5">
-        <v>46133.62181768518</v>
+        <v>46133.45515101852</v>
       </c>
       <c r="D68" s="5">
-        <v>46133.6218338426</v>
+        <v>46133.455167175925</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>245</v>
@@ -5493,13 +5493,13 @@
         <v>247</v>
       </c>
       <c r="B69" s="8">
-        <v>46080.778288217596</v>
+        <v>46080.611621550925</v>
       </c>
       <c r="C69" s="8">
-        <v>46133.621873553246</v>
+        <v>46133.455206886574</v>
       </c>
       <c r="D69" s="8">
-        <v>46133.621889710645</v>
+        <v>46133.45522304398</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>181</v>
@@ -5558,13 +5558,13 @@
         <v>250</v>
       </c>
       <c r="B70" s="5">
-        <v>46080.77828846065</v>
+        <v>46080.611621793985</v>
       </c>
       <c r="C70" s="5">
-        <v>46140.8390024074</v>
+        <v>46140.67233574074</v>
       </c>
       <c r="D70" s="5">
-        <v>46141.711773055555</v>
+        <v>46141.54510638889</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>182</v>
@@ -5623,13 +5623,13 @@
         <v>252</v>
       </c>
       <c r="B71" s="8">
-        <v>46080.7782887037</v>
+        <v>46080.61162203704</v>
       </c>
       <c r="C71" s="8">
-        <v>46141.71205135417</v>
+        <v>46141.5453846875</v>
       </c>
       <c r="D71" s="8">
-        <v>46141.712052731484</v>
+        <v>46141.54538606481</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>253</v>
@@ -5672,13 +5672,13 @@
         <v>255</v>
       </c>
       <c r="B72" s="5">
-        <v>46080.77828895833</v>
+        <v>46080.61162229167</v>
       </c>
       <c r="C72" s="5">
-        <v>46140.83904666667</v>
+        <v>46140.67238</v>
       </c>
       <c r="D72" s="5">
-        <v>46141.711805625004</v>
+        <v>46141.54513895833</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>256</v>
@@ -5737,13 +5737,13 @@
         <v>260</v>
       </c>
       <c r="B73" s="8">
-        <v>46080.778287152774</v>
+        <v>46080.61162048611</v>
       </c>
       <c r="C73" s="8">
-        <v>46141.711726180554</v>
+        <v>46141.54505951389</v>
       </c>
       <c r="D73" s="8">
-        <v>46141.7118290162</v>
+        <v>46141.54516234953</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>261</v>
@@ -5802,13 +5802,13 @@
         <v>264</v>
       </c>
       <c r="B74" s="5">
-        <v>46080.77828751157</v>
+        <v>46080.61162084491</v>
       </c>
       <c r="C74" s="5">
-        <v>46141.7119153588</v>
+        <v>46141.54524869213</v>
       </c>
       <c r="D74" s="5">
-        <v>46141.711917002314</v>
+        <v>46141.54525033565</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>265</v>
@@ -5867,13 +5867,13 @@
         <v>267</v>
       </c>
       <c r="B75" s="8">
-        <v>46080.77828782407</v>
+        <v>46080.61162115741</v>
       </c>
       <c r="C75" s="8">
-        <v>46141.71196090278</v>
+        <v>46141.545294236115</v>
       </c>
       <c r="D75" s="8">
-        <v>46141.71196212963</v>
+        <v>46141.54529546296</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>268</v>
@@ -5932,11 +5932,11 @@
         <v>270</v>
       </c>
       <c r="B76" s="5">
-        <v>46080.77828809028</v>
+        <v>46080.61162142361</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46090.61092975695</v>
+        <v>46090.44426309028</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>271</v>
@@ -5979,11 +5979,11 @@
         <v>273</v>
       </c>
       <c r="B77" s="8">
-        <v>46080.77828868055</v>
+        <v>46080.611622013894</v>
       </c>
       <c r="C77" s="9"/>
       <c r="D77" s="8">
-        <v>46141.711969386575</v>
+        <v>46141.54530271991</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>73</v>
@@ -6042,11 +6042,11 @@
         <v>277</v>
       </c>
       <c r="B78" s="5">
-        <v>46080.77828835648</v>
+        <v>46080.611621689815</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46141.711970648146</v>
+        <v>46141.54530398148</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>278</v>
@@ -6105,11 +6105,11 @@
         <v>279</v>
       </c>
       <c r="B79" s="8">
-        <v>46090.61171577546</v>
+        <v>46090.44504910879</v>
       </c>
       <c r="C79" s="9"/>
       <c r="D79" s="8">
-        <v>46090.614530335646</v>
+        <v>46090.44786366898</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>280</v>
@@ -6158,11 +6158,11 @@
         <v>282</v>
       </c>
       <c r="B80" s="5">
-        <v>46090.61199928241</v>
+        <v>46090.44533261574</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46141.711971944445</v>
+        <v>46141.545305277774</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>283</v>
@@ -6221,11 +6221,11 @@
         <v>285</v>
       </c>
       <c r="B81" s="8">
-        <v>46090.61208010417</v>
+        <v>46090.4454134375</v>
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="8">
-        <v>46090.61869820602</v>
+        <v>46090.45203153935</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>286</v>

--- a/data/50001524 - ATACAMA KOZAN.xlsx
+++ b/data/50001524 - ATACAMA KOZAN.xlsx
@@ -1498,13 +1498,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46080.61161974537</v>
+        <v>46080.77828641204</v>
       </c>
       <c r="C4" s="5">
-        <v>46097.66998934028</v>
+        <v>46097.83665600694</v>
       </c>
       <c r="D4" s="5">
-        <v>46097.67008267361</v>
+        <v>46097.83674934028</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1547,13 +1547,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46080.611620138894</v>
+        <v>46080.77828680555</v>
       </c>
       <c r="C5" s="8">
-        <v>46097.669548425925</v>
+        <v>46097.8362150926</v>
       </c>
       <c r="D5" s="8">
-        <v>46097.66956912037</v>
+        <v>46097.836235787036</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1610,13 +1610,13 @@
         <v>33</v>
       </c>
       <c r="B6" s="5">
-        <v>46080.61162043981</v>
+        <v>46080.778287106485</v>
       </c>
       <c r="C6" s="5">
-        <v>46097.66955386574</v>
+        <v>46097.83622053241</v>
       </c>
       <c r="D6" s="5">
-        <v>46097.66956886574</v>
+        <v>46097.836235532406</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>34</v>
@@ -1673,13 +1673,13 @@
         <v>37</v>
       </c>
       <c r="B7" s="8">
-        <v>46080.61162074074</v>
+        <v>46080.778287407404</v>
       </c>
       <c r="C7" s="8">
-        <v>46097.66956028935</v>
+        <v>46097.83622695602</v>
       </c>
       <c r="D7" s="8">
-        <v>46097.669575266205</v>
+        <v>46097.83624193287</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>38</v>
@@ -1736,13 +1736,13 @@
         <v>39</v>
       </c>
       <c r="B8" s="5">
-        <v>46080.61162106482</v>
+        <v>46080.77828773148</v>
       </c>
       <c r="C8" s="5">
-        <v>46093.47637546297</v>
+        <v>46093.643042129625</v>
       </c>
       <c r="D8" s="5">
-        <v>46100.62501127315</v>
+        <v>46100.791677939815</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>40</v>
@@ -1799,13 +1799,13 @@
         <v>42</v>
       </c>
       <c r="B9" s="8">
-        <v>46080.61162134259</v>
+        <v>46080.778288009256</v>
       </c>
       <c r="C9" s="8">
-        <v>46097.66957738426</v>
+        <v>46097.83624405092</v>
       </c>
       <c r="D9" s="8">
-        <v>46097.669591805556</v>
+        <v>46097.83625847222</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>43</v>
@@ -1862,13 +1862,13 @@
         <v>44</v>
       </c>
       <c r="B10" s="5">
-        <v>46080.61691350694</v>
+        <v>46080.78358017361</v>
       </c>
       <c r="C10" s="5">
-        <v>46141.54493447917</v>
+        <v>46141.711601145835</v>
       </c>
       <c r="D10" s="5">
-        <v>46141.54493556713</v>
+        <v>46141.7116022338</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>45</v>
@@ -1911,13 +1911,13 @@
         <v>47</v>
       </c>
       <c r="B11" s="8">
-        <v>46080.617096863425</v>
+        <v>46080.7837635301</v>
       </c>
       <c r="C11" s="8">
-        <v>46114.345154421295</v>
+        <v>46114.51182108796</v>
       </c>
       <c r="D11" s="8">
-        <v>46114.34517267361</v>
+        <v>46114.51183934028</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>48</v>
@@ -1976,13 +1976,13 @@
         <v>52</v>
       </c>
       <c r="B12" s="5">
-        <v>46080.61714857639</v>
+        <v>46080.783815243056</v>
       </c>
       <c r="C12" s="5">
-        <v>46141.54484769676</v>
+        <v>46141.71151436343</v>
       </c>
       <c r="D12" s="5">
-        <v>46197.01965607639</v>
+        <v>46197.18632274306</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>53</v>
@@ -2041,13 +2041,13 @@
         <v>58</v>
       </c>
       <c r="B13" s="8">
-        <v>46080.61162163195</v>
+        <v>46080.77828829861</v>
       </c>
       <c r="C13" s="8">
-        <v>46114.34593138889</v>
+        <v>46114.51259805556</v>
       </c>
       <c r="D13" s="8">
-        <v>46114.59239144676</v>
+        <v>46114.75905811343</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>59</v>
@@ -2092,13 +2092,13 @@
         <v>61</v>
       </c>
       <c r="B14" s="5">
-        <v>46080.6116219213</v>
+        <v>46080.778288587964</v>
       </c>
       <c r="C14" s="5">
-        <v>46114.34528306713</v>
+        <v>46114.511949733795</v>
       </c>
       <c r="D14" s="5">
-        <v>46114.34529875</v>
+        <v>46114.51196541666</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>62</v>
@@ -2157,13 +2157,13 @@
         <v>64</v>
       </c>
       <c r="B15" s="8">
-        <v>46080.61162287037</v>
+        <v>46080.77828953703</v>
       </c>
       <c r="C15" s="8">
-        <v>46114.34543883102</v>
+        <v>46114.512105497684</v>
       </c>
       <c r="D15" s="8">
-        <v>46114.345454849536</v>
+        <v>46114.51212151621</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>65</v>
@@ -2222,13 +2222,13 @@
         <v>67</v>
       </c>
       <c r="B16" s="5">
-        <v>46080.61161952546</v>
+        <v>46080.77828619213</v>
       </c>
       <c r="C16" s="5">
-        <v>46114.345740000004</v>
+        <v>46114.51240666666</v>
       </c>
       <c r="D16" s="5">
-        <v>46114.34575462963</v>
+        <v>46114.5124212963</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>68</v>
@@ -2287,13 +2287,13 @@
         <v>70</v>
       </c>
       <c r="B17" s="8">
-        <v>46080.61161986111</v>
+        <v>46080.77828652778</v>
       </c>
       <c r="C17" s="8">
-        <v>46114.34591538194</v>
+        <v>46114.512582048614</v>
       </c>
       <c r="D17" s="8">
-        <v>46114.34593252315</v>
+        <v>46114.51259918981</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>71</v>
@@ -2352,13 +2352,13 @@
         <v>74</v>
       </c>
       <c r="B18" s="5">
-        <v>46080.611620208336</v>
+        <v>46080.778286875</v>
       </c>
       <c r="C18" s="5">
-        <v>46126.68891861111</v>
+        <v>46126.85558527778</v>
       </c>
       <c r="D18" s="5">
-        <v>46126.6889318287</v>
+        <v>46126.85559849537</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>75</v>
@@ -2405,13 +2405,13 @@
         <v>77</v>
       </c>
       <c r="B19" s="8">
-        <v>46080.61162048611</v>
+        <v>46080.778287152774</v>
       </c>
       <c r="C19" s="8">
-        <v>46114.345347615745</v>
+        <v>46114.51201428241</v>
       </c>
       <c r="D19" s="8">
-        <v>46114.345363518514</v>
+        <v>46114.512030185186</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>78</v>
@@ -2470,13 +2470,13 @@
         <v>80</v>
       </c>
       <c r="B20" s="5">
-        <v>46080.61162085648</v>
+        <v>46080.77828752315</v>
       </c>
       <c r="C20" s="5">
-        <v>46114.34608914352</v>
+        <v>46114.51275581018</v>
       </c>
       <c r="D20" s="5">
-        <v>46114.34610408565</v>
+        <v>46114.51277075231</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>81</v>
@@ -2535,13 +2535,13 @@
         <v>83</v>
       </c>
       <c r="B21" s="8">
-        <v>46080.61162113426</v>
+        <v>46080.77828780093</v>
       </c>
       <c r="C21" s="8">
-        <v>46126.68889943287</v>
+        <v>46126.85556609953</v>
       </c>
       <c r="D21" s="8">
-        <v>46126.6889155324</v>
+        <v>46126.855582199074</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>84</v>
@@ -2600,13 +2600,13 @@
         <v>87</v>
       </c>
       <c r="B22" s="5">
-        <v>46080.61739265046</v>
+        <v>46080.78405931713</v>
       </c>
       <c r="C22" s="5">
-        <v>46114.34641268519</v>
+        <v>46114.51307935185</v>
       </c>
       <c r="D22" s="5">
-        <v>46114.34642909722</v>
+        <v>46114.51309576389</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>88</v>
@@ -2665,13 +2665,13 @@
         <v>90</v>
       </c>
       <c r="B23" s="8">
-        <v>46080.61162144676</v>
+        <v>46080.778288113426</v>
       </c>
       <c r="C23" s="8">
-        <v>46114.34650914352</v>
+        <v>46114.513175810185</v>
       </c>
       <c r="D23" s="8">
-        <v>46114.34660958333</v>
+        <v>46114.51327625</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>91</v>
@@ -2730,13 +2730,13 @@
         <v>93</v>
       </c>
       <c r="B24" s="5">
-        <v>46080.61162173611</v>
+        <v>46080.77828840278</v>
       </c>
       <c r="C24" s="5">
-        <v>46114.593050069445</v>
+        <v>46114.75971673611</v>
       </c>
       <c r="D24" s="5">
-        <v>46114.593065532405</v>
+        <v>46114.759732199076</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>94</v>
@@ -2795,13 +2795,13 @@
         <v>98</v>
       </c>
       <c r="B25" s="8">
-        <v>46080.61162202546</v>
+        <v>46080.778288692134</v>
       </c>
       <c r="C25" s="8">
-        <v>46140.67228493055</v>
+        <v>46140.83895159722</v>
       </c>
       <c r="D25" s="8">
-        <v>46140.67228600694</v>
+        <v>46140.838952673614</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>99</v>
@@ -2844,13 +2844,13 @@
         <v>101</v>
       </c>
       <c r="B26" s="5">
-        <v>46080.61162231481</v>
+        <v>46080.778288981484</v>
       </c>
       <c r="C26" s="5">
-        <v>46139.61452841436</v>
+        <v>46139.781195081014</v>
       </c>
       <c r="D26" s="5">
-        <v>46139.614539560185</v>
+        <v>46139.78120622685</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>102</v>
@@ -2909,13 +2909,13 @@
         <v>107</v>
       </c>
       <c r="B27" s="8">
-        <v>46080.611619351854</v>
+        <v>46080.77828601852</v>
       </c>
       <c r="C27" s="8">
-        <v>46139.61441649306</v>
+        <v>46139.78108315972</v>
       </c>
       <c r="D27" s="8">
-        <v>46139.61441783565</v>
+        <v>46139.78108450232</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>108</v>
@@ -2970,13 +2970,13 @@
         <v>111</v>
       </c>
       <c r="B28" s="5">
-        <v>46080.61161972222</v>
+        <v>46080.778286388886</v>
       </c>
       <c r="C28" s="5">
-        <v>46139.6145152199</v>
+        <v>46139.781181886574</v>
       </c>
       <c r="D28" s="5">
-        <v>46139.61451663195</v>
+        <v>46139.78118329861</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>112</v>
@@ -3031,13 +3031,13 @@
         <v>113</v>
       </c>
       <c r="B29" s="8">
-        <v>46080.617547939815</v>
+        <v>46080.78421460648</v>
       </c>
       <c r="C29" s="8">
-        <v>46140.64236803241</v>
+        <v>46140.80903469908</v>
       </c>
       <c r="D29" s="8">
-        <v>46191.03731707176</v>
+        <v>46191.20398373842</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>114</v>
@@ -3096,13 +3096,13 @@
         <v>116</v>
       </c>
       <c r="B30" s="5">
-        <v>46080.61797731482</v>
+        <v>46080.78464398148</v>
       </c>
       <c r="C30" s="5">
-        <v>46114.59513332176</v>
+        <v>46114.761799988424</v>
       </c>
       <c r="D30" s="5">
-        <v>46114.595134641204</v>
+        <v>46114.761801307875</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>117</v>
@@ -3151,13 +3151,13 @@
         <v>119</v>
       </c>
       <c r="B31" s="8">
-        <v>46080.61805363426</v>
+        <v>46080.78472030093</v>
       </c>
       <c r="C31" s="8">
-        <v>46140.64228364584</v>
+        <v>46140.8089503125</v>
       </c>
       <c r="D31" s="8">
-        <v>46140.642285671296</v>
+        <v>46140.80895233796</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>120</v>
@@ -3206,13 +3206,13 @@
         <v>122</v>
       </c>
       <c r="B32" s="5">
-        <v>46080.61161998843</v>
+        <v>46080.77828665509</v>
       </c>
       <c r="C32" s="5">
-        <v>46133.45426238426</v>
+        <v>46133.62092905093</v>
       </c>
       <c r="D32" s="5">
-        <v>46154.02539614584</v>
+        <v>46154.1920628125</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>123</v>
@@ -3271,13 +3271,13 @@
         <v>125</v>
       </c>
       <c r="B33" s="8">
-        <v>46080.611620254625</v>
+        <v>46080.7782869213</v>
       </c>
       <c r="C33" s="8">
-        <v>46133.45419553241</v>
+        <v>46133.62086219907</v>
       </c>
       <c r="D33" s="8">
-        <v>46133.454196597224</v>
+        <v>46133.62086326389</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>126</v>
@@ -3332,13 +3332,13 @@
         <v>128</v>
       </c>
       <c r="B34" s="5">
-        <v>46080.61162052084</v>
+        <v>46080.778287187495</v>
       </c>
       <c r="C34" s="5">
-        <v>46133.45423341435</v>
+        <v>46133.62090008102</v>
       </c>
       <c r="D34" s="5">
-        <v>46133.45423459491</v>
+        <v>46133.62090126157</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>129</v>
@@ -3393,13 +3393,13 @@
         <v>131</v>
       </c>
       <c r="B35" s="8">
-        <v>46080.61162079861</v>
+        <v>46080.77828746528</v>
       </c>
       <c r="C35" s="8">
-        <v>46114.59660967592</v>
+        <v>46114.76327634259</v>
       </c>
       <c r="D35" s="8">
-        <v>46114.59662506945</v>
+        <v>46114.76329173611</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>132</v>
@@ -3458,13 +3458,13 @@
         <v>134</v>
       </c>
       <c r="B36" s="5">
-        <v>46080.61162106482</v>
+        <v>46080.77828773148</v>
       </c>
       <c r="C36" s="5">
-        <v>46114.59652575231</v>
+        <v>46114.76319241898</v>
       </c>
       <c r="D36" s="5">
-        <v>46114.596526875</v>
+        <v>46114.76319354167</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>135</v>
@@ -3519,13 +3519,13 @@
         <v>137</v>
       </c>
       <c r="B37" s="8">
-        <v>46080.611621331016</v>
+        <v>46080.77828799769</v>
       </c>
       <c r="C37" s="8">
-        <v>46114.59658092592</v>
+        <v>46114.76324759259</v>
       </c>
       <c r="D37" s="8">
-        <v>46114.59658221065</v>
+        <v>46114.763248877316</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>138</v>
@@ -3580,13 +3580,13 @@
         <v>140</v>
       </c>
       <c r="B38" s="5">
-        <v>46080.611621585645</v>
+        <v>46080.77828825232</v>
       </c>
       <c r="C38" s="5">
-        <v>46114.596591678244</v>
+        <v>46114.76325834491</v>
       </c>
       <c r="D38" s="5">
-        <v>46114.59659328704</v>
+        <v>46114.7632599537</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>141</v>
@@ -3641,13 +3641,13 @@
         <v>143</v>
       </c>
       <c r="B39" s="8">
-        <v>46080.61162185185</v>
+        <v>46080.778288518515</v>
       </c>
       <c r="C39" s="8">
-        <v>46121.69341248843</v>
+        <v>46121.86007915509</v>
       </c>
       <c r="D39" s="8">
-        <v>46149.030915219904</v>
+        <v>46149.197581886576</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>144</v>
@@ -3706,13 +3706,13 @@
         <v>148</v>
       </c>
       <c r="B40" s="5">
-        <v>46080.611620069445</v>
+        <v>46080.77828673611</v>
       </c>
       <c r="C40" s="5">
-        <v>46114.5931810301</v>
+        <v>46114.759847696754</v>
       </c>
       <c r="D40" s="5">
-        <v>46121.693403067125</v>
+        <v>46121.8600697338</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>149</v>
@@ -3767,13 +3767,13 @@
         <v>151</v>
       </c>
       <c r="B41" s="8">
-        <v>46080.611620358795</v>
+        <v>46080.77828702546</v>
       </c>
       <c r="C41" s="8">
-        <v>46121.69339813657</v>
+        <v>46121.860064803244</v>
       </c>
       <c r="D41" s="8">
-        <v>46121.69339930556</v>
+        <v>46121.86006597222</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>150</v>
@@ -3828,13 +3828,13 @@
         <v>153</v>
       </c>
       <c r="B42" s="5">
-        <v>46080.611620578704</v>
+        <v>46080.77828724537</v>
       </c>
       <c r="C42" s="5">
-        <v>46114.59384487268</v>
+        <v>46114.76051153935</v>
       </c>
       <c r="D42" s="5">
-        <v>46114.593975717595</v>
+        <v>46114.76064238426</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>154</v>
@@ -3893,13 +3893,13 @@
         <v>156</v>
       </c>
       <c r="B43" s="8">
-        <v>46080.61162082176</v>
+        <v>46080.77828748843</v>
       </c>
       <c r="C43" s="8">
-        <v>46114.59378298611</v>
+        <v>46114.76044965278</v>
       </c>
       <c r="D43" s="8">
-        <v>46114.593784282406</v>
+        <v>46114.76045094908</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>157</v>
@@ -3954,13 +3954,13 @@
         <v>159</v>
       </c>
       <c r="B44" s="5">
-        <v>46080.611621041666</v>
+        <v>46080.77828770834</v>
       </c>
       <c r="C44" s="5">
-        <v>46114.593829687496</v>
+        <v>46114.76049635417</v>
       </c>
       <c r="D44" s="5">
-        <v>46114.59383114583</v>
+        <v>46114.7604978125</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>160</v>
@@ -4015,13 +4015,13 @@
         <v>162</v>
       </c>
       <c r="B45" s="8">
-        <v>46080.61162127314</v>
+        <v>46080.778287939815</v>
       </c>
       <c r="C45" s="8">
-        <v>46140.672237499995</v>
+        <v>46140.83890416667</v>
       </c>
       <c r="D45" s="8">
-        <v>46141.60567505787</v>
+        <v>46141.772341724536</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>163</v>
@@ -4064,13 +4064,13 @@
         <v>165</v>
       </c>
       <c r="B46" s="5">
-        <v>46080.611621516204</v>
+        <v>46080.778288182875</v>
       </c>
       <c r="C46" s="5">
-        <v>46127.511413229164</v>
+        <v>46127.678079895835</v>
       </c>
       <c r="D46" s="5">
-        <v>46127.51143438657</v>
+        <v>46127.67810105324</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>166</v>
@@ -4129,13 +4129,13 @@
         <v>170</v>
       </c>
       <c r="B47" s="8">
-        <v>46080.611621759264</v>
+        <v>46080.77828842592</v>
       </c>
       <c r="C47" s="8">
-        <v>46127.511464745374</v>
+        <v>46127.67813141204</v>
       </c>
       <c r="D47" s="8">
-        <v>46158.00329228009</v>
+        <v>46158.16995894676</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>171</v>
@@ -4194,13 +4194,13 @@
         <v>176</v>
       </c>
       <c r="B48" s="5">
-        <v>46087.36977493056</v>
+        <v>46087.53644159722</v>
       </c>
       <c r="C48" s="5">
-        <v>46127.51151408565</v>
+        <v>46127.678180752315</v>
       </c>
       <c r="D48" s="5">
-        <v>46161.04121914352</v>
+        <v>46161.20788581019</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>177</v>
@@ -4257,13 +4257,13 @@
         <v>179</v>
       </c>
       <c r="B49" s="8">
-        <v>46087.36985466436</v>
+        <v>46087.536521331014</v>
       </c>
       <c r="C49" s="8">
-        <v>46140.67220598379</v>
+        <v>46140.83887265046</v>
       </c>
       <c r="D49" s="8">
-        <v>46141.60512039352</v>
+        <v>46141.771787060185</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>180</v>
@@ -4322,13 +4322,13 @@
         <v>183</v>
       </c>
       <c r="B50" s="5">
-        <v>46080.61162200231</v>
+        <v>46080.77828866898</v>
       </c>
       <c r="C50" s="5">
-        <v>46133.453843993055</v>
+        <v>46133.62051065972</v>
       </c>
       <c r="D50" s="5">
-        <v>46141.60591856482</v>
+        <v>46141.772585231476</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>184</v>
@@ -4371,13 +4371,13 @@
         <v>186</v>
       </c>
       <c r="B51" s="8">
-        <v>46080.61162225694</v>
+        <v>46080.77828892361</v>
       </c>
       <c r="C51" s="8">
-        <v>46133.45377119213</v>
+        <v>46133.6204378588</v>
       </c>
       <c r="D51" s="8">
-        <v>46151.01806096065</v>
+        <v>46151.18472762732</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>187</v>
@@ -4436,13 +4436,13 @@
         <v>191</v>
       </c>
       <c r="B52" s="5">
-        <v>46080.6116209375</v>
+        <v>46080.77828760417</v>
       </c>
       <c r="C52" s="5">
-        <v>46133.45382759259</v>
+        <v>46133.62049425926</v>
       </c>
       <c r="D52" s="5">
-        <v>46155.03748122686</v>
+        <v>46155.20414789351</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>192</v>
@@ -4501,13 +4501,13 @@
         <v>196</v>
       </c>
       <c r="B53" s="8">
-        <v>46080.61162134259</v>
+        <v>46080.778288009256</v>
       </c>
       <c r="C53" s="8">
-        <v>46132.6010328125</v>
+        <v>46132.76769947917</v>
       </c>
       <c r="D53" s="8">
-        <v>46141.60519509259</v>
+        <v>46141.77186175926</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>197</v>
@@ -4550,13 +4550,13 @@
         <v>199</v>
       </c>
       <c r="B54" s="5">
-        <v>46080.61162165509</v>
+        <v>46080.77828832176</v>
       </c>
       <c r="C54" s="5">
-        <v>46128.32315582176</v>
+        <v>46128.489822488424</v>
       </c>
       <c r="D54" s="5">
-        <v>46165.01464451389</v>
+        <v>46165.18131118055</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>200</v>
@@ -4615,13 +4615,13 @@
         <v>204</v>
       </c>
       <c r="B55" s="8">
-        <v>46080.611621944445</v>
+        <v>46080.77828861111</v>
       </c>
       <c r="C55" s="8">
-        <v>46128.323210532406</v>
+        <v>46128.48987719907</v>
       </c>
       <c r="D55" s="8">
-        <v>46170.01854524306</v>
+        <v>46170.185211909724</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>205</v>
@@ -4680,13 +4680,13 @@
         <v>208</v>
       </c>
       <c r="B56" s="5">
-        <v>46080.61162224537</v>
+        <v>46080.778288912035</v>
       </c>
       <c r="C56" s="5">
-        <v>46132.601014907406</v>
+        <v>46132.76768157407</v>
       </c>
       <c r="D56" s="5">
-        <v>46172.03607802083</v>
+        <v>46172.2027446875</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>209</v>
@@ -4745,13 +4745,13 @@
         <v>212</v>
       </c>
       <c r="B57" s="8">
-        <v>46080.6116225463</v>
+        <v>46080.77828921296</v>
       </c>
       <c r="C57" s="8">
-        <v>46141.54462414352</v>
+        <v>46141.711290810184</v>
       </c>
       <c r="D57" s="8">
-        <v>46141.60565009259</v>
+        <v>46141.77231675926</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>184</v>
@@ -4794,13 +4794,13 @@
         <v>214</v>
       </c>
       <c r="B58" s="5">
-        <v>46080.6116229051</v>
+        <v>46080.77828957176</v>
       </c>
       <c r="C58" s="5">
-        <v>46133.45436618055</v>
+        <v>46133.62103284722</v>
       </c>
       <c r="D58" s="5">
-        <v>46156.00241715278</v>
+        <v>46156.16908381945</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>215</v>
@@ -4859,13 +4859,13 @@
         <v>217</v>
       </c>
       <c r="B59" s="8">
-        <v>46080.61162319445</v>
+        <v>46080.77828986111</v>
       </c>
       <c r="C59" s="8">
-        <v>46133.454379965275</v>
+        <v>46133.621046631946</v>
       </c>
       <c r="D59" s="8">
-        <v>46133.45523274306</v>
+        <v>46133.62189940972</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>218</v>
@@ -4924,13 +4924,13 @@
         <v>220</v>
       </c>
       <c r="B60" s="5">
-        <v>46080.61162347222</v>
+        <v>46080.778290138885</v>
       </c>
       <c r="C60" s="5">
-        <v>46121.70129114583</v>
+        <v>46121.8679578125</v>
       </c>
       <c r="D60" s="5">
-        <v>46121.70131851852</v>
+        <v>46121.867985185185</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>221</v>
@@ -4989,13 +4989,13 @@
         <v>223</v>
       </c>
       <c r="B61" s="8">
-        <v>46080.61162372685</v>
+        <v>46080.778290393515</v>
       </c>
       <c r="C61" s="8">
-        <v>46121.70122795139</v>
+        <v>46121.86789461806</v>
       </c>
       <c r="D61" s="8">
-        <v>46121.701245069446</v>
+        <v>46121.86791173611</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>224</v>
@@ -5054,13 +5054,13 @@
         <v>226</v>
       </c>
       <c r="B62" s="5">
-        <v>46080.61881302083</v>
+        <v>46080.7854796875</v>
       </c>
       <c r="C62" s="5">
-        <v>46141.60555273148</v>
+        <v>46141.772219398146</v>
       </c>
       <c r="D62" s="5">
-        <v>46195.01217002315</v>
+        <v>46195.17883668981</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>54</v>
@@ -5119,13 +5119,13 @@
         <v>228</v>
       </c>
       <c r="B63" s="8">
-        <v>46080.61161995371</v>
+        <v>46080.77828662037</v>
       </c>
       <c r="C63" s="8">
-        <v>46141.54460908565</v>
+        <v>46141.711275752314</v>
       </c>
       <c r="D63" s="8">
-        <v>46141.544611226855</v>
+        <v>46141.71127789352</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>229</v>
@@ -5168,13 +5168,13 @@
         <v>231</v>
       </c>
       <c r="B64" s="5">
-        <v>46080.61162027778</v>
+        <v>46080.77828694445</v>
       </c>
       <c r="C64" s="5">
-        <v>46133.454125856486</v>
+        <v>46133.62079252314</v>
       </c>
       <c r="D64" s="5">
-        <v>46192.02040033565</v>
+        <v>46192.18706700232</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>232</v>
@@ -5233,13 +5233,13 @@
         <v>234</v>
       </c>
       <c r="B65" s="8">
-        <v>46080.61162052084</v>
+        <v>46080.778287187495</v>
       </c>
       <c r="C65" s="8">
-        <v>46133.45420378472</v>
+        <v>46133.620870451385</v>
       </c>
       <c r="D65" s="8">
-        <v>46133.454246608795</v>
+        <v>46133.62091327546</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>235</v>
@@ -5298,13 +5298,13 @@
         <v>238</v>
       </c>
       <c r="B66" s="5">
-        <v>46080.61162079861</v>
+        <v>46080.77828746528</v>
       </c>
       <c r="C66" s="5">
-        <v>46133.45511944444</v>
+        <v>46133.62178611111</v>
       </c>
       <c r="D66" s="5">
-        <v>46133.455135324075</v>
+        <v>46133.62180199074</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>239</v>
@@ -5363,13 +5363,13 @@
         <v>241</v>
       </c>
       <c r="B67" s="8">
-        <v>46080.611621041666</v>
+        <v>46080.77828770834</v>
       </c>
       <c r="C67" s="8">
-        <v>46133.45513137731</v>
+        <v>46133.62179804398</v>
       </c>
       <c r="D67" s="8">
-        <v>46133.45514824074</v>
+        <v>46133.62181490741</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>242</v>
@@ -5428,13 +5428,13 @@
         <v>244</v>
       </c>
       <c r="B68" s="5">
-        <v>46080.611621296295</v>
+        <v>46080.77828796297</v>
       </c>
       <c r="C68" s="5">
-        <v>46133.45515101852</v>
+        <v>46133.62181768518</v>
       </c>
       <c r="D68" s="5">
-        <v>46133.455167175925</v>
+        <v>46133.6218338426</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>245</v>
@@ -5493,13 +5493,13 @@
         <v>247</v>
       </c>
       <c r="B69" s="8">
-        <v>46080.611621550925</v>
+        <v>46080.778288217596</v>
       </c>
       <c r="C69" s="8">
-        <v>46133.455206886574</v>
+        <v>46133.621873553246</v>
       </c>
       <c r="D69" s="8">
-        <v>46133.45522304398</v>
+        <v>46133.621889710645</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>181</v>
@@ -5558,13 +5558,13 @@
         <v>250</v>
       </c>
       <c r="B70" s="5">
-        <v>46080.611621793985</v>
+        <v>46080.77828846065</v>
       </c>
       <c r="C70" s="5">
-        <v>46140.67233574074</v>
+        <v>46140.8390024074</v>
       </c>
       <c r="D70" s="5">
-        <v>46141.54510638889</v>
+        <v>46141.711773055555</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>182</v>
@@ -5623,13 +5623,13 @@
         <v>252</v>
       </c>
       <c r="B71" s="8">
-        <v>46080.61162203704</v>
+        <v>46080.7782887037</v>
       </c>
       <c r="C71" s="8">
-        <v>46141.5453846875</v>
+        <v>46141.71205135417</v>
       </c>
       <c r="D71" s="8">
-        <v>46141.54538606481</v>
+        <v>46141.712052731484</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>253</v>
@@ -5672,13 +5672,13 @@
         <v>255</v>
       </c>
       <c r="B72" s="5">
-        <v>46080.61162229167</v>
+        <v>46080.77828895833</v>
       </c>
       <c r="C72" s="5">
-        <v>46140.67238</v>
+        <v>46140.83904666667</v>
       </c>
       <c r="D72" s="5">
-        <v>46141.54513895833</v>
+        <v>46141.711805625004</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>256</v>
@@ -5737,13 +5737,13 @@
         <v>260</v>
       </c>
       <c r="B73" s="8">
-        <v>46080.61162048611</v>
+        <v>46080.778287152774</v>
       </c>
       <c r="C73" s="8">
-        <v>46141.54505951389</v>
+        <v>46141.711726180554</v>
       </c>
       <c r="D73" s="8">
-        <v>46141.54516234953</v>
+        <v>46141.7118290162</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>261</v>
@@ -5802,13 +5802,13 @@
         <v>264</v>
       </c>
       <c r="B74" s="5">
-        <v>46080.61162084491</v>
+        <v>46080.77828751157</v>
       </c>
       <c r="C74" s="5">
-        <v>46141.54524869213</v>
+        <v>46141.7119153588</v>
       </c>
       <c r="D74" s="5">
-        <v>46141.54525033565</v>
+        <v>46141.711917002314</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>265</v>
@@ -5867,13 +5867,13 @@
         <v>267</v>
       </c>
       <c r="B75" s="8">
-        <v>46080.61162115741</v>
+        <v>46080.77828782407</v>
       </c>
       <c r="C75" s="8">
-        <v>46141.545294236115</v>
+        <v>46141.71196090278</v>
       </c>
       <c r="D75" s="8">
-        <v>46141.54529546296</v>
+        <v>46141.71196212963</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>268</v>
@@ -5932,11 +5932,11 @@
         <v>270</v>
       </c>
       <c r="B76" s="5">
-        <v>46080.61162142361</v>
+        <v>46080.77828809028</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46090.44426309028</v>
+        <v>46090.61092975695</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>271</v>
@@ -5979,11 +5979,11 @@
         <v>273</v>
       </c>
       <c r="B77" s="8">
-        <v>46080.611622013894</v>
+        <v>46080.77828868055</v>
       </c>
       <c r="C77" s="9"/>
       <c r="D77" s="8">
-        <v>46141.54530271991</v>
+        <v>46141.711969386575</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>73</v>
@@ -6042,11 +6042,11 @@
         <v>277</v>
       </c>
       <c r="B78" s="5">
-        <v>46080.611621689815</v>
+        <v>46080.77828835648</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46141.54530398148</v>
+        <v>46141.711970648146</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>278</v>
@@ -6105,11 +6105,11 @@
         <v>279</v>
       </c>
       <c r="B79" s="8">
-        <v>46090.44504910879</v>
+        <v>46090.61171577546</v>
       </c>
       <c r="C79" s="9"/>
       <c r="D79" s="8">
-        <v>46090.44786366898</v>
+        <v>46090.614530335646</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>280</v>
@@ -6158,11 +6158,11 @@
         <v>282</v>
       </c>
       <c r="B80" s="5">
-        <v>46090.44533261574</v>
+        <v>46090.61199928241</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46141.545305277774</v>
+        <v>46141.711971944445</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>283</v>
@@ -6221,11 +6221,11 @@
         <v>285</v>
       </c>
       <c r="B81" s="8">
-        <v>46090.4454134375</v>
+        <v>46090.61208010417</v>
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="8">
-        <v>46090.45203153935</v>
+        <v>46090.61869820602</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>286</v>

--- a/data/50001524 - ATACAMA KOZAN.xlsx
+++ b/data/50001524 - ATACAMA KOZAN.xlsx
@@ -3037,7 +3037,7 @@
         <v>46140.80903469908</v>
       </c>
       <c r="D29" s="8">
-        <v>46191.20398373842</v>
+        <v>46199.207547604165</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>114</v>
@@ -3075,8 +3075,8 @@
       <c r="P29" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="Q29" s="12" t="s">
-        <v>56</v>
+      <c r="Q29" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="R29" s="9">
         <v>1</v>

--- a/data/50001524 - ATACAMA KOZAN.xlsx
+++ b/data/50001524 - ATACAMA KOZAN.xlsx
@@ -3834,7 +3834,7 @@
         <v>46114.76051153935</v>
       </c>
       <c r="D42" s="5">
-        <v>46114.76064238426</v>
+        <v>46202.187087708335</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>154</v>
@@ -3872,8 +3872,8 @@
       <c r="P42" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="Q42" s="11" t="s">
-        <v>106</v>
+      <c r="Q42" s="12" t="s">
+        <v>56</v>
       </c>
       <c r="R42" s="6">
         <v>1</v>

--- a/data/50001524 - ATACAMA KOZAN.xlsx
+++ b/data/50001524 - ATACAMA KOZAN.xlsx
@@ -5060,7 +5060,7 @@
         <v>46141.772219398146</v>
       </c>
       <c r="D62" s="5">
-        <v>46195.17883668981</v>
+        <v>46203.19232511574</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>54</v>
@@ -5098,8 +5098,8 @@
       <c r="P62" s="6" t="s">
         <v>227</v>
       </c>
-      <c r="Q62" s="12" t="s">
-        <v>56</v>
+      <c r="Q62" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="R62" s="6">
         <v>1</v>

--- a/data/50001524 - ATACAMA KOZAN.xlsx
+++ b/data/50001524 - ATACAMA KOZAN.xlsx
@@ -4995,7 +4995,7 @@
         <v>46121.86789461806</v>
       </c>
       <c r="D61" s="8">
-        <v>46121.86791173611</v>
+        <v>46204.20245239583</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>224</v>
@@ -5033,8 +5033,8 @@
       <c r="P61" s="9" t="s">
         <v>225</v>
       </c>
-      <c r="Q61" s="11" t="s">
-        <v>106</v>
+      <c r="Q61" s="12" t="s">
+        <v>56</v>
       </c>
       <c r="R61" s="9">
         <v>1</v>

--- a/data/50001524 - ATACAMA KOZAN.xlsx
+++ b/data/50001524 - ATACAMA KOZAN.xlsx
@@ -181,304 +181,304 @@
     <t>Embalaje,Ingenieria Servicios</t>
   </si>
   <si>
+    <t>Tarea en curso</t>
+  </si>
+  <si>
+    <t>1213412709779748</t>
+  </si>
+  <si>
+    <t>Ingenieria Jefe de proyecto:</t>
+  </si>
+  <si>
+    <t>Ingenieria Detalle,Ingenieria Basica Motor,Ingenieria basica Rodete</t>
+  </si>
+  <si>
+    <t>1213412709779749</t>
+  </si>
+  <si>
+    <t>Ingenieria Basica Motor</t>
+  </si>
+  <si>
+    <t>Analisis de costeo,Ingenieria Jefe de proyecto:,propuesta motor</t>
+  </si>
+  <si>
+    <t>1213412709779751</t>
+  </si>
+  <si>
+    <t>Ingenieria basica Rodete</t>
+  </si>
+  <si>
+    <t>Analisis de costeo,Ingenieria Jefe de proyecto:,propuesta nucleo rodete,propuesta alabes</t>
+  </si>
+  <si>
+    <t>1213412709779752</t>
+  </si>
+  <si>
+    <t>Ingenieria Detalle</t>
+  </si>
+  <si>
+    <t>Analisis de costeo,Ingenieria Jefe de proyecto:,Propuesta Sensores y accesorios,propuesta compras a codigo // aprovisionamiento,Planos Preliminar</t>
+  </si>
+  <si>
+    <t>1213412709779753</t>
+  </si>
+  <si>
+    <t>Analisis de costeo</t>
+  </si>
+  <si>
+    <t>Ingenieria Basica Motor,Ingenieria Detalle,Ingenieria basica Rodete</t>
+  </si>
+  <si>
+    <t>Costos</t>
+  </si>
+  <si>
+    <t>1213412709779754</t>
+  </si>
+  <si>
+    <t>Propuesta compras:</t>
+  </si>
+  <si>
+    <t>propuesta motor,propuesta alabes,propuesta nucleo rodete,Propuesta Tablero,Propuesta Sensores y accesorios,propuesta compras a codigo // aprovisionamiento</t>
+  </si>
+  <si>
+    <t>1213412709779755</t>
+  </si>
+  <si>
+    <t>propuesta motor</t>
+  </si>
+  <si>
+    <t>Propuesta compras:,Generación OC motor</t>
+  </si>
+  <si>
+    <t>1213412709779756</t>
+  </si>
+  <si>
+    <t>propuesta alabes</t>
+  </si>
+  <si>
+    <t>Propuesta compras:,Generación OC Alabe</t>
+  </si>
+  <si>
+    <t>1213412709779757</t>
+  </si>
+  <si>
+    <t>propuesta nucleo rodete</t>
+  </si>
+  <si>
+    <t>benjamin.bustos@zitron.com</t>
+  </si>
+  <si>
+    <t>Propuesta compras:,Generación OC Rodete</t>
+  </si>
+  <si>
+    <t>1213458788103568</t>
+  </si>
+  <si>
+    <t>Propuesta Tablero</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Propuesta compras:,Generacion oc Tableros </t>
+  </si>
+  <si>
+    <t>1213412709779758</t>
+  </si>
+  <si>
+    <t>Propuesta Sensores y accesorios</t>
+  </si>
+  <si>
+    <t>Propuesta compras:,Generación Oc sensores</t>
+  </si>
+  <si>
+    <t>1213412709779759</t>
+  </si>
+  <si>
+    <t>propuesta compras a codigo // aprovisionamiento</t>
+  </si>
+  <si>
+    <t>hugo isla martinez</t>
+  </si>
+  <si>
+    <t>hugo.isla@zitron.com</t>
+  </si>
+  <si>
+    <t>Propuesta compras:,Fabricacion a codigo y compras locales</t>
+  </si>
+  <si>
+    <t>1213412709779760</t>
+  </si>
+  <si>
+    <t>Compras:</t>
+  </si>
+  <si>
+    <t>Alabe,Tableros,rodete,Motor,Materiales a codigo // compras locales aprovisionamientomiento:,Sensores</t>
+  </si>
+  <si>
+    <t>1213412709779761</t>
+  </si>
+  <si>
+    <t>Alabe</t>
+  </si>
+  <si>
+    <t>Eliana</t>
+  </si>
+  <si>
+    <t>ecarico@zitron.com</t>
+  </si>
+  <si>
+    <t>Generación OC Alabe,Fabricación Alabe</t>
+  </si>
+  <si>
+    <t>Baja</t>
+  </si>
+  <si>
+    <t>1213412709779762</t>
+  </si>
+  <si>
+    <t>Generación OC Alabe</t>
+  </si>
+  <si>
+    <t>Fabricación Alabe,Alabe</t>
+  </si>
+  <si>
+    <t>Tarea sin iniciar</t>
+  </si>
+  <si>
+    <t>1213412709779763</t>
+  </si>
+  <si>
+    <t>Fabricación Alabe</t>
+  </si>
+  <si>
+    <t>1213458788103569</t>
+  </si>
+  <si>
+    <t>Tableros</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generacion oc Tableros ,Fabricacion Tableros </t>
+  </si>
+  <si>
+    <t>1213458788103571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generacion oc Tableros </t>
+  </si>
+  <si>
+    <t>Fabricacion Tableros ,Tableros</t>
+  </si>
+  <si>
+    <t>1213458788103572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fabricacion Tableros </t>
+  </si>
+  <si>
+    <t>Tableros,Recepcion Tableros</t>
+  </si>
+  <si>
+    <t>1213412709779764</t>
+  </si>
+  <si>
+    <t>rodete</t>
+  </si>
+  <si>
+    <t>Generación OC Rodete,Fabricación Rodete</t>
+  </si>
+  <si>
+    <t>1213412709779765</t>
+  </si>
+  <si>
+    <t>Generación OC Rodete</t>
+  </si>
+  <si>
+    <t>Fabricación Rodete,rodete</t>
+  </si>
+  <si>
+    <t>1213412709779766</t>
+  </si>
+  <si>
+    <t>Fabricación Rodete</t>
+  </si>
+  <si>
+    <t>rodete,Recepcion Rodete,Recepcion Alabe</t>
+  </si>
+  <si>
+    <t>1213470416901259</t>
+  </si>
+  <si>
+    <t>Motor</t>
+  </si>
+  <si>
+    <t>Generación OC motor,Fabricación motor,Planos motor proveedor</t>
+  </si>
+  <si>
+    <t>1213470416901260</t>
+  </si>
+  <si>
+    <t>Generación OC motor</t>
+  </si>
+  <si>
+    <t>Fabricación motor,Planos motor proveedor,Motor</t>
+  </si>
+  <si>
+    <t>1213470416901261</t>
+  </si>
+  <si>
+    <t>Fabricación motor</t>
+  </si>
+  <si>
+    <t>Motor,Recepcion  motor</t>
+  </si>
+  <si>
+    <t>1213470416901262</t>
+  </si>
+  <si>
+    <t>Planos motor proveedor</t>
+  </si>
+  <si>
+    <t>Motor,Planos Definitivos</t>
+  </si>
+  <si>
+    <t>1213470416901263</t>
+  </si>
+  <si>
+    <t>Materiales a codigo // compras locales aprovisionamientomiento:</t>
+  </si>
+  <si>
+    <t>Yerlia Ayleen Castillo Diaz</t>
+  </si>
+  <si>
+    <t>yerlia.castillo@zitron.com</t>
+  </si>
+  <si>
+    <t>Generación OC materiales,Fabricacion a codigo y compras locales</t>
+  </si>
+  <si>
+    <t>1213470416901264</t>
+  </si>
+  <si>
+    <t>Generación OC materiales</t>
+  </si>
+  <si>
+    <t>Fabricacion a codigo y compras locales</t>
+  </si>
+  <si>
+    <t>1213470416901265</t>
+  </si>
+  <si>
+    <t>Generación OC materiales,Materiales a codigo // compras locales aprovisionamientomiento:,Recepcion materiales a codigos // compras locales aprovisionamiento</t>
+  </si>
+  <si>
+    <t>1213470416901266</t>
+  </si>
+  <si>
+    <t>Sensores</t>
+  </si>
+  <si>
+    <t>Generación Oc sensores,Fabricación Sensores</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>Tarea en curso</t>
-  </si>
-  <si>
-    <t>1213412709779748</t>
-  </si>
-  <si>
-    <t>Ingenieria Jefe de proyecto:</t>
-  </si>
-  <si>
-    <t>Ingenieria Detalle,Ingenieria Basica Motor,Ingenieria basica Rodete</t>
-  </si>
-  <si>
-    <t>1213412709779749</t>
-  </si>
-  <si>
-    <t>Ingenieria Basica Motor</t>
-  </si>
-  <si>
-    <t>Analisis de costeo,Ingenieria Jefe de proyecto:,propuesta motor</t>
-  </si>
-  <si>
-    <t>1213412709779751</t>
-  </si>
-  <si>
-    <t>Ingenieria basica Rodete</t>
-  </si>
-  <si>
-    <t>Analisis de costeo,Ingenieria Jefe de proyecto:,propuesta nucleo rodete,propuesta alabes</t>
-  </si>
-  <si>
-    <t>1213412709779752</t>
-  </si>
-  <si>
-    <t>Ingenieria Detalle</t>
-  </si>
-  <si>
-    <t>Analisis de costeo,Ingenieria Jefe de proyecto:,Propuesta Sensores y accesorios,propuesta compras a codigo // aprovisionamiento,Planos Preliminar</t>
-  </si>
-  <si>
-    <t>1213412709779753</t>
-  </si>
-  <si>
-    <t>Analisis de costeo</t>
-  </si>
-  <si>
-    <t>Ingenieria Basica Motor,Ingenieria Detalle,Ingenieria basica Rodete</t>
-  </si>
-  <si>
-    <t>Costos</t>
-  </si>
-  <si>
-    <t>1213412709779754</t>
-  </si>
-  <si>
-    <t>Propuesta compras:</t>
-  </si>
-  <si>
-    <t>propuesta motor,propuesta alabes,propuesta nucleo rodete,Propuesta Tablero,Propuesta Sensores y accesorios,propuesta compras a codigo // aprovisionamiento</t>
-  </si>
-  <si>
-    <t>1213412709779755</t>
-  </si>
-  <si>
-    <t>propuesta motor</t>
-  </si>
-  <si>
-    <t>Propuesta compras:,Generación OC motor</t>
-  </si>
-  <si>
-    <t>1213412709779756</t>
-  </si>
-  <si>
-    <t>propuesta alabes</t>
-  </si>
-  <si>
-    <t>Propuesta compras:,Generación OC Alabe</t>
-  </si>
-  <si>
-    <t>1213412709779757</t>
-  </si>
-  <si>
-    <t>propuesta nucleo rodete</t>
-  </si>
-  <si>
-    <t>benjamin.bustos@zitron.com</t>
-  </si>
-  <si>
-    <t>Propuesta compras:,Generación OC Rodete</t>
-  </si>
-  <si>
-    <t>1213458788103568</t>
-  </si>
-  <si>
-    <t>Propuesta Tablero</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Propuesta compras:,Generacion oc Tableros </t>
-  </si>
-  <si>
-    <t>1213412709779758</t>
-  </si>
-  <si>
-    <t>Propuesta Sensores y accesorios</t>
-  </si>
-  <si>
-    <t>Propuesta compras:,Generación Oc sensores</t>
-  </si>
-  <si>
-    <t>1213412709779759</t>
-  </si>
-  <si>
-    <t>propuesta compras a codigo // aprovisionamiento</t>
-  </si>
-  <si>
-    <t>hugo isla martinez</t>
-  </si>
-  <si>
-    <t>hugo.isla@zitron.com</t>
-  </si>
-  <si>
-    <t>Propuesta compras:,Fabricacion a codigo y compras locales</t>
-  </si>
-  <si>
-    <t>1213412709779760</t>
-  </si>
-  <si>
-    <t>Compras:</t>
-  </si>
-  <si>
-    <t>Alabe,Tableros,rodete,Motor,Materiales a codigo // compras locales aprovisionamientomiento:,Sensores</t>
-  </si>
-  <si>
-    <t>1213412709779761</t>
-  </si>
-  <si>
-    <t>Alabe</t>
-  </si>
-  <si>
-    <t>Eliana</t>
-  </si>
-  <si>
-    <t>ecarico@zitron.com</t>
-  </si>
-  <si>
-    <t>Generación OC Alabe,Fabricación Alabe</t>
-  </si>
-  <si>
-    <t>Baja</t>
-  </si>
-  <si>
-    <t>1213412709779762</t>
-  </si>
-  <si>
-    <t>Generación OC Alabe</t>
-  </si>
-  <si>
-    <t>Fabricación Alabe,Alabe</t>
-  </si>
-  <si>
-    <t>Tarea sin iniciar</t>
-  </si>
-  <si>
-    <t>1213412709779763</t>
-  </si>
-  <si>
-    <t>Fabricación Alabe</t>
-  </si>
-  <si>
-    <t>1213458788103569</t>
-  </si>
-  <si>
-    <t>Tableros</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generacion oc Tableros ,Fabricacion Tableros </t>
-  </si>
-  <si>
-    <t>1213458788103571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generacion oc Tableros </t>
-  </si>
-  <si>
-    <t>Fabricacion Tableros ,Tableros</t>
-  </si>
-  <si>
-    <t>1213458788103572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fabricacion Tableros </t>
-  </si>
-  <si>
-    <t>Tableros,Recepcion Tableros</t>
-  </si>
-  <si>
-    <t>1213412709779764</t>
-  </si>
-  <si>
-    <t>rodete</t>
-  </si>
-  <si>
-    <t>Generación OC Rodete,Fabricación Rodete</t>
-  </si>
-  <si>
-    <t>1213412709779765</t>
-  </si>
-  <si>
-    <t>Generación OC Rodete</t>
-  </si>
-  <si>
-    <t>Fabricación Rodete,rodete</t>
-  </si>
-  <si>
-    <t>1213412709779766</t>
-  </si>
-  <si>
-    <t>Fabricación Rodete</t>
-  </si>
-  <si>
-    <t>rodete,Recepcion Rodete,Recepcion Alabe</t>
-  </si>
-  <si>
-    <t>1213470416901259</t>
-  </si>
-  <si>
-    <t>Motor</t>
-  </si>
-  <si>
-    <t>Generación OC motor,Fabricación motor,Planos motor proveedor</t>
-  </si>
-  <si>
-    <t>1213470416901260</t>
-  </si>
-  <si>
-    <t>Generación OC motor</t>
-  </si>
-  <si>
-    <t>Fabricación motor,Planos motor proveedor,Motor</t>
-  </si>
-  <si>
-    <t>1213470416901261</t>
-  </si>
-  <si>
-    <t>Fabricación motor</t>
-  </si>
-  <si>
-    <t>Motor,Recepcion  motor</t>
-  </si>
-  <si>
-    <t>1213470416901262</t>
-  </si>
-  <si>
-    <t>Planos motor proveedor</t>
-  </si>
-  <si>
-    <t>Motor,Planos Definitivos</t>
-  </si>
-  <si>
-    <t>1213470416901263</t>
-  </si>
-  <si>
-    <t>Materiales a codigo // compras locales aprovisionamientomiento:</t>
-  </si>
-  <si>
-    <t>Yerlia Ayleen Castillo Diaz</t>
-  </si>
-  <si>
-    <t>yerlia.castillo@zitron.com</t>
-  </si>
-  <si>
-    <t>Generación OC materiales,Fabricacion a codigo y compras locales</t>
-  </si>
-  <si>
-    <t>1213470416901264</t>
-  </si>
-  <si>
-    <t>Generación OC materiales</t>
-  </si>
-  <si>
-    <t>Fabricacion a codigo y compras locales</t>
-  </si>
-  <si>
-    <t>1213470416901265</t>
-  </si>
-  <si>
-    <t>Generación OC materiales,Materiales a codigo // compras locales aprovisionamientomiento:,Recepcion materiales a codigos // compras locales aprovisionamiento</t>
-  </si>
-  <si>
-    <t>1213470416901266</t>
-  </si>
-  <si>
-    <t>Sensores</t>
-  </si>
-  <si>
-    <t>Generación Oc sensores,Fabricación Sensores</t>
   </si>
   <si>
     <t>1213470416901267</t>
@@ -1498,13 +1498,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46080.77828641204</v>
+        <v>46080.61161974537</v>
       </c>
       <c r="C4" s="5">
-        <v>46097.83665600694</v>
+        <v>46097.66998934028</v>
       </c>
       <c r="D4" s="5">
-        <v>46097.83674934028</v>
+        <v>46097.67008267361</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1547,13 +1547,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46080.77828680555</v>
+        <v>46080.611620138894</v>
       </c>
       <c r="C5" s="8">
-        <v>46097.8362150926</v>
+        <v>46097.669548425925</v>
       </c>
       <c r="D5" s="8">
-        <v>46097.836235787036</v>
+        <v>46097.66956912037</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1610,13 +1610,13 @@
         <v>33</v>
       </c>
       <c r="B6" s="5">
-        <v>46080.778287106485</v>
+        <v>46080.61162043981</v>
       </c>
       <c r="C6" s="5">
-        <v>46097.83622053241</v>
+        <v>46097.66955386574</v>
       </c>
       <c r="D6" s="5">
-        <v>46097.836235532406</v>
+        <v>46097.66956886574</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>34</v>
@@ -1673,13 +1673,13 @@
         <v>37</v>
       </c>
       <c r="B7" s="8">
-        <v>46080.778287407404</v>
+        <v>46080.61162074074</v>
       </c>
       <c r="C7" s="8">
-        <v>46097.83622695602</v>
+        <v>46097.66956028935</v>
       </c>
       <c r="D7" s="8">
-        <v>46097.83624193287</v>
+        <v>46097.669575266205</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>38</v>
@@ -1736,13 +1736,13 @@
         <v>39</v>
       </c>
       <c r="B8" s="5">
-        <v>46080.77828773148</v>
+        <v>46080.61162106482</v>
       </c>
       <c r="C8" s="5">
-        <v>46093.643042129625</v>
+        <v>46093.47637546297</v>
       </c>
       <c r="D8" s="5">
-        <v>46100.791677939815</v>
+        <v>46100.62501127315</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>40</v>
@@ -1799,13 +1799,13 @@
         <v>42</v>
       </c>
       <c r="B9" s="8">
-        <v>46080.778288009256</v>
+        <v>46080.61162134259</v>
       </c>
       <c r="C9" s="8">
-        <v>46097.83624405092</v>
+        <v>46097.66957738426</v>
       </c>
       <c r="D9" s="8">
-        <v>46097.83625847222</v>
+        <v>46097.669591805556</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>43</v>
@@ -1862,13 +1862,13 @@
         <v>44</v>
       </c>
       <c r="B10" s="5">
-        <v>46080.78358017361</v>
+        <v>46080.61691350694</v>
       </c>
       <c r="C10" s="5">
-        <v>46141.711601145835</v>
+        <v>46141.54493447917</v>
       </c>
       <c r="D10" s="5">
-        <v>46141.7116022338</v>
+        <v>46141.54493556713</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>45</v>
@@ -1911,13 +1911,13 @@
         <v>47</v>
       </c>
       <c r="B11" s="8">
-        <v>46080.7837635301</v>
+        <v>46080.617096863425</v>
       </c>
       <c r="C11" s="8">
-        <v>46114.51182108796</v>
+        <v>46114.345154421295</v>
       </c>
       <c r="D11" s="8">
-        <v>46114.51183934028</v>
+        <v>46114.34517267361</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>48</v>
@@ -1976,13 +1976,13 @@
         <v>52</v>
       </c>
       <c r="B12" s="5">
-        <v>46080.783815243056</v>
+        <v>46080.61714857639</v>
       </c>
       <c r="C12" s="5">
-        <v>46141.71151436343</v>
+        <v>46141.54484769676</v>
       </c>
       <c r="D12" s="5">
-        <v>46197.18632274306</v>
+        <v>46205.01245163195</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>53</v>
@@ -2020,14 +2020,14 @@
       <c r="P12" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="Q12" s="12" t="s">
-        <v>56</v>
+      <c r="Q12" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="R12" s="6">
         <v>1</v>
       </c>
       <c r="S12" s="12" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="T12" s="5">
         <v>46203</v>
@@ -2038,19 +2038,19 @@
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="B13" s="8">
+        <v>46080.61162163195</v>
+      </c>
+      <c r="C13" s="8">
+        <v>46114.34593138889</v>
+      </c>
+      <c r="D13" s="8">
+        <v>46114.59239144676</v>
+      </c>
+      <c r="E13" s="9" t="s">
         <v>58</v>
-      </c>
-      <c r="B13" s="8">
-        <v>46080.77828829861</v>
-      </c>
-      <c r="C13" s="8">
-        <v>46114.51259805556</v>
-      </c>
-      <c r="D13" s="8">
-        <v>46114.75905811343</v>
-      </c>
-      <c r="E13" s="9" t="s">
-        <v>59</v>
       </c>
       <c r="F13" s="9" t="s">
         <v>25</v>
@@ -2074,7 +2074,7 @@
         <v>26</v>
       </c>
       <c r="O13" s="9" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="P13" s="9" t="s">
         <v>26</v>
@@ -2089,19 +2089,19 @@
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B14" s="5">
+        <v>46080.6116219213</v>
+      </c>
+      <c r="C14" s="5">
+        <v>46114.34528306713</v>
+      </c>
+      <c r="D14" s="5">
+        <v>46114.34529875</v>
+      </c>
+      <c r="E14" s="6" t="s">
         <v>61</v>
-      </c>
-      <c r="B14" s="5">
-        <v>46080.778288587964</v>
-      </c>
-      <c r="C14" s="5">
-        <v>46114.511949733795</v>
-      </c>
-      <c r="D14" s="5">
-        <v>46114.51196541666</v>
-      </c>
-      <c r="E14" s="6" t="s">
-        <v>62</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>26</v>
@@ -2128,13 +2128,13 @@
         <v>26</v>
       </c>
       <c r="N14" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="O14" s="6" t="s">
         <v>40</v>
       </c>
       <c r="P14" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Q14" s="10" t="s">
         <v>31</v>
@@ -2154,19 +2154,19 @@
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="B15" s="8">
+        <v>46080.61162287037</v>
+      </c>
+      <c r="C15" s="8">
+        <v>46114.34543883102</v>
+      </c>
+      <c r="D15" s="8">
+        <v>46114.345454849536</v>
+      </c>
+      <c r="E15" s="9" t="s">
         <v>64</v>
-      </c>
-      <c r="B15" s="8">
-        <v>46080.77828953703</v>
-      </c>
-      <c r="C15" s="8">
-        <v>46114.512105497684</v>
-      </c>
-      <c r="D15" s="8">
-        <v>46114.51212151621</v>
-      </c>
-      <c r="E15" s="9" t="s">
-        <v>65</v>
       </c>
       <c r="F15" s="9" t="s">
         <v>26</v>
@@ -2193,13 +2193,13 @@
         <v>26</v>
       </c>
       <c r="N15" s="9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="O15" s="9" t="s">
         <v>40</v>
       </c>
       <c r="P15" s="9" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="Q15" s="10" t="s">
         <v>31</v>
@@ -2219,19 +2219,19 @@
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B16" s="5">
+        <v>46080.61161952546</v>
+      </c>
+      <c r="C16" s="5">
+        <v>46114.345740000004</v>
+      </c>
+      <c r="D16" s="5">
+        <v>46114.34575462963</v>
+      </c>
+      <c r="E16" s="6" t="s">
         <v>67</v>
-      </c>
-      <c r="B16" s="5">
-        <v>46080.77828619213</v>
-      </c>
-      <c r="C16" s="5">
-        <v>46114.51240666666</v>
-      </c>
-      <c r="D16" s="5">
-        <v>46114.5124212963</v>
-      </c>
-      <c r="E16" s="6" t="s">
-        <v>68</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>26</v>
@@ -2258,13 +2258,13 @@
         <v>26</v>
       </c>
       <c r="N16" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="O16" s="6" t="s">
         <v>40</v>
       </c>
       <c r="P16" s="6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="Q16" s="10" t="s">
         <v>31</v>
@@ -2284,19 +2284,19 @@
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="B17" s="8">
+        <v>46080.61161986111</v>
+      </c>
+      <c r="C17" s="8">
+        <v>46114.34591538194</v>
+      </c>
+      <c r="D17" s="8">
+        <v>46114.34593252315</v>
+      </c>
+      <c r="E17" s="9" t="s">
         <v>70</v>
-      </c>
-      <c r="B17" s="8">
-        <v>46080.77828652778</v>
-      </c>
-      <c r="C17" s="8">
-        <v>46114.512582048614</v>
-      </c>
-      <c r="D17" s="8">
-        <v>46114.51259918981</v>
-      </c>
-      <c r="E17" s="9" t="s">
-        <v>71</v>
       </c>
       <c r="F17" s="9" t="s">
         <v>26</v>
@@ -2323,13 +2323,13 @@
         <v>26</v>
       </c>
       <c r="N17" s="9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="O17" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="P17" s="9" t="s">
         <v>72</v>
-      </c>
-      <c r="P17" s="9" t="s">
-        <v>73</v>
       </c>
       <c r="Q17" s="10" t="s">
         <v>31</v>
@@ -2349,19 +2349,19 @@
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B18" s="5">
+        <v>46080.611620208336</v>
+      </c>
+      <c r="C18" s="5">
+        <v>46126.68891861111</v>
+      </c>
+      <c r="D18" s="5">
+        <v>46126.6889318287</v>
+      </c>
+      <c r="E18" s="6" t="s">
         <v>74</v>
-      </c>
-      <c r="B18" s="5">
-        <v>46080.778286875</v>
-      </c>
-      <c r="C18" s="5">
-        <v>46126.85558527778</v>
-      </c>
-      <c r="D18" s="5">
-        <v>46126.85559849537</v>
-      </c>
-      <c r="E18" s="6" t="s">
-        <v>75</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>25</v>
@@ -2385,7 +2385,7 @@
         <v>26</v>
       </c>
       <c r="O18" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="P18" s="6" t="s">
         <v>26</v>
@@ -2402,19 +2402,19 @@
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="B19" s="8">
+        <v>46080.61162048611</v>
+      </c>
+      <c r="C19" s="8">
+        <v>46114.345347615745</v>
+      </c>
+      <c r="D19" s="8">
+        <v>46114.345363518514</v>
+      </c>
+      <c r="E19" s="9" t="s">
         <v>77</v>
-      </c>
-      <c r="B19" s="8">
-        <v>46080.778287152774</v>
-      </c>
-      <c r="C19" s="8">
-        <v>46114.51201428241</v>
-      </c>
-      <c r="D19" s="8">
-        <v>46114.512030185186</v>
-      </c>
-      <c r="E19" s="9" t="s">
-        <v>78</v>
       </c>
       <c r="F19" s="9" t="s">
         <v>26</v>
@@ -2441,13 +2441,13 @@
         <v>26</v>
       </c>
       <c r="N19" s="9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="O19" s="9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="P19" s="9" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="Q19" s="10" t="s">
         <v>31</v>
@@ -2467,19 +2467,19 @@
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="B20" s="5">
+        <v>46080.61162085648</v>
+      </c>
+      <c r="C20" s="5">
+        <v>46114.34608914352</v>
+      </c>
+      <c r="D20" s="5">
+        <v>46114.34610408565</v>
+      </c>
+      <c r="E20" s="6" t="s">
         <v>80</v>
-      </c>
-      <c r="B20" s="5">
-        <v>46080.77828752315</v>
-      </c>
-      <c r="C20" s="5">
-        <v>46114.51275581018</v>
-      </c>
-      <c r="D20" s="5">
-        <v>46114.51277075231</v>
-      </c>
-      <c r="E20" s="6" t="s">
-        <v>81</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>26</v>
@@ -2506,13 +2506,13 @@
         <v>26</v>
       </c>
       <c r="N20" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="Q20" s="10" t="s">
         <v>31</v>
@@ -2532,28 +2532,28 @@
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="B21" s="8">
+        <v>46080.61162113426</v>
+      </c>
+      <c r="C21" s="8">
+        <v>46126.68889943287</v>
+      </c>
+      <c r="D21" s="8">
+        <v>46126.6889155324</v>
+      </c>
+      <c r="E21" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="B21" s="8">
-        <v>46080.77828780093</v>
-      </c>
-      <c r="C21" s="8">
-        <v>46126.85556609953</v>
-      </c>
-      <c r="D21" s="8">
-        <v>46126.855582199074</v>
-      </c>
-      <c r="E21" s="9" t="s">
+      <c r="F21" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G21" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="F21" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G21" s="9" t="s">
-        <v>85</v>
-      </c>
       <c r="H21" s="9" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I21" s="8">
         <v>46098</v>
@@ -2571,13 +2571,13 @@
         <v>26</v>
       </c>
       <c r="N21" s="9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="O21" s="9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="P21" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="Q21" s="10" t="s">
         <v>31</v>
@@ -2597,19 +2597,19 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="B22" s="5">
+        <v>46080.61739265046</v>
+      </c>
+      <c r="C22" s="5">
+        <v>46114.34641268519</v>
+      </c>
+      <c r="D22" s="5">
+        <v>46114.34642909722</v>
+      </c>
+      <c r="E22" s="6" t="s">
         <v>87</v>
-      </c>
-      <c r="B22" s="5">
-        <v>46080.78405931713</v>
-      </c>
-      <c r="C22" s="5">
-        <v>46114.51307935185</v>
-      </c>
-      <c r="D22" s="5">
-        <v>46114.51309576389</v>
-      </c>
-      <c r="E22" s="6" t="s">
-        <v>88</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>26</v>
@@ -2636,13 +2636,13 @@
         <v>26</v>
       </c>
       <c r="N22" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="O22" s="6" t="s">
         <v>48</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="Q22" s="10" t="s">
         <v>31</v>
@@ -2662,19 +2662,19 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="B23" s="8">
+        <v>46080.61162144676</v>
+      </c>
+      <c r="C23" s="8">
+        <v>46114.34650914352</v>
+      </c>
+      <c r="D23" s="8">
+        <v>46114.34660958333</v>
+      </c>
+      <c r="E23" s="9" t="s">
         <v>90</v>
-      </c>
-      <c r="B23" s="8">
-        <v>46080.778288113426</v>
-      </c>
-      <c r="C23" s="8">
-        <v>46114.513175810185</v>
-      </c>
-      <c r="D23" s="8">
-        <v>46114.51327625</v>
-      </c>
-      <c r="E23" s="9" t="s">
-        <v>91</v>
       </c>
       <c r="F23" s="9" t="s">
         <v>26</v>
@@ -2701,13 +2701,13 @@
         <v>26</v>
       </c>
       <c r="N23" s="9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="O23" s="9" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="P23" s="9" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="Q23" s="10" t="s">
         <v>31</v>
@@ -2727,28 +2727,28 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B24" s="5">
+        <v>46080.61162173611</v>
+      </c>
+      <c r="C24" s="5">
+        <v>46114.593050069445</v>
+      </c>
+      <c r="D24" s="5">
+        <v>46114.593065532405</v>
+      </c>
+      <c r="E24" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="B24" s="5">
-        <v>46080.77828840278</v>
-      </c>
-      <c r="C24" s="5">
-        <v>46114.75971673611</v>
-      </c>
-      <c r="D24" s="5">
-        <v>46114.759732199076</v>
-      </c>
-      <c r="E24" s="6" t="s">
+      <c r="F24" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G24" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="F24" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G24" s="6" t="s">
+      <c r="H24" s="6" t="s">
         <v>95</v>
-      </c>
-      <c r="H24" s="6" t="s">
-        <v>96</v>
       </c>
       <c r="I24" s="5">
         <v>46098</v>
@@ -2766,13 +2766,13 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="Q24" s="10" t="s">
         <v>31</v>
@@ -2792,19 +2792,19 @@
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="B25" s="8">
+        <v>46080.61162202546</v>
+      </c>
+      <c r="C25" s="8">
+        <v>46140.67228493055</v>
+      </c>
+      <c r="D25" s="8">
+        <v>46140.67228600694</v>
+      </c>
+      <c r="E25" s="9" t="s">
         <v>98</v>
-      </c>
-      <c r="B25" s="8">
-        <v>46080.778288692134</v>
-      </c>
-      <c r="C25" s="8">
-        <v>46140.83895159722</v>
-      </c>
-      <c r="D25" s="8">
-        <v>46140.838952673614</v>
-      </c>
-      <c r="E25" s="9" t="s">
-        <v>99</v>
       </c>
       <c r="F25" s="9" t="s">
         <v>25</v>
@@ -2828,7 +2828,7 @@
         <v>26</v>
       </c>
       <c r="O25" s="9" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="P25" s="9" t="s">
         <v>26</v>
@@ -2841,28 +2841,28 @@
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="B26" s="5">
+        <v>46080.61162231481</v>
+      </c>
+      <c r="C26" s="5">
+        <v>46139.61452841436</v>
+      </c>
+      <c r="D26" s="5">
+        <v>46139.614539560185</v>
+      </c>
+      <c r="E26" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="B26" s="5">
-        <v>46080.778288981484</v>
-      </c>
-      <c r="C26" s="5">
-        <v>46139.781195081014</v>
-      </c>
-      <c r="D26" s="5">
-        <v>46139.78120622685</v>
-      </c>
-      <c r="E26" s="6" t="s">
+      <c r="F26" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G26" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="F26" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G26" s="6" t="s">
+      <c r="H26" s="6" t="s">
         <v>103</v>
-      </c>
-      <c r="H26" s="6" t="s">
-        <v>104</v>
       </c>
       <c r="I26" s="5">
         <v>46100</v>
@@ -2880,16 +2880,16 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="O26" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="P26" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q26" s="11" t="s">
         <v>105</v>
-      </c>
-      <c r="P26" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="Q26" s="11" t="s">
-        <v>106</v>
       </c>
       <c r="R26" s="6">
         <v>1</v>
@@ -2906,28 +2906,28 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="B27" s="8">
+        <v>46080.611619351854</v>
+      </c>
+      <c r="C27" s="8">
+        <v>46139.61441649306</v>
+      </c>
+      <c r="D27" s="8">
+        <v>46139.61441783565</v>
+      </c>
+      <c r="E27" s="9" t="s">
         <v>107</v>
       </c>
-      <c r="B27" s="8">
-        <v>46080.77828601852</v>
-      </c>
-      <c r="C27" s="8">
-        <v>46139.78108315972</v>
-      </c>
-      <c r="D27" s="8">
-        <v>46139.78108450232</v>
-      </c>
-      <c r="E27" s="9" t="s">
-        <v>108</v>
-      </c>
       <c r="F27" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="H27" s="9" t="s">
         <v>103</v>
-      </c>
-      <c r="H27" s="9" t="s">
-        <v>104</v>
       </c>
       <c r="I27" s="8">
         <v>46100</v>
@@ -2945,50 +2945,50 @@
         <v>26</v>
       </c>
       <c r="N27" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="O27" s="9" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="P27" s="9" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Q27" s="11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="R27" s="9">
         <v>0</v>
       </c>
       <c r="S27" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="T27" s="9"/>
       <c r="U27" s="9"/>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B28" s="5">
+        <v>46080.61161972222</v>
+      </c>
+      <c r="C28" s="5">
+        <v>46139.6145152199</v>
+      </c>
+      <c r="D28" s="5">
+        <v>46139.61451663195</v>
+      </c>
+      <c r="E28" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="B28" s="5">
-        <v>46080.778286388886</v>
-      </c>
-      <c r="C28" s="5">
-        <v>46139.781181886574</v>
-      </c>
-      <c r="D28" s="5">
-        <v>46139.78118329861</v>
-      </c>
-      <c r="E28" s="6" t="s">
-        <v>112</v>
-      </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="H28" s="6" t="s">
         <v>103</v>
-      </c>
-      <c r="H28" s="6" t="s">
-        <v>104</v>
       </c>
       <c r="I28" s="5">
         <v>46101</v>
@@ -3006,50 +3006,50 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="Q28" s="11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="R28" s="6">
         <v>0</v>
       </c>
       <c r="S28" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="T28" s="6"/>
       <c r="U28" s="6"/>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="B29" s="8">
+        <v>46080.617547939815</v>
+      </c>
+      <c r="C29" s="8">
+        <v>46140.64236803241</v>
+      </c>
+      <c r="D29" s="8">
+        <v>46199.0408809375</v>
+      </c>
+      <c r="E29" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="B29" s="8">
-        <v>46080.78421460648</v>
-      </c>
-      <c r="C29" s="8">
-        <v>46140.80903469908</v>
-      </c>
-      <c r="D29" s="8">
-        <v>46199.207547604165</v>
-      </c>
-      <c r="E29" s="9" t="s">
-        <v>114</v>
-      </c>
       <c r="F29" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="H29" s="9" t="s">
         <v>103</v>
-      </c>
-      <c r="H29" s="9" t="s">
-        <v>104</v>
       </c>
       <c r="I29" s="8">
         <v>46092</v>
@@ -3067,13 +3067,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="9" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="O29" s="9" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="P29" s="9" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="Q29" s="10" t="s">
         <v>31</v>
@@ -3082,7 +3082,7 @@
         <v>1</v>
       </c>
       <c r="S29" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="T29" s="8">
         <v>46092</v>
@@ -3093,28 +3093,28 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="B30" s="5">
+        <v>46080.61797731482</v>
+      </c>
+      <c r="C30" s="5">
+        <v>46114.59513332176</v>
+      </c>
+      <c r="D30" s="5">
+        <v>46114.595134641204</v>
+      </c>
+      <c r="E30" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="B30" s="5">
-        <v>46080.78464398148</v>
-      </c>
-      <c r="C30" s="5">
-        <v>46114.761799988424</v>
-      </c>
-      <c r="D30" s="5">
-        <v>46114.761801307875</v>
-      </c>
-      <c r="E30" s="6" t="s">
-        <v>117</v>
-      </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="H30" s="6" t="s">
         <v>103</v>
-      </c>
-      <c r="H30" s="6" t="s">
-        <v>104</v>
       </c>
       <c r="I30" s="5">
         <v>46092</v>
@@ -3132,13 +3132,13 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
@@ -3148,28 +3148,28 @@
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="B31" s="8">
+        <v>46080.61805363426</v>
+      </c>
+      <c r="C31" s="8">
+        <v>46140.64228364584</v>
+      </c>
+      <c r="D31" s="8">
+        <v>46140.642285671296</v>
+      </c>
+      <c r="E31" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="B31" s="8">
-        <v>46080.78472030093</v>
-      </c>
-      <c r="C31" s="8">
-        <v>46140.8089503125</v>
-      </c>
-      <c r="D31" s="8">
-        <v>46140.80895233796</v>
-      </c>
-      <c r="E31" s="9" t="s">
-        <v>120</v>
-      </c>
       <c r="F31" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="H31" s="9" t="s">
         <v>103</v>
-      </c>
-      <c r="H31" s="9" t="s">
-        <v>104</v>
       </c>
       <c r="I31" s="8">
         <v>46101</v>
@@ -3187,13 +3187,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="9" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="O31" s="9" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="P31" s="9" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="Q31" s="9"/>
       <c r="R31" s="9"/>
@@ -3203,28 +3203,28 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="B32" s="5">
+        <v>46080.61161998843</v>
+      </c>
+      <c r="C32" s="5">
+        <v>46133.45426238426</v>
+      </c>
+      <c r="D32" s="5">
+        <v>46154.02539614584</v>
+      </c>
+      <c r="E32" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="B32" s="5">
-        <v>46080.77828665509</v>
-      </c>
-      <c r="C32" s="5">
-        <v>46133.62092905093</v>
-      </c>
-      <c r="D32" s="5">
-        <v>46154.1920628125</v>
-      </c>
-      <c r="E32" s="6" t="s">
-        <v>123</v>
-      </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="H32" s="6" t="s">
         <v>103</v>
-      </c>
-      <c r="H32" s="6" t="s">
-        <v>104</v>
       </c>
       <c r="I32" s="5">
         <v>46100</v>
@@ -3242,13 +3242,13 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="Q32" s="10" t="s">
         <v>31</v>
@@ -3268,28 +3268,28 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="B33" s="8">
+        <v>46080.611620254625</v>
+      </c>
+      <c r="C33" s="8">
+        <v>46133.45419553241</v>
+      </c>
+      <c r="D33" s="8">
+        <v>46133.454196597224</v>
+      </c>
+      <c r="E33" s="9" t="s">
         <v>125</v>
       </c>
-      <c r="B33" s="8">
-        <v>46080.7782869213</v>
-      </c>
-      <c r="C33" s="8">
-        <v>46133.62086219907</v>
-      </c>
-      <c r="D33" s="8">
-        <v>46133.62086326389</v>
-      </c>
-      <c r="E33" s="9" t="s">
-        <v>126</v>
-      </c>
       <c r="F33" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="H33" s="9" t="s">
         <v>103</v>
-      </c>
-      <c r="H33" s="9" t="s">
-        <v>104</v>
       </c>
       <c r="I33" s="8">
         <v>46100</v>
@@ -3307,50 +3307,50 @@
         <v>26</v>
       </c>
       <c r="N33" s="9" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O33" s="9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="P33" s="9" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="Q33" s="11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="R33" s="9">
         <v>0</v>
       </c>
       <c r="S33" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="T33" s="9"/>
       <c r="U33" s="9"/>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="B34" s="5">
+        <v>46080.61162052084</v>
+      </c>
+      <c r="C34" s="5">
+        <v>46133.45423341435</v>
+      </c>
+      <c r="D34" s="5">
+        <v>46133.45423459491</v>
+      </c>
+      <c r="E34" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="B34" s="5">
-        <v>46080.778287187495</v>
-      </c>
-      <c r="C34" s="5">
-        <v>46133.62090008102</v>
-      </c>
-      <c r="D34" s="5">
-        <v>46133.62090126157</v>
-      </c>
-      <c r="E34" s="6" t="s">
-        <v>129</v>
-      </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="H34" s="6" t="s">
         <v>103</v>
-      </c>
-      <c r="H34" s="6" t="s">
-        <v>104</v>
       </c>
       <c r="I34" s="5">
         <v>46104</v>
@@ -3368,50 +3368,50 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="Q34" s="11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="R34" s="6">
         <v>0</v>
       </c>
       <c r="S34" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="T34" s="6"/>
       <c r="U34" s="6"/>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="B35" s="8">
+        <v>46080.61162079861</v>
+      </c>
+      <c r="C35" s="8">
+        <v>46114.59660967592</v>
+      </c>
+      <c r="D35" s="8">
+        <v>46114.59662506945</v>
+      </c>
+      <c r="E35" s="9" t="s">
         <v>131</v>
       </c>
-      <c r="B35" s="8">
-        <v>46080.77828746528</v>
-      </c>
-      <c r="C35" s="8">
-        <v>46114.76327634259</v>
-      </c>
-      <c r="D35" s="8">
-        <v>46114.76329173611</v>
-      </c>
-      <c r="E35" s="9" t="s">
-        <v>132</v>
-      </c>
       <c r="F35" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="H35" s="9" t="s">
         <v>103</v>
-      </c>
-      <c r="H35" s="9" t="s">
-        <v>104</v>
       </c>
       <c r="I35" s="8">
         <v>46091</v>
@@ -3429,16 +3429,16 @@
         <v>26</v>
       </c>
       <c r="N35" s="9" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="O35" s="9" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="P35" s="9" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="Q35" s="11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="R35" s="9">
         <v>1</v>
@@ -3455,28 +3455,28 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="B36" s="5">
+        <v>46080.61162106482</v>
+      </c>
+      <c r="C36" s="5">
+        <v>46114.59652575231</v>
+      </c>
+      <c r="D36" s="5">
+        <v>46114.596526875</v>
+      </c>
+      <c r="E36" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="B36" s="5">
-        <v>46080.77828773148</v>
-      </c>
-      <c r="C36" s="5">
-        <v>46114.76319241898</v>
-      </c>
-      <c r="D36" s="5">
-        <v>46114.76319354167</v>
-      </c>
-      <c r="E36" s="6" t="s">
-        <v>135</v>
-      </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="H36" s="6" t="s">
         <v>103</v>
-      </c>
-      <c r="H36" s="6" t="s">
-        <v>104</v>
       </c>
       <c r="I36" s="5">
         <v>46091</v>
@@ -3494,50 +3494,50 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="Q36" s="11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="R36" s="6">
         <v>0</v>
       </c>
       <c r="S36" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="T36" s="6"/>
       <c r="U36" s="6"/>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="B37" s="8">
+        <v>46080.611621331016</v>
+      </c>
+      <c r="C37" s="8">
+        <v>46114.59658092592</v>
+      </c>
+      <c r="D37" s="8">
+        <v>46114.59658221065</v>
+      </c>
+      <c r="E37" s="9" t="s">
         <v>137</v>
       </c>
-      <c r="B37" s="8">
-        <v>46080.77828799769</v>
-      </c>
-      <c r="C37" s="8">
-        <v>46114.76324759259</v>
-      </c>
-      <c r="D37" s="8">
-        <v>46114.763248877316</v>
-      </c>
-      <c r="E37" s="9" t="s">
-        <v>138</v>
-      </c>
       <c r="F37" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="H37" s="9" t="s">
         <v>103</v>
-      </c>
-      <c r="H37" s="9" t="s">
-        <v>104</v>
       </c>
       <c r="I37" s="8">
         <v>46100</v>
@@ -3555,50 +3555,50 @@
         <v>26</v>
       </c>
       <c r="N37" s="9" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="O37" s="9" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P37" s="9" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="Q37" s="11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="R37" s="9">
         <v>0</v>
       </c>
       <c r="S37" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="T37" s="9"/>
       <c r="U37" s="9"/>
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="B38" s="5">
+        <v>46080.611621585645</v>
+      </c>
+      <c r="C38" s="5">
+        <v>46114.596591678244</v>
+      </c>
+      <c r="D38" s="5">
+        <v>46114.59659328704</v>
+      </c>
+      <c r="E38" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="B38" s="5">
-        <v>46080.77828825232</v>
-      </c>
-      <c r="C38" s="5">
-        <v>46114.76325834491</v>
-      </c>
-      <c r="D38" s="5">
-        <v>46114.7632599537</v>
-      </c>
-      <c r="E38" s="6" t="s">
-        <v>141</v>
-      </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="H38" s="6" t="s">
         <v>103</v>
-      </c>
-      <c r="H38" s="6" t="s">
-        <v>104</v>
       </c>
       <c r="I38" s="5">
         <v>46100</v>
@@ -3616,50 +3616,50 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="Q38" s="11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="R38" s="6">
         <v>0</v>
       </c>
       <c r="S38" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="T38" s="6"/>
       <c r="U38" s="6"/>
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="B39" s="8">
+        <v>46080.61162185185</v>
+      </c>
+      <c r="C39" s="8">
+        <v>46121.69341248843</v>
+      </c>
+      <c r="D39" s="8">
+        <v>46149.030915219904</v>
+      </c>
+      <c r="E39" s="9" t="s">
         <v>143</v>
       </c>
-      <c r="B39" s="8">
-        <v>46080.778288518515</v>
-      </c>
-      <c r="C39" s="8">
-        <v>46121.86007915509</v>
-      </c>
-      <c r="D39" s="8">
-        <v>46149.197581886576</v>
-      </c>
-      <c r="E39" s="9" t="s">
+      <c r="F39" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G39" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="F39" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G39" s="9" t="s">
+      <c r="H39" s="9" t="s">
         <v>145</v>
-      </c>
-      <c r="H39" s="9" t="s">
-        <v>146</v>
       </c>
       <c r="I39" s="8">
         <v>46100</v>
@@ -3677,13 +3677,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="9" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="O39" s="9" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="P39" s="9" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="Q39" s="10" t="s">
         <v>31</v>
@@ -3703,28 +3703,28 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="B40" s="5">
+        <v>46080.611620069445</v>
+      </c>
+      <c r="C40" s="5">
+        <v>46114.5931810301</v>
+      </c>
+      <c r="D40" s="5">
+        <v>46121.693403067125</v>
+      </c>
+      <c r="E40" s="6" t="s">
         <v>148</v>
       </c>
-      <c r="B40" s="5">
-        <v>46080.77828673611</v>
-      </c>
-      <c r="C40" s="5">
-        <v>46114.759847696754</v>
-      </c>
-      <c r="D40" s="5">
-        <v>46121.8600697338</v>
-      </c>
-      <c r="E40" s="6" t="s">
-        <v>149</v>
-      </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="H40" s="6" t="s">
         <v>145</v>
-      </c>
-      <c r="H40" s="6" t="s">
-        <v>146</v>
       </c>
       <c r="I40" s="5">
         <v>46100</v>
@@ -3742,50 +3742,50 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="Q40" s="11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="R40" s="6">
         <v>0</v>
       </c>
       <c r="S40" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="T40" s="6"/>
       <c r="U40" s="6"/>
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B41" s="8">
-        <v>46080.77828702546</v>
+        <v>46080.611620358795</v>
       </c>
       <c r="C41" s="8">
-        <v>46121.860064803244</v>
+        <v>46121.69339813657</v>
       </c>
       <c r="D41" s="8">
-        <v>46121.86006597222</v>
+        <v>46121.69339930556</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="H41" s="9" t="s">
         <v>145</v>
-      </c>
-      <c r="H41" s="9" t="s">
-        <v>146</v>
       </c>
       <c r="I41" s="8">
         <v>46120</v>
@@ -3803,50 +3803,50 @@
         <v>26</v>
       </c>
       <c r="N41" s="9" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="O41" s="9" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="P41" s="9" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q41" s="11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="R41" s="9">
         <v>0</v>
       </c>
       <c r="S41" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="T41" s="9"/>
       <c r="U41" s="9"/>
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="B42" s="5">
+        <v>46080.611620578704</v>
+      </c>
+      <c r="C42" s="5">
+        <v>46114.59384487268</v>
+      </c>
+      <c r="D42" s="5">
+        <v>46202.02042104167</v>
+      </c>
+      <c r="E42" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="B42" s="5">
-        <v>46080.77828724537</v>
-      </c>
-      <c r="C42" s="5">
-        <v>46114.76051153935</v>
-      </c>
-      <c r="D42" s="5">
-        <v>46202.187087708335</v>
-      </c>
-      <c r="E42" s="6" t="s">
-        <v>154</v>
-      </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="H42" s="6" t="s">
         <v>145</v>
-      </c>
-      <c r="H42" s="6" t="s">
-        <v>146</v>
       </c>
       <c r="I42" s="5">
         <v>46100</v>
@@ -3864,16 +3864,16 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="O42" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="P42" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q42" s="12" t="s">
         <v>155</v>
-      </c>
-      <c r="P42" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="Q42" s="12" t="s">
-        <v>56</v>
       </c>
       <c r="R42" s="6">
         <v>1</v>
@@ -3893,13 +3893,13 @@
         <v>156</v>
       </c>
       <c r="B43" s="8">
-        <v>46080.77828748843</v>
+        <v>46080.61162082176</v>
       </c>
       <c r="C43" s="8">
-        <v>46114.76044965278</v>
+        <v>46114.59378298611</v>
       </c>
       <c r="D43" s="8">
-        <v>46114.76045094908</v>
+        <v>46114.593784282406</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>157</v>
@@ -3908,10 +3908,10 @@
         <v>26</v>
       </c>
       <c r="G43" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="H43" s="9" t="s">
         <v>145</v>
-      </c>
-      <c r="H43" s="9" t="s">
-        <v>146</v>
       </c>
       <c r="I43" s="8">
         <v>46100</v>
@@ -3929,22 +3929,22 @@
         <v>26</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="O43" s="9" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="P43" s="9" t="s">
         <v>158</v>
       </c>
       <c r="Q43" s="11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="R43" s="9">
         <v>0</v>
       </c>
       <c r="S43" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="T43" s="9"/>
       <c r="U43" s="9"/>
@@ -3954,13 +3954,13 @@
         <v>159</v>
       </c>
       <c r="B44" s="5">
-        <v>46080.77828770834</v>
+        <v>46080.611621041666</v>
       </c>
       <c r="C44" s="5">
-        <v>46114.76049635417</v>
+        <v>46114.593829687496</v>
       </c>
       <c r="D44" s="5">
-        <v>46114.7604978125</v>
+        <v>46114.59383114583</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>160</v>
@@ -3969,10 +3969,10 @@
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="H44" s="6" t="s">
         <v>145</v>
-      </c>
-      <c r="H44" s="6" t="s">
-        <v>146</v>
       </c>
       <c r="I44" s="5">
         <v>46129</v>
@@ -3990,7 +3990,7 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="O44" s="6" t="s">
         <v>157</v>
@@ -3999,13 +3999,13 @@
         <v>161</v>
       </c>
       <c r="Q44" s="11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="R44" s="6">
         <v>0</v>
       </c>
       <c r="S44" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="T44" s="6"/>
       <c r="U44" s="6"/>
@@ -4015,13 +4015,13 @@
         <v>162</v>
       </c>
       <c r="B45" s="8">
-        <v>46080.778287939815</v>
+        <v>46080.61162127314</v>
       </c>
       <c r="C45" s="8">
-        <v>46140.83890416667</v>
+        <v>46140.672237499995</v>
       </c>
       <c r="D45" s="8">
-        <v>46141.772341724536</v>
+        <v>46141.60567505787</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>163</v>
@@ -4064,13 +4064,13 @@
         <v>165</v>
       </c>
       <c r="B46" s="5">
-        <v>46080.778288182875</v>
+        <v>46080.611621516204</v>
       </c>
       <c r="C46" s="5">
-        <v>46127.678079895835</v>
+        <v>46127.511413229164</v>
       </c>
       <c r="D46" s="5">
-        <v>46127.67810105324</v>
+        <v>46127.51143438657</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>166</v>
@@ -4103,7 +4103,7 @@
         <v>163</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>169</v>
@@ -4129,13 +4129,13 @@
         <v>170</v>
       </c>
       <c r="B47" s="8">
-        <v>46080.77828842592</v>
+        <v>46080.611621759264</v>
       </c>
       <c r="C47" s="8">
-        <v>46127.67813141204</v>
+        <v>46127.511464745374</v>
       </c>
       <c r="D47" s="8">
-        <v>46158.16995894676</v>
+        <v>46158.00329228009</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>171</v>
@@ -4194,13 +4194,13 @@
         <v>176</v>
       </c>
       <c r="B48" s="5">
-        <v>46087.53644159722</v>
+        <v>46087.36977493056</v>
       </c>
       <c r="C48" s="5">
-        <v>46127.678180752315</v>
+        <v>46127.51151408565</v>
       </c>
       <c r="D48" s="5">
-        <v>46161.20788581019</v>
+        <v>46161.04121914352</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>177</v>
@@ -4257,13 +4257,13 @@
         <v>179</v>
       </c>
       <c r="B49" s="8">
-        <v>46087.536521331014</v>
+        <v>46087.36985466436</v>
       </c>
       <c r="C49" s="8">
-        <v>46140.83887265046</v>
+        <v>46140.67220598379</v>
       </c>
       <c r="D49" s="8">
-        <v>46141.771787060185</v>
+        <v>46141.60512039352</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>180</v>
@@ -4302,13 +4302,13 @@
         <v>182</v>
       </c>
       <c r="Q49" s="11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="R49" s="9">
         <v>1</v>
       </c>
       <c r="S49" s="12" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="T49" s="8">
         <v>46233</v>
@@ -4322,13 +4322,13 @@
         <v>183</v>
       </c>
       <c r="B50" s="5">
-        <v>46080.77828866898</v>
+        <v>46080.61162200231</v>
       </c>
       <c r="C50" s="5">
-        <v>46133.62051065972</v>
+        <v>46133.453843993055</v>
       </c>
       <c r="D50" s="5">
-        <v>46141.772585231476</v>
+        <v>46141.60591856482</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>184</v>
@@ -4371,13 +4371,13 @@
         <v>186</v>
       </c>
       <c r="B51" s="8">
-        <v>46080.77828892361</v>
+        <v>46080.61162225694</v>
       </c>
       <c r="C51" s="8">
-        <v>46133.6204378588</v>
+        <v>46133.45377119213</v>
       </c>
       <c r="D51" s="8">
-        <v>46151.18472762732</v>
+        <v>46151.01806096065</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>187</v>
@@ -4410,7 +4410,7 @@
         <v>184</v>
       </c>
       <c r="O51" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P51" s="9" t="s">
         <v>190</v>
@@ -4436,13 +4436,13 @@
         <v>191</v>
       </c>
       <c r="B52" s="5">
-        <v>46080.77828760417</v>
+        <v>46080.6116209375</v>
       </c>
       <c r="C52" s="5">
-        <v>46133.62049425926</v>
+        <v>46133.45382759259</v>
       </c>
       <c r="D52" s="5">
-        <v>46155.20414789351</v>
+        <v>46155.03748122686</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>192</v>
@@ -4501,13 +4501,13 @@
         <v>196</v>
       </c>
       <c r="B53" s="8">
-        <v>46080.778288009256</v>
+        <v>46080.61162134259</v>
       </c>
       <c r="C53" s="8">
-        <v>46132.76769947917</v>
+        <v>46132.6010328125</v>
       </c>
       <c r="D53" s="8">
-        <v>46141.77186175926</v>
+        <v>46141.60519509259</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>197</v>
@@ -4550,13 +4550,13 @@
         <v>199</v>
       </c>
       <c r="B54" s="5">
-        <v>46080.77828832176</v>
+        <v>46080.61162165509</v>
       </c>
       <c r="C54" s="5">
-        <v>46128.489822488424</v>
+        <v>46128.32315582176</v>
       </c>
       <c r="D54" s="5">
-        <v>46165.18131118055</v>
+        <v>46165.01464451389</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>200</v>
@@ -4615,13 +4615,13 @@
         <v>204</v>
       </c>
       <c r="B55" s="8">
-        <v>46080.77828861111</v>
+        <v>46080.611621944445</v>
       </c>
       <c r="C55" s="8">
-        <v>46128.48987719907</v>
+        <v>46128.323210532406</v>
       </c>
       <c r="D55" s="8">
-        <v>46170.185211909724</v>
+        <v>46170.01854524306</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>205</v>
@@ -4680,13 +4680,13 @@
         <v>208</v>
       </c>
       <c r="B56" s="5">
-        <v>46080.778288912035</v>
+        <v>46080.61162224537</v>
       </c>
       <c r="C56" s="5">
-        <v>46132.76768157407</v>
+        <v>46132.601014907406</v>
       </c>
       <c r="D56" s="5">
-        <v>46172.2027446875</v>
+        <v>46172.03607802083</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>209</v>
@@ -4745,13 +4745,13 @@
         <v>212</v>
       </c>
       <c r="B57" s="8">
-        <v>46080.77828921296</v>
+        <v>46080.6116225463</v>
       </c>
       <c r="C57" s="8">
-        <v>46141.711290810184</v>
+        <v>46141.54462414352</v>
       </c>
       <c r="D57" s="8">
-        <v>46141.77231675926</v>
+        <v>46141.60565009259</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>184</v>
@@ -4794,13 +4794,13 @@
         <v>214</v>
       </c>
       <c r="B58" s="5">
-        <v>46080.77828957176</v>
+        <v>46080.6116229051</v>
       </c>
       <c r="C58" s="5">
-        <v>46133.62103284722</v>
+        <v>46133.45436618055</v>
       </c>
       <c r="D58" s="5">
-        <v>46156.16908381945</v>
+        <v>46156.00241715278</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>215</v>
@@ -4833,7 +4833,7 @@
         <v>184</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="P58" s="6" t="s">
         <v>216</v>
@@ -4859,13 +4859,13 @@
         <v>217</v>
       </c>
       <c r="B59" s="8">
-        <v>46080.77828986111</v>
+        <v>46080.61162319445</v>
       </c>
       <c r="C59" s="8">
-        <v>46133.621046631946</v>
+        <v>46133.454379965275</v>
       </c>
       <c r="D59" s="8">
-        <v>46133.62189940972</v>
+        <v>46133.45523274306</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>218</v>
@@ -4898,13 +4898,13 @@
         <v>184</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="P59" s="9" t="s">
         <v>219</v>
       </c>
       <c r="Q59" s="11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="R59" s="9">
         <v>1</v>
@@ -4924,13 +4924,13 @@
         <v>220</v>
       </c>
       <c r="B60" s="5">
-        <v>46080.778290138885</v>
+        <v>46080.61162347222</v>
       </c>
       <c r="C60" s="5">
-        <v>46121.8679578125</v>
+        <v>46121.70129114583</v>
       </c>
       <c r="D60" s="5">
-        <v>46121.867985185185</v>
+        <v>46121.70131851852</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>221</v>
@@ -4963,13 +4963,13 @@
         <v>184</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="P60" s="6" t="s">
         <v>222</v>
       </c>
       <c r="Q60" s="11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="R60" s="6">
         <v>1</v>
@@ -4989,13 +4989,13 @@
         <v>223</v>
       </c>
       <c r="B61" s="8">
-        <v>46080.778290393515</v>
+        <v>46080.61162372685</v>
       </c>
       <c r="C61" s="8">
-        <v>46121.86789461806</v>
+        <v>46121.70122795139</v>
       </c>
       <c r="D61" s="8">
-        <v>46204.20245239583</v>
+        <v>46204.03578572917</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>224</v>
@@ -5034,7 +5034,7 @@
         <v>225</v>
       </c>
       <c r="Q61" s="12" t="s">
-        <v>56</v>
+        <v>155</v>
       </c>
       <c r="R61" s="9">
         <v>1</v>
@@ -5054,13 +5054,13 @@
         <v>226</v>
       </c>
       <c r="B62" s="5">
-        <v>46080.7854796875</v>
+        <v>46080.61881302083</v>
       </c>
       <c r="C62" s="5">
-        <v>46141.772219398146</v>
+        <v>46141.60555273148</v>
       </c>
       <c r="D62" s="5">
-        <v>46203.19232511574</v>
+        <v>46203.02565844907</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>54</v>
@@ -5093,7 +5093,7 @@
         <v>184</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="P62" s="6" t="s">
         <v>227</v>
@@ -5119,13 +5119,13 @@
         <v>228</v>
       </c>
       <c r="B63" s="8">
-        <v>46080.77828662037</v>
+        <v>46080.61161995371</v>
       </c>
       <c r="C63" s="8">
-        <v>46141.711275752314</v>
+        <v>46141.54460908565</v>
       </c>
       <c r="D63" s="8">
-        <v>46141.71127789352</v>
+        <v>46141.544611226855</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>229</v>
@@ -5168,13 +5168,13 @@
         <v>231</v>
       </c>
       <c r="B64" s="5">
-        <v>46080.77828694445</v>
+        <v>46080.61162027778</v>
       </c>
       <c r="C64" s="5">
-        <v>46133.62079252314</v>
+        <v>46133.454125856486</v>
       </c>
       <c r="D64" s="5">
-        <v>46192.18706700232</v>
+        <v>46192.02040033565</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>232</v>
@@ -5183,10 +5183,10 @@
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I64" s="5">
         <v>46174</v>
@@ -5233,13 +5233,13 @@
         <v>234</v>
       </c>
       <c r="B65" s="8">
-        <v>46080.778287187495</v>
+        <v>46080.61162052084</v>
       </c>
       <c r="C65" s="8">
-        <v>46133.620870451385</v>
+        <v>46133.45420378472</v>
       </c>
       <c r="D65" s="8">
-        <v>46133.62091327546</v>
+        <v>46133.454246608795</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>235</v>
@@ -5248,10 +5248,10 @@
         <v>26</v>
       </c>
       <c r="G65" s="9" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H65" s="9" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I65" s="8">
         <v>46230</v>
@@ -5278,7 +5278,7 @@
         <v>237</v>
       </c>
       <c r="Q65" s="11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="R65" s="9">
         <v>1</v>
@@ -5298,13 +5298,13 @@
         <v>238</v>
       </c>
       <c r="B66" s="5">
-        <v>46080.77828746528</v>
+        <v>46080.61162079861</v>
       </c>
       <c r="C66" s="5">
-        <v>46133.62178611111</v>
+        <v>46133.45511944444</v>
       </c>
       <c r="D66" s="5">
-        <v>46133.62180199074</v>
+        <v>46133.455135324075</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>239</v>
@@ -5313,10 +5313,10 @@
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I66" s="5">
         <v>46218</v>
@@ -5343,7 +5343,7 @@
         <v>237</v>
       </c>
       <c r="Q66" s="11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="R66" s="6">
         <v>1</v>
@@ -5363,13 +5363,13 @@
         <v>241</v>
       </c>
       <c r="B67" s="8">
-        <v>46080.77828770834</v>
+        <v>46080.611621041666</v>
       </c>
       <c r="C67" s="8">
-        <v>46133.62179804398</v>
+        <v>46133.45513137731</v>
       </c>
       <c r="D67" s="8">
-        <v>46133.62181490741</v>
+        <v>46133.45514824074</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>242</v>
@@ -5378,10 +5378,10 @@
         <v>26</v>
       </c>
       <c r="G67" s="9" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H67" s="9" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I67" s="8">
         <v>46220</v>
@@ -5408,7 +5408,7 @@
         <v>237</v>
       </c>
       <c r="Q67" s="11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="R67" s="9">
         <v>1</v>
@@ -5428,13 +5428,13 @@
         <v>244</v>
       </c>
       <c r="B68" s="5">
-        <v>46080.77828796297</v>
+        <v>46080.611621296295</v>
       </c>
       <c r="C68" s="5">
-        <v>46133.62181768518</v>
+        <v>46133.45515101852</v>
       </c>
       <c r="D68" s="5">
-        <v>46133.6218338426</v>
+        <v>46133.455167175925</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>245</v>
@@ -5443,10 +5443,10 @@
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I68" s="5">
         <v>46212</v>
@@ -5473,7 +5473,7 @@
         <v>237</v>
       </c>
       <c r="Q68" s="11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="R68" s="6">
         <v>1</v>
@@ -5493,13 +5493,13 @@
         <v>247</v>
       </c>
       <c r="B69" s="8">
-        <v>46080.778288217596</v>
+        <v>46080.611621550925</v>
       </c>
       <c r="C69" s="8">
-        <v>46133.621873553246</v>
+        <v>46133.455206886574</v>
       </c>
       <c r="D69" s="8">
-        <v>46133.621889710645</v>
+        <v>46133.45522304398</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>181</v>
@@ -5508,10 +5508,10 @@
         <v>26</v>
       </c>
       <c r="G69" s="9" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H69" s="9" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I69" s="8">
         <v>46232</v>
@@ -5538,7 +5538,7 @@
         <v>249</v>
       </c>
       <c r="Q69" s="11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="R69" s="9">
         <v>1</v>
@@ -5558,13 +5558,13 @@
         <v>250</v>
       </c>
       <c r="B70" s="5">
-        <v>46080.77828846065</v>
+        <v>46080.611621793985</v>
       </c>
       <c r="C70" s="5">
-        <v>46140.8390024074</v>
+        <v>46140.67233574074</v>
       </c>
       <c r="D70" s="5">
-        <v>46141.711773055555</v>
+        <v>46141.54510638889</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>182</v>
@@ -5573,10 +5573,10 @@
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I70" s="5">
         <v>46234</v>
@@ -5603,13 +5603,13 @@
         <v>251</v>
       </c>
       <c r="Q70" s="11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="R70" s="6">
         <v>1</v>
       </c>
       <c r="S70" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="T70" s="5">
         <v>46234</v>
@@ -5623,13 +5623,13 @@
         <v>252</v>
       </c>
       <c r="B71" s="8">
-        <v>46080.7782887037</v>
+        <v>46080.61162203704</v>
       </c>
       <c r="C71" s="8">
-        <v>46141.71205135417</v>
+        <v>46141.5453846875</v>
       </c>
       <c r="D71" s="8">
-        <v>46141.712052731484</v>
+        <v>46141.54538606481</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>253</v>
@@ -5672,13 +5672,13 @@
         <v>255</v>
       </c>
       <c r="B72" s="5">
-        <v>46080.77828895833</v>
+        <v>46080.61162229167</v>
       </c>
       <c r="C72" s="5">
-        <v>46140.83904666667</v>
+        <v>46140.67238</v>
       </c>
       <c r="D72" s="5">
-        <v>46141.711805625004</v>
+        <v>46141.54513895833</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>256</v>
@@ -5717,13 +5717,13 @@
         <v>259</v>
       </c>
       <c r="Q72" s="11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="R72" s="6">
         <v>1</v>
       </c>
       <c r="S72" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="T72" s="5">
         <v>46237</v>
@@ -5737,13 +5737,13 @@
         <v>260</v>
       </c>
       <c r="B73" s="8">
-        <v>46080.778287152774</v>
+        <v>46080.61162048611</v>
       </c>
       <c r="C73" s="8">
-        <v>46141.711726180554</v>
+        <v>46141.54505951389</v>
       </c>
       <c r="D73" s="8">
-        <v>46141.7118290162</v>
+        <v>46141.54516234953</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>261</v>
@@ -5752,10 +5752,10 @@
         <v>26</v>
       </c>
       <c r="G73" s="9" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H73" s="9" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I73" s="8">
         <v>46238</v>
@@ -5782,13 +5782,13 @@
         <v>263</v>
       </c>
       <c r="Q73" s="11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="R73" s="9">
         <v>1</v>
       </c>
       <c r="S73" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="T73" s="8">
         <v>46238</v>
@@ -5802,13 +5802,13 @@
         <v>264</v>
       </c>
       <c r="B74" s="5">
-        <v>46080.77828751157</v>
+        <v>46080.61162084491</v>
       </c>
       <c r="C74" s="5">
-        <v>46141.7119153588</v>
+        <v>46141.54524869213</v>
       </c>
       <c r="D74" s="5">
-        <v>46141.711917002314</v>
+        <v>46141.54525033565</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>265</v>
@@ -5847,13 +5847,13 @@
         <v>266</v>
       </c>
       <c r="Q74" s="11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="R74" s="6">
         <v>1</v>
       </c>
       <c r="S74" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="T74" s="5">
         <v>46239</v>
@@ -5867,13 +5867,13 @@
         <v>267</v>
       </c>
       <c r="B75" s="8">
-        <v>46080.77828782407</v>
+        <v>46080.61162115741</v>
       </c>
       <c r="C75" s="8">
-        <v>46141.71196090278</v>
+        <v>46141.545294236115</v>
       </c>
       <c r="D75" s="8">
-        <v>46141.71196212963</v>
+        <v>46141.54529546296</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>268</v>
@@ -5912,13 +5912,13 @@
         <v>269</v>
       </c>
       <c r="Q75" s="11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="R75" s="9">
         <v>1</v>
       </c>
       <c r="S75" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="T75" s="8">
         <v>46240</v>
@@ -5932,11 +5932,11 @@
         <v>270</v>
       </c>
       <c r="B76" s="5">
-        <v>46080.77828809028</v>
+        <v>46080.61162142361</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46090.61092975695</v>
+        <v>46090.44426309028</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>271</v>
@@ -5979,14 +5979,14 @@
         <v>273</v>
       </c>
       <c r="B77" s="8">
-        <v>46080.77828868055</v>
+        <v>46080.611622013894</v>
       </c>
       <c r="C77" s="9"/>
       <c r="D77" s="8">
-        <v>46141.711969386575</v>
+        <v>46141.54530271991</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>26</v>
@@ -6022,13 +6022,13 @@
         <v>271</v>
       </c>
       <c r="Q77" s="11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="R77" s="9">
         <v>0</v>
       </c>
       <c r="S77" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="T77" s="8">
         <v>46241</v>
@@ -6042,11 +6042,11 @@
         <v>277</v>
       </c>
       <c r="B78" s="5">
-        <v>46080.77828835648</v>
+        <v>46080.611621689815</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46141.711970648146</v>
+        <v>46141.54530398148</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>278</v>
@@ -6085,13 +6085,13 @@
         <v>271</v>
       </c>
       <c r="Q78" s="11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="R78" s="6">
         <v>0</v>
       </c>
       <c r="S78" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="T78" s="5">
         <v>46241</v>
@@ -6105,11 +6105,11 @@
         <v>279</v>
       </c>
       <c r="B79" s="8">
-        <v>46090.61171577546</v>
+        <v>46090.44504910879</v>
       </c>
       <c r="C79" s="9"/>
       <c r="D79" s="8">
-        <v>46090.614530335646</v>
+        <v>46090.44786366898</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>280</v>
@@ -6142,13 +6142,13 @@
         <v>26</v>
       </c>
       <c r="Q79" s="11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="R79" s="9">
         <v>0</v>
       </c>
       <c r="S79" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="T79" s="9"/>
       <c r="U79" s="9"/>
@@ -6158,11 +6158,11 @@
         <v>282</v>
       </c>
       <c r="B80" s="5">
-        <v>46090.61199928241</v>
+        <v>46090.44533261574</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46141.711971944445</v>
+        <v>46141.545305277774</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>283</v>
@@ -6201,13 +6201,13 @@
         <v>284</v>
       </c>
       <c r="Q80" s="11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="R80" s="6">
         <v>0</v>
       </c>
       <c r="S80" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="T80" s="5">
         <v>46241</v>
@@ -6221,11 +6221,11 @@
         <v>285</v>
       </c>
       <c r="B81" s="8">
-        <v>46090.61208010417</v>
+        <v>46090.4454134375</v>
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="8">
-        <v>46090.61869820602</v>
+        <v>46090.45203153935</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>286</v>
@@ -6264,13 +6264,13 @@
         <v>280</v>
       </c>
       <c r="Q81" s="11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="R81" s="9">
         <v>0</v>
       </c>
       <c r="S81" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="T81" s="8">
         <v>46252</v>

--- a/data/50001524 - ATACAMA KOZAN.xlsx
+++ b/data/50001524 - ATACAMA KOZAN.xlsx
@@ -1498,13 +1498,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46080.61161974537</v>
+        <v>46080.77828641204</v>
       </c>
       <c r="C4" s="5">
-        <v>46097.66998934028</v>
+        <v>46097.83665600694</v>
       </c>
       <c r="D4" s="5">
-        <v>46097.67008267361</v>
+        <v>46097.83674934028</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1547,13 +1547,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46080.611620138894</v>
+        <v>46080.77828680555</v>
       </c>
       <c r="C5" s="8">
-        <v>46097.669548425925</v>
+        <v>46097.8362150926</v>
       </c>
       <c r="D5" s="8">
-        <v>46097.66956912037</v>
+        <v>46097.836235787036</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1610,13 +1610,13 @@
         <v>33</v>
       </c>
       <c r="B6" s="5">
-        <v>46080.61162043981</v>
+        <v>46080.778287106485</v>
       </c>
       <c r="C6" s="5">
-        <v>46097.66955386574</v>
+        <v>46097.83622053241</v>
       </c>
       <c r="D6" s="5">
-        <v>46097.66956886574</v>
+        <v>46097.836235532406</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>34</v>
@@ -1673,13 +1673,13 @@
         <v>37</v>
       </c>
       <c r="B7" s="8">
-        <v>46080.61162074074</v>
+        <v>46080.778287407404</v>
       </c>
       <c r="C7" s="8">
-        <v>46097.66956028935</v>
+        <v>46097.83622695602</v>
       </c>
       <c r="D7" s="8">
-        <v>46097.669575266205</v>
+        <v>46097.83624193287</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>38</v>
@@ -1736,13 +1736,13 @@
         <v>39</v>
       </c>
       <c r="B8" s="5">
-        <v>46080.61162106482</v>
+        <v>46080.77828773148</v>
       </c>
       <c r="C8" s="5">
-        <v>46093.47637546297</v>
+        <v>46093.643042129625</v>
       </c>
       <c r="D8" s="5">
-        <v>46100.62501127315</v>
+        <v>46100.791677939815</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>40</v>
@@ -1799,13 +1799,13 @@
         <v>42</v>
       </c>
       <c r="B9" s="8">
-        <v>46080.61162134259</v>
+        <v>46080.778288009256</v>
       </c>
       <c r="C9" s="8">
-        <v>46097.66957738426</v>
+        <v>46097.83624405092</v>
       </c>
       <c r="D9" s="8">
-        <v>46097.669591805556</v>
+        <v>46097.83625847222</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>43</v>
@@ -1862,13 +1862,13 @@
         <v>44</v>
       </c>
       <c r="B10" s="5">
-        <v>46080.61691350694</v>
+        <v>46080.78358017361</v>
       </c>
       <c r="C10" s="5">
-        <v>46141.54493447917</v>
+        <v>46141.711601145835</v>
       </c>
       <c r="D10" s="5">
-        <v>46141.54493556713</v>
+        <v>46141.7116022338</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>45</v>
@@ -1911,13 +1911,13 @@
         <v>47</v>
       </c>
       <c r="B11" s="8">
-        <v>46080.617096863425</v>
+        <v>46080.7837635301</v>
       </c>
       <c r="C11" s="8">
-        <v>46114.345154421295</v>
+        <v>46114.51182108796</v>
       </c>
       <c r="D11" s="8">
-        <v>46114.34517267361</v>
+        <v>46114.51183934028</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>48</v>
@@ -1976,13 +1976,13 @@
         <v>52</v>
       </c>
       <c r="B12" s="5">
-        <v>46080.61714857639</v>
+        <v>46080.783815243056</v>
       </c>
       <c r="C12" s="5">
-        <v>46141.54484769676</v>
+        <v>46141.71151436343</v>
       </c>
       <c r="D12" s="5">
-        <v>46205.01245163195</v>
+        <v>46205.17911829861</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>53</v>
@@ -2041,13 +2041,13 @@
         <v>57</v>
       </c>
       <c r="B13" s="8">
-        <v>46080.61162163195</v>
+        <v>46080.77828829861</v>
       </c>
       <c r="C13" s="8">
-        <v>46114.34593138889</v>
+        <v>46114.51259805556</v>
       </c>
       <c r="D13" s="8">
-        <v>46114.59239144676</v>
+        <v>46114.75905811343</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>58</v>
@@ -2092,13 +2092,13 @@
         <v>60</v>
       </c>
       <c r="B14" s="5">
-        <v>46080.6116219213</v>
+        <v>46080.778288587964</v>
       </c>
       <c r="C14" s="5">
-        <v>46114.34528306713</v>
+        <v>46114.511949733795</v>
       </c>
       <c r="D14" s="5">
-        <v>46114.34529875</v>
+        <v>46114.51196541666</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>61</v>
@@ -2157,13 +2157,13 @@
         <v>63</v>
       </c>
       <c r="B15" s="8">
-        <v>46080.61162287037</v>
+        <v>46080.77828953703</v>
       </c>
       <c r="C15" s="8">
-        <v>46114.34543883102</v>
+        <v>46114.512105497684</v>
       </c>
       <c r="D15" s="8">
-        <v>46114.345454849536</v>
+        <v>46114.51212151621</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>64</v>
@@ -2222,13 +2222,13 @@
         <v>66</v>
       </c>
       <c r="B16" s="5">
-        <v>46080.61161952546</v>
+        <v>46080.77828619213</v>
       </c>
       <c r="C16" s="5">
-        <v>46114.345740000004</v>
+        <v>46114.51240666666</v>
       </c>
       <c r="D16" s="5">
-        <v>46114.34575462963</v>
+        <v>46114.5124212963</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>67</v>
@@ -2287,13 +2287,13 @@
         <v>69</v>
       </c>
       <c r="B17" s="8">
-        <v>46080.61161986111</v>
+        <v>46080.77828652778</v>
       </c>
       <c r="C17" s="8">
-        <v>46114.34591538194</v>
+        <v>46114.512582048614</v>
       </c>
       <c r="D17" s="8">
-        <v>46114.34593252315</v>
+        <v>46114.51259918981</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>70</v>
@@ -2352,13 +2352,13 @@
         <v>73</v>
       </c>
       <c r="B18" s="5">
-        <v>46080.611620208336</v>
+        <v>46080.778286875</v>
       </c>
       <c r="C18" s="5">
-        <v>46126.68891861111</v>
+        <v>46126.85558527778</v>
       </c>
       <c r="D18" s="5">
-        <v>46126.6889318287</v>
+        <v>46126.85559849537</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>74</v>
@@ -2405,13 +2405,13 @@
         <v>76</v>
       </c>
       <c r="B19" s="8">
-        <v>46080.61162048611</v>
+        <v>46080.778287152774</v>
       </c>
       <c r="C19" s="8">
-        <v>46114.345347615745</v>
+        <v>46114.51201428241</v>
       </c>
       <c r="D19" s="8">
-        <v>46114.345363518514</v>
+        <v>46114.512030185186</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>77</v>
@@ -2470,13 +2470,13 @@
         <v>79</v>
       </c>
       <c r="B20" s="5">
-        <v>46080.61162085648</v>
+        <v>46080.77828752315</v>
       </c>
       <c r="C20" s="5">
-        <v>46114.34608914352</v>
+        <v>46114.51275581018</v>
       </c>
       <c r="D20" s="5">
-        <v>46114.34610408565</v>
+        <v>46114.51277075231</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>80</v>
@@ -2535,13 +2535,13 @@
         <v>82</v>
       </c>
       <c r="B21" s="8">
-        <v>46080.61162113426</v>
+        <v>46080.77828780093</v>
       </c>
       <c r="C21" s="8">
-        <v>46126.68889943287</v>
+        <v>46126.85556609953</v>
       </c>
       <c r="D21" s="8">
-        <v>46126.6889155324</v>
+        <v>46126.855582199074</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>83</v>
@@ -2600,13 +2600,13 @@
         <v>86</v>
       </c>
       <c r="B22" s="5">
-        <v>46080.61739265046</v>
+        <v>46080.78405931713</v>
       </c>
       <c r="C22" s="5">
-        <v>46114.34641268519</v>
+        <v>46114.51307935185</v>
       </c>
       <c r="D22" s="5">
-        <v>46114.34642909722</v>
+        <v>46114.51309576389</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>87</v>
@@ -2665,13 +2665,13 @@
         <v>89</v>
       </c>
       <c r="B23" s="8">
-        <v>46080.61162144676</v>
+        <v>46080.778288113426</v>
       </c>
       <c r="C23" s="8">
-        <v>46114.34650914352</v>
+        <v>46114.513175810185</v>
       </c>
       <c r="D23" s="8">
-        <v>46114.34660958333</v>
+        <v>46114.51327625</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>90</v>
@@ -2730,13 +2730,13 @@
         <v>92</v>
       </c>
       <c r="B24" s="5">
-        <v>46080.61162173611</v>
+        <v>46080.77828840278</v>
       </c>
       <c r="C24" s="5">
-        <v>46114.593050069445</v>
+        <v>46114.75971673611</v>
       </c>
       <c r="D24" s="5">
-        <v>46114.593065532405</v>
+        <v>46114.759732199076</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>93</v>
@@ -2795,13 +2795,13 @@
         <v>97</v>
       </c>
       <c r="B25" s="8">
-        <v>46080.61162202546</v>
+        <v>46080.778288692134</v>
       </c>
       <c r="C25" s="8">
-        <v>46140.67228493055</v>
+        <v>46140.83895159722</v>
       </c>
       <c r="D25" s="8">
-        <v>46140.67228600694</v>
+        <v>46140.838952673614</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>98</v>
@@ -2844,13 +2844,13 @@
         <v>100</v>
       </c>
       <c r="B26" s="5">
-        <v>46080.61162231481</v>
+        <v>46080.778288981484</v>
       </c>
       <c r="C26" s="5">
-        <v>46139.61452841436</v>
+        <v>46139.781195081014</v>
       </c>
       <c r="D26" s="5">
-        <v>46139.614539560185</v>
+        <v>46139.78120622685</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>101</v>
@@ -2909,13 +2909,13 @@
         <v>106</v>
       </c>
       <c r="B27" s="8">
-        <v>46080.611619351854</v>
+        <v>46080.77828601852</v>
       </c>
       <c r="C27" s="8">
-        <v>46139.61441649306</v>
+        <v>46139.78108315972</v>
       </c>
       <c r="D27" s="8">
-        <v>46139.61441783565</v>
+        <v>46139.78108450232</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>107</v>
@@ -2970,13 +2970,13 @@
         <v>110</v>
       </c>
       <c r="B28" s="5">
-        <v>46080.61161972222</v>
+        <v>46080.778286388886</v>
       </c>
       <c r="C28" s="5">
-        <v>46139.6145152199</v>
+        <v>46139.781181886574</v>
       </c>
       <c r="D28" s="5">
-        <v>46139.61451663195</v>
+        <v>46139.78118329861</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>111</v>
@@ -3031,13 +3031,13 @@
         <v>112</v>
       </c>
       <c r="B29" s="8">
-        <v>46080.617547939815</v>
+        <v>46080.78421460648</v>
       </c>
       <c r="C29" s="8">
-        <v>46140.64236803241</v>
+        <v>46140.80903469908</v>
       </c>
       <c r="D29" s="8">
-        <v>46199.0408809375</v>
+        <v>46199.207547604165</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>113</v>
@@ -3096,13 +3096,13 @@
         <v>115</v>
       </c>
       <c r="B30" s="5">
-        <v>46080.61797731482</v>
+        <v>46080.78464398148</v>
       </c>
       <c r="C30" s="5">
-        <v>46114.59513332176</v>
+        <v>46114.761799988424</v>
       </c>
       <c r="D30" s="5">
-        <v>46114.595134641204</v>
+        <v>46114.761801307875</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>116</v>
@@ -3151,13 +3151,13 @@
         <v>118</v>
       </c>
       <c r="B31" s="8">
-        <v>46080.61805363426</v>
+        <v>46080.78472030093</v>
       </c>
       <c r="C31" s="8">
-        <v>46140.64228364584</v>
+        <v>46140.8089503125</v>
       </c>
       <c r="D31" s="8">
-        <v>46140.642285671296</v>
+        <v>46140.80895233796</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>119</v>
@@ -3206,13 +3206,13 @@
         <v>121</v>
       </c>
       <c r="B32" s="5">
-        <v>46080.61161998843</v>
+        <v>46080.77828665509</v>
       </c>
       <c r="C32" s="5">
-        <v>46133.45426238426</v>
+        <v>46133.62092905093</v>
       </c>
       <c r="D32" s="5">
-        <v>46154.02539614584</v>
+        <v>46154.1920628125</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>122</v>
@@ -3271,13 +3271,13 @@
         <v>124</v>
       </c>
       <c r="B33" s="8">
-        <v>46080.611620254625</v>
+        <v>46080.7782869213</v>
       </c>
       <c r="C33" s="8">
-        <v>46133.45419553241</v>
+        <v>46133.62086219907</v>
       </c>
       <c r="D33" s="8">
-        <v>46133.454196597224</v>
+        <v>46133.62086326389</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>125</v>
@@ -3332,13 +3332,13 @@
         <v>127</v>
       </c>
       <c r="B34" s="5">
-        <v>46080.61162052084</v>
+        <v>46080.778287187495</v>
       </c>
       <c r="C34" s="5">
-        <v>46133.45423341435</v>
+        <v>46133.62090008102</v>
       </c>
       <c r="D34" s="5">
-        <v>46133.45423459491</v>
+        <v>46133.62090126157</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>128</v>
@@ -3393,13 +3393,13 @@
         <v>130</v>
       </c>
       <c r="B35" s="8">
-        <v>46080.61162079861</v>
+        <v>46080.77828746528</v>
       </c>
       <c r="C35" s="8">
-        <v>46114.59660967592</v>
+        <v>46114.76327634259</v>
       </c>
       <c r="D35" s="8">
-        <v>46114.59662506945</v>
+        <v>46114.76329173611</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>131</v>
@@ -3458,13 +3458,13 @@
         <v>133</v>
       </c>
       <c r="B36" s="5">
-        <v>46080.61162106482</v>
+        <v>46080.77828773148</v>
       </c>
       <c r="C36" s="5">
-        <v>46114.59652575231</v>
+        <v>46114.76319241898</v>
       </c>
       <c r="D36" s="5">
-        <v>46114.596526875</v>
+        <v>46114.76319354167</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>134</v>
@@ -3519,13 +3519,13 @@
         <v>136</v>
       </c>
       <c r="B37" s="8">
-        <v>46080.611621331016</v>
+        <v>46080.77828799769</v>
       </c>
       <c r="C37" s="8">
-        <v>46114.59658092592</v>
+        <v>46114.76324759259</v>
       </c>
       <c r="D37" s="8">
-        <v>46114.59658221065</v>
+        <v>46114.763248877316</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>137</v>
@@ -3580,13 +3580,13 @@
         <v>139</v>
       </c>
       <c r="B38" s="5">
-        <v>46080.611621585645</v>
+        <v>46080.77828825232</v>
       </c>
       <c r="C38" s="5">
-        <v>46114.596591678244</v>
+        <v>46114.76325834491</v>
       </c>
       <c r="D38" s="5">
-        <v>46114.59659328704</v>
+        <v>46114.7632599537</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>140</v>
@@ -3641,13 +3641,13 @@
         <v>142</v>
       </c>
       <c r="B39" s="8">
-        <v>46080.61162185185</v>
+        <v>46080.778288518515</v>
       </c>
       <c r="C39" s="8">
-        <v>46121.69341248843</v>
+        <v>46121.86007915509</v>
       </c>
       <c r="D39" s="8">
-        <v>46149.030915219904</v>
+        <v>46149.197581886576</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>143</v>
@@ -3706,13 +3706,13 @@
         <v>147</v>
       </c>
       <c r="B40" s="5">
-        <v>46080.611620069445</v>
+        <v>46080.77828673611</v>
       </c>
       <c r="C40" s="5">
-        <v>46114.5931810301</v>
+        <v>46114.759847696754</v>
       </c>
       <c r="D40" s="5">
-        <v>46121.693403067125</v>
+        <v>46121.8600697338</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>148</v>
@@ -3767,13 +3767,13 @@
         <v>150</v>
       </c>
       <c r="B41" s="8">
-        <v>46080.611620358795</v>
+        <v>46080.77828702546</v>
       </c>
       <c r="C41" s="8">
-        <v>46121.69339813657</v>
+        <v>46121.860064803244</v>
       </c>
       <c r="D41" s="8">
-        <v>46121.69339930556</v>
+        <v>46121.86006597222</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>149</v>
@@ -3828,13 +3828,13 @@
         <v>152</v>
       </c>
       <c r="B42" s="5">
-        <v>46080.611620578704</v>
+        <v>46080.77828724537</v>
       </c>
       <c r="C42" s="5">
-        <v>46114.59384487268</v>
+        <v>46114.76051153935</v>
       </c>
       <c r="D42" s="5">
-        <v>46202.02042104167</v>
+        <v>46202.187087708335</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>153</v>
@@ -3893,13 +3893,13 @@
         <v>156</v>
       </c>
       <c r="B43" s="8">
-        <v>46080.61162082176</v>
+        <v>46080.77828748843</v>
       </c>
       <c r="C43" s="8">
-        <v>46114.59378298611</v>
+        <v>46114.76044965278</v>
       </c>
       <c r="D43" s="8">
-        <v>46114.593784282406</v>
+        <v>46114.76045094908</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>157</v>
@@ -3954,13 +3954,13 @@
         <v>159</v>
       </c>
       <c r="B44" s="5">
-        <v>46080.611621041666</v>
+        <v>46080.77828770834</v>
       </c>
       <c r="C44" s="5">
-        <v>46114.593829687496</v>
+        <v>46114.76049635417</v>
       </c>
       <c r="D44" s="5">
-        <v>46114.59383114583</v>
+        <v>46114.7604978125</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>160</v>
@@ -4015,13 +4015,13 @@
         <v>162</v>
       </c>
       <c r="B45" s="8">
-        <v>46080.61162127314</v>
+        <v>46080.778287939815</v>
       </c>
       <c r="C45" s="8">
-        <v>46140.672237499995</v>
+        <v>46140.83890416667</v>
       </c>
       <c r="D45" s="8">
-        <v>46141.60567505787</v>
+        <v>46141.772341724536</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>163</v>
@@ -4064,13 +4064,13 @@
         <v>165</v>
       </c>
       <c r="B46" s="5">
-        <v>46080.611621516204</v>
+        <v>46080.778288182875</v>
       </c>
       <c r="C46" s="5">
-        <v>46127.511413229164</v>
+        <v>46127.678079895835</v>
       </c>
       <c r="D46" s="5">
-        <v>46127.51143438657</v>
+        <v>46127.67810105324</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>166</v>
@@ -4129,13 +4129,13 @@
         <v>170</v>
       </c>
       <c r="B47" s="8">
-        <v>46080.611621759264</v>
+        <v>46080.77828842592</v>
       </c>
       <c r="C47" s="8">
-        <v>46127.511464745374</v>
+        <v>46127.67813141204</v>
       </c>
       <c r="D47" s="8">
-        <v>46158.00329228009</v>
+        <v>46158.16995894676</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>171</v>
@@ -4194,13 +4194,13 @@
         <v>176</v>
       </c>
       <c r="B48" s="5">
-        <v>46087.36977493056</v>
+        <v>46087.53644159722</v>
       </c>
       <c r="C48" s="5">
-        <v>46127.51151408565</v>
+        <v>46127.678180752315</v>
       </c>
       <c r="D48" s="5">
-        <v>46161.04121914352</v>
+        <v>46161.20788581019</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>177</v>
@@ -4257,13 +4257,13 @@
         <v>179</v>
       </c>
       <c r="B49" s="8">
-        <v>46087.36985466436</v>
+        <v>46087.536521331014</v>
       </c>
       <c r="C49" s="8">
-        <v>46140.67220598379</v>
+        <v>46140.83887265046</v>
       </c>
       <c r="D49" s="8">
-        <v>46141.60512039352</v>
+        <v>46141.771787060185</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>180</v>
@@ -4322,13 +4322,13 @@
         <v>183</v>
       </c>
       <c r="B50" s="5">
-        <v>46080.61162200231</v>
+        <v>46080.77828866898</v>
       </c>
       <c r="C50" s="5">
-        <v>46133.453843993055</v>
+        <v>46133.62051065972</v>
       </c>
       <c r="D50" s="5">
-        <v>46141.60591856482</v>
+        <v>46141.772585231476</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>184</v>
@@ -4371,13 +4371,13 @@
         <v>186</v>
       </c>
       <c r="B51" s="8">
-        <v>46080.61162225694</v>
+        <v>46080.77828892361</v>
       </c>
       <c r="C51" s="8">
-        <v>46133.45377119213</v>
+        <v>46133.6204378588</v>
       </c>
       <c r="D51" s="8">
-        <v>46151.01806096065</v>
+        <v>46151.18472762732</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>187</v>
@@ -4436,13 +4436,13 @@
         <v>191</v>
       </c>
       <c r="B52" s="5">
-        <v>46080.6116209375</v>
+        <v>46080.77828760417</v>
       </c>
       <c r="C52" s="5">
-        <v>46133.45382759259</v>
+        <v>46133.62049425926</v>
       </c>
       <c r="D52" s="5">
-        <v>46155.03748122686</v>
+        <v>46155.20414789351</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>192</v>
@@ -4501,13 +4501,13 @@
         <v>196</v>
       </c>
       <c r="B53" s="8">
-        <v>46080.61162134259</v>
+        <v>46080.778288009256</v>
       </c>
       <c r="C53" s="8">
-        <v>46132.6010328125</v>
+        <v>46132.76769947917</v>
       </c>
       <c r="D53" s="8">
-        <v>46141.60519509259</v>
+        <v>46141.77186175926</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>197</v>
@@ -4550,13 +4550,13 @@
         <v>199</v>
       </c>
       <c r="B54" s="5">
-        <v>46080.61162165509</v>
+        <v>46080.77828832176</v>
       </c>
       <c r="C54" s="5">
-        <v>46128.32315582176</v>
+        <v>46128.489822488424</v>
       </c>
       <c r="D54" s="5">
-        <v>46165.01464451389</v>
+        <v>46165.18131118055</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>200</v>
@@ -4615,13 +4615,13 @@
         <v>204</v>
       </c>
       <c r="B55" s="8">
-        <v>46080.611621944445</v>
+        <v>46080.77828861111</v>
       </c>
       <c r="C55" s="8">
-        <v>46128.323210532406</v>
+        <v>46128.48987719907</v>
       </c>
       <c r="D55" s="8">
-        <v>46170.01854524306</v>
+        <v>46170.185211909724</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>205</v>
@@ -4680,13 +4680,13 @@
         <v>208</v>
       </c>
       <c r="B56" s="5">
-        <v>46080.61162224537</v>
+        <v>46080.778288912035</v>
       </c>
       <c r="C56" s="5">
-        <v>46132.601014907406</v>
+        <v>46132.76768157407</v>
       </c>
       <c r="D56" s="5">
-        <v>46172.03607802083</v>
+        <v>46172.2027446875</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>209</v>
@@ -4745,13 +4745,13 @@
         <v>212</v>
       </c>
       <c r="B57" s="8">
-        <v>46080.6116225463</v>
+        <v>46080.77828921296</v>
       </c>
       <c r="C57" s="8">
-        <v>46141.54462414352</v>
+        <v>46141.711290810184</v>
       </c>
       <c r="D57" s="8">
-        <v>46141.60565009259</v>
+        <v>46141.77231675926</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>184</v>
@@ -4794,13 +4794,13 @@
         <v>214</v>
       </c>
       <c r="B58" s="5">
-        <v>46080.6116229051</v>
+        <v>46080.77828957176</v>
       </c>
       <c r="C58" s="5">
-        <v>46133.45436618055</v>
+        <v>46133.62103284722</v>
       </c>
       <c r="D58" s="5">
-        <v>46156.00241715278</v>
+        <v>46156.16908381945</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>215</v>
@@ -4859,13 +4859,13 @@
         <v>217</v>
       </c>
       <c r="B59" s="8">
-        <v>46080.61162319445</v>
+        <v>46080.77828986111</v>
       </c>
       <c r="C59" s="8">
-        <v>46133.454379965275</v>
+        <v>46133.621046631946</v>
       </c>
       <c r="D59" s="8">
-        <v>46133.45523274306</v>
+        <v>46133.62189940972</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>218</v>
@@ -4924,13 +4924,13 @@
         <v>220</v>
       </c>
       <c r="B60" s="5">
-        <v>46080.61162347222</v>
+        <v>46080.778290138885</v>
       </c>
       <c r="C60" s="5">
-        <v>46121.70129114583</v>
+        <v>46121.8679578125</v>
       </c>
       <c r="D60" s="5">
-        <v>46121.70131851852</v>
+        <v>46121.867985185185</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>221</v>
@@ -4989,13 +4989,13 @@
         <v>223</v>
       </c>
       <c r="B61" s="8">
-        <v>46080.61162372685</v>
+        <v>46080.778290393515</v>
       </c>
       <c r="C61" s="8">
-        <v>46121.70122795139</v>
+        <v>46121.86789461806</v>
       </c>
       <c r="D61" s="8">
-        <v>46204.03578572917</v>
+        <v>46204.20245239583</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>224</v>
@@ -5054,13 +5054,13 @@
         <v>226</v>
       </c>
       <c r="B62" s="5">
-        <v>46080.61881302083</v>
+        <v>46080.7854796875</v>
       </c>
       <c r="C62" s="5">
-        <v>46141.60555273148</v>
+        <v>46141.772219398146</v>
       </c>
       <c r="D62" s="5">
-        <v>46203.02565844907</v>
+        <v>46203.19232511574</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>54</v>
@@ -5119,13 +5119,13 @@
         <v>228</v>
       </c>
       <c r="B63" s="8">
-        <v>46080.61161995371</v>
+        <v>46080.77828662037</v>
       </c>
       <c r="C63" s="8">
-        <v>46141.54460908565</v>
+        <v>46141.711275752314</v>
       </c>
       <c r="D63" s="8">
-        <v>46141.544611226855</v>
+        <v>46141.71127789352</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>229</v>
@@ -5168,13 +5168,13 @@
         <v>231</v>
       </c>
       <c r="B64" s="5">
-        <v>46080.61162027778</v>
+        <v>46080.77828694445</v>
       </c>
       <c r="C64" s="5">
-        <v>46133.454125856486</v>
+        <v>46133.62079252314</v>
       </c>
       <c r="D64" s="5">
-        <v>46192.02040033565</v>
+        <v>46192.18706700232</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>232</v>
@@ -5233,13 +5233,13 @@
         <v>234</v>
       </c>
       <c r="B65" s="8">
-        <v>46080.61162052084</v>
+        <v>46080.778287187495</v>
       </c>
       <c r="C65" s="8">
-        <v>46133.45420378472</v>
+        <v>46133.620870451385</v>
       </c>
       <c r="D65" s="8">
-        <v>46133.454246608795</v>
+        <v>46133.62091327546</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>235</v>
@@ -5298,13 +5298,13 @@
         <v>238</v>
       </c>
       <c r="B66" s="5">
-        <v>46080.61162079861</v>
+        <v>46080.77828746528</v>
       </c>
       <c r="C66" s="5">
-        <v>46133.45511944444</v>
+        <v>46133.62178611111</v>
       </c>
       <c r="D66" s="5">
-        <v>46133.455135324075</v>
+        <v>46133.62180199074</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>239</v>
@@ -5363,13 +5363,13 @@
         <v>241</v>
       </c>
       <c r="B67" s="8">
-        <v>46080.611621041666</v>
+        <v>46080.77828770834</v>
       </c>
       <c r="C67" s="8">
-        <v>46133.45513137731</v>
+        <v>46133.62179804398</v>
       </c>
       <c r="D67" s="8">
-        <v>46133.45514824074</v>
+        <v>46133.62181490741</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>242</v>
@@ -5428,13 +5428,13 @@
         <v>244</v>
       </c>
       <c r="B68" s="5">
-        <v>46080.611621296295</v>
+        <v>46080.77828796297</v>
       </c>
       <c r="C68" s="5">
-        <v>46133.45515101852</v>
+        <v>46133.62181768518</v>
       </c>
       <c r="D68" s="5">
-        <v>46133.455167175925</v>
+        <v>46133.6218338426</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>245</v>
@@ -5493,13 +5493,13 @@
         <v>247</v>
       </c>
       <c r="B69" s="8">
-        <v>46080.611621550925</v>
+        <v>46080.778288217596</v>
       </c>
       <c r="C69" s="8">
-        <v>46133.455206886574</v>
+        <v>46133.621873553246</v>
       </c>
       <c r="D69" s="8">
-        <v>46133.45522304398</v>
+        <v>46133.621889710645</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>181</v>
@@ -5558,13 +5558,13 @@
         <v>250</v>
       </c>
       <c r="B70" s="5">
-        <v>46080.611621793985</v>
+        <v>46080.77828846065</v>
       </c>
       <c r="C70" s="5">
-        <v>46140.67233574074</v>
+        <v>46140.8390024074</v>
       </c>
       <c r="D70" s="5">
-        <v>46141.54510638889</v>
+        <v>46141.711773055555</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>182</v>
@@ -5623,13 +5623,13 @@
         <v>252</v>
       </c>
       <c r="B71" s="8">
-        <v>46080.61162203704</v>
+        <v>46080.7782887037</v>
       </c>
       <c r="C71" s="8">
-        <v>46141.5453846875</v>
+        <v>46141.71205135417</v>
       </c>
       <c r="D71" s="8">
-        <v>46141.54538606481</v>
+        <v>46141.712052731484</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>253</v>
@@ -5672,13 +5672,13 @@
         <v>255</v>
       </c>
       <c r="B72" s="5">
-        <v>46080.61162229167</v>
+        <v>46080.77828895833</v>
       </c>
       <c r="C72" s="5">
-        <v>46140.67238</v>
+        <v>46140.83904666667</v>
       </c>
       <c r="D72" s="5">
-        <v>46141.54513895833</v>
+        <v>46141.711805625004</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>256</v>
@@ -5737,13 +5737,13 @@
         <v>260</v>
       </c>
       <c r="B73" s="8">
-        <v>46080.61162048611</v>
+        <v>46080.778287152774</v>
       </c>
       <c r="C73" s="8">
-        <v>46141.54505951389</v>
+        <v>46141.711726180554</v>
       </c>
       <c r="D73" s="8">
-        <v>46141.54516234953</v>
+        <v>46141.7118290162</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>261</v>
@@ -5802,13 +5802,13 @@
         <v>264</v>
       </c>
       <c r="B74" s="5">
-        <v>46080.61162084491</v>
+        <v>46080.77828751157</v>
       </c>
       <c r="C74" s="5">
-        <v>46141.54524869213</v>
+        <v>46141.7119153588</v>
       </c>
       <c r="D74" s="5">
-        <v>46141.54525033565</v>
+        <v>46141.711917002314</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>265</v>
@@ -5867,13 +5867,13 @@
         <v>267</v>
       </c>
       <c r="B75" s="8">
-        <v>46080.61162115741</v>
+        <v>46080.77828782407</v>
       </c>
       <c r="C75" s="8">
-        <v>46141.545294236115</v>
+        <v>46141.71196090278</v>
       </c>
       <c r="D75" s="8">
-        <v>46141.54529546296</v>
+        <v>46141.71196212963</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>268</v>
@@ -5932,11 +5932,11 @@
         <v>270</v>
       </c>
       <c r="B76" s="5">
-        <v>46080.61162142361</v>
+        <v>46080.77828809028</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46090.44426309028</v>
+        <v>46090.61092975695</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>271</v>
@@ -5979,11 +5979,11 @@
         <v>273</v>
       </c>
       <c r="B77" s="8">
-        <v>46080.611622013894</v>
+        <v>46080.77828868055</v>
       </c>
       <c r="C77" s="9"/>
       <c r="D77" s="8">
-        <v>46141.54530271991</v>
+        <v>46141.711969386575</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>72</v>
@@ -6042,11 +6042,11 @@
         <v>277</v>
       </c>
       <c r="B78" s="5">
-        <v>46080.611621689815</v>
+        <v>46080.77828835648</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46141.54530398148</v>
+        <v>46141.711970648146</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>278</v>
@@ -6105,11 +6105,11 @@
         <v>279</v>
       </c>
       <c r="B79" s="8">
-        <v>46090.44504910879</v>
+        <v>46090.61171577546</v>
       </c>
       <c r="C79" s="9"/>
       <c r="D79" s="8">
-        <v>46090.44786366898</v>
+        <v>46090.614530335646</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>280</v>
@@ -6158,11 +6158,11 @@
         <v>282</v>
       </c>
       <c r="B80" s="5">
-        <v>46090.44533261574</v>
+        <v>46090.61199928241</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46141.545305277774</v>
+        <v>46141.711971944445</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>283</v>
@@ -6221,11 +6221,11 @@
         <v>285</v>
       </c>
       <c r="B81" s="8">
-        <v>46090.4454134375</v>
+        <v>46090.61208010417</v>
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="8">
-        <v>46090.45203153935</v>
+        <v>46090.61869820602</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>286</v>

--- a/data/50001524 - ATACAMA KOZAN.xlsx
+++ b/data/50001524 - ATACAMA KOZAN.xlsx
@@ -328,18 +328,21 @@
     <t>Generación OC Alabe,Fabricación Alabe</t>
   </si>
   <si>
+    <t>Media</t>
+  </si>
+  <si>
+    <t>1213412709779762</t>
+  </si>
+  <si>
+    <t>Generación OC Alabe</t>
+  </si>
+  <si>
+    <t>Fabricación Alabe,Alabe</t>
+  </si>
+  <si>
     <t>Baja</t>
   </si>
   <si>
-    <t>1213412709779762</t>
-  </si>
-  <si>
-    <t>Generación OC Alabe</t>
-  </si>
-  <si>
-    <t>Fabricación Alabe,Alabe</t>
-  </si>
-  <si>
     <t>Tarea sin iniciar</t>
   </si>
   <si>
@@ -476,9 +479,6 @@
   </si>
   <si>
     <t>Generación Oc sensores,Fabricación Sensores</t>
-  </si>
-  <si>
-    <t>Media</t>
   </si>
   <si>
     <t>1213470416901267</t>
@@ -2850,7 +2850,7 @@
         <v>46139.781195081014</v>
       </c>
       <c r="D26" s="5">
-        <v>46139.78120622685</v>
+        <v>46206.19700488426</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>101</v>
@@ -2888,7 +2888,7 @@
       <c r="P26" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="Q26" s="11" t="s">
+      <c r="Q26" s="12" t="s">
         <v>105</v>
       </c>
       <c r="R26" s="6">
@@ -2954,20 +2954,20 @@
         <v>108</v>
       </c>
       <c r="Q27" s="11" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="R27" s="9">
         <v>0</v>
       </c>
       <c r="S27" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="T27" s="9"/>
       <c r="U27" s="9"/>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B28" s="5">
         <v>46080.778286388886</v>
@@ -2979,7 +2979,7 @@
         <v>46139.78118329861</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
@@ -3015,20 +3015,20 @@
         <v>101</v>
       </c>
       <c r="Q28" s="11" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="R28" s="6">
         <v>0</v>
       </c>
       <c r="S28" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="T28" s="6"/>
       <c r="U28" s="6"/>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B29" s="8">
         <v>46080.78421460648</v>
@@ -3040,7 +3040,7 @@
         <v>46199.207547604165</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>26</v>
@@ -3070,7 +3070,7 @@
         <v>98</v>
       </c>
       <c r="O29" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="P29" s="9" t="s">
         <v>98</v>
@@ -3082,7 +3082,7 @@
         <v>1</v>
       </c>
       <c r="S29" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="T29" s="8">
         <v>46092</v>
@@ -3093,7 +3093,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B30" s="5">
         <v>46080.78464398148</v>
@@ -3105,7 +3105,7 @@
         <v>46114.761801307875</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
@@ -3132,13 +3132,13 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="O30" s="6" t="s">
         <v>87</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
@@ -3148,7 +3148,7 @@
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B31" s="8">
         <v>46080.78472030093</v>
@@ -3160,7 +3160,7 @@
         <v>46140.80895233796</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>26</v>
@@ -3187,13 +3187,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="9" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="O31" s="9" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="P31" s="9" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="Q31" s="9"/>
       <c r="R31" s="9"/>
@@ -3203,7 +3203,7 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B32" s="5">
         <v>46080.77828665509</v>
@@ -3215,7 +3215,7 @@
         <v>46154.1920628125</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
@@ -3245,7 +3245,7 @@
         <v>98</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="P32" s="6" t="s">
         <v>98</v>
@@ -3268,7 +3268,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B33" s="8">
         <v>46080.7782869213</v>
@@ -3280,7 +3280,7 @@
         <v>46133.62086326389</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>26</v>
@@ -3307,29 +3307,29 @@
         <v>26</v>
       </c>
       <c r="N33" s="9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="O33" s="9" t="s">
         <v>83</v>
       </c>
       <c r="P33" s="9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="Q33" s="11" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="R33" s="9">
         <v>0</v>
       </c>
       <c r="S33" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="T33" s="9"/>
       <c r="U33" s="9"/>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B34" s="5">
         <v>46080.778287187495</v>
@@ -3341,7 +3341,7 @@
         <v>46133.62090126157</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
@@ -3368,29 +3368,29 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="Q34" s="11" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="R34" s="6">
         <v>0</v>
       </c>
       <c r="S34" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="T34" s="6"/>
       <c r="U34" s="6"/>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B35" s="8">
         <v>46080.77828746528</v>
@@ -3402,7 +3402,7 @@
         <v>46114.76329173611</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>26</v>
@@ -3432,13 +3432,13 @@
         <v>98</v>
       </c>
       <c r="O35" s="9" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="P35" s="9" t="s">
         <v>98</v>
       </c>
       <c r="Q35" s="11" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="R35" s="9">
         <v>1</v>
@@ -3455,7 +3455,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B36" s="5">
         <v>46080.77828773148</v>
@@ -3467,7 +3467,7 @@
         <v>46114.76319354167</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
@@ -3494,29 +3494,29 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="O36" s="6" t="s">
         <v>77</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="Q36" s="11" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="R36" s="6">
         <v>0</v>
       </c>
       <c r="S36" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="T36" s="6"/>
       <c r="U36" s="6"/>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B37" s="8">
         <v>46080.77828799769</v>
@@ -3528,7 +3528,7 @@
         <v>46114.763248877316</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>26</v>
@@ -3555,29 +3555,29 @@
         <v>26</v>
       </c>
       <c r="N37" s="9" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="O37" s="9" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="P37" s="9" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="Q37" s="11" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="R37" s="9">
         <v>0</v>
       </c>
       <c r="S37" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="T37" s="9"/>
       <c r="U37" s="9"/>
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B38" s="5">
         <v>46080.77828825232</v>
@@ -3589,7 +3589,7 @@
         <v>46114.7632599537</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
@@ -3616,29 +3616,29 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="Q38" s="11" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="R38" s="6">
         <v>0</v>
       </c>
       <c r="S38" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="T38" s="6"/>
       <c r="U38" s="6"/>
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B39" s="8">
         <v>46080.778288518515</v>
@@ -3650,16 +3650,16 @@
         <v>46149.197581886576</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="I39" s="8">
         <v>46100</v>
@@ -3680,7 +3680,7 @@
         <v>98</v>
       </c>
       <c r="O39" s="9" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="P39" s="9" t="s">
         <v>98</v>
@@ -3703,7 +3703,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B40" s="5">
         <v>46080.77828673611</v>
@@ -3715,16 +3715,16 @@
         <v>46121.8600697338</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="I40" s="5">
         <v>46100</v>
@@ -3742,29 +3742,29 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="Q40" s="11" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="R40" s="6">
         <v>0</v>
       </c>
       <c r="S40" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="T40" s="6"/>
       <c r="U40" s="6"/>
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B41" s="8">
         <v>46080.77828702546</v>
@@ -3776,16 +3776,16 @@
         <v>46121.86006597222</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="I41" s="8">
         <v>46120</v>
@@ -3803,29 +3803,29 @@
         <v>26</v>
       </c>
       <c r="N41" s="9" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O41" s="9" t="s">
         <v>93</v>
       </c>
       <c r="P41" s="9" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Q41" s="11" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="R41" s="9">
         <v>0</v>
       </c>
       <c r="S41" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="T41" s="9"/>
       <c r="U41" s="9"/>
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B42" s="5">
         <v>46080.77828724537</v>
@@ -3837,16 +3837,16 @@
         <v>46202.187087708335</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="I42" s="5">
         <v>46100</v>
@@ -3867,13 +3867,13 @@
         <v>98</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>98</v>
       </c>
       <c r="Q42" s="12" t="s">
-        <v>155</v>
+        <v>105</v>
       </c>
       <c r="R42" s="6">
         <v>1</v>
@@ -3908,10 +3908,10 @@
         <v>26</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="I43" s="8">
         <v>46100</v>
@@ -3929,7 +3929,7 @@
         <v>26</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="O43" s="9" t="s">
         <v>90</v>
@@ -3938,13 +3938,13 @@
         <v>158</v>
       </c>
       <c r="Q43" s="11" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="R43" s="9">
         <v>0</v>
       </c>
       <c r="S43" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="T43" s="9"/>
       <c r="U43" s="9"/>
@@ -3969,10 +3969,10 @@
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="I44" s="5">
         <v>46129</v>
@@ -3990,7 +3990,7 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="O44" s="6" t="s">
         <v>157</v>
@@ -3999,13 +3999,13 @@
         <v>161</v>
       </c>
       <c r="Q44" s="11" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="R44" s="6">
         <v>0</v>
       </c>
       <c r="S44" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="T44" s="6"/>
       <c r="U44" s="6"/>
@@ -4302,7 +4302,7 @@
         <v>182</v>
       </c>
       <c r="Q49" s="11" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="R49" s="9">
         <v>1</v>
@@ -4410,7 +4410,7 @@
         <v>184</v>
       </c>
       <c r="O51" s="9" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P51" s="9" t="s">
         <v>190</v>
@@ -4833,7 +4833,7 @@
         <v>184</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="P58" s="6" t="s">
         <v>216</v>
@@ -4898,13 +4898,13 @@
         <v>184</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="P59" s="9" t="s">
         <v>219</v>
       </c>
       <c r="Q59" s="11" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="R59" s="9">
         <v>1</v>
@@ -4963,13 +4963,13 @@
         <v>184</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="P60" s="6" t="s">
         <v>222</v>
       </c>
       <c r="Q60" s="11" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="R60" s="6">
         <v>1</v>
@@ -5034,7 +5034,7 @@
         <v>225</v>
       </c>
       <c r="Q61" s="12" t="s">
-        <v>155</v>
+        <v>105</v>
       </c>
       <c r="R61" s="9">
         <v>1</v>
@@ -5093,7 +5093,7 @@
         <v>184</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="P62" s="6" t="s">
         <v>227</v>
@@ -5278,7 +5278,7 @@
         <v>237</v>
       </c>
       <c r="Q65" s="11" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="R65" s="9">
         <v>1</v>
@@ -5343,7 +5343,7 @@
         <v>237</v>
       </c>
       <c r="Q66" s="11" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="R66" s="6">
         <v>1</v>
@@ -5408,7 +5408,7 @@
         <v>237</v>
       </c>
       <c r="Q67" s="11" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="R67" s="9">
         <v>1</v>
@@ -5434,7 +5434,7 @@
         <v>46133.62181768518</v>
       </c>
       <c r="D68" s="5">
-        <v>46133.6218338426</v>
+        <v>46206.19700435185</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>245</v>
@@ -5472,7 +5472,7 @@
       <c r="P68" s="6" t="s">
         <v>237</v>
       </c>
-      <c r="Q68" s="11" t="s">
+      <c r="Q68" s="12" t="s">
         <v>105</v>
       </c>
       <c r="R68" s="6">
@@ -5538,7 +5538,7 @@
         <v>249</v>
       </c>
       <c r="Q69" s="11" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="R69" s="9">
         <v>1</v>
@@ -5603,13 +5603,13 @@
         <v>251</v>
       </c>
       <c r="Q70" s="11" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="R70" s="6">
         <v>1</v>
       </c>
       <c r="S70" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="T70" s="5">
         <v>46234</v>
@@ -5717,13 +5717,13 @@
         <v>259</v>
       </c>
       <c r="Q72" s="11" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="R72" s="6">
         <v>1</v>
       </c>
       <c r="S72" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="T72" s="5">
         <v>46237</v>
@@ -5782,13 +5782,13 @@
         <v>263</v>
       </c>
       <c r="Q73" s="11" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="R73" s="9">
         <v>1</v>
       </c>
       <c r="S73" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="T73" s="8">
         <v>46238</v>
@@ -5847,13 +5847,13 @@
         <v>266</v>
       </c>
       <c r="Q74" s="11" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="R74" s="6">
         <v>1</v>
       </c>
       <c r="S74" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="T74" s="5">
         <v>46239</v>
@@ -5912,13 +5912,13 @@
         <v>269</v>
       </c>
       <c r="Q75" s="11" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="R75" s="9">
         <v>1</v>
       </c>
       <c r="S75" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="T75" s="8">
         <v>46240</v>
@@ -6022,13 +6022,13 @@
         <v>271</v>
       </c>
       <c r="Q77" s="11" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="R77" s="9">
         <v>0</v>
       </c>
       <c r="S77" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="T77" s="8">
         <v>46241</v>
@@ -6085,13 +6085,13 @@
         <v>271</v>
       </c>
       <c r="Q78" s="11" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="R78" s="6">
         <v>0</v>
       </c>
       <c r="S78" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="T78" s="5">
         <v>46241</v>
@@ -6142,13 +6142,13 @@
         <v>26</v>
       </c>
       <c r="Q79" s="11" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="R79" s="9">
         <v>0</v>
       </c>
       <c r="S79" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="T79" s="9"/>
       <c r="U79" s="9"/>
@@ -6201,13 +6201,13 @@
         <v>284</v>
       </c>
       <c r="Q80" s="11" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="R80" s="6">
         <v>0</v>
       </c>
       <c r="S80" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="T80" s="5">
         <v>46241</v>
@@ -6264,13 +6264,13 @@
         <v>280</v>
       </c>
       <c r="Q81" s="11" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="R81" s="9">
         <v>0</v>
       </c>
       <c r="S81" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="T81" s="8">
         <v>46252</v>

--- a/data/50001524 - ATACAMA KOZAN.xlsx
+++ b/data/50001524 - ATACAMA KOZAN.xlsx
@@ -3834,7 +3834,7 @@
         <v>46114.76051153935</v>
       </c>
       <c r="D42" s="5">
-        <v>46202.187087708335</v>
+        <v>46210.17465634259</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>154</v>
@@ -3872,8 +3872,8 @@
       <c r="P42" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="Q42" s="12" t="s">
-        <v>105</v>
+      <c r="Q42" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="R42" s="6">
         <v>1</v>
@@ -4865,7 +4865,7 @@
         <v>46133.621046631946</v>
       </c>
       <c r="D59" s="8">
-        <v>46133.62189940972</v>
+        <v>46210.17008761574</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>218</v>
@@ -4903,8 +4903,8 @@
       <c r="P59" s="9" t="s">
         <v>219</v>
       </c>
-      <c r="Q59" s="11" t="s">
-        <v>109</v>
+      <c r="Q59" s="12" t="s">
+        <v>105</v>
       </c>
       <c r="R59" s="9">
         <v>1</v>

--- a/data/50001524 - ATACAMA KOZAN.xlsx
+++ b/data/50001524 - ATACAMA KOZAN.xlsx
@@ -1498,13 +1498,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46080.77828641204</v>
+        <v>46080.61161974537</v>
       </c>
       <c r="C4" s="5">
-        <v>46097.83665600694</v>
+        <v>46097.66998934028</v>
       </c>
       <c r="D4" s="5">
-        <v>46097.83674934028</v>
+        <v>46097.67008267361</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1547,13 +1547,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46080.77828680555</v>
+        <v>46080.611620138894</v>
       </c>
       <c r="C5" s="8">
-        <v>46097.8362150926</v>
+        <v>46097.669548425925</v>
       </c>
       <c r="D5" s="8">
-        <v>46097.836235787036</v>
+        <v>46097.66956912037</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1610,13 +1610,13 @@
         <v>33</v>
       </c>
       <c r="B6" s="5">
-        <v>46080.778287106485</v>
+        <v>46080.61162043981</v>
       </c>
       <c r="C6" s="5">
-        <v>46097.83622053241</v>
+        <v>46097.66955386574</v>
       </c>
       <c r="D6" s="5">
-        <v>46097.836235532406</v>
+        <v>46097.66956886574</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>34</v>
@@ -1673,13 +1673,13 @@
         <v>37</v>
       </c>
       <c r="B7" s="8">
-        <v>46080.778287407404</v>
+        <v>46080.61162074074</v>
       </c>
       <c r="C7" s="8">
-        <v>46097.83622695602</v>
+        <v>46097.66956028935</v>
       </c>
       <c r="D7" s="8">
-        <v>46097.83624193287</v>
+        <v>46097.669575266205</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>38</v>
@@ -1736,13 +1736,13 @@
         <v>39</v>
       </c>
       <c r="B8" s="5">
-        <v>46080.77828773148</v>
+        <v>46080.61162106482</v>
       </c>
       <c r="C8" s="5">
-        <v>46093.643042129625</v>
+        <v>46093.47637546297</v>
       </c>
       <c r="D8" s="5">
-        <v>46100.791677939815</v>
+        <v>46100.62501127315</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>40</v>
@@ -1799,13 +1799,13 @@
         <v>42</v>
       </c>
       <c r="B9" s="8">
-        <v>46080.778288009256</v>
+        <v>46080.61162134259</v>
       </c>
       <c r="C9" s="8">
-        <v>46097.83624405092</v>
+        <v>46097.66957738426</v>
       </c>
       <c r="D9" s="8">
-        <v>46097.83625847222</v>
+        <v>46097.669591805556</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>43</v>
@@ -1862,13 +1862,13 @@
         <v>44</v>
       </c>
       <c r="B10" s="5">
-        <v>46080.78358017361</v>
+        <v>46080.61691350694</v>
       </c>
       <c r="C10" s="5">
-        <v>46141.711601145835</v>
+        <v>46141.54493447917</v>
       </c>
       <c r="D10" s="5">
-        <v>46141.7116022338</v>
+        <v>46141.54493556713</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>45</v>
@@ -1911,13 +1911,13 @@
         <v>47</v>
       </c>
       <c r="B11" s="8">
-        <v>46080.7837635301</v>
+        <v>46080.617096863425</v>
       </c>
       <c r="C11" s="8">
-        <v>46114.51182108796</v>
+        <v>46114.345154421295</v>
       </c>
       <c r="D11" s="8">
-        <v>46114.51183934028</v>
+        <v>46114.34517267361</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>48</v>
@@ -1976,13 +1976,13 @@
         <v>52</v>
       </c>
       <c r="B12" s="5">
-        <v>46080.783815243056</v>
+        <v>46080.61714857639</v>
       </c>
       <c r="C12" s="5">
-        <v>46141.71151436343</v>
+        <v>46141.54484769676</v>
       </c>
       <c r="D12" s="5">
-        <v>46205.17911829861</v>
+        <v>46205.01245163195</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>53</v>
@@ -2041,13 +2041,13 @@
         <v>57</v>
       </c>
       <c r="B13" s="8">
-        <v>46080.77828829861</v>
+        <v>46080.61162163195</v>
       </c>
       <c r="C13" s="8">
-        <v>46114.51259805556</v>
+        <v>46114.34593138889</v>
       </c>
       <c r="D13" s="8">
-        <v>46114.75905811343</v>
+        <v>46114.59239144676</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>58</v>
@@ -2092,13 +2092,13 @@
         <v>60</v>
       </c>
       <c r="B14" s="5">
-        <v>46080.778288587964</v>
+        <v>46080.6116219213</v>
       </c>
       <c r="C14" s="5">
-        <v>46114.511949733795</v>
+        <v>46114.34528306713</v>
       </c>
       <c r="D14" s="5">
-        <v>46114.51196541666</v>
+        <v>46114.34529875</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>61</v>
@@ -2157,13 +2157,13 @@
         <v>63</v>
       </c>
       <c r="B15" s="8">
-        <v>46080.77828953703</v>
+        <v>46080.61162287037</v>
       </c>
       <c r="C15" s="8">
-        <v>46114.512105497684</v>
+        <v>46114.34543883102</v>
       </c>
       <c r="D15" s="8">
-        <v>46114.51212151621</v>
+        <v>46114.345454849536</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>64</v>
@@ -2222,13 +2222,13 @@
         <v>66</v>
       </c>
       <c r="B16" s="5">
-        <v>46080.77828619213</v>
+        <v>46080.61161952546</v>
       </c>
       <c r="C16" s="5">
-        <v>46114.51240666666</v>
+        <v>46114.345740000004</v>
       </c>
       <c r="D16" s="5">
-        <v>46114.5124212963</v>
+        <v>46114.34575462963</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>67</v>
@@ -2287,13 +2287,13 @@
         <v>69</v>
       </c>
       <c r="B17" s="8">
-        <v>46080.77828652778</v>
+        <v>46080.61161986111</v>
       </c>
       <c r="C17" s="8">
-        <v>46114.512582048614</v>
+        <v>46114.34591538194</v>
       </c>
       <c r="D17" s="8">
-        <v>46114.51259918981</v>
+        <v>46114.34593252315</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>70</v>
@@ -2352,13 +2352,13 @@
         <v>73</v>
       </c>
       <c r="B18" s="5">
-        <v>46080.778286875</v>
+        <v>46080.611620208336</v>
       </c>
       <c r="C18" s="5">
-        <v>46126.85558527778</v>
+        <v>46126.68891861111</v>
       </c>
       <c r="D18" s="5">
-        <v>46126.85559849537</v>
+        <v>46126.6889318287</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>74</v>
@@ -2405,13 +2405,13 @@
         <v>76</v>
       </c>
       <c r="B19" s="8">
-        <v>46080.778287152774</v>
+        <v>46080.61162048611</v>
       </c>
       <c r="C19" s="8">
-        <v>46114.51201428241</v>
+        <v>46114.345347615745</v>
       </c>
       <c r="D19" s="8">
-        <v>46114.512030185186</v>
+        <v>46114.345363518514</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>77</v>
@@ -2470,13 +2470,13 @@
         <v>79</v>
       </c>
       <c r="B20" s="5">
-        <v>46080.77828752315</v>
+        <v>46080.61162085648</v>
       </c>
       <c r="C20" s="5">
-        <v>46114.51275581018</v>
+        <v>46114.34608914352</v>
       </c>
       <c r="D20" s="5">
-        <v>46114.51277075231</v>
+        <v>46114.34610408565</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>80</v>
@@ -2535,13 +2535,13 @@
         <v>82</v>
       </c>
       <c r="B21" s="8">
-        <v>46080.77828780093</v>
+        <v>46080.61162113426</v>
       </c>
       <c r="C21" s="8">
-        <v>46126.85556609953</v>
+        <v>46126.68889943287</v>
       </c>
       <c r="D21" s="8">
-        <v>46126.855582199074</v>
+        <v>46126.6889155324</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>83</v>
@@ -2600,13 +2600,13 @@
         <v>86</v>
       </c>
       <c r="B22" s="5">
-        <v>46080.78405931713</v>
+        <v>46080.61739265046</v>
       </c>
       <c r="C22" s="5">
-        <v>46114.51307935185</v>
+        <v>46114.34641268519</v>
       </c>
       <c r="D22" s="5">
-        <v>46114.51309576389</v>
+        <v>46114.34642909722</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>87</v>
@@ -2665,13 +2665,13 @@
         <v>89</v>
       </c>
       <c r="B23" s="8">
-        <v>46080.778288113426</v>
+        <v>46080.61162144676</v>
       </c>
       <c r="C23" s="8">
-        <v>46114.513175810185</v>
+        <v>46114.34650914352</v>
       </c>
       <c r="D23" s="8">
-        <v>46114.51327625</v>
+        <v>46114.34660958333</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>90</v>
@@ -2730,13 +2730,13 @@
         <v>92</v>
       </c>
       <c r="B24" s="5">
-        <v>46080.77828840278</v>
+        <v>46080.61162173611</v>
       </c>
       <c r="C24" s="5">
-        <v>46114.75971673611</v>
+        <v>46114.593050069445</v>
       </c>
       <c r="D24" s="5">
-        <v>46114.759732199076</v>
+        <v>46114.593065532405</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>93</v>
@@ -2795,13 +2795,13 @@
         <v>97</v>
       </c>
       <c r="B25" s="8">
-        <v>46080.778288692134</v>
+        <v>46080.61162202546</v>
       </c>
       <c r="C25" s="8">
-        <v>46140.83895159722</v>
+        <v>46140.67228493055</v>
       </c>
       <c r="D25" s="8">
-        <v>46140.838952673614</v>
+        <v>46140.67228600694</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>98</v>
@@ -2844,13 +2844,13 @@
         <v>100</v>
       </c>
       <c r="B26" s="5">
-        <v>46080.778288981484</v>
+        <v>46080.61162231481</v>
       </c>
       <c r="C26" s="5">
-        <v>46139.781195081014</v>
+        <v>46139.61452841436</v>
       </c>
       <c r="D26" s="5">
-        <v>46206.19700488426</v>
+        <v>46206.03033821759</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>101</v>
@@ -2909,13 +2909,13 @@
         <v>106</v>
       </c>
       <c r="B27" s="8">
-        <v>46080.77828601852</v>
+        <v>46080.611619351854</v>
       </c>
       <c r="C27" s="8">
-        <v>46139.78108315972</v>
+        <v>46139.61441649306</v>
       </c>
       <c r="D27" s="8">
-        <v>46139.78108450232</v>
+        <v>46139.61441783565</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>107</v>
@@ -2970,13 +2970,13 @@
         <v>111</v>
       </c>
       <c r="B28" s="5">
-        <v>46080.778286388886</v>
+        <v>46080.61161972222</v>
       </c>
       <c r="C28" s="5">
-        <v>46139.781181886574</v>
+        <v>46139.6145152199</v>
       </c>
       <c r="D28" s="5">
-        <v>46139.78118329861</v>
+        <v>46139.61451663195</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>112</v>
@@ -3031,13 +3031,13 @@
         <v>113</v>
       </c>
       <c r="B29" s="8">
-        <v>46080.78421460648</v>
+        <v>46080.617547939815</v>
       </c>
       <c r="C29" s="8">
-        <v>46140.80903469908</v>
+        <v>46140.64236803241</v>
       </c>
       <c r="D29" s="8">
-        <v>46199.207547604165</v>
+        <v>46199.0408809375</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>114</v>
@@ -3096,13 +3096,13 @@
         <v>116</v>
       </c>
       <c r="B30" s="5">
-        <v>46080.78464398148</v>
+        <v>46080.61797731482</v>
       </c>
       <c r="C30" s="5">
-        <v>46114.761799988424</v>
+        <v>46114.59513332176</v>
       </c>
       <c r="D30" s="5">
-        <v>46114.761801307875</v>
+        <v>46114.595134641204</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>117</v>
@@ -3151,13 +3151,13 @@
         <v>119</v>
       </c>
       <c r="B31" s="8">
-        <v>46080.78472030093</v>
+        <v>46080.61805363426</v>
       </c>
       <c r="C31" s="8">
-        <v>46140.8089503125</v>
+        <v>46140.64228364584</v>
       </c>
       <c r="D31" s="8">
-        <v>46140.80895233796</v>
+        <v>46140.642285671296</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>120</v>
@@ -3206,13 +3206,13 @@
         <v>122</v>
       </c>
       <c r="B32" s="5">
-        <v>46080.77828665509</v>
+        <v>46080.61161998843</v>
       </c>
       <c r="C32" s="5">
-        <v>46133.62092905093</v>
+        <v>46133.45426238426</v>
       </c>
       <c r="D32" s="5">
-        <v>46154.1920628125</v>
+        <v>46154.02539614584</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>123</v>
@@ -3271,13 +3271,13 @@
         <v>125</v>
       </c>
       <c r="B33" s="8">
-        <v>46080.7782869213</v>
+        <v>46080.611620254625</v>
       </c>
       <c r="C33" s="8">
-        <v>46133.62086219907</v>
+        <v>46133.45419553241</v>
       </c>
       <c r="D33" s="8">
-        <v>46133.62086326389</v>
+        <v>46133.454196597224</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>126</v>
@@ -3332,13 +3332,13 @@
         <v>128</v>
       </c>
       <c r="B34" s="5">
-        <v>46080.778287187495</v>
+        <v>46080.61162052084</v>
       </c>
       <c r="C34" s="5">
-        <v>46133.62090008102</v>
+        <v>46133.45423341435</v>
       </c>
       <c r="D34" s="5">
-        <v>46133.62090126157</v>
+        <v>46133.45423459491</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>129</v>
@@ -3393,13 +3393,13 @@
         <v>131</v>
       </c>
       <c r="B35" s="8">
-        <v>46080.77828746528</v>
+        <v>46080.61162079861</v>
       </c>
       <c r="C35" s="8">
-        <v>46114.76327634259</v>
+        <v>46114.59660967592</v>
       </c>
       <c r="D35" s="8">
-        <v>46114.76329173611</v>
+        <v>46114.59662506945</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>132</v>
@@ -3458,13 +3458,13 @@
         <v>134</v>
       </c>
       <c r="B36" s="5">
-        <v>46080.77828773148</v>
+        <v>46080.61162106482</v>
       </c>
       <c r="C36" s="5">
-        <v>46114.76319241898</v>
+        <v>46114.59652575231</v>
       </c>
       <c r="D36" s="5">
-        <v>46114.76319354167</v>
+        <v>46114.596526875</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>135</v>
@@ -3519,13 +3519,13 @@
         <v>137</v>
       </c>
       <c r="B37" s="8">
-        <v>46080.77828799769</v>
+        <v>46080.611621331016</v>
       </c>
       <c r="C37" s="8">
-        <v>46114.76324759259</v>
+        <v>46114.59658092592</v>
       </c>
       <c r="D37" s="8">
-        <v>46114.763248877316</v>
+        <v>46114.59658221065</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>138</v>
@@ -3580,13 +3580,13 @@
         <v>140</v>
       </c>
       <c r="B38" s="5">
-        <v>46080.77828825232</v>
+        <v>46080.611621585645</v>
       </c>
       <c r="C38" s="5">
-        <v>46114.76325834491</v>
+        <v>46114.596591678244</v>
       </c>
       <c r="D38" s="5">
-        <v>46114.7632599537</v>
+        <v>46114.59659328704</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>141</v>
@@ -3641,13 +3641,13 @@
         <v>143</v>
       </c>
       <c r="B39" s="8">
-        <v>46080.778288518515</v>
+        <v>46080.61162185185</v>
       </c>
       <c r="C39" s="8">
-        <v>46121.86007915509</v>
+        <v>46121.69341248843</v>
       </c>
       <c r="D39" s="8">
-        <v>46149.197581886576</v>
+        <v>46149.030915219904</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>144</v>
@@ -3706,13 +3706,13 @@
         <v>148</v>
       </c>
       <c r="B40" s="5">
-        <v>46080.77828673611</v>
+        <v>46080.611620069445</v>
       </c>
       <c r="C40" s="5">
-        <v>46114.759847696754</v>
+        <v>46114.5931810301</v>
       </c>
       <c r="D40" s="5">
-        <v>46121.8600697338</v>
+        <v>46121.693403067125</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>149</v>
@@ -3767,13 +3767,13 @@
         <v>151</v>
       </c>
       <c r="B41" s="8">
-        <v>46080.77828702546</v>
+        <v>46080.611620358795</v>
       </c>
       <c r="C41" s="8">
-        <v>46121.860064803244</v>
+        <v>46121.69339813657</v>
       </c>
       <c r="D41" s="8">
-        <v>46121.86006597222</v>
+        <v>46121.69339930556</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>150</v>
@@ -3828,13 +3828,13 @@
         <v>153</v>
       </c>
       <c r="B42" s="5">
-        <v>46080.77828724537</v>
+        <v>46080.611620578704</v>
       </c>
       <c r="C42" s="5">
-        <v>46114.76051153935</v>
+        <v>46114.59384487268</v>
       </c>
       <c r="D42" s="5">
-        <v>46210.17465634259</v>
+        <v>46210.00798967593</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>154</v>
@@ -3893,13 +3893,13 @@
         <v>156</v>
       </c>
       <c r="B43" s="8">
-        <v>46080.77828748843</v>
+        <v>46080.61162082176</v>
       </c>
       <c r="C43" s="8">
-        <v>46114.76044965278</v>
+        <v>46114.59378298611</v>
       </c>
       <c r="D43" s="8">
-        <v>46114.76045094908</v>
+        <v>46114.593784282406</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>157</v>
@@ -3954,13 +3954,13 @@
         <v>159</v>
       </c>
       <c r="B44" s="5">
-        <v>46080.77828770834</v>
+        <v>46080.611621041666</v>
       </c>
       <c r="C44" s="5">
-        <v>46114.76049635417</v>
+        <v>46114.593829687496</v>
       </c>
       <c r="D44" s="5">
-        <v>46114.7604978125</v>
+        <v>46114.59383114583</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>160</v>
@@ -4015,13 +4015,13 @@
         <v>162</v>
       </c>
       <c r="B45" s="8">
-        <v>46080.778287939815</v>
+        <v>46080.61162127314</v>
       </c>
       <c r="C45" s="8">
-        <v>46140.83890416667</v>
+        <v>46140.672237499995</v>
       </c>
       <c r="D45" s="8">
-        <v>46141.772341724536</v>
+        <v>46141.60567505787</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>163</v>
@@ -4064,13 +4064,13 @@
         <v>165</v>
       </c>
       <c r="B46" s="5">
-        <v>46080.778288182875</v>
+        <v>46080.611621516204</v>
       </c>
       <c r="C46" s="5">
-        <v>46127.678079895835</v>
+        <v>46127.511413229164</v>
       </c>
       <c r="D46" s="5">
-        <v>46127.67810105324</v>
+        <v>46127.51143438657</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>166</v>
@@ -4129,13 +4129,13 @@
         <v>170</v>
       </c>
       <c r="B47" s="8">
-        <v>46080.77828842592</v>
+        <v>46080.611621759264</v>
       </c>
       <c r="C47" s="8">
-        <v>46127.67813141204</v>
+        <v>46127.511464745374</v>
       </c>
       <c r="D47" s="8">
-        <v>46158.16995894676</v>
+        <v>46158.00329228009</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>171</v>
@@ -4194,13 +4194,13 @@
         <v>176</v>
       </c>
       <c r="B48" s="5">
-        <v>46087.53644159722</v>
+        <v>46087.36977493056</v>
       </c>
       <c r="C48" s="5">
-        <v>46127.678180752315</v>
+        <v>46127.51151408565</v>
       </c>
       <c r="D48" s="5">
-        <v>46161.20788581019</v>
+        <v>46161.04121914352</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>177</v>
@@ -4257,13 +4257,13 @@
         <v>179</v>
       </c>
       <c r="B49" s="8">
-        <v>46087.536521331014</v>
+        <v>46087.36985466436</v>
       </c>
       <c r="C49" s="8">
-        <v>46140.83887265046</v>
+        <v>46140.67220598379</v>
       </c>
       <c r="D49" s="8">
-        <v>46141.771787060185</v>
+        <v>46141.60512039352</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>180</v>
@@ -4322,13 +4322,13 @@
         <v>183</v>
       </c>
       <c r="B50" s="5">
-        <v>46080.77828866898</v>
+        <v>46080.61162200231</v>
       </c>
       <c r="C50" s="5">
-        <v>46133.62051065972</v>
+        <v>46133.453843993055</v>
       </c>
       <c r="D50" s="5">
-        <v>46141.772585231476</v>
+        <v>46141.60591856482</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>184</v>
@@ -4371,13 +4371,13 @@
         <v>186</v>
       </c>
       <c r="B51" s="8">
-        <v>46080.77828892361</v>
+        <v>46080.61162225694</v>
       </c>
       <c r="C51" s="8">
-        <v>46133.6204378588</v>
+        <v>46133.45377119213</v>
       </c>
       <c r="D51" s="8">
-        <v>46151.18472762732</v>
+        <v>46151.01806096065</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>187</v>
@@ -4436,13 +4436,13 @@
         <v>191</v>
       </c>
       <c r="B52" s="5">
-        <v>46080.77828760417</v>
+        <v>46080.6116209375</v>
       </c>
       <c r="C52" s="5">
-        <v>46133.62049425926</v>
+        <v>46133.45382759259</v>
       </c>
       <c r="D52" s="5">
-        <v>46155.20414789351</v>
+        <v>46155.03748122686</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>192</v>
@@ -4501,13 +4501,13 @@
         <v>196</v>
       </c>
       <c r="B53" s="8">
-        <v>46080.778288009256</v>
+        <v>46080.61162134259</v>
       </c>
       <c r="C53" s="8">
-        <v>46132.76769947917</v>
+        <v>46132.6010328125</v>
       </c>
       <c r="D53" s="8">
-        <v>46141.77186175926</v>
+        <v>46141.60519509259</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>197</v>
@@ -4550,13 +4550,13 @@
         <v>199</v>
       </c>
       <c r="B54" s="5">
-        <v>46080.77828832176</v>
+        <v>46080.61162165509</v>
       </c>
       <c r="C54" s="5">
-        <v>46128.489822488424</v>
+        <v>46128.32315582176</v>
       </c>
       <c r="D54" s="5">
-        <v>46165.18131118055</v>
+        <v>46165.01464451389</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>200</v>
@@ -4615,13 +4615,13 @@
         <v>204</v>
       </c>
       <c r="B55" s="8">
-        <v>46080.77828861111</v>
+        <v>46080.611621944445</v>
       </c>
       <c r="C55" s="8">
-        <v>46128.48987719907</v>
+        <v>46128.323210532406</v>
       </c>
       <c r="D55" s="8">
-        <v>46170.185211909724</v>
+        <v>46170.01854524306</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>205</v>
@@ -4680,13 +4680,13 @@
         <v>208</v>
       </c>
       <c r="B56" s="5">
-        <v>46080.778288912035</v>
+        <v>46080.61162224537</v>
       </c>
       <c r="C56" s="5">
-        <v>46132.76768157407</v>
+        <v>46132.601014907406</v>
       </c>
       <c r="D56" s="5">
-        <v>46172.2027446875</v>
+        <v>46172.03607802083</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>209</v>
@@ -4745,13 +4745,13 @@
         <v>212</v>
       </c>
       <c r="B57" s="8">
-        <v>46080.77828921296</v>
+        <v>46080.6116225463</v>
       </c>
       <c r="C57" s="8">
-        <v>46141.711290810184</v>
+        <v>46141.54462414352</v>
       </c>
       <c r="D57" s="8">
-        <v>46141.77231675926</v>
+        <v>46141.60565009259</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>184</v>
@@ -4794,13 +4794,13 @@
         <v>214</v>
       </c>
       <c r="B58" s="5">
-        <v>46080.77828957176</v>
+        <v>46080.6116229051</v>
       </c>
       <c r="C58" s="5">
-        <v>46133.62103284722</v>
+        <v>46133.45436618055</v>
       </c>
       <c r="D58" s="5">
-        <v>46156.16908381945</v>
+        <v>46156.00241715278</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>215</v>
@@ -4859,13 +4859,13 @@
         <v>217</v>
       </c>
       <c r="B59" s="8">
-        <v>46080.77828986111</v>
+        <v>46080.61162319445</v>
       </c>
       <c r="C59" s="8">
-        <v>46133.621046631946</v>
+        <v>46133.454379965275</v>
       </c>
       <c r="D59" s="8">
-        <v>46210.17008761574</v>
+        <v>46210.00342094907</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>218</v>
@@ -4924,13 +4924,13 @@
         <v>220</v>
       </c>
       <c r="B60" s="5">
-        <v>46080.778290138885</v>
+        <v>46080.61162347222</v>
       </c>
       <c r="C60" s="5">
-        <v>46121.8679578125</v>
+        <v>46121.70129114583</v>
       </c>
       <c r="D60" s="5">
-        <v>46121.867985185185</v>
+        <v>46121.70131851852</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>221</v>
@@ -4989,13 +4989,13 @@
         <v>223</v>
       </c>
       <c r="B61" s="8">
-        <v>46080.778290393515</v>
+        <v>46080.61162372685</v>
       </c>
       <c r="C61" s="8">
-        <v>46121.86789461806</v>
+        <v>46121.70122795139</v>
       </c>
       <c r="D61" s="8">
-        <v>46204.20245239583</v>
+        <v>46204.03578572917</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>224</v>
@@ -5054,13 +5054,13 @@
         <v>226</v>
       </c>
       <c r="B62" s="5">
-        <v>46080.7854796875</v>
+        <v>46080.61881302083</v>
       </c>
       <c r="C62" s="5">
-        <v>46141.772219398146</v>
+        <v>46141.60555273148</v>
       </c>
       <c r="D62" s="5">
-        <v>46203.19232511574</v>
+        <v>46203.02565844907</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>54</v>
@@ -5119,13 +5119,13 @@
         <v>228</v>
       </c>
       <c r="B63" s="8">
-        <v>46080.77828662037</v>
+        <v>46080.61161995371</v>
       </c>
       <c r="C63" s="8">
-        <v>46141.711275752314</v>
+        <v>46141.54460908565</v>
       </c>
       <c r="D63" s="8">
-        <v>46141.71127789352</v>
+        <v>46141.544611226855</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>229</v>
@@ -5168,13 +5168,13 @@
         <v>231</v>
       </c>
       <c r="B64" s="5">
-        <v>46080.77828694445</v>
+        <v>46080.61162027778</v>
       </c>
       <c r="C64" s="5">
-        <v>46133.62079252314</v>
+        <v>46133.454125856486</v>
       </c>
       <c r="D64" s="5">
-        <v>46192.18706700232</v>
+        <v>46192.02040033565</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>232</v>
@@ -5233,13 +5233,13 @@
         <v>234</v>
       </c>
       <c r="B65" s="8">
-        <v>46080.778287187495</v>
+        <v>46080.61162052084</v>
       </c>
       <c r="C65" s="8">
-        <v>46133.620870451385</v>
+        <v>46133.45420378472</v>
       </c>
       <c r="D65" s="8">
-        <v>46133.62091327546</v>
+        <v>46133.454246608795</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>235</v>
@@ -5298,13 +5298,13 @@
         <v>238</v>
       </c>
       <c r="B66" s="5">
-        <v>46080.77828746528</v>
+        <v>46080.61162079861</v>
       </c>
       <c r="C66" s="5">
-        <v>46133.62178611111</v>
+        <v>46133.45511944444</v>
       </c>
       <c r="D66" s="5">
-        <v>46133.62180199074</v>
+        <v>46133.455135324075</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>239</v>
@@ -5363,13 +5363,13 @@
         <v>241</v>
       </c>
       <c r="B67" s="8">
-        <v>46080.77828770834</v>
+        <v>46080.611621041666</v>
       </c>
       <c r="C67" s="8">
-        <v>46133.62179804398</v>
+        <v>46133.45513137731</v>
       </c>
       <c r="D67" s="8">
-        <v>46133.62181490741</v>
+        <v>46133.45514824074</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>242</v>
@@ -5428,13 +5428,13 @@
         <v>244</v>
       </c>
       <c r="B68" s="5">
-        <v>46080.77828796297</v>
+        <v>46080.611621296295</v>
       </c>
       <c r="C68" s="5">
-        <v>46133.62181768518</v>
+        <v>46133.45515101852</v>
       </c>
       <c r="D68" s="5">
-        <v>46206.19700435185</v>
+        <v>46206.03033768518</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>245</v>
@@ -5493,13 +5493,13 @@
         <v>247</v>
       </c>
       <c r="B69" s="8">
-        <v>46080.778288217596</v>
+        <v>46080.611621550925</v>
       </c>
       <c r="C69" s="8">
-        <v>46133.621873553246</v>
+        <v>46133.455206886574</v>
       </c>
       <c r="D69" s="8">
-        <v>46133.621889710645</v>
+        <v>46133.45522304398</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>181</v>
@@ -5558,13 +5558,13 @@
         <v>250</v>
       </c>
       <c r="B70" s="5">
-        <v>46080.77828846065</v>
+        <v>46080.611621793985</v>
       </c>
       <c r="C70" s="5">
-        <v>46140.8390024074</v>
+        <v>46140.67233574074</v>
       </c>
       <c r="D70" s="5">
-        <v>46141.711773055555</v>
+        <v>46141.54510638889</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>182</v>
@@ -5623,13 +5623,13 @@
         <v>252</v>
       </c>
       <c r="B71" s="8">
-        <v>46080.7782887037</v>
+        <v>46080.61162203704</v>
       </c>
       <c r="C71" s="8">
-        <v>46141.71205135417</v>
+        <v>46141.5453846875</v>
       </c>
       <c r="D71" s="8">
-        <v>46141.712052731484</v>
+        <v>46141.54538606481</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>253</v>
@@ -5672,13 +5672,13 @@
         <v>255</v>
       </c>
       <c r="B72" s="5">
-        <v>46080.77828895833</v>
+        <v>46080.61162229167</v>
       </c>
       <c r="C72" s="5">
-        <v>46140.83904666667</v>
+        <v>46140.67238</v>
       </c>
       <c r="D72" s="5">
-        <v>46141.711805625004</v>
+        <v>46141.54513895833</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>256</v>
@@ -5737,13 +5737,13 @@
         <v>260</v>
       </c>
       <c r="B73" s="8">
-        <v>46080.778287152774</v>
+        <v>46080.61162048611</v>
       </c>
       <c r="C73" s="8">
-        <v>46141.711726180554</v>
+        <v>46141.54505951389</v>
       </c>
       <c r="D73" s="8">
-        <v>46141.7118290162</v>
+        <v>46141.54516234953</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>261</v>
@@ -5802,13 +5802,13 @@
         <v>264</v>
       </c>
       <c r="B74" s="5">
-        <v>46080.77828751157</v>
+        <v>46080.61162084491</v>
       </c>
       <c r="C74" s="5">
-        <v>46141.7119153588</v>
+        <v>46141.54524869213</v>
       </c>
       <c r="D74" s="5">
-        <v>46141.711917002314</v>
+        <v>46141.54525033565</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>265</v>
@@ -5867,13 +5867,13 @@
         <v>267</v>
       </c>
       <c r="B75" s="8">
-        <v>46080.77828782407</v>
+        <v>46080.61162115741</v>
       </c>
       <c r="C75" s="8">
-        <v>46141.71196090278</v>
+        <v>46141.545294236115</v>
       </c>
       <c r="D75" s="8">
-        <v>46141.71196212963</v>
+        <v>46141.54529546296</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>268</v>
@@ -5932,11 +5932,11 @@
         <v>270</v>
       </c>
       <c r="B76" s="5">
-        <v>46080.77828809028</v>
+        <v>46080.61162142361</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46090.61092975695</v>
+        <v>46090.44426309028</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>271</v>
@@ -5979,11 +5979,11 @@
         <v>273</v>
       </c>
       <c r="B77" s="8">
-        <v>46080.77828868055</v>
+        <v>46080.611622013894</v>
       </c>
       <c r="C77" s="9"/>
       <c r="D77" s="8">
-        <v>46141.711969386575</v>
+        <v>46141.54530271991</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>72</v>
@@ -6042,11 +6042,11 @@
         <v>277</v>
       </c>
       <c r="B78" s="5">
-        <v>46080.77828835648</v>
+        <v>46080.611621689815</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46141.711970648146</v>
+        <v>46141.54530398148</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>278</v>
@@ -6105,11 +6105,11 @@
         <v>279</v>
       </c>
       <c r="B79" s="8">
-        <v>46090.61171577546</v>
+        <v>46090.44504910879</v>
       </c>
       <c r="C79" s="9"/>
       <c r="D79" s="8">
-        <v>46090.614530335646</v>
+        <v>46090.44786366898</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>280</v>
@@ -6158,11 +6158,11 @@
         <v>282</v>
       </c>
       <c r="B80" s="5">
-        <v>46090.61199928241</v>
+        <v>46090.44533261574</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46141.711971944445</v>
+        <v>46141.545305277774</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>283</v>
@@ -6221,11 +6221,11 @@
         <v>285</v>
       </c>
       <c r="B81" s="8">
-        <v>46090.61208010417</v>
+        <v>46090.4454134375</v>
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="8">
-        <v>46090.61869820602</v>
+        <v>46090.45203153935</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>286</v>

--- a/data/50001524 - ATACAMA KOZAN.xlsx
+++ b/data/50001524 - ATACAMA KOZAN.xlsx
@@ -1498,13 +1498,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46080.61161974537</v>
+        <v>46080.77828641204</v>
       </c>
       <c r="C4" s="5">
-        <v>46097.66998934028</v>
+        <v>46097.83665600694</v>
       </c>
       <c r="D4" s="5">
-        <v>46097.67008267361</v>
+        <v>46097.83674934028</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1547,13 +1547,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46080.611620138894</v>
+        <v>46080.77828680555</v>
       </c>
       <c r="C5" s="8">
-        <v>46097.669548425925</v>
+        <v>46097.8362150926</v>
       </c>
       <c r="D5" s="8">
-        <v>46097.66956912037</v>
+        <v>46097.836235787036</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1610,13 +1610,13 @@
         <v>33</v>
       </c>
       <c r="B6" s="5">
-        <v>46080.61162043981</v>
+        <v>46080.778287106485</v>
       </c>
       <c r="C6" s="5">
-        <v>46097.66955386574</v>
+        <v>46097.83622053241</v>
       </c>
       <c r="D6" s="5">
-        <v>46097.66956886574</v>
+        <v>46097.836235532406</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>34</v>
@@ -1673,13 +1673,13 @@
         <v>37</v>
       </c>
       <c r="B7" s="8">
-        <v>46080.61162074074</v>
+        <v>46080.778287407404</v>
       </c>
       <c r="C7" s="8">
-        <v>46097.66956028935</v>
+        <v>46097.83622695602</v>
       </c>
       <c r="D7" s="8">
-        <v>46097.669575266205</v>
+        <v>46097.83624193287</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>38</v>
@@ -1736,13 +1736,13 @@
         <v>39</v>
       </c>
       <c r="B8" s="5">
-        <v>46080.61162106482</v>
+        <v>46080.77828773148</v>
       </c>
       <c r="C8" s="5">
-        <v>46093.47637546297</v>
+        <v>46093.643042129625</v>
       </c>
       <c r="D8" s="5">
-        <v>46100.62501127315</v>
+        <v>46100.791677939815</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>40</v>
@@ -1799,13 +1799,13 @@
         <v>42</v>
       </c>
       <c r="B9" s="8">
-        <v>46080.61162134259</v>
+        <v>46080.778288009256</v>
       </c>
       <c r="C9" s="8">
-        <v>46097.66957738426</v>
+        <v>46097.83624405092</v>
       </c>
       <c r="D9" s="8">
-        <v>46097.669591805556</v>
+        <v>46097.83625847222</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>43</v>
@@ -1862,13 +1862,13 @@
         <v>44</v>
       </c>
       <c r="B10" s="5">
-        <v>46080.61691350694</v>
+        <v>46080.78358017361</v>
       </c>
       <c r="C10" s="5">
-        <v>46141.54493447917</v>
+        <v>46141.711601145835</v>
       </c>
       <c r="D10" s="5">
-        <v>46141.54493556713</v>
+        <v>46141.7116022338</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>45</v>
@@ -1911,13 +1911,13 @@
         <v>47</v>
       </c>
       <c r="B11" s="8">
-        <v>46080.617096863425</v>
+        <v>46080.7837635301</v>
       </c>
       <c r="C11" s="8">
-        <v>46114.345154421295</v>
+        <v>46114.51182108796</v>
       </c>
       <c r="D11" s="8">
-        <v>46114.34517267361</v>
+        <v>46114.51183934028</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>48</v>
@@ -1976,13 +1976,13 @@
         <v>52</v>
       </c>
       <c r="B12" s="5">
-        <v>46080.61714857639</v>
+        <v>46080.783815243056</v>
       </c>
       <c r="C12" s="5">
-        <v>46141.54484769676</v>
+        <v>46141.71151436343</v>
       </c>
       <c r="D12" s="5">
-        <v>46205.01245163195</v>
+        <v>46205.17911829861</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>53</v>
@@ -2041,13 +2041,13 @@
         <v>57</v>
       </c>
       <c r="B13" s="8">
-        <v>46080.61162163195</v>
+        <v>46080.77828829861</v>
       </c>
       <c r="C13" s="8">
-        <v>46114.34593138889</v>
+        <v>46114.51259805556</v>
       </c>
       <c r="D13" s="8">
-        <v>46114.59239144676</v>
+        <v>46114.75905811343</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>58</v>
@@ -2092,13 +2092,13 @@
         <v>60</v>
       </c>
       <c r="B14" s="5">
-        <v>46080.6116219213</v>
+        <v>46080.778288587964</v>
       </c>
       <c r="C14" s="5">
-        <v>46114.34528306713</v>
+        <v>46114.511949733795</v>
       </c>
       <c r="D14" s="5">
-        <v>46114.34529875</v>
+        <v>46114.51196541666</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>61</v>
@@ -2157,13 +2157,13 @@
         <v>63</v>
       </c>
       <c r="B15" s="8">
-        <v>46080.61162287037</v>
+        <v>46080.77828953703</v>
       </c>
       <c r="C15" s="8">
-        <v>46114.34543883102</v>
+        <v>46114.512105497684</v>
       </c>
       <c r="D15" s="8">
-        <v>46114.345454849536</v>
+        <v>46114.51212151621</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>64</v>
@@ -2222,13 +2222,13 @@
         <v>66</v>
       </c>
       <c r="B16" s="5">
-        <v>46080.61161952546</v>
+        <v>46080.77828619213</v>
       </c>
       <c r="C16" s="5">
-        <v>46114.345740000004</v>
+        <v>46114.51240666666</v>
       </c>
       <c r="D16" s="5">
-        <v>46114.34575462963</v>
+        <v>46114.5124212963</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>67</v>
@@ -2287,13 +2287,13 @@
         <v>69</v>
       </c>
       <c r="B17" s="8">
-        <v>46080.61161986111</v>
+        <v>46080.77828652778</v>
       </c>
       <c r="C17" s="8">
-        <v>46114.34591538194</v>
+        <v>46114.512582048614</v>
       </c>
       <c r="D17" s="8">
-        <v>46114.34593252315</v>
+        <v>46114.51259918981</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>70</v>
@@ -2352,13 +2352,13 @@
         <v>73</v>
       </c>
       <c r="B18" s="5">
-        <v>46080.611620208336</v>
+        <v>46080.778286875</v>
       </c>
       <c r="C18" s="5">
-        <v>46126.68891861111</v>
+        <v>46126.85558527778</v>
       </c>
       <c r="D18" s="5">
-        <v>46126.6889318287</v>
+        <v>46126.85559849537</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>74</v>
@@ -2405,13 +2405,13 @@
         <v>76</v>
       </c>
       <c r="B19" s="8">
-        <v>46080.61162048611</v>
+        <v>46080.778287152774</v>
       </c>
       <c r="C19" s="8">
-        <v>46114.345347615745</v>
+        <v>46114.51201428241</v>
       </c>
       <c r="D19" s="8">
-        <v>46114.345363518514</v>
+        <v>46114.512030185186</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>77</v>
@@ -2470,13 +2470,13 @@
         <v>79</v>
       </c>
       <c r="B20" s="5">
-        <v>46080.61162085648</v>
+        <v>46080.77828752315</v>
       </c>
       <c r="C20" s="5">
-        <v>46114.34608914352</v>
+        <v>46114.51275581018</v>
       </c>
       <c r="D20" s="5">
-        <v>46114.34610408565</v>
+        <v>46114.51277075231</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>80</v>
@@ -2535,13 +2535,13 @@
         <v>82</v>
       </c>
       <c r="B21" s="8">
-        <v>46080.61162113426</v>
+        <v>46080.77828780093</v>
       </c>
       <c r="C21" s="8">
-        <v>46126.68889943287</v>
+        <v>46126.85556609953</v>
       </c>
       <c r="D21" s="8">
-        <v>46126.6889155324</v>
+        <v>46126.855582199074</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>83</v>
@@ -2600,13 +2600,13 @@
         <v>86</v>
       </c>
       <c r="B22" s="5">
-        <v>46080.61739265046</v>
+        <v>46080.78405931713</v>
       </c>
       <c r="C22" s="5">
-        <v>46114.34641268519</v>
+        <v>46114.51307935185</v>
       </c>
       <c r="D22" s="5">
-        <v>46114.34642909722</v>
+        <v>46114.51309576389</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>87</v>
@@ -2665,13 +2665,13 @@
         <v>89</v>
       </c>
       <c r="B23" s="8">
-        <v>46080.61162144676</v>
+        <v>46080.778288113426</v>
       </c>
       <c r="C23" s="8">
-        <v>46114.34650914352</v>
+        <v>46114.513175810185</v>
       </c>
       <c r="D23" s="8">
-        <v>46114.34660958333</v>
+        <v>46114.51327625</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>90</v>
@@ -2730,13 +2730,13 @@
         <v>92</v>
       </c>
       <c r="B24" s="5">
-        <v>46080.61162173611</v>
+        <v>46080.77828840278</v>
       </c>
       <c r="C24" s="5">
-        <v>46114.593050069445</v>
+        <v>46114.75971673611</v>
       </c>
       <c r="D24" s="5">
-        <v>46114.593065532405</v>
+        <v>46114.759732199076</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>93</v>
@@ -2795,13 +2795,13 @@
         <v>97</v>
       </c>
       <c r="B25" s="8">
-        <v>46080.61162202546</v>
+        <v>46080.778288692134</v>
       </c>
       <c r="C25" s="8">
-        <v>46140.67228493055</v>
+        <v>46140.83895159722</v>
       </c>
       <c r="D25" s="8">
-        <v>46140.67228600694</v>
+        <v>46140.838952673614</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>98</v>
@@ -2844,13 +2844,13 @@
         <v>100</v>
       </c>
       <c r="B26" s="5">
-        <v>46080.61162231481</v>
+        <v>46080.778288981484</v>
       </c>
       <c r="C26" s="5">
-        <v>46139.61452841436</v>
+        <v>46139.781195081014</v>
       </c>
       <c r="D26" s="5">
-        <v>46206.03033821759</v>
+        <v>46206.19700488426</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>101</v>
@@ -2909,13 +2909,13 @@
         <v>106</v>
       </c>
       <c r="B27" s="8">
-        <v>46080.611619351854</v>
+        <v>46080.77828601852</v>
       </c>
       <c r="C27" s="8">
-        <v>46139.61441649306</v>
+        <v>46139.78108315972</v>
       </c>
       <c r="D27" s="8">
-        <v>46139.61441783565</v>
+        <v>46139.78108450232</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>107</v>
@@ -2970,13 +2970,13 @@
         <v>111</v>
       </c>
       <c r="B28" s="5">
-        <v>46080.61161972222</v>
+        <v>46080.778286388886</v>
       </c>
       <c r="C28" s="5">
-        <v>46139.6145152199</v>
+        <v>46139.781181886574</v>
       </c>
       <c r="D28" s="5">
-        <v>46139.61451663195</v>
+        <v>46139.78118329861</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>112</v>
@@ -3031,13 +3031,13 @@
         <v>113</v>
       </c>
       <c r="B29" s="8">
-        <v>46080.617547939815</v>
+        <v>46080.78421460648</v>
       </c>
       <c r="C29" s="8">
-        <v>46140.64236803241</v>
+        <v>46140.80903469908</v>
       </c>
       <c r="D29" s="8">
-        <v>46199.0408809375</v>
+        <v>46199.207547604165</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>114</v>
@@ -3096,13 +3096,13 @@
         <v>116</v>
       </c>
       <c r="B30" s="5">
-        <v>46080.61797731482</v>
+        <v>46080.78464398148</v>
       </c>
       <c r="C30" s="5">
-        <v>46114.59513332176</v>
+        <v>46114.761799988424</v>
       </c>
       <c r="D30" s="5">
-        <v>46114.595134641204</v>
+        <v>46114.761801307875</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>117</v>
@@ -3151,13 +3151,13 @@
         <v>119</v>
       </c>
       <c r="B31" s="8">
-        <v>46080.61805363426</v>
+        <v>46080.78472030093</v>
       </c>
       <c r="C31" s="8">
-        <v>46140.64228364584</v>
+        <v>46140.8089503125</v>
       </c>
       <c r="D31" s="8">
-        <v>46140.642285671296</v>
+        <v>46140.80895233796</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>120</v>
@@ -3206,13 +3206,13 @@
         <v>122</v>
       </c>
       <c r="B32" s="5">
-        <v>46080.61161998843</v>
+        <v>46080.77828665509</v>
       </c>
       <c r="C32" s="5">
-        <v>46133.45426238426</v>
+        <v>46133.62092905093</v>
       </c>
       <c r="D32" s="5">
-        <v>46154.02539614584</v>
+        <v>46154.1920628125</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>123</v>
@@ -3271,13 +3271,13 @@
         <v>125</v>
       </c>
       <c r="B33" s="8">
-        <v>46080.611620254625</v>
+        <v>46080.7782869213</v>
       </c>
       <c r="C33" s="8">
-        <v>46133.45419553241</v>
+        <v>46133.62086219907</v>
       </c>
       <c r="D33" s="8">
-        <v>46133.454196597224</v>
+        <v>46133.62086326389</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>126</v>
@@ -3332,13 +3332,13 @@
         <v>128</v>
       </c>
       <c r="B34" s="5">
-        <v>46080.61162052084</v>
+        <v>46080.778287187495</v>
       </c>
       <c r="C34" s="5">
-        <v>46133.45423341435</v>
+        <v>46133.62090008102</v>
       </c>
       <c r="D34" s="5">
-        <v>46133.45423459491</v>
+        <v>46133.62090126157</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>129</v>
@@ -3393,13 +3393,13 @@
         <v>131</v>
       </c>
       <c r="B35" s="8">
-        <v>46080.61162079861</v>
+        <v>46080.77828746528</v>
       </c>
       <c r="C35" s="8">
-        <v>46114.59660967592</v>
+        <v>46114.76327634259</v>
       </c>
       <c r="D35" s="8">
-        <v>46114.59662506945</v>
+        <v>46114.76329173611</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>132</v>
@@ -3458,13 +3458,13 @@
         <v>134</v>
       </c>
       <c r="B36" s="5">
-        <v>46080.61162106482</v>
+        <v>46080.77828773148</v>
       </c>
       <c r="C36" s="5">
-        <v>46114.59652575231</v>
+        <v>46114.76319241898</v>
       </c>
       <c r="D36" s="5">
-        <v>46114.596526875</v>
+        <v>46114.76319354167</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>135</v>
@@ -3519,13 +3519,13 @@
         <v>137</v>
       </c>
       <c r="B37" s="8">
-        <v>46080.611621331016</v>
+        <v>46080.77828799769</v>
       </c>
       <c r="C37" s="8">
-        <v>46114.59658092592</v>
+        <v>46114.76324759259</v>
       </c>
       <c r="D37" s="8">
-        <v>46114.59658221065</v>
+        <v>46114.763248877316</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>138</v>
@@ -3580,13 +3580,13 @@
         <v>140</v>
       </c>
       <c r="B38" s="5">
-        <v>46080.611621585645</v>
+        <v>46080.77828825232</v>
       </c>
       <c r="C38" s="5">
-        <v>46114.596591678244</v>
+        <v>46114.76325834491</v>
       </c>
       <c r="D38" s="5">
-        <v>46114.59659328704</v>
+        <v>46114.7632599537</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>141</v>
@@ -3641,13 +3641,13 @@
         <v>143</v>
       </c>
       <c r="B39" s="8">
-        <v>46080.61162185185</v>
+        <v>46080.778288518515</v>
       </c>
       <c r="C39" s="8">
-        <v>46121.69341248843</v>
+        <v>46121.86007915509</v>
       </c>
       <c r="D39" s="8">
-        <v>46149.030915219904</v>
+        <v>46149.197581886576</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>144</v>
@@ -3706,13 +3706,13 @@
         <v>148</v>
       </c>
       <c r="B40" s="5">
-        <v>46080.611620069445</v>
+        <v>46080.77828673611</v>
       </c>
       <c r="C40" s="5">
-        <v>46114.5931810301</v>
+        <v>46114.759847696754</v>
       </c>
       <c r="D40" s="5">
-        <v>46121.693403067125</v>
+        <v>46121.8600697338</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>149</v>
@@ -3767,13 +3767,13 @@
         <v>151</v>
       </c>
       <c r="B41" s="8">
-        <v>46080.611620358795</v>
+        <v>46080.77828702546</v>
       </c>
       <c r="C41" s="8">
-        <v>46121.69339813657</v>
+        <v>46121.860064803244</v>
       </c>
       <c r="D41" s="8">
-        <v>46121.69339930556</v>
+        <v>46121.86006597222</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>150</v>
@@ -3828,13 +3828,13 @@
         <v>153</v>
       </c>
       <c r="B42" s="5">
-        <v>46080.611620578704</v>
+        <v>46080.77828724537</v>
       </c>
       <c r="C42" s="5">
-        <v>46114.59384487268</v>
+        <v>46114.76051153935</v>
       </c>
       <c r="D42" s="5">
-        <v>46210.00798967593</v>
+        <v>46210.17465634259</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>154</v>
@@ -3893,13 +3893,13 @@
         <v>156</v>
       </c>
       <c r="B43" s="8">
-        <v>46080.61162082176</v>
+        <v>46080.77828748843</v>
       </c>
       <c r="C43" s="8">
-        <v>46114.59378298611</v>
+        <v>46114.76044965278</v>
       </c>
       <c r="D43" s="8">
-        <v>46114.593784282406</v>
+        <v>46114.76045094908</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>157</v>
@@ -3954,13 +3954,13 @@
         <v>159</v>
       </c>
       <c r="B44" s="5">
-        <v>46080.611621041666</v>
+        <v>46080.77828770834</v>
       </c>
       <c r="C44" s="5">
-        <v>46114.593829687496</v>
+        <v>46114.76049635417</v>
       </c>
       <c r="D44" s="5">
-        <v>46114.59383114583</v>
+        <v>46114.7604978125</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>160</v>
@@ -4015,13 +4015,13 @@
         <v>162</v>
       </c>
       <c r="B45" s="8">
-        <v>46080.61162127314</v>
+        <v>46080.778287939815</v>
       </c>
       <c r="C45" s="8">
-        <v>46140.672237499995</v>
+        <v>46140.83890416667</v>
       </c>
       <c r="D45" s="8">
-        <v>46141.60567505787</v>
+        <v>46141.772341724536</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>163</v>
@@ -4064,13 +4064,13 @@
         <v>165</v>
       </c>
       <c r="B46" s="5">
-        <v>46080.611621516204</v>
+        <v>46080.778288182875</v>
       </c>
       <c r="C46" s="5">
-        <v>46127.511413229164</v>
+        <v>46127.678079895835</v>
       </c>
       <c r="D46" s="5">
-        <v>46127.51143438657</v>
+        <v>46127.67810105324</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>166</v>
@@ -4129,13 +4129,13 @@
         <v>170</v>
       </c>
       <c r="B47" s="8">
-        <v>46080.611621759264</v>
+        <v>46080.77828842592</v>
       </c>
       <c r="C47" s="8">
-        <v>46127.511464745374</v>
+        <v>46127.67813141204</v>
       </c>
       <c r="D47" s="8">
-        <v>46158.00329228009</v>
+        <v>46158.16995894676</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>171</v>
@@ -4194,13 +4194,13 @@
         <v>176</v>
       </c>
       <c r="B48" s="5">
-        <v>46087.36977493056</v>
+        <v>46087.53644159722</v>
       </c>
       <c r="C48" s="5">
-        <v>46127.51151408565</v>
+        <v>46127.678180752315</v>
       </c>
       <c r="D48" s="5">
-        <v>46161.04121914352</v>
+        <v>46161.20788581019</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>177</v>
@@ -4257,13 +4257,13 @@
         <v>179</v>
       </c>
       <c r="B49" s="8">
-        <v>46087.36985466436</v>
+        <v>46087.536521331014</v>
       </c>
       <c r="C49" s="8">
-        <v>46140.67220598379</v>
+        <v>46140.83887265046</v>
       </c>
       <c r="D49" s="8">
-        <v>46141.60512039352</v>
+        <v>46141.771787060185</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>180</v>
@@ -4322,13 +4322,13 @@
         <v>183</v>
       </c>
       <c r="B50" s="5">
-        <v>46080.61162200231</v>
+        <v>46080.77828866898</v>
       </c>
       <c r="C50" s="5">
-        <v>46133.453843993055</v>
+        <v>46133.62051065972</v>
       </c>
       <c r="D50" s="5">
-        <v>46141.60591856482</v>
+        <v>46141.772585231476</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>184</v>
@@ -4371,13 +4371,13 @@
         <v>186</v>
       </c>
       <c r="B51" s="8">
-        <v>46080.61162225694</v>
+        <v>46080.77828892361</v>
       </c>
       <c r="C51" s="8">
-        <v>46133.45377119213</v>
+        <v>46133.6204378588</v>
       </c>
       <c r="D51" s="8">
-        <v>46151.01806096065</v>
+        <v>46151.18472762732</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>187</v>
@@ -4436,13 +4436,13 @@
         <v>191</v>
       </c>
       <c r="B52" s="5">
-        <v>46080.6116209375</v>
+        <v>46080.77828760417</v>
       </c>
       <c r="C52" s="5">
-        <v>46133.45382759259</v>
+        <v>46133.62049425926</v>
       </c>
       <c r="D52" s="5">
-        <v>46155.03748122686</v>
+        <v>46155.20414789351</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>192</v>
@@ -4501,13 +4501,13 @@
         <v>196</v>
       </c>
       <c r="B53" s="8">
-        <v>46080.61162134259</v>
+        <v>46080.778288009256</v>
       </c>
       <c r="C53" s="8">
-        <v>46132.6010328125</v>
+        <v>46132.76769947917</v>
       </c>
       <c r="D53" s="8">
-        <v>46141.60519509259</v>
+        <v>46141.77186175926</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>197</v>
@@ -4550,13 +4550,13 @@
         <v>199</v>
       </c>
       <c r="B54" s="5">
-        <v>46080.61162165509</v>
+        <v>46080.77828832176</v>
       </c>
       <c r="C54" s="5">
-        <v>46128.32315582176</v>
+        <v>46128.489822488424</v>
       </c>
       <c r="D54" s="5">
-        <v>46165.01464451389</v>
+        <v>46165.18131118055</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>200</v>
@@ -4615,13 +4615,13 @@
         <v>204</v>
       </c>
       <c r="B55" s="8">
-        <v>46080.611621944445</v>
+        <v>46080.77828861111</v>
       </c>
       <c r="C55" s="8">
-        <v>46128.323210532406</v>
+        <v>46128.48987719907</v>
       </c>
       <c r="D55" s="8">
-        <v>46170.01854524306</v>
+        <v>46170.185211909724</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>205</v>
@@ -4680,13 +4680,13 @@
         <v>208</v>
       </c>
       <c r="B56" s="5">
-        <v>46080.61162224537</v>
+        <v>46080.778288912035</v>
       </c>
       <c r="C56" s="5">
-        <v>46132.601014907406</v>
+        <v>46132.76768157407</v>
       </c>
       <c r="D56" s="5">
-        <v>46172.03607802083</v>
+        <v>46172.2027446875</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>209</v>
@@ -4745,13 +4745,13 @@
         <v>212</v>
       </c>
       <c r="B57" s="8">
-        <v>46080.6116225463</v>
+        <v>46080.77828921296</v>
       </c>
       <c r="C57" s="8">
-        <v>46141.54462414352</v>
+        <v>46141.711290810184</v>
       </c>
       <c r="D57" s="8">
-        <v>46141.60565009259</v>
+        <v>46141.77231675926</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>184</v>
@@ -4794,13 +4794,13 @@
         <v>214</v>
       </c>
       <c r="B58" s="5">
-        <v>46080.6116229051</v>
+        <v>46080.77828957176</v>
       </c>
       <c r="C58" s="5">
-        <v>46133.45436618055</v>
+        <v>46133.62103284722</v>
       </c>
       <c r="D58" s="5">
-        <v>46156.00241715278</v>
+        <v>46156.16908381945</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>215</v>
@@ -4859,13 +4859,13 @@
         <v>217</v>
       </c>
       <c r="B59" s="8">
-        <v>46080.61162319445</v>
+        <v>46080.77828986111</v>
       </c>
       <c r="C59" s="8">
-        <v>46133.454379965275</v>
+        <v>46133.621046631946</v>
       </c>
       <c r="D59" s="8">
-        <v>46210.00342094907</v>
+        <v>46210.17008761574</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>218</v>
@@ -4924,13 +4924,13 @@
         <v>220</v>
       </c>
       <c r="B60" s="5">
-        <v>46080.61162347222</v>
+        <v>46080.778290138885</v>
       </c>
       <c r="C60" s="5">
-        <v>46121.70129114583</v>
+        <v>46121.8679578125</v>
       </c>
       <c r="D60" s="5">
-        <v>46121.70131851852</v>
+        <v>46121.867985185185</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>221</v>
@@ -4989,13 +4989,13 @@
         <v>223</v>
       </c>
       <c r="B61" s="8">
-        <v>46080.61162372685</v>
+        <v>46080.778290393515</v>
       </c>
       <c r="C61" s="8">
-        <v>46121.70122795139</v>
+        <v>46121.86789461806</v>
       </c>
       <c r="D61" s="8">
-        <v>46204.03578572917</v>
+        <v>46204.20245239583</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>224</v>
@@ -5054,13 +5054,13 @@
         <v>226</v>
       </c>
       <c r="B62" s="5">
-        <v>46080.61881302083</v>
+        <v>46080.7854796875</v>
       </c>
       <c r="C62" s="5">
-        <v>46141.60555273148</v>
+        <v>46141.772219398146</v>
       </c>
       <c r="D62" s="5">
-        <v>46203.02565844907</v>
+        <v>46203.19232511574</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>54</v>
@@ -5119,13 +5119,13 @@
         <v>228</v>
       </c>
       <c r="B63" s="8">
-        <v>46080.61161995371</v>
+        <v>46080.77828662037</v>
       </c>
       <c r="C63" s="8">
-        <v>46141.54460908565</v>
+        <v>46141.711275752314</v>
       </c>
       <c r="D63" s="8">
-        <v>46141.544611226855</v>
+        <v>46141.71127789352</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>229</v>
@@ -5168,13 +5168,13 @@
         <v>231</v>
       </c>
       <c r="B64" s="5">
-        <v>46080.61162027778</v>
+        <v>46080.77828694445</v>
       </c>
       <c r="C64" s="5">
-        <v>46133.454125856486</v>
+        <v>46133.62079252314</v>
       </c>
       <c r="D64" s="5">
-        <v>46192.02040033565</v>
+        <v>46192.18706700232</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>232</v>
@@ -5233,13 +5233,13 @@
         <v>234</v>
       </c>
       <c r="B65" s="8">
-        <v>46080.61162052084</v>
+        <v>46080.778287187495</v>
       </c>
       <c r="C65" s="8">
-        <v>46133.45420378472</v>
+        <v>46133.620870451385</v>
       </c>
       <c r="D65" s="8">
-        <v>46133.454246608795</v>
+        <v>46133.62091327546</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>235</v>
@@ -5298,13 +5298,13 @@
         <v>238</v>
       </c>
       <c r="B66" s="5">
-        <v>46080.61162079861</v>
+        <v>46080.77828746528</v>
       </c>
       <c r="C66" s="5">
-        <v>46133.45511944444</v>
+        <v>46133.62178611111</v>
       </c>
       <c r="D66" s="5">
-        <v>46133.455135324075</v>
+        <v>46133.62180199074</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>239</v>
@@ -5363,13 +5363,13 @@
         <v>241</v>
       </c>
       <c r="B67" s="8">
-        <v>46080.611621041666</v>
+        <v>46080.77828770834</v>
       </c>
       <c r="C67" s="8">
-        <v>46133.45513137731</v>
+        <v>46133.62179804398</v>
       </c>
       <c r="D67" s="8">
-        <v>46133.45514824074</v>
+        <v>46133.62181490741</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>242</v>
@@ -5428,13 +5428,13 @@
         <v>244</v>
       </c>
       <c r="B68" s="5">
-        <v>46080.611621296295</v>
+        <v>46080.77828796297</v>
       </c>
       <c r="C68" s="5">
-        <v>46133.45515101852</v>
+        <v>46133.62181768518</v>
       </c>
       <c r="D68" s="5">
-        <v>46206.03033768518</v>
+        <v>46206.19700435185</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>245</v>
@@ -5493,13 +5493,13 @@
         <v>247</v>
       </c>
       <c r="B69" s="8">
-        <v>46080.611621550925</v>
+        <v>46080.778288217596</v>
       </c>
       <c r="C69" s="8">
-        <v>46133.455206886574</v>
+        <v>46133.621873553246</v>
       </c>
       <c r="D69" s="8">
-        <v>46133.45522304398</v>
+        <v>46133.621889710645</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>181</v>
@@ -5558,13 +5558,13 @@
         <v>250</v>
       </c>
       <c r="B70" s="5">
-        <v>46080.611621793985</v>
+        <v>46080.77828846065</v>
       </c>
       <c r="C70" s="5">
-        <v>46140.67233574074</v>
+        <v>46140.8390024074</v>
       </c>
       <c r="D70" s="5">
-        <v>46141.54510638889</v>
+        <v>46141.711773055555</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>182</v>
@@ -5623,13 +5623,13 @@
         <v>252</v>
       </c>
       <c r="B71" s="8">
-        <v>46080.61162203704</v>
+        <v>46080.7782887037</v>
       </c>
       <c r="C71" s="8">
-        <v>46141.5453846875</v>
+        <v>46141.71205135417</v>
       </c>
       <c r="D71" s="8">
-        <v>46141.54538606481</v>
+        <v>46141.712052731484</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>253</v>
@@ -5672,13 +5672,13 @@
         <v>255</v>
       </c>
       <c r="B72" s="5">
-        <v>46080.61162229167</v>
+        <v>46080.77828895833</v>
       </c>
       <c r="C72" s="5">
-        <v>46140.67238</v>
+        <v>46140.83904666667</v>
       </c>
       <c r="D72" s="5">
-        <v>46141.54513895833</v>
+        <v>46141.711805625004</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>256</v>
@@ -5737,13 +5737,13 @@
         <v>260</v>
       </c>
       <c r="B73" s="8">
-        <v>46080.61162048611</v>
+        <v>46080.778287152774</v>
       </c>
       <c r="C73" s="8">
-        <v>46141.54505951389</v>
+        <v>46141.711726180554</v>
       </c>
       <c r="D73" s="8">
-        <v>46141.54516234953</v>
+        <v>46141.7118290162</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>261</v>
@@ -5802,13 +5802,13 @@
         <v>264</v>
       </c>
       <c r="B74" s="5">
-        <v>46080.61162084491</v>
+        <v>46080.77828751157</v>
       </c>
       <c r="C74" s="5">
-        <v>46141.54524869213</v>
+        <v>46141.7119153588</v>
       </c>
       <c r="D74" s="5">
-        <v>46141.54525033565</v>
+        <v>46141.711917002314</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>265</v>
@@ -5867,13 +5867,13 @@
         <v>267</v>
       </c>
       <c r="B75" s="8">
-        <v>46080.61162115741</v>
+        <v>46080.77828782407</v>
       </c>
       <c r="C75" s="8">
-        <v>46141.545294236115</v>
+        <v>46141.71196090278</v>
       </c>
       <c r="D75" s="8">
-        <v>46141.54529546296</v>
+        <v>46141.71196212963</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>268</v>
@@ -5932,11 +5932,11 @@
         <v>270</v>
       </c>
       <c r="B76" s="5">
-        <v>46080.61162142361</v>
+        <v>46080.77828809028</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46090.44426309028</v>
+        <v>46090.61092975695</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>271</v>
@@ -5979,11 +5979,11 @@
         <v>273</v>
       </c>
       <c r="B77" s="8">
-        <v>46080.611622013894</v>
+        <v>46080.77828868055</v>
       </c>
       <c r="C77" s="9"/>
       <c r="D77" s="8">
-        <v>46141.54530271991</v>
+        <v>46141.711969386575</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>72</v>
@@ -6042,11 +6042,11 @@
         <v>277</v>
       </c>
       <c r="B78" s="5">
-        <v>46080.611621689815</v>
+        <v>46080.77828835648</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46141.54530398148</v>
+        <v>46141.711970648146</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>278</v>
@@ -6105,11 +6105,11 @@
         <v>279</v>
       </c>
       <c r="B79" s="8">
-        <v>46090.44504910879</v>
+        <v>46090.61171577546</v>
       </c>
       <c r="C79" s="9"/>
       <c r="D79" s="8">
-        <v>46090.44786366898</v>
+        <v>46090.614530335646</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>280</v>
@@ -6158,11 +6158,11 @@
         <v>282</v>
       </c>
       <c r="B80" s="5">
-        <v>46090.44533261574</v>
+        <v>46090.61199928241</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46141.545305277774</v>
+        <v>46141.711971944445</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>283</v>
@@ -6221,11 +6221,11 @@
         <v>285</v>
       </c>
       <c r="B81" s="8">
-        <v>46090.4454134375</v>
+        <v>46090.61208010417</v>
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="8">
-        <v>46090.45203153935</v>
+        <v>46090.61869820602</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>286</v>

--- a/data/50001524 - ATACAMA KOZAN.xlsx
+++ b/data/50001524 - ATACAMA KOZAN.xlsx
@@ -4995,7 +4995,7 @@
         <v>46121.86789461806</v>
       </c>
       <c r="D61" s="8">
-        <v>46204.20245239583</v>
+        <v>46212.18789364584</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>224</v>
@@ -5033,8 +5033,8 @@
       <c r="P61" s="9" t="s">
         <v>225</v>
       </c>
-      <c r="Q61" s="12" t="s">
-        <v>105</v>
+      <c r="Q61" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="R61" s="9">
         <v>1</v>
@@ -5304,7 +5304,7 @@
         <v>46133.62178611111</v>
       </c>
       <c r="D66" s="5">
-        <v>46133.62180199074</v>
+        <v>46212.17993510417</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>239</v>
@@ -5342,8 +5342,8 @@
       <c r="P66" s="6" t="s">
         <v>237</v>
       </c>
-      <c r="Q66" s="11" t="s">
-        <v>109</v>
+      <c r="Q66" s="12" t="s">
+        <v>105</v>
       </c>
       <c r="R66" s="6">
         <v>1</v>

--- a/data/50001524 - ATACAMA KOZAN.xlsx
+++ b/data/50001524 - ATACAMA KOZAN.xlsx
@@ -328,349 +328,349 @@
     <t>Generación OC Alabe,Fabricación Alabe</t>
   </si>
   <si>
+    <t>1213412709779762</t>
+  </si>
+  <si>
+    <t>Generación OC Alabe</t>
+  </si>
+  <si>
+    <t>Fabricación Alabe,Alabe</t>
+  </si>
+  <si>
+    <t>Baja</t>
+  </si>
+  <si>
+    <t>Tarea sin iniciar</t>
+  </si>
+  <si>
+    <t>1213412709779763</t>
+  </si>
+  <si>
+    <t>Fabricación Alabe</t>
+  </si>
+  <si>
+    <t>1213458788103569</t>
+  </si>
+  <si>
+    <t>Tableros</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generacion oc Tableros ,Fabricacion Tableros </t>
+  </si>
+  <si>
+    <t>1213458788103571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generacion oc Tableros </t>
+  </si>
+  <si>
+    <t>Fabricacion Tableros ,Tableros</t>
+  </si>
+  <si>
+    <t>1213458788103572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fabricacion Tableros </t>
+  </si>
+  <si>
+    <t>Tableros,Recepcion Tableros</t>
+  </si>
+  <si>
+    <t>1213412709779764</t>
+  </si>
+  <si>
+    <t>rodete</t>
+  </si>
+  <si>
+    <t>Generación OC Rodete,Fabricación Rodete</t>
+  </si>
+  <si>
+    <t>1213412709779765</t>
+  </si>
+  <si>
+    <t>Generación OC Rodete</t>
+  </si>
+  <si>
+    <t>Fabricación Rodete,rodete</t>
+  </si>
+  <si>
+    <t>1213412709779766</t>
+  </si>
+  <si>
+    <t>Fabricación Rodete</t>
+  </si>
+  <si>
+    <t>rodete,Recepcion Rodete,Recepcion Alabe</t>
+  </si>
+  <si>
+    <t>1213470416901259</t>
+  </si>
+  <si>
+    <t>Motor</t>
+  </si>
+  <si>
+    <t>Generación OC motor,Fabricación motor,Planos motor proveedor</t>
+  </si>
+  <si>
+    <t>1213470416901260</t>
+  </si>
+  <si>
+    <t>Generación OC motor</t>
+  </si>
+  <si>
+    <t>Fabricación motor,Planos motor proveedor,Motor</t>
+  </si>
+  <si>
+    <t>1213470416901261</t>
+  </si>
+  <si>
+    <t>Fabricación motor</t>
+  </si>
+  <si>
+    <t>Motor,Recepcion  motor</t>
+  </si>
+  <si>
+    <t>1213470416901262</t>
+  </si>
+  <si>
+    <t>Planos motor proveedor</t>
+  </si>
+  <si>
+    <t>Motor,Planos Definitivos</t>
+  </si>
+  <si>
+    <t>1213470416901263</t>
+  </si>
+  <si>
+    <t>Materiales a codigo // compras locales aprovisionamientomiento:</t>
+  </si>
+  <si>
+    <t>Yerlia Ayleen Castillo Diaz</t>
+  </si>
+  <si>
+    <t>yerlia.castillo@zitron.com</t>
+  </si>
+  <si>
+    <t>Generación OC materiales,Fabricacion a codigo y compras locales</t>
+  </si>
+  <si>
+    <t>1213470416901264</t>
+  </si>
+  <si>
+    <t>Generación OC materiales</t>
+  </si>
+  <si>
+    <t>Fabricacion a codigo y compras locales</t>
+  </si>
+  <si>
+    <t>1213470416901265</t>
+  </si>
+  <si>
+    <t>Generación OC materiales,Materiales a codigo // compras locales aprovisionamientomiento:,Recepcion materiales a codigos // compras locales aprovisionamiento</t>
+  </si>
+  <si>
+    <t>1213470416901266</t>
+  </si>
+  <si>
+    <t>Sensores</t>
+  </si>
+  <si>
+    <t>Generación Oc sensores,Fabricación Sensores</t>
+  </si>
+  <si>
+    <t>1213470416901267</t>
+  </si>
+  <si>
+    <t>Generación Oc sensores</t>
+  </si>
+  <si>
+    <t>Fabricación Sensores,Sensores</t>
+  </si>
+  <si>
+    <t>1213470416901268</t>
+  </si>
+  <si>
+    <t>Fabricación Sensores</t>
+  </si>
+  <si>
+    <t>Sensores,Recepcion sensores</t>
+  </si>
+  <si>
+    <t>1213470416901269</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseño:</t>
+  </si>
+  <si>
+    <t>Planos Preliminar,Planos Definitivos</t>
+  </si>
+  <si>
+    <t>1213470416901270</t>
+  </si>
+  <si>
+    <t>Planos Preliminar</t>
+  </si>
+  <si>
+    <t>Francisca González Cornejo</t>
+  </si>
+  <si>
+    <t>francisca.gonzalez@zitron.com</t>
+  </si>
+  <si>
+    <t>Planos Definitivos,Ingenieria y diseño:</t>
+  </si>
+  <si>
+    <t>1213470416901271</t>
+  </si>
+  <si>
+    <t>Planos Definitivos</t>
+  </si>
+  <si>
+    <t>Hernan Roberto Gutierrez Barrientos</t>
+  </si>
+  <si>
+    <t>hgutierrez@zitron.com</t>
+  </si>
+  <si>
+    <t>Planos motor proveedor,Planos Preliminar</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseño:,Check planos</t>
+  </si>
+  <si>
+    <t>1213561126963324</t>
+  </si>
+  <si>
+    <t>Check planos</t>
+  </si>
+  <si>
+    <t>Armado,Control de calidad Armado,Montaje motor,Montaje Alabe,Montaje Rodete,Montaje Sensor</t>
+  </si>
+  <si>
+    <t>1213561126963325</t>
+  </si>
+  <si>
+    <t>Check pruebas FAT</t>
+  </si>
+  <si>
+    <t>Pruebas FAT</t>
+  </si>
+  <si>
+    <t>RE-PINTADO</t>
+  </si>
+  <si>
+    <t>1213470416901272</t>
+  </si>
+  <si>
+    <t>Bodega:</t>
+  </si>
+  <si>
+    <t>Recepcion materiales a codigos // compras locales aprovisionamiento,Control de calidad compras materiales a codigo // compras locale aprovisionamiento</t>
+  </si>
+  <si>
+    <t>1213470416901273</t>
+  </si>
+  <si>
+    <t>Recepcion materiales a codigos // compras locales aprovisionamiento</t>
+  </si>
+  <si>
+    <t>Victor Muñoz</t>
+  </si>
+  <si>
+    <t>victor.munoz@zitron.com</t>
+  </si>
+  <si>
+    <t>Control de calidad compras materiales a codigo // compras locale aprovisionamiento,Bodega:</t>
+  </si>
+  <si>
+    <t>1213470416901274</t>
+  </si>
+  <si>
+    <t>Control de calidad compras materiales a codigo // compras locale aprovisionamiento</t>
+  </si>
+  <si>
+    <t>Nicolás López</t>
+  </si>
+  <si>
+    <t>nicolas.lopez@zitron.com</t>
+  </si>
+  <si>
+    <t>Bodega:,Preparación Materiales</t>
+  </si>
+  <si>
+    <t>1213470416901275</t>
+  </si>
+  <si>
+    <t>Caldereria:</t>
+  </si>
+  <si>
+    <t>Preparación Materiales,Armado,Control de calidad Armado</t>
+  </si>
+  <si>
+    <t>1213470416901276</t>
+  </si>
+  <si>
+    <t>Preparación Materiales</t>
+  </si>
+  <si>
+    <t>Nicolás Mol</t>
+  </si>
+  <si>
+    <t>nicolas.mol@zitron.com</t>
+  </si>
+  <si>
+    <t>Armado,Caldereria:</t>
+  </si>
+  <si>
+    <t>1213470416901277</t>
+  </si>
+  <si>
+    <t>Armado</t>
+  </si>
+  <si>
+    <t>Preparación Materiales,Check planos</t>
+  </si>
+  <si>
+    <t>Control de calidad Armado,Caldereria:</t>
+  </si>
+  <si>
+    <t>1213470416901278</t>
+  </si>
+  <si>
+    <t>Control de calidad Armado</t>
+  </si>
+  <si>
+    <t>Armado,Check planos</t>
+  </si>
+  <si>
+    <t>Caldereria:,Revestimiento</t>
+  </si>
+  <si>
+    <t>1213470416901279</t>
+  </si>
+  <si>
+    <t>Recepcion Rodete,Recepcion Alabe,Recepcion  motor,Recepcion sensores,Recepcion Tableros</t>
+  </si>
+  <si>
+    <t>1213470416901280</t>
+  </si>
+  <si>
+    <t>Recepcion Rodete</t>
+  </si>
+  <si>
+    <t>Bodega:,Montaje Rodete</t>
+  </si>
+  <si>
+    <t>1213470416901281</t>
+  </si>
+  <si>
+    <t>Recepcion Alabe</t>
+  </si>
+  <si>
+    <t>Bodega:,Montaje Alabe</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1213412709779762</t>
-  </si>
-  <si>
-    <t>Generación OC Alabe</t>
-  </si>
-  <si>
-    <t>Fabricación Alabe,Alabe</t>
-  </si>
-  <si>
-    <t>Baja</t>
-  </si>
-  <si>
-    <t>Tarea sin iniciar</t>
-  </si>
-  <si>
-    <t>1213412709779763</t>
-  </si>
-  <si>
-    <t>Fabricación Alabe</t>
-  </si>
-  <si>
-    <t>1213458788103569</t>
-  </si>
-  <si>
-    <t>Tableros</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generacion oc Tableros ,Fabricacion Tableros </t>
-  </si>
-  <si>
-    <t>1213458788103571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generacion oc Tableros </t>
-  </si>
-  <si>
-    <t>Fabricacion Tableros ,Tableros</t>
-  </si>
-  <si>
-    <t>1213458788103572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fabricacion Tableros </t>
-  </si>
-  <si>
-    <t>Tableros,Recepcion Tableros</t>
-  </si>
-  <si>
-    <t>1213412709779764</t>
-  </si>
-  <si>
-    <t>rodete</t>
-  </si>
-  <si>
-    <t>Generación OC Rodete,Fabricación Rodete</t>
-  </si>
-  <si>
-    <t>1213412709779765</t>
-  </si>
-  <si>
-    <t>Generación OC Rodete</t>
-  </si>
-  <si>
-    <t>Fabricación Rodete,rodete</t>
-  </si>
-  <si>
-    <t>1213412709779766</t>
-  </si>
-  <si>
-    <t>Fabricación Rodete</t>
-  </si>
-  <si>
-    <t>rodete,Recepcion Rodete,Recepcion Alabe</t>
-  </si>
-  <si>
-    <t>1213470416901259</t>
-  </si>
-  <si>
-    <t>Motor</t>
-  </si>
-  <si>
-    <t>Generación OC motor,Fabricación motor,Planos motor proveedor</t>
-  </si>
-  <si>
-    <t>1213470416901260</t>
-  </si>
-  <si>
-    <t>Generación OC motor</t>
-  </si>
-  <si>
-    <t>Fabricación motor,Planos motor proveedor,Motor</t>
-  </si>
-  <si>
-    <t>1213470416901261</t>
-  </si>
-  <si>
-    <t>Fabricación motor</t>
-  </si>
-  <si>
-    <t>Motor,Recepcion  motor</t>
-  </si>
-  <si>
-    <t>1213470416901262</t>
-  </si>
-  <si>
-    <t>Planos motor proveedor</t>
-  </si>
-  <si>
-    <t>Motor,Planos Definitivos</t>
-  </si>
-  <si>
-    <t>1213470416901263</t>
-  </si>
-  <si>
-    <t>Materiales a codigo // compras locales aprovisionamientomiento:</t>
-  </si>
-  <si>
-    <t>Yerlia Ayleen Castillo Diaz</t>
-  </si>
-  <si>
-    <t>yerlia.castillo@zitron.com</t>
-  </si>
-  <si>
-    <t>Generación OC materiales,Fabricacion a codigo y compras locales</t>
-  </si>
-  <si>
-    <t>1213470416901264</t>
-  </si>
-  <si>
-    <t>Generación OC materiales</t>
-  </si>
-  <si>
-    <t>Fabricacion a codigo y compras locales</t>
-  </si>
-  <si>
-    <t>1213470416901265</t>
-  </si>
-  <si>
-    <t>Generación OC materiales,Materiales a codigo // compras locales aprovisionamientomiento:,Recepcion materiales a codigos // compras locales aprovisionamiento</t>
-  </si>
-  <si>
-    <t>1213470416901266</t>
-  </si>
-  <si>
-    <t>Sensores</t>
-  </si>
-  <si>
-    <t>Generación Oc sensores,Fabricación Sensores</t>
-  </si>
-  <si>
-    <t>1213470416901267</t>
-  </si>
-  <si>
-    <t>Generación Oc sensores</t>
-  </si>
-  <si>
-    <t>Fabricación Sensores,Sensores</t>
-  </si>
-  <si>
-    <t>1213470416901268</t>
-  </si>
-  <si>
-    <t>Fabricación Sensores</t>
-  </si>
-  <si>
-    <t>Sensores,Recepcion sensores</t>
-  </si>
-  <si>
-    <t>1213470416901269</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseño:</t>
-  </si>
-  <si>
-    <t>Planos Preliminar,Planos Definitivos</t>
-  </si>
-  <si>
-    <t>1213470416901270</t>
-  </si>
-  <si>
-    <t>Planos Preliminar</t>
-  </si>
-  <si>
-    <t>Francisca González Cornejo</t>
-  </si>
-  <si>
-    <t>francisca.gonzalez@zitron.com</t>
-  </si>
-  <si>
-    <t>Planos Definitivos,Ingenieria y diseño:</t>
-  </si>
-  <si>
-    <t>1213470416901271</t>
-  </si>
-  <si>
-    <t>Planos Definitivos</t>
-  </si>
-  <si>
-    <t>Hernan Roberto Gutierrez Barrientos</t>
-  </si>
-  <si>
-    <t>hgutierrez@zitron.com</t>
-  </si>
-  <si>
-    <t>Planos motor proveedor,Planos Preliminar</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseño:,Check planos</t>
-  </si>
-  <si>
-    <t>1213561126963324</t>
-  </si>
-  <si>
-    <t>Check planos</t>
-  </si>
-  <si>
-    <t>Armado,Control de calidad Armado,Montaje motor,Montaje Alabe,Montaje Rodete,Montaje Sensor</t>
-  </si>
-  <si>
-    <t>1213561126963325</t>
-  </si>
-  <si>
-    <t>Check pruebas FAT</t>
-  </si>
-  <si>
-    <t>Pruebas FAT</t>
-  </si>
-  <si>
-    <t>RE-PINTADO</t>
-  </si>
-  <si>
-    <t>1213470416901272</t>
-  </si>
-  <si>
-    <t>Bodega:</t>
-  </si>
-  <si>
-    <t>Recepcion materiales a codigos // compras locales aprovisionamiento,Control de calidad compras materiales a codigo // compras locale aprovisionamiento</t>
-  </si>
-  <si>
-    <t>1213470416901273</t>
-  </si>
-  <si>
-    <t>Recepcion materiales a codigos // compras locales aprovisionamiento</t>
-  </si>
-  <si>
-    <t>Victor Muñoz</t>
-  </si>
-  <si>
-    <t>victor.munoz@zitron.com</t>
-  </si>
-  <si>
-    <t>Control de calidad compras materiales a codigo // compras locale aprovisionamiento,Bodega:</t>
-  </si>
-  <si>
-    <t>1213470416901274</t>
-  </si>
-  <si>
-    <t>Control de calidad compras materiales a codigo // compras locale aprovisionamiento</t>
-  </si>
-  <si>
-    <t>Nicolás López</t>
-  </si>
-  <si>
-    <t>nicolas.lopez@zitron.com</t>
-  </si>
-  <si>
-    <t>Bodega:,Preparación Materiales</t>
-  </si>
-  <si>
-    <t>1213470416901275</t>
-  </si>
-  <si>
-    <t>Caldereria:</t>
-  </si>
-  <si>
-    <t>Preparación Materiales,Armado,Control de calidad Armado</t>
-  </si>
-  <si>
-    <t>1213470416901276</t>
-  </si>
-  <si>
-    <t>Preparación Materiales</t>
-  </si>
-  <si>
-    <t>Nicolás Mol</t>
-  </si>
-  <si>
-    <t>nicolas.mol@zitron.com</t>
-  </si>
-  <si>
-    <t>Armado,Caldereria:</t>
-  </si>
-  <si>
-    <t>1213470416901277</t>
-  </si>
-  <si>
-    <t>Armado</t>
-  </si>
-  <si>
-    <t>Preparación Materiales,Check planos</t>
-  </si>
-  <si>
-    <t>Control de calidad Armado,Caldereria:</t>
-  </si>
-  <si>
-    <t>1213470416901278</t>
-  </si>
-  <si>
-    <t>Control de calidad Armado</t>
-  </si>
-  <si>
-    <t>Armado,Check planos</t>
-  </si>
-  <si>
-    <t>Caldereria:,Revestimiento</t>
-  </si>
-  <si>
-    <t>1213470416901279</t>
-  </si>
-  <si>
-    <t>Recepcion Rodete,Recepcion Alabe,Recepcion  motor,Recepcion sensores,Recepcion Tableros</t>
-  </si>
-  <si>
-    <t>1213470416901280</t>
-  </si>
-  <si>
-    <t>Recepcion Rodete</t>
-  </si>
-  <si>
-    <t>Bodega:,Montaje Rodete</t>
-  </si>
-  <si>
-    <t>1213470416901281</t>
-  </si>
-  <si>
-    <t>Recepcion Alabe</t>
-  </si>
-  <si>
-    <t>Bodega:,Montaje Alabe</t>
   </si>
   <si>
     <t>1213470416901282</t>
@@ -2850,7 +2850,7 @@
         <v>46139.781195081014</v>
       </c>
       <c r="D26" s="5">
-        <v>46206.19700488426</v>
+        <v>46214.19413398148</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>101</v>
@@ -2888,8 +2888,8 @@
       <c r="P26" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="Q26" s="12" t="s">
-        <v>105</v>
+      <c r="Q26" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="R26" s="6">
         <v>1</v>
@@ -2906,7 +2906,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B27" s="8">
         <v>46080.77828601852</v>
@@ -2918,7 +2918,7 @@
         <v>46139.78108450232</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>26</v>
@@ -2951,23 +2951,23 @@
         <v>80</v>
       </c>
       <c r="P27" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="Q27" s="11" t="s">
         <v>108</v>
-      </c>
-      <c r="Q27" s="11" t="s">
-        <v>109</v>
       </c>
       <c r="R27" s="9">
         <v>0</v>
       </c>
       <c r="S27" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="T27" s="9"/>
       <c r="U27" s="9"/>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B28" s="5">
         <v>46080.778286388886</v>
@@ -2979,7 +2979,7 @@
         <v>46139.78118329861</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
@@ -3009,26 +3009,26 @@
         <v>101</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="P28" s="6" t="s">
         <v>101</v>
       </c>
       <c r="Q28" s="11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R28" s="6">
         <v>0</v>
       </c>
       <c r="S28" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="T28" s="6"/>
       <c r="U28" s="6"/>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B29" s="8">
         <v>46080.78421460648</v>
@@ -3040,7 +3040,7 @@
         <v>46199.207547604165</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>26</v>
@@ -3070,7 +3070,7 @@
         <v>98</v>
       </c>
       <c r="O29" s="9" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="P29" s="9" t="s">
         <v>98</v>
@@ -3082,7 +3082,7 @@
         <v>1</v>
       </c>
       <c r="S29" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="T29" s="8">
         <v>46092</v>
@@ -3093,7 +3093,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B30" s="5">
         <v>46080.78464398148</v>
@@ -3105,7 +3105,7 @@
         <v>46114.761801307875</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
@@ -3132,13 +3132,13 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="O30" s="6" t="s">
         <v>87</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
@@ -3148,7 +3148,7 @@
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B31" s="8">
         <v>46080.78472030093</v>
@@ -3160,7 +3160,7 @@
         <v>46140.80895233796</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>26</v>
@@ -3187,13 +3187,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="9" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="O31" s="9" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="P31" s="9" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="Q31" s="9"/>
       <c r="R31" s="9"/>
@@ -3203,7 +3203,7 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B32" s="5">
         <v>46080.77828665509</v>
@@ -3215,7 +3215,7 @@
         <v>46154.1920628125</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
@@ -3245,7 +3245,7 @@
         <v>98</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="P32" s="6" t="s">
         <v>98</v>
@@ -3268,7 +3268,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B33" s="8">
         <v>46080.7782869213</v>
@@ -3280,7 +3280,7 @@
         <v>46133.62086326389</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>26</v>
@@ -3307,29 +3307,29 @@
         <v>26</v>
       </c>
       <c r="N33" s="9" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O33" s="9" t="s">
         <v>83</v>
       </c>
       <c r="P33" s="9" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="Q33" s="11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R33" s="9">
         <v>0</v>
       </c>
       <c r="S33" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="T33" s="9"/>
       <c r="U33" s="9"/>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B34" s="5">
         <v>46080.778287187495</v>
@@ -3341,7 +3341,7 @@
         <v>46133.62090126157</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
@@ -3368,29 +3368,29 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="Q34" s="11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R34" s="6">
         <v>0</v>
       </c>
       <c r="S34" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="T34" s="6"/>
       <c r="U34" s="6"/>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B35" s="8">
         <v>46080.77828746528</v>
@@ -3402,7 +3402,7 @@
         <v>46114.76329173611</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>26</v>
@@ -3432,13 +3432,13 @@
         <v>98</v>
       </c>
       <c r="O35" s="9" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="P35" s="9" t="s">
         <v>98</v>
       </c>
       <c r="Q35" s="11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R35" s="9">
         <v>1</v>
@@ -3455,7 +3455,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B36" s="5">
         <v>46080.77828773148</v>
@@ -3467,7 +3467,7 @@
         <v>46114.76319354167</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
@@ -3494,29 +3494,29 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="O36" s="6" t="s">
         <v>77</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="Q36" s="11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R36" s="6">
         <v>0</v>
       </c>
       <c r="S36" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="T36" s="6"/>
       <c r="U36" s="6"/>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B37" s="8">
         <v>46080.77828799769</v>
@@ -3528,7 +3528,7 @@
         <v>46114.763248877316</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>26</v>
@@ -3555,29 +3555,29 @@
         <v>26</v>
       </c>
       <c r="N37" s="9" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="O37" s="9" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P37" s="9" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="Q37" s="11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R37" s="9">
         <v>0</v>
       </c>
       <c r="S37" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="T37" s="9"/>
       <c r="U37" s="9"/>
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B38" s="5">
         <v>46080.77828825232</v>
@@ -3589,7 +3589,7 @@
         <v>46114.7632599537</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
@@ -3616,29 +3616,29 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="Q38" s="11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R38" s="6">
         <v>0</v>
       </c>
       <c r="S38" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="T38" s="6"/>
       <c r="U38" s="6"/>
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B39" s="8">
         <v>46080.778288518515</v>
@@ -3650,16 +3650,16 @@
         <v>46149.197581886576</v>
       </c>
       <c r="E39" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="F39" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G39" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="F39" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G39" s="9" t="s">
+      <c r="H39" s="9" t="s">
         <v>145</v>
-      </c>
-      <c r="H39" s="9" t="s">
-        <v>146</v>
       </c>
       <c r="I39" s="8">
         <v>46100</v>
@@ -3680,7 +3680,7 @@
         <v>98</v>
       </c>
       <c r="O39" s="9" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="P39" s="9" t="s">
         <v>98</v>
@@ -3703,7 +3703,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B40" s="5">
         <v>46080.77828673611</v>
@@ -3715,16 +3715,16 @@
         <v>46121.8600697338</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="H40" s="6" t="s">
         <v>145</v>
-      </c>
-      <c r="H40" s="6" t="s">
-        <v>146</v>
       </c>
       <c r="I40" s="5">
         <v>46100</v>
@@ -3742,29 +3742,29 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="Q40" s="11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R40" s="6">
         <v>0</v>
       </c>
       <c r="S40" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="T40" s="6"/>
       <c r="U40" s="6"/>
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B41" s="8">
         <v>46080.77828702546</v>
@@ -3776,16 +3776,16 @@
         <v>46121.86006597222</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="H41" s="9" t="s">
         <v>145</v>
-      </c>
-      <c r="H41" s="9" t="s">
-        <v>146</v>
       </c>
       <c r="I41" s="8">
         <v>46120</v>
@@ -3803,29 +3803,29 @@
         <v>26</v>
       </c>
       <c r="N41" s="9" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="O41" s="9" t="s">
         <v>93</v>
       </c>
       <c r="P41" s="9" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q41" s="11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R41" s="9">
         <v>0</v>
       </c>
       <c r="S41" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="T41" s="9"/>
       <c r="U41" s="9"/>
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B42" s="5">
         <v>46080.77828724537</v>
@@ -3837,16 +3837,16 @@
         <v>46210.17465634259</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="H42" s="6" t="s">
         <v>145</v>
-      </c>
-      <c r="H42" s="6" t="s">
-        <v>146</v>
       </c>
       <c r="I42" s="5">
         <v>46100</v>
@@ -3867,7 +3867,7 @@
         <v>98</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>98</v>
@@ -3890,7 +3890,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B43" s="8">
         <v>46080.77828748843</v>
@@ -3902,16 +3902,16 @@
         <v>46114.76045094908</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="H43" s="9" t="s">
         <v>145</v>
-      </c>
-      <c r="H43" s="9" t="s">
-        <v>146</v>
       </c>
       <c r="I43" s="8">
         <v>46100</v>
@@ -3929,29 +3929,29 @@
         <v>26</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="O43" s="9" t="s">
         <v>90</v>
       </c>
       <c r="P43" s="9" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="Q43" s="11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R43" s="9">
         <v>0</v>
       </c>
       <c r="S43" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="T43" s="9"/>
       <c r="U43" s="9"/>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B44" s="5">
         <v>46080.77828770834</v>
@@ -3963,16 +3963,16 @@
         <v>46114.7604978125</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="H44" s="6" t="s">
         <v>145</v>
-      </c>
-      <c r="H44" s="6" t="s">
-        <v>146</v>
       </c>
       <c r="I44" s="5">
         <v>46129</v>
@@ -3990,29 +3990,29 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="Q44" s="11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R44" s="6">
         <v>0</v>
       </c>
       <c r="S44" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="T44" s="6"/>
       <c r="U44" s="6"/>
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B45" s="8">
         <v>46080.778287939815</v>
@@ -4024,7 +4024,7 @@
         <v>46141.772341724536</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>25</v>
@@ -4048,7 +4048,7 @@
         <v>26</v>
       </c>
       <c r="O45" s="9" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="P45" s="9" t="s">
         <v>26</v>
@@ -4061,7 +4061,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B46" s="5">
         <v>46080.778288182875</v>
@@ -4073,16 +4073,16 @@
         <v>46127.67810105324</v>
       </c>
       <c r="E46" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="F46" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G46" s="6" t="s">
         <v>166</v>
       </c>
-      <c r="F46" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G46" s="6" t="s">
+      <c r="H46" s="6" t="s">
         <v>167</v>
-      </c>
-      <c r="H46" s="6" t="s">
-        <v>168</v>
       </c>
       <c r="I46" s="5">
         <v>46098</v>
@@ -4100,13 +4100,13 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="O46" s="6" t="s">
         <v>67</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="Q46" s="10" t="s">
         <v>31</v>
@@ -4126,7 +4126,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B47" s="8">
         <v>46080.77828842592</v>
@@ -4138,16 +4138,16 @@
         <v>46158.16995894676</v>
       </c>
       <c r="E47" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="F47" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G47" s="9" t="s">
         <v>171</v>
       </c>
-      <c r="F47" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G47" s="9" t="s">
+      <c r="H47" s="9" t="s">
         <v>172</v>
-      </c>
-      <c r="H47" s="9" t="s">
-        <v>173</v>
       </c>
       <c r="I47" s="8">
         <v>46140</v>
@@ -4165,13 +4165,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="O47" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="P47" s="9" t="s">
         <v>174</v>
-      </c>
-      <c r="P47" s="9" t="s">
-        <v>175</v>
       </c>
       <c r="Q47" s="10" t="s">
         <v>31</v>
@@ -4191,7 +4191,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B48" s="5">
         <v>46087.53644159722</v>
@@ -4203,16 +4203,16 @@
         <v>46161.20788581019</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="H48" s="6" t="s">
         <v>172</v>
-      </c>
-      <c r="H48" s="6" t="s">
-        <v>173</v>
       </c>
       <c r="I48" s="6"/>
       <c r="J48" s="5">
@@ -4228,13 +4228,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Q48" s="10" t="s">
         <v>31</v>
@@ -4254,7 +4254,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B49" s="8">
         <v>46087.536521331014</v>
@@ -4266,16 +4266,16 @@
         <v>46141.771787060185</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="H49" s="9" t="s">
         <v>167</v>
-      </c>
-      <c r="H49" s="9" t="s">
-        <v>168</v>
       </c>
       <c r="I49" s="8">
         <v>46233</v>
@@ -4293,16 +4293,16 @@
         <v>26</v>
       </c>
       <c r="N49" s="9" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="O49" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="P49" s="9" t="s">
         <v>181</v>
       </c>
-      <c r="P49" s="9" t="s">
-        <v>182</v>
-      </c>
       <c r="Q49" s="11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R49" s="9">
         <v>1</v>
@@ -4319,7 +4319,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B50" s="5">
         <v>46080.77828866898</v>
@@ -4331,7 +4331,7 @@
         <v>46141.772585231476</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>25</v>
@@ -4355,7 +4355,7 @@
         <v>26</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>26</v>
@@ -4368,7 +4368,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B51" s="8">
         <v>46080.77828892361</v>
@@ -4380,16 +4380,16 @@
         <v>46151.18472762732</v>
       </c>
       <c r="E51" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="F51" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G51" s="9" t="s">
         <v>187</v>
       </c>
-      <c r="F51" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G51" s="9" t="s">
+      <c r="H51" s="9" t="s">
         <v>188</v>
-      </c>
-      <c r="H51" s="9" t="s">
-        <v>189</v>
       </c>
       <c r="I51" s="8">
         <v>46149</v>
@@ -4407,13 +4407,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="O51" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q51" s="10" t="s">
         <v>31</v>
@@ -4433,7 +4433,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B52" s="5">
         <v>46080.77828760417</v>
@@ -4445,16 +4445,16 @@
         <v>46155.20414789351</v>
       </c>
       <c r="E52" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="F52" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G52" s="6" t="s">
         <v>192</v>
       </c>
-      <c r="F52" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G52" s="6" t="s">
+      <c r="H52" s="6" t="s">
         <v>193</v>
-      </c>
-      <c r="H52" s="6" t="s">
-        <v>194</v>
       </c>
       <c r="I52" s="5">
         <v>46153</v>
@@ -4472,13 +4472,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="Q52" s="10" t="s">
         <v>31</v>
@@ -4498,7 +4498,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B53" s="8">
         <v>46080.778288009256</v>
@@ -4510,7 +4510,7 @@
         <v>46141.77186175926</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>25</v>
@@ -4534,7 +4534,7 @@
         <v>26</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="P53" s="9" t="s">
         <v>26</v>
@@ -4547,7 +4547,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B54" s="5">
         <v>46080.77828832176</v>
@@ -4559,16 +4559,16 @@
         <v>46165.18131118055</v>
       </c>
       <c r="E54" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="F54" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G54" s="6" t="s">
         <v>200</v>
       </c>
-      <c r="F54" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G54" s="6" t="s">
+      <c r="H54" s="6" t="s">
         <v>201</v>
-      </c>
-      <c r="H54" s="6" t="s">
-        <v>202</v>
       </c>
       <c r="I54" s="5">
         <v>46155</v>
@@ -4586,13 +4586,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="Q54" s="10" t="s">
         <v>31</v>
@@ -4612,7 +4612,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B55" s="8">
         <v>46080.77828861111</v>
@@ -4624,16 +4624,16 @@
         <v>46170.185211909724</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="9" t="s">
+        <v>200</v>
+      </c>
+      <c r="H55" s="9" t="s">
         <v>201</v>
-      </c>
-      <c r="H55" s="9" t="s">
-        <v>202</v>
       </c>
       <c r="I55" s="8">
         <v>46167</v>
@@ -4651,13 +4651,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="9" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="O55" s="9" t="s">
+        <v>205</v>
+      </c>
+      <c r="P55" s="9" t="s">
         <v>206</v>
-      </c>
-      <c r="P55" s="9" t="s">
-        <v>207</v>
       </c>
       <c r="Q55" s="10" t="s">
         <v>31</v>
@@ -4677,7 +4677,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B56" s="5">
         <v>46080.778288912035</v>
@@ -4689,16 +4689,16 @@
         <v>46172.2027446875</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="H56" s="6" t="s">
         <v>193</v>
-      </c>
-      <c r="H56" s="6" t="s">
-        <v>194</v>
       </c>
       <c r="I56" s="5">
         <v>46170</v>
@@ -4716,13 +4716,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="O56" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="P56" s="6" t="s">
         <v>210</v>
-      </c>
-      <c r="P56" s="6" t="s">
-        <v>211</v>
       </c>
       <c r="Q56" s="10" t="s">
         <v>31</v>
@@ -4742,7 +4742,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B57" s="8">
         <v>46080.77828921296</v>
@@ -4754,7 +4754,7 @@
         <v>46141.77231675926</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>25</v>
@@ -4778,7 +4778,7 @@
         <v>26</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="P57" s="9" t="s">
         <v>26</v>
@@ -4791,7 +4791,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B58" s="5">
         <v>46080.77828957176</v>
@@ -4803,16 +4803,16 @@
         <v>46156.16908381945</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="H58" s="6" t="s">
         <v>188</v>
-      </c>
-      <c r="H58" s="6" t="s">
-        <v>189</v>
       </c>
       <c r="I58" s="5">
         <v>46154</v>
@@ -4830,13 +4830,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="Q58" s="10" t="s">
         <v>31</v>
@@ -4856,7 +4856,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B59" s="8">
         <v>46080.77828986111</v>
@@ -4868,16 +4868,16 @@
         <v>46210.17008761574</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="9" t="s">
+        <v>187</v>
+      </c>
+      <c r="H59" s="9" t="s">
         <v>188</v>
-      </c>
-      <c r="H59" s="9" t="s">
-        <v>189</v>
       </c>
       <c r="I59" s="8">
         <v>46216</v>
@@ -4895,16 +4895,16 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="P59" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="Q59" s="12" t="s">
         <v>219</v>
-      </c>
-      <c r="Q59" s="12" t="s">
-        <v>105</v>
       </c>
       <c r="R59" s="9">
         <v>1</v>
@@ -4939,10 +4939,10 @@
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="H60" s="6" t="s">
         <v>188</v>
-      </c>
-      <c r="H60" s="6" t="s">
-        <v>189</v>
       </c>
       <c r="I60" s="5">
         <v>46226</v>
@@ -4960,16 +4960,16 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="P60" s="6" t="s">
         <v>222</v>
       </c>
       <c r="Q60" s="11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R60" s="6">
         <v>1</v>
@@ -5004,10 +5004,10 @@
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
+        <v>187</v>
+      </c>
+      <c r="H61" s="9" t="s">
         <v>188</v>
-      </c>
-      <c r="H61" s="9" t="s">
-        <v>189</v>
       </c>
       <c r="I61" s="8">
         <v>46210</v>
@@ -5025,10 +5025,10 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="P61" s="9" t="s">
         <v>225</v>
@@ -5069,10 +5069,10 @@
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="H62" s="6" t="s">
         <v>188</v>
-      </c>
-      <c r="H62" s="6" t="s">
-        <v>189</v>
       </c>
       <c r="I62" s="5">
         <v>46199</v>
@@ -5090,10 +5090,10 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="P62" s="6" t="s">
         <v>227</v>
@@ -5207,7 +5207,7 @@
         <v>229</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="P64" s="6" t="s">
         <v>233</v>
@@ -5278,7 +5278,7 @@
         <v>237</v>
       </c>
       <c r="Q65" s="11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R65" s="9">
         <v>1</v>
@@ -5343,7 +5343,7 @@
         <v>237</v>
       </c>
       <c r="Q66" s="12" t="s">
-        <v>105</v>
+        <v>219</v>
       </c>
       <c r="R66" s="6">
         <v>1</v>
@@ -5408,7 +5408,7 @@
         <v>237</v>
       </c>
       <c r="Q67" s="11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R67" s="9">
         <v>1</v>
@@ -5434,7 +5434,7 @@
         <v>46133.62181768518</v>
       </c>
       <c r="D68" s="5">
-        <v>46206.19700435185</v>
+        <v>46214.19413130787</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>245</v>
@@ -5472,8 +5472,8 @@
       <c r="P68" s="6" t="s">
         <v>237</v>
       </c>
-      <c r="Q68" s="12" t="s">
-        <v>105</v>
+      <c r="Q68" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="R68" s="6">
         <v>1</v>
@@ -5502,7 +5502,7 @@
         <v>46133.621889710645</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>26</v>
@@ -5538,7 +5538,7 @@
         <v>249</v>
       </c>
       <c r="Q69" s="11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R69" s="9">
         <v>1</v>
@@ -5567,7 +5567,7 @@
         <v>46141.711773055555</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
@@ -5597,19 +5597,19 @@
         <v>229</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="P70" s="6" t="s">
         <v>251</v>
       </c>
       <c r="Q70" s="11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R70" s="6">
         <v>1</v>
       </c>
       <c r="S70" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="T70" s="5">
         <v>46234</v>
@@ -5711,19 +5711,19 @@
         <v>253</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="P72" s="6" t="s">
         <v>259</v>
       </c>
       <c r="Q72" s="11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R72" s="6">
         <v>1</v>
       </c>
       <c r="S72" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="T72" s="5">
         <v>46237</v>
@@ -5782,13 +5782,13 @@
         <v>263</v>
       </c>
       <c r="Q73" s="11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R73" s="9">
         <v>1</v>
       </c>
       <c r="S73" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="T73" s="8">
         <v>46238</v>
@@ -5817,10 +5817,10 @@
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="H74" s="6" t="s">
         <v>201</v>
-      </c>
-      <c r="H74" s="6" t="s">
-        <v>202</v>
       </c>
       <c r="I74" s="5">
         <v>46239</v>
@@ -5847,13 +5847,13 @@
         <v>266</v>
       </c>
       <c r="Q74" s="11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R74" s="6">
         <v>1</v>
       </c>
       <c r="S74" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="T74" s="5">
         <v>46239</v>
@@ -5882,10 +5882,10 @@
         <v>26</v>
       </c>
       <c r="G75" s="9" t="s">
+        <v>200</v>
+      </c>
+      <c r="H75" s="9" t="s">
         <v>201</v>
-      </c>
-      <c r="H75" s="9" t="s">
-        <v>202</v>
       </c>
       <c r="I75" s="8">
         <v>46240</v>
@@ -5912,13 +5912,13 @@
         <v>269</v>
       </c>
       <c r="Q75" s="11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R75" s="9">
         <v>1</v>
       </c>
       <c r="S75" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="T75" s="8">
         <v>46240</v>
@@ -6022,13 +6022,13 @@
         <v>271</v>
       </c>
       <c r="Q77" s="11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R77" s="9">
         <v>0</v>
       </c>
       <c r="S77" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="T77" s="8">
         <v>46241</v>
@@ -6085,13 +6085,13 @@
         <v>271</v>
       </c>
       <c r="Q78" s="11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R78" s="6">
         <v>0</v>
       </c>
       <c r="S78" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="T78" s="5">
         <v>46241</v>
@@ -6142,13 +6142,13 @@
         <v>26</v>
       </c>
       <c r="Q79" s="11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R79" s="9">
         <v>0</v>
       </c>
       <c r="S79" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="T79" s="9"/>
       <c r="U79" s="9"/>
@@ -6201,13 +6201,13 @@
         <v>284</v>
       </c>
       <c r="Q80" s="11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R80" s="6">
         <v>0</v>
       </c>
       <c r="S80" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="T80" s="5">
         <v>46241</v>
@@ -6264,13 +6264,13 @@
         <v>280</v>
       </c>
       <c r="Q81" s="11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R81" s="9">
         <v>0</v>
       </c>
       <c r="S81" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="T81" s="8">
         <v>46252</v>

--- a/data/50001524 - ATACAMA KOZAN.xlsx
+++ b/data/50001524 - ATACAMA KOZAN.xlsx
@@ -5369,7 +5369,7 @@
         <v>46133.62179804398</v>
       </c>
       <c r="D67" s="8">
-        <v>46133.62181490741</v>
+        <v>46216.19658863426</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>242</v>
@@ -5407,8 +5407,8 @@
       <c r="P67" s="9" t="s">
         <v>237</v>
       </c>
-      <c r="Q67" s="11" t="s">
-        <v>108</v>
+      <c r="Q67" s="12" t="s">
+        <v>219</v>
       </c>
       <c r="R67" s="9">
         <v>1</v>

--- a/data/50001524 - ATACAMA KOZAN.xlsx
+++ b/data/50001524 - ATACAMA KOZAN.xlsx
@@ -412,6 +412,9 @@
     <t>Generación OC motor,Fabricación motor,Planos motor proveedor</t>
   </si>
   <si>
+    <t>Media</t>
+  </si>
+  <si>
     <t>1213470416901260</t>
   </si>
   <si>
@@ -668,9 +671,6 @@
   </si>
   <si>
     <t>Bodega:,Montaje Alabe</t>
-  </si>
-  <si>
-    <t>Media</t>
   </si>
   <si>
     <t>1213470416901282</t>
@@ -3399,7 +3399,7 @@
         <v>46114.76327634259</v>
       </c>
       <c r="D35" s="8">
-        <v>46114.76329173611</v>
+        <v>46218.1834093287</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>131</v>
@@ -3437,8 +3437,8 @@
       <c r="P35" s="9" t="s">
         <v>98</v>
       </c>
-      <c r="Q35" s="11" t="s">
-        <v>108</v>
+      <c r="Q35" s="12" t="s">
+        <v>133</v>
       </c>
       <c r="R35" s="9">
         <v>1</v>
@@ -3455,7 +3455,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B36" s="5">
         <v>46080.77828773148</v>
@@ -3467,7 +3467,7 @@
         <v>46114.76319354167</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
@@ -3500,7 +3500,7 @@
         <v>77</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="Q36" s="11" t="s">
         <v>108</v>
@@ -3516,7 +3516,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B37" s="8">
         <v>46080.77828799769</v>
@@ -3528,7 +3528,7 @@
         <v>46114.763248877316</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>26</v>
@@ -3558,10 +3558,10 @@
         <v>131</v>
       </c>
       <c r="O37" s="9" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="P37" s="9" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="Q37" s="11" t="s">
         <v>108</v>
@@ -3577,7 +3577,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B38" s="5">
         <v>46080.77828825232</v>
@@ -3589,7 +3589,7 @@
         <v>46114.7632599537</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
@@ -3619,10 +3619,10 @@
         <v>131</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="Q38" s="11" t="s">
         <v>108</v>
@@ -3638,7 +3638,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B39" s="8">
         <v>46080.778288518515</v>
@@ -3650,16 +3650,16 @@
         <v>46149.197581886576</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="I39" s="8">
         <v>46100</v>
@@ -3680,7 +3680,7 @@
         <v>98</v>
       </c>
       <c r="O39" s="9" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="P39" s="9" t="s">
         <v>98</v>
@@ -3703,7 +3703,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B40" s="5">
         <v>46080.77828673611</v>
@@ -3715,16 +3715,16 @@
         <v>46121.8600697338</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="I40" s="5">
         <v>46100</v>
@@ -3742,13 +3742,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="Q40" s="11" t="s">
         <v>108</v>
@@ -3764,7 +3764,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B41" s="8">
         <v>46080.77828702546</v>
@@ -3776,16 +3776,16 @@
         <v>46121.86006597222</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="I41" s="8">
         <v>46120</v>
@@ -3803,13 +3803,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="9" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O41" s="9" t="s">
         <v>93</v>
       </c>
       <c r="P41" s="9" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Q41" s="11" t="s">
         <v>108</v>
@@ -3825,7 +3825,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B42" s="5">
         <v>46080.77828724537</v>
@@ -3837,16 +3837,16 @@
         <v>46210.17465634259</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="I42" s="5">
         <v>46100</v>
@@ -3867,7 +3867,7 @@
         <v>98</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>98</v>
@@ -3890,7 +3890,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B43" s="8">
         <v>46080.77828748843</v>
@@ -3902,16 +3902,16 @@
         <v>46114.76045094908</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="I43" s="8">
         <v>46100</v>
@@ -3929,13 +3929,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="O43" s="9" t="s">
         <v>90</v>
       </c>
       <c r="P43" s="9" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Q43" s="11" t="s">
         <v>108</v>
@@ -3951,7 +3951,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B44" s="5">
         <v>46080.77828770834</v>
@@ -3963,16 +3963,16 @@
         <v>46114.7604978125</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="I44" s="5">
         <v>46129</v>
@@ -3990,13 +3990,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q44" s="11" t="s">
         <v>108</v>
@@ -4012,7 +4012,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B45" s="8">
         <v>46080.778287939815</v>
@@ -4024,7 +4024,7 @@
         <v>46141.772341724536</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>25</v>
@@ -4048,7 +4048,7 @@
         <v>26</v>
       </c>
       <c r="O45" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="P45" s="9" t="s">
         <v>26</v>
@@ -4061,7 +4061,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B46" s="5">
         <v>46080.778288182875</v>
@@ -4073,16 +4073,16 @@
         <v>46127.67810105324</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="I46" s="5">
         <v>46098</v>
@@ -4100,13 +4100,13 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="O46" s="6" t="s">
         <v>67</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q46" s="10" t="s">
         <v>31</v>
@@ -4126,7 +4126,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B47" s="8">
         <v>46080.77828842592</v>
@@ -4138,16 +4138,16 @@
         <v>46158.16995894676</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="I47" s="8">
         <v>46140</v>
@@ -4165,13 +4165,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="O47" s="9" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="P47" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q47" s="10" t="s">
         <v>31</v>
@@ -4191,7 +4191,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B48" s="5">
         <v>46087.53644159722</v>
@@ -4203,16 +4203,16 @@
         <v>46161.20788581019</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="I48" s="6"/>
       <c r="J48" s="5">
@@ -4228,13 +4228,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q48" s="10" t="s">
         <v>31</v>
@@ -4254,7 +4254,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B49" s="8">
         <v>46087.536521331014</v>
@@ -4266,16 +4266,16 @@
         <v>46141.771787060185</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="I49" s="8">
         <v>46233</v>
@@ -4293,13 +4293,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="9" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P49" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q49" s="11" t="s">
         <v>108</v>
@@ -4319,7 +4319,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B50" s="5">
         <v>46080.77828866898</v>
@@ -4331,7 +4331,7 @@
         <v>46141.772585231476</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>25</v>
@@ -4355,7 +4355,7 @@
         <v>26</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>26</v>
@@ -4368,7 +4368,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B51" s="8">
         <v>46080.77828892361</v>
@@ -4380,16 +4380,16 @@
         <v>46151.18472762732</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="I51" s="8">
         <v>46149</v>
@@ -4407,13 +4407,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="O51" s="9" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q51" s="10" t="s">
         <v>31</v>
@@ -4433,7 +4433,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B52" s="5">
         <v>46080.77828760417</v>
@@ -4445,16 +4445,16 @@
         <v>46155.20414789351</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I52" s="5">
         <v>46153</v>
@@ -4472,13 +4472,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q52" s="10" t="s">
         <v>31</v>
@@ -4498,7 +4498,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B53" s="8">
         <v>46080.778288009256</v>
@@ -4510,7 +4510,7 @@
         <v>46141.77186175926</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>25</v>
@@ -4534,7 +4534,7 @@
         <v>26</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P53" s="9" t="s">
         <v>26</v>
@@ -4547,7 +4547,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B54" s="5">
         <v>46080.77828832176</v>
@@ -4559,16 +4559,16 @@
         <v>46165.18131118055</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="I54" s="5">
         <v>46155</v>
@@ -4586,13 +4586,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q54" s="10" t="s">
         <v>31</v>
@@ -4612,7 +4612,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B55" s="8">
         <v>46080.77828861111</v>
@@ -4624,16 +4624,16 @@
         <v>46170.185211909724</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H55" s="9" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="I55" s="8">
         <v>46167</v>
@@ -4651,13 +4651,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="9" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="P55" s="9" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q55" s="10" t="s">
         <v>31</v>
@@ -4677,7 +4677,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B56" s="5">
         <v>46080.778288912035</v>
@@ -4689,16 +4689,16 @@
         <v>46172.2027446875</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I56" s="5">
         <v>46170</v>
@@ -4716,13 +4716,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q56" s="10" t="s">
         <v>31</v>
@@ -4742,7 +4742,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B57" s="8">
         <v>46080.77828921296</v>
@@ -4754,7 +4754,7 @@
         <v>46141.77231675926</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>25</v>
@@ -4778,7 +4778,7 @@
         <v>26</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P57" s="9" t="s">
         <v>26</v>
@@ -4791,7 +4791,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B58" s="5">
         <v>46080.77828957176</v>
@@ -4803,16 +4803,16 @@
         <v>46156.16908381945</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="I58" s="5">
         <v>46154</v>
@@ -4830,13 +4830,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="O58" s="6" t="s">
         <v>128</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q58" s="10" t="s">
         <v>31</v>
@@ -4856,7 +4856,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B59" s="8">
         <v>46080.77828986111</v>
@@ -4865,19 +4865,19 @@
         <v>46133.621046631946</v>
       </c>
       <c r="D59" s="8">
-        <v>46210.17008761574</v>
+        <v>46218.18543643519</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="I59" s="8">
         <v>46216</v>
@@ -4895,16 +4895,16 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="O59" s="9" t="s">
         <v>128</v>
       </c>
       <c r="P59" s="9" t="s">
-        <v>218</v>
-      </c>
-      <c r="Q59" s="12" t="s">
         <v>219</v>
+      </c>
+      <c r="Q59" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="R59" s="9">
         <v>1</v>
@@ -4939,10 +4939,10 @@
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="I60" s="5">
         <v>46226</v>
@@ -4960,10 +4960,10 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="P60" s="6" t="s">
         <v>222</v>
@@ -5004,10 +5004,10 @@
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H61" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="I61" s="8">
         <v>46210</v>
@@ -5025,10 +5025,10 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="P61" s="9" t="s">
         <v>225</v>
@@ -5069,10 +5069,10 @@
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="I62" s="5">
         <v>46199</v>
@@ -5090,7 +5090,7 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="O62" s="6" t="s">
         <v>119</v>
@@ -5207,7 +5207,7 @@
         <v>229</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="P64" s="6" t="s">
         <v>233</v>
@@ -5343,7 +5343,7 @@
         <v>237</v>
       </c>
       <c r="Q66" s="12" t="s">
-        <v>219</v>
+        <v>133</v>
       </c>
       <c r="R66" s="6">
         <v>1</v>
@@ -5408,7 +5408,7 @@
         <v>237</v>
       </c>
       <c r="Q67" s="12" t="s">
-        <v>219</v>
+        <v>133</v>
       </c>
       <c r="R67" s="9">
         <v>1</v>
@@ -5502,7 +5502,7 @@
         <v>46133.621889710645</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>26</v>
@@ -5567,7 +5567,7 @@
         <v>46141.711773055555</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
@@ -5597,7 +5597,7 @@
         <v>229</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="P70" s="6" t="s">
         <v>251</v>
@@ -5711,7 +5711,7 @@
         <v>253</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="P72" s="6" t="s">
         <v>259</v>
@@ -5817,10 +5817,10 @@
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="I74" s="5">
         <v>46239</v>
@@ -5882,10 +5882,10 @@
         <v>26</v>
       </c>
       <c r="G75" s="9" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H75" s="9" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="I75" s="8">
         <v>46240</v>

--- a/data/50001524 - ATACAMA KOZAN.xlsx
+++ b/data/50001524 - ATACAMA KOZAN.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="998" uniqueCount="287">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="988" uniqueCount="284">
   <si>
     <t>50001524 - ATACAMA KOZAN</t>
   </si>
@@ -265,9 +265,6 @@
     <t>propuesta nucleo rodete</t>
   </si>
   <si>
-    <t>benjamin.bustos@zitron.com</t>
-  </si>
-  <si>
     <t>Propuesta compras:,Generación OC Rodete</t>
   </si>
   <si>
@@ -293,12 +290,6 @@
   </si>
   <si>
     <t>propuesta compras a codigo // aprovisionamiento</t>
-  </si>
-  <si>
-    <t>hugo isla martinez</t>
-  </si>
-  <si>
-    <t>hugo.isla@zitron.com</t>
   </si>
   <si>
     <t>Propuesta compras:,Fabricacion a codigo y compras locales</t>
@@ -2550,11 +2541,9 @@
         <v>26</v>
       </c>
       <c r="G21" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="H21" s="9" t="s">
-        <v>84</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H21" s="9"/>
       <c r="I21" s="8">
         <v>46098</v>
       </c>
@@ -2577,7 +2566,7 @@
         <v>64</v>
       </c>
       <c r="P21" s="9" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Q21" s="10" t="s">
         <v>31</v>
@@ -2597,7 +2586,7 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B22" s="5">
         <v>46080.78405931713</v>
@@ -2609,7 +2598,7 @@
         <v>46114.51309576389</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>26</v>
@@ -2642,7 +2631,7 @@
         <v>48</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="Q22" s="10" t="s">
         <v>31</v>
@@ -2662,7 +2651,7 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B23" s="8">
         <v>46080.778288113426</v>
@@ -2674,7 +2663,7 @@
         <v>46114.51327625</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F23" s="9" t="s">
         <v>26</v>
@@ -2707,7 +2696,7 @@
         <v>67</v>
       </c>
       <c r="P23" s="9" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="Q23" s="10" t="s">
         <v>31</v>
@@ -2727,7 +2716,7 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B24" s="5">
         <v>46080.77828840278</v>
@@ -2739,17 +2728,15 @@
         <v>46114.759732199076</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="H24" s="6" t="s">
-        <v>95</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H24" s="6"/>
       <c r="I24" s="5">
         <v>46098</v>
       </c>
@@ -2772,7 +2759,7 @@
         <v>67</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="Q24" s="10" t="s">
         <v>31</v>
@@ -2792,7 +2779,7 @@
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B25" s="8">
         <v>46080.778288692134</v>
@@ -2804,7 +2791,7 @@
         <v>46140.838952673614</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="F25" s="9" t="s">
         <v>25</v>
@@ -2828,7 +2815,7 @@
         <v>26</v>
       </c>
       <c r="O25" s="9" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="P25" s="9" t="s">
         <v>26</v>
@@ -2841,7 +2828,7 @@
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B26" s="5">
         <v>46080.778288981484</v>
@@ -2853,16 +2840,16 @@
         <v>46214.19413398148</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="I26" s="5">
         <v>46100</v>
@@ -2880,13 +2867,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="Q26" s="10" t="s">
         <v>31</v>
@@ -2906,7 +2893,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B27" s="8">
         <v>46080.77828601852</v>
@@ -2918,16 +2905,16 @@
         <v>46139.78108450232</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="I27" s="8">
         <v>46100</v>
@@ -2945,29 +2932,29 @@
         <v>26</v>
       </c>
       <c r="N27" s="9" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="O27" s="9" t="s">
         <v>80</v>
       </c>
       <c r="P27" s="9" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="Q27" s="11" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="R27" s="9">
         <v>0</v>
       </c>
       <c r="S27" s="10" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="T27" s="9"/>
       <c r="U27" s="9"/>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="B28" s="5">
         <v>46080.778286388886</v>
@@ -2979,16 +2966,16 @@
         <v>46139.78118329861</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="I28" s="5">
         <v>46101</v>
@@ -3006,29 +2993,29 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="Q28" s="11" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="R28" s="6">
         <v>0</v>
       </c>
       <c r="S28" s="10" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="T28" s="6"/>
       <c r="U28" s="6"/>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="B29" s="8">
         <v>46080.78421460648</v>
@@ -3040,16 +3027,16 @@
         <v>46199.207547604165</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="I29" s="8">
         <v>46092</v>
@@ -3067,13 +3054,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="9" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="O29" s="9" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="P29" s="9" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="Q29" s="10" t="s">
         <v>31</v>
@@ -3082,7 +3069,7 @@
         <v>1</v>
       </c>
       <c r="S29" s="10" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="T29" s="8">
         <v>46092</v>
@@ -3093,7 +3080,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B30" s="5">
         <v>46080.78464398148</v>
@@ -3105,16 +3092,16 @@
         <v>46114.761801307875</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="I30" s="5">
         <v>46092</v>
@@ -3132,13 +3119,13 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
@@ -3148,7 +3135,7 @@
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B31" s="8">
         <v>46080.78472030093</v>
@@ -3160,16 +3147,16 @@
         <v>46140.80895233796</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="I31" s="8">
         <v>46101</v>
@@ -3187,13 +3174,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="O31" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="O31" s="9" t="s">
-        <v>116</v>
-      </c>
       <c r="P31" s="9" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="Q31" s="9"/>
       <c r="R31" s="9"/>
@@ -3203,7 +3190,7 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="B32" s="5">
         <v>46080.77828665509</v>
@@ -3215,16 +3202,16 @@
         <v>46154.1920628125</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="I32" s="5">
         <v>46100</v>
@@ -3242,13 +3229,13 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="Q32" s="10" t="s">
         <v>31</v>
@@ -3268,7 +3255,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B33" s="8">
         <v>46080.7782869213</v>
@@ -3280,16 +3267,16 @@
         <v>46133.62086326389</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="I33" s="8">
         <v>46100</v>
@@ -3307,29 +3294,29 @@
         <v>26</v>
       </c>
       <c r="N33" s="9" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="O33" s="9" t="s">
         <v>83</v>
       </c>
       <c r="P33" s="9" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="Q33" s="11" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="R33" s="9">
         <v>0</v>
       </c>
       <c r="S33" s="10" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="T33" s="9"/>
       <c r="U33" s="9"/>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B34" s="5">
         <v>46080.778287187495</v>
@@ -3341,16 +3328,16 @@
         <v>46133.62090126157</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="I34" s="5">
         <v>46104</v>
@@ -3368,29 +3355,29 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="O34" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="O34" s="6" t="s">
-        <v>125</v>
-      </c>
       <c r="P34" s="6" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="Q34" s="11" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="R34" s="6">
         <v>0</v>
       </c>
       <c r="S34" s="10" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="T34" s="6"/>
       <c r="U34" s="6"/>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B35" s="8">
         <v>46080.77828746528</v>
@@ -3402,16 +3389,16 @@
         <v>46218.1834093287</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="I35" s="8">
         <v>46091</v>
@@ -3429,16 +3416,16 @@
         <v>26</v>
       </c>
       <c r="N35" s="9" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="O35" s="9" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="P35" s="9" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="Q35" s="12" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="R35" s="9">
         <v>1</v>
@@ -3455,7 +3442,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="B36" s="5">
         <v>46080.77828773148</v>
@@ -3467,16 +3454,16 @@
         <v>46114.76319354167</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="I36" s="5">
         <v>46091</v>
@@ -3494,29 +3481,29 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="O36" s="6" t="s">
         <v>77</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="Q36" s="11" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="R36" s="6">
         <v>0</v>
       </c>
       <c r="S36" s="10" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="T36" s="6"/>
       <c r="U36" s="6"/>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="B37" s="8">
         <v>46080.77828799769</v>
@@ -3528,16 +3515,16 @@
         <v>46114.763248877316</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="I37" s="8">
         <v>46100</v>
@@ -3555,29 +3542,29 @@
         <v>26</v>
       </c>
       <c r="N37" s="9" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="O37" s="9" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="P37" s="9" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="Q37" s="11" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="R37" s="9">
         <v>0</v>
       </c>
       <c r="S37" s="10" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="T37" s="9"/>
       <c r="U37" s="9"/>
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B38" s="5">
         <v>46080.77828825232</v>
@@ -3589,16 +3576,16 @@
         <v>46114.7632599537</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="I38" s="5">
         <v>46100</v>
@@ -3616,29 +3603,29 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="Q38" s="11" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="R38" s="6">
         <v>0</v>
       </c>
       <c r="S38" s="10" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="T38" s="6"/>
       <c r="U38" s="6"/>
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="B39" s="8">
         <v>46080.778288518515</v>
@@ -3650,16 +3637,16 @@
         <v>46149.197581886576</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="I39" s="8">
         <v>46100</v>
@@ -3677,13 +3664,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="9" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="O39" s="9" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="P39" s="9" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="Q39" s="10" t="s">
         <v>31</v>
@@ -3703,7 +3690,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="B40" s="5">
         <v>46080.77828673611</v>
@@ -3715,16 +3702,16 @@
         <v>46121.8600697338</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="I40" s="5">
         <v>46100</v>
@@ -3742,29 +3729,29 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="Q40" s="11" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="R40" s="6">
         <v>0</v>
       </c>
       <c r="S40" s="10" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="T40" s="6"/>
       <c r="U40" s="6"/>
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="B41" s="8">
         <v>46080.77828702546</v>
@@ -3776,16 +3763,16 @@
         <v>46121.86006597222</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="I41" s="8">
         <v>46120</v>
@@ -3803,29 +3790,29 @@
         <v>26</v>
       </c>
       <c r="N41" s="9" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="O41" s="9" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="P41" s="9" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="Q41" s="11" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="R41" s="9">
         <v>0</v>
       </c>
       <c r="S41" s="10" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="T41" s="9"/>
       <c r="U41" s="9"/>
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="B42" s="5">
         <v>46080.77828724537</v>
@@ -3837,16 +3824,16 @@
         <v>46210.17465634259</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="I42" s="5">
         <v>46100</v>
@@ -3864,13 +3851,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="Q42" s="10" t="s">
         <v>31</v>
@@ -3890,7 +3877,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B43" s="8">
         <v>46080.77828748843</v>
@@ -3902,16 +3889,16 @@
         <v>46114.76045094908</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="I43" s="8">
         <v>46100</v>
@@ -3929,29 +3916,29 @@
         <v>26</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="O43" s="9" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P43" s="9" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="Q43" s="11" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="R43" s="9">
         <v>0</v>
       </c>
       <c r="S43" s="10" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="T43" s="9"/>
       <c r="U43" s="9"/>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B44" s="5">
         <v>46080.77828770834</v>
@@ -3963,16 +3950,16 @@
         <v>46114.7604978125</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="I44" s="5">
         <v>46129</v>
@@ -3990,29 +3977,29 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="O44" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="O44" s="6" t="s">
-        <v>157</v>
-      </c>
       <c r="P44" s="6" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="Q44" s="11" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="R44" s="6">
         <v>0</v>
       </c>
       <c r="S44" s="10" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="T44" s="6"/>
       <c r="U44" s="6"/>
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="B45" s="8">
         <v>46080.778287939815</v>
@@ -4024,7 +4011,7 @@
         <v>46141.772341724536</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>25</v>
@@ -4048,7 +4035,7 @@
         <v>26</v>
       </c>
       <c r="O45" s="9" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="P45" s="9" t="s">
         <v>26</v>
@@ -4061,7 +4048,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="B46" s="5">
         <v>46080.778288182875</v>
@@ -4073,16 +4060,16 @@
         <v>46127.67810105324</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="I46" s="5">
         <v>46098</v>
@@ -4100,13 +4087,13 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="O46" s="6" t="s">
         <v>67</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="Q46" s="10" t="s">
         <v>31</v>
@@ -4126,7 +4113,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B47" s="8">
         <v>46080.77828842592</v>
@@ -4138,16 +4125,16 @@
         <v>46158.16995894676</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="I47" s="8">
         <v>46140</v>
@@ -4165,13 +4152,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="O47" s="9" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="P47" s="9" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="Q47" s="10" t="s">
         <v>31</v>
@@ -4191,7 +4178,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="B48" s="5">
         <v>46087.53644159722</v>
@@ -4203,16 +4190,16 @@
         <v>46161.20788581019</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="I48" s="6"/>
       <c r="J48" s="5">
@@ -4228,13 +4215,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="Q48" s="10" t="s">
         <v>31</v>
@@ -4254,7 +4241,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="B49" s="8">
         <v>46087.536521331014</v>
@@ -4266,16 +4253,16 @@
         <v>46141.771787060185</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="I49" s="8">
         <v>46233</v>
@@ -4293,16 +4280,16 @@
         <v>26</v>
       </c>
       <c r="N49" s="9" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="P49" s="9" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="Q49" s="11" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="R49" s="9">
         <v>1</v>
@@ -4319,7 +4306,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="B50" s="5">
         <v>46080.77828866898</v>
@@ -4331,7 +4318,7 @@
         <v>46141.772585231476</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>25</v>
@@ -4355,7 +4342,7 @@
         <v>26</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>26</v>
@@ -4368,7 +4355,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="B51" s="8">
         <v>46080.77828892361</v>
@@ -4380,16 +4367,16 @@
         <v>46151.18472762732</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="I51" s="8">
         <v>46149</v>
@@ -4407,13 +4394,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="O51" s="9" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="Q51" s="10" t="s">
         <v>31</v>
@@ -4433,7 +4420,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="B52" s="5">
         <v>46080.77828760417</v>
@@ -4445,16 +4432,16 @@
         <v>46155.20414789351</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="I52" s="5">
         <v>46153</v>
@@ -4472,13 +4459,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="O52" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="O52" s="6" t="s">
-        <v>187</v>
-      </c>
       <c r="P52" s="6" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="Q52" s="10" t="s">
         <v>31</v>
@@ -4498,7 +4485,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="B53" s="8">
         <v>46080.778288009256</v>
@@ -4510,7 +4497,7 @@
         <v>46141.77186175926</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>25</v>
@@ -4534,7 +4521,7 @@
         <v>26</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="P53" s="9" t="s">
         <v>26</v>
@@ -4547,7 +4534,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="B54" s="5">
         <v>46080.77828832176</v>
@@ -4559,16 +4546,16 @@
         <v>46165.18131118055</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="I54" s="5">
         <v>46155</v>
@@ -4586,13 +4573,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="Q54" s="10" t="s">
         <v>31</v>
@@ -4612,7 +4599,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="B55" s="8">
         <v>46080.77828861111</v>
@@ -4624,16 +4611,16 @@
         <v>46170.185211909724</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="H55" s="9" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="I55" s="8">
         <v>46167</v>
@@ -4651,13 +4638,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="9" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="P55" s="9" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="Q55" s="10" t="s">
         <v>31</v>
@@ -4677,7 +4664,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="B56" s="5">
         <v>46080.778288912035</v>
@@ -4689,16 +4676,16 @@
         <v>46172.2027446875</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="I56" s="5">
         <v>46170</v>
@@ -4716,13 +4703,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="Q56" s="10" t="s">
         <v>31</v>
@@ -4742,7 +4729,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="B57" s="8">
         <v>46080.77828921296</v>
@@ -4754,7 +4741,7 @@
         <v>46141.77231675926</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>25</v>
@@ -4778,7 +4765,7 @@
         <v>26</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="P57" s="9" t="s">
         <v>26</v>
@@ -4791,7 +4778,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="B58" s="5">
         <v>46080.77828957176</v>
@@ -4803,16 +4790,16 @@
         <v>46156.16908381945</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="I58" s="5">
         <v>46154</v>
@@ -4830,13 +4817,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="Q58" s="10" t="s">
         <v>31</v>
@@ -4856,7 +4843,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="B59" s="8">
         <v>46080.77828986111</v>
@@ -4868,16 +4855,16 @@
         <v>46218.18543643519</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="I59" s="8">
         <v>46216</v>
@@ -4895,13 +4882,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="P59" s="9" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="Q59" s="10" t="s">
         <v>31</v>
@@ -4921,7 +4908,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="B60" s="5">
         <v>46080.778290138885</v>
@@ -4933,16 +4920,16 @@
         <v>46121.867985185185</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="I60" s="5">
         <v>46226</v>
@@ -4960,16 +4947,16 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="Q60" s="11" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="R60" s="6">
         <v>1</v>
@@ -4986,7 +4973,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="B61" s="8">
         <v>46080.778290393515</v>
@@ -4998,16 +4985,16 @@
         <v>46212.18789364584</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="H61" s="9" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="I61" s="8">
         <v>46210</v>
@@ -5025,13 +5012,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="P61" s="9" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="Q61" s="10" t="s">
         <v>31</v>
@@ -5051,7 +5038,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="B62" s="5">
         <v>46080.7854796875</v>
@@ -5069,10 +5056,10 @@
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="I62" s="5">
         <v>46199</v>
@@ -5090,13 +5077,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="Q62" s="10" t="s">
         <v>31</v>
@@ -5116,7 +5103,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="B63" s="8">
         <v>46080.77828662037</v>
@@ -5128,7 +5115,7 @@
         <v>46141.71127789352</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>25</v>
@@ -5152,7 +5139,7 @@
         <v>26</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="P63" s="9" t="s">
         <v>26</v>
@@ -5165,7 +5152,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="B64" s="5">
         <v>46080.77828694445</v>
@@ -5177,17 +5164,15 @@
         <v>46192.18706700232</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="H64" s="6" t="s">
-        <v>84</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H64" s="6"/>
       <c r="I64" s="5">
         <v>46174</v>
       </c>
@@ -5204,13 +5189,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="Q64" s="10" t="s">
         <v>31</v>
@@ -5230,7 +5215,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="B65" s="8">
         <v>46080.778287187495</v>
@@ -5242,17 +5227,15 @@
         <v>46133.62091327546</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="H65" s="9" t="s">
-        <v>84</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H65" s="9"/>
       <c r="I65" s="8">
         <v>46230</v>
       </c>
@@ -5269,16 +5252,16 @@
         <v>26</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="O65" s="9" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="P65" s="9" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="Q65" s="11" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="R65" s="9">
         <v>1</v>
@@ -5295,7 +5278,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="B66" s="5">
         <v>46080.77828746528</v>
@@ -5307,17 +5290,15 @@
         <v>46212.17993510417</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="H66" s="6" t="s">
-        <v>84</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H66" s="6"/>
       <c r="I66" s="5">
         <v>46218</v>
       </c>
@@ -5334,16 +5315,16 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="Q66" s="12" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="R66" s="6">
         <v>1</v>
@@ -5360,7 +5341,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="B67" s="8">
         <v>46080.77828770834</v>
@@ -5372,17 +5353,15 @@
         <v>46216.19658863426</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="H67" s="9" t="s">
-        <v>84</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H67" s="9"/>
       <c r="I67" s="8">
         <v>46220</v>
       </c>
@@ -5399,16 +5378,16 @@
         <v>26</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="P67" s="9" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="Q67" s="12" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="R67" s="9">
         <v>1</v>
@@ -5425,7 +5404,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="B68" s="5">
         <v>46080.77828796297</v>
@@ -5437,17 +5416,15 @@
         <v>46214.19413130787</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="H68" s="6" t="s">
-        <v>84</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H68" s="6"/>
       <c r="I68" s="5">
         <v>46212</v>
       </c>
@@ -5464,13 +5441,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="Q68" s="10" t="s">
         <v>31</v>
@@ -5490,7 +5467,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="B69" s="8">
         <v>46080.778288217596</v>
@@ -5502,17 +5479,15 @@
         <v>46133.621889710645</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="H69" s="9" t="s">
-        <v>84</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H69" s="9"/>
       <c r="I69" s="8">
         <v>46232</v>
       </c>
@@ -5529,16 +5504,16 @@
         <v>26</v>
       </c>
       <c r="N69" s="9" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="P69" s="9" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="Q69" s="11" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="R69" s="9">
         <v>1</v>
@@ -5555,7 +5530,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="B70" s="5">
         <v>46080.77828846065</v>
@@ -5567,17 +5542,15 @@
         <v>46141.711773055555</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="H70" s="6" t="s">
-        <v>84</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H70" s="6"/>
       <c r="I70" s="5">
         <v>46234</v>
       </c>
@@ -5594,22 +5567,22 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="Q70" s="11" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="R70" s="6">
         <v>1</v>
       </c>
       <c r="S70" s="10" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="T70" s="5">
         <v>46234</v>
@@ -5620,7 +5593,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="B71" s="8">
         <v>46080.7782887037</v>
@@ -5632,7 +5605,7 @@
         <v>46141.712052731484</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>25</v>
@@ -5656,7 +5629,7 @@
         <v>26</v>
       </c>
       <c r="O71" s="9" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="P71" s="9" t="s">
         <v>26</v>
@@ -5669,7 +5642,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="B72" s="5">
         <v>46080.77828895833</v>
@@ -5681,16 +5654,16 @@
         <v>46141.711805625004</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="I72" s="5">
         <v>46237</v>
@@ -5708,22 +5681,22 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="Q72" s="11" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="R72" s="6">
         <v>1</v>
       </c>
       <c r="S72" s="10" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="T72" s="5">
         <v>46237</v>
@@ -5734,7 +5707,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="B73" s="8">
         <v>46080.778287152774</v>
@@ -5746,17 +5719,15 @@
         <v>46141.7118290162</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="H73" s="9" t="s">
-        <v>84</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H73" s="9"/>
       <c r="I73" s="8">
         <v>46238</v>
       </c>
@@ -5773,22 +5744,22 @@
         <v>26</v>
       </c>
       <c r="N73" s="9" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="P73" s="9" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="Q73" s="11" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="R73" s="9">
         <v>1</v>
       </c>
       <c r="S73" s="10" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="T73" s="8">
         <v>46238</v>
@@ -5799,7 +5770,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="B74" s="5">
         <v>46080.77828751157</v>
@@ -5811,16 +5782,16 @@
         <v>46141.711917002314</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="I74" s="5">
         <v>46239</v>
@@ -5838,22 +5809,22 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="Q74" s="11" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="R74" s="6">
         <v>1</v>
       </c>
       <c r="S74" s="10" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="T74" s="5">
         <v>46239</v>
@@ -5864,7 +5835,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="B75" s="8">
         <v>46080.77828782407</v>
@@ -5876,16 +5847,16 @@
         <v>46141.71196212963</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="9" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="H75" s="9" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="I75" s="8">
         <v>46240</v>
@@ -5903,22 +5874,22 @@
         <v>26</v>
       </c>
       <c r="N75" s="9" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="P75" s="9" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="Q75" s="11" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="R75" s="9">
         <v>1</v>
       </c>
       <c r="S75" s="10" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="T75" s="8">
         <v>46240</v>
@@ -5929,7 +5900,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="B76" s="5">
         <v>46080.77828809028</v>
@@ -5939,7 +5910,7 @@
         <v>46090.61092975695</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>25</v>
@@ -5963,7 +5934,7 @@
         <v>26</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="P76" s="6" t="s">
         <v>26</v>
@@ -5976,7 +5947,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="B77" s="8">
         <v>46080.77828868055</v>
@@ -5992,10 +5963,10 @@
         <v>26</v>
       </c>
       <c r="G77" s="9" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="H77" s="9" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="I77" s="8">
         <v>46241</v>
@@ -6013,22 +5984,22 @@
         <v>26</v>
       </c>
       <c r="N77" s="9" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="P77" s="9" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="Q77" s="11" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="R77" s="9">
         <v>0</v>
       </c>
       <c r="S77" s="10" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="T77" s="8">
         <v>46241</v>
@@ -6039,7 +6010,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="B78" s="5">
         <v>46080.77828835648</v>
@@ -6049,16 +6020,16 @@
         <v>46141.711970648146</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="I78" s="5">
         <v>46241</v>
@@ -6076,22 +6047,22 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="O78" s="6" t="s">
+        <v>265</v>
+      </c>
+      <c r="P78" s="6" t="s">
         <v>268</v>
       </c>
-      <c r="P78" s="6" t="s">
-        <v>271</v>
-      </c>
       <c r="Q78" s="11" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="R78" s="6">
         <v>0</v>
       </c>
       <c r="S78" s="10" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="T78" s="5">
         <v>46241</v>
@@ -6102,7 +6073,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="B79" s="8">
         <v>46090.61171577546</v>
@@ -6112,7 +6083,7 @@
         <v>46090.614530335646</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>25</v>
@@ -6136,26 +6107,26 @@
         <v>26</v>
       </c>
       <c r="O79" s="9" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="P79" s="9" t="s">
         <v>26</v>
       </c>
       <c r="Q79" s="11" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="R79" s="9">
         <v>0</v>
       </c>
       <c r="S79" s="10" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="T79" s="9"/>
       <c r="U79" s="9"/>
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="B80" s="5">
         <v>46090.61199928241</v>
@@ -6165,7 +6136,7 @@
         <v>46141.711971944445</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
@@ -6192,22 +6163,22 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="Q80" s="11" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="R80" s="6">
         <v>0</v>
       </c>
       <c r="S80" s="10" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="T80" s="5">
         <v>46241</v>
@@ -6218,7 +6189,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="B81" s="8">
         <v>46090.61208010417</v>
@@ -6228,7 +6199,7 @@
         <v>46090.61869820602</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>26</v>
@@ -6255,22 +6226,22 @@
         <v>26</v>
       </c>
       <c r="N81" s="9" t="s">
+        <v>277</v>
+      </c>
+      <c r="O81" s="9" t="s">
         <v>280</v>
       </c>
-      <c r="O81" s="9" t="s">
-        <v>283</v>
-      </c>
       <c r="P81" s="9" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="Q81" s="11" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="R81" s="9">
         <v>0</v>
       </c>
       <c r="S81" s="10" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="T81" s="8">
         <v>46252</v>

--- a/data/50001524 - ATACAMA KOZAN.xlsx
+++ b/data/50001524 - ATACAMA KOZAN.xlsx
@@ -4917,7 +4917,7 @@
         <v>46121.8679578125</v>
       </c>
       <c r="D60" s="5">
-        <v>46121.867985185185</v>
+        <v>46220.19441659722</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>218</v>
@@ -4955,8 +4955,8 @@
       <c r="P60" s="6" t="s">
         <v>219</v>
       </c>
-      <c r="Q60" s="11" t="s">
-        <v>105</v>
+      <c r="Q60" s="12" t="s">
+        <v>130</v>
       </c>
       <c r="R60" s="6">
         <v>1</v>
@@ -5287,7 +5287,7 @@
         <v>46133.62178611111</v>
       </c>
       <c r="D66" s="5">
-        <v>46212.17993510417</v>
+        <v>46220.19710090278</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>236</v>
@@ -5323,8 +5323,8 @@
       <c r="P66" s="6" t="s">
         <v>234</v>
       </c>
-      <c r="Q66" s="12" t="s">
-        <v>130</v>
+      <c r="Q66" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="R66" s="6">
         <v>1</v>

--- a/data/50001524 - ATACAMA KOZAN.xlsx
+++ b/data/50001524 - ATACAMA KOZAN.xlsx
@@ -1859,7 +1859,7 @@
         <v>46141.711601145835</v>
       </c>
       <c r="D10" s="5">
-        <v>46141.7116022338</v>
+        <v>46223.40299935185</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>45</v>

--- a/data/50001524 - ATACAMA KOZAN.xlsx
+++ b/data/50001524 - ATACAMA KOZAN.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="988" uniqueCount="284">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="997" uniqueCount="285">
   <si>
     <t>50001524 - ATACAMA KOZAN</t>
   </si>
@@ -263,6 +263,9 @@
   </si>
   <si>
     <t>propuesta nucleo rodete</t>
+  </si>
+  <si>
+    <t>nespinoza@zitron.com</t>
   </si>
   <si>
     <t>Propuesta compras:,Generación OC Rodete</t>
@@ -2532,7 +2535,7 @@
         <v>46126.85556609953</v>
       </c>
       <c r="D21" s="8">
-        <v>46126.855582199074</v>
+        <v>46223.80697723379</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>83</v>
@@ -2541,9 +2544,11 @@
         <v>26</v>
       </c>
       <c r="G21" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H21" s="9"/>
+        <v>84</v>
+      </c>
+      <c r="H21" s="9" t="s">
+        <v>84</v>
+      </c>
       <c r="I21" s="8">
         <v>46098</v>
       </c>
@@ -2566,7 +2571,7 @@
         <v>64</v>
       </c>
       <c r="P21" s="9" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q21" s="10" t="s">
         <v>31</v>
@@ -2586,7 +2591,7 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B22" s="5">
         <v>46080.78405931713</v>
@@ -2598,7 +2603,7 @@
         <v>46114.51309576389</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>26</v>
@@ -2631,7 +2636,7 @@
         <v>48</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="Q22" s="10" t="s">
         <v>31</v>
@@ -2651,7 +2656,7 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B23" s="8">
         <v>46080.778288113426</v>
@@ -2663,7 +2668,7 @@
         <v>46114.51327625</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F23" s="9" t="s">
         <v>26</v>
@@ -2696,7 +2701,7 @@
         <v>67</v>
       </c>
       <c r="P23" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="Q23" s="10" t="s">
         <v>31</v>
@@ -2716,7 +2721,7 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B24" s="5">
         <v>46080.77828840278</v>
@@ -2725,18 +2730,20 @@
         <v>46114.75971673611</v>
       </c>
       <c r="D24" s="5">
-        <v>46114.759732199076</v>
+        <v>46223.80697344907</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H24" s="6"/>
+        <v>84</v>
+      </c>
+      <c r="H24" s="6" t="s">
+        <v>84</v>
+      </c>
       <c r="I24" s="5">
         <v>46098</v>
       </c>
@@ -2759,7 +2766,7 @@
         <v>67</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="Q24" s="10" t="s">
         <v>31</v>
@@ -2779,7 +2786,7 @@
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B25" s="8">
         <v>46080.778288692134</v>
@@ -2791,7 +2798,7 @@
         <v>46140.838952673614</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F25" s="9" t="s">
         <v>25</v>
@@ -2815,7 +2822,7 @@
         <v>26</v>
       </c>
       <c r="O25" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="P25" s="9" t="s">
         <v>26</v>
@@ -2828,7 +2835,7 @@
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B26" s="5">
         <v>46080.778288981484</v>
@@ -2840,16 +2847,16 @@
         <v>46214.19413398148</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I26" s="5">
         <v>46100</v>
@@ -2867,13 +2874,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="Q26" s="10" t="s">
         <v>31</v>
@@ -2893,7 +2900,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B27" s="8">
         <v>46080.77828601852</v>
@@ -2905,16 +2912,16 @@
         <v>46139.78108450232</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I27" s="8">
         <v>46100</v>
@@ -2932,29 +2939,29 @@
         <v>26</v>
       </c>
       <c r="N27" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="O27" s="9" t="s">
         <v>80</v>
       </c>
       <c r="P27" s="9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="Q27" s="11" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="R27" s="9">
         <v>0</v>
       </c>
       <c r="S27" s="10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="T27" s="9"/>
       <c r="U27" s="9"/>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B28" s="5">
         <v>46080.778286388886</v>
@@ -2966,16 +2973,16 @@
         <v>46139.78118329861</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I28" s="5">
         <v>46101</v>
@@ -2993,29 +3000,29 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Q28" s="11" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="R28" s="6">
         <v>0</v>
       </c>
       <c r="S28" s="10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="T28" s="6"/>
       <c r="U28" s="6"/>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B29" s="8">
         <v>46080.78421460648</v>
@@ -3027,16 +3034,16 @@
         <v>46199.207547604165</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I29" s="8">
         <v>46092</v>
@@ -3054,13 +3061,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="O29" s="9" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="P29" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="Q29" s="10" t="s">
         <v>31</v>
@@ -3069,7 +3076,7 @@
         <v>1</v>
       </c>
       <c r="S29" s="10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="T29" s="8">
         <v>46092</v>
@@ -3080,7 +3087,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B30" s="5">
         <v>46080.78464398148</v>
@@ -3092,16 +3099,16 @@
         <v>46114.761801307875</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I30" s="5">
         <v>46092</v>
@@ -3119,13 +3126,13 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
@@ -3135,7 +3142,7 @@
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B31" s="8">
         <v>46080.78472030093</v>
@@ -3147,16 +3154,16 @@
         <v>46140.80895233796</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I31" s="8">
         <v>46101</v>
@@ -3174,13 +3181,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="9" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="O31" s="9" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="P31" s="9" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="Q31" s="9"/>
       <c r="R31" s="9"/>
@@ -3190,7 +3197,7 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B32" s="5">
         <v>46080.77828665509</v>
@@ -3202,16 +3209,16 @@
         <v>46154.1920628125</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I32" s="5">
         <v>46100</v>
@@ -3229,13 +3236,13 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="Q32" s="10" t="s">
         <v>31</v>
@@ -3255,7 +3262,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B33" s="8">
         <v>46080.7782869213</v>
@@ -3267,16 +3274,16 @@
         <v>46133.62086326389</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I33" s="8">
         <v>46100</v>
@@ -3294,29 +3301,29 @@
         <v>26</v>
       </c>
       <c r="N33" s="9" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="O33" s="9" t="s">
         <v>83</v>
       </c>
       <c r="P33" s="9" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="Q33" s="11" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="R33" s="9">
         <v>0</v>
       </c>
       <c r="S33" s="10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="T33" s="9"/>
       <c r="U33" s="9"/>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B34" s="5">
         <v>46080.778287187495</v>
@@ -3328,16 +3335,16 @@
         <v>46133.62090126157</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I34" s="5">
         <v>46104</v>
@@ -3355,29 +3362,29 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="Q34" s="11" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="R34" s="6">
         <v>0</v>
       </c>
       <c r="S34" s="10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="T34" s="6"/>
       <c r="U34" s="6"/>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B35" s="8">
         <v>46080.77828746528</v>
@@ -3389,16 +3396,16 @@
         <v>46218.1834093287</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I35" s="8">
         <v>46091</v>
@@ -3416,16 +3423,16 @@
         <v>26</v>
       </c>
       <c r="N35" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="O35" s="9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="P35" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="Q35" s="12" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="R35" s="9">
         <v>1</v>
@@ -3442,7 +3449,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B36" s="5">
         <v>46080.77828773148</v>
@@ -3454,16 +3461,16 @@
         <v>46114.76319354167</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I36" s="5">
         <v>46091</v>
@@ -3481,29 +3488,29 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O36" s="6" t="s">
         <v>77</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="Q36" s="11" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="R36" s="6">
         <v>0</v>
       </c>
       <c r="S36" s="10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="T36" s="6"/>
       <c r="U36" s="6"/>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B37" s="8">
         <v>46080.77828799769</v>
@@ -3515,16 +3522,16 @@
         <v>46114.763248877316</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I37" s="8">
         <v>46100</v>
@@ -3542,29 +3549,29 @@
         <v>26</v>
       </c>
       <c r="N37" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O37" s="9" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="P37" s="9" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="Q37" s="11" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="R37" s="9">
         <v>0</v>
       </c>
       <c r="S37" s="10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="T37" s="9"/>
       <c r="U37" s="9"/>
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B38" s="5">
         <v>46080.77828825232</v>
@@ -3576,16 +3583,16 @@
         <v>46114.7632599537</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I38" s="5">
         <v>46100</v>
@@ -3603,29 +3610,29 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="Q38" s="11" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="R38" s="6">
         <v>0</v>
       </c>
       <c r="S38" s="10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="T38" s="6"/>
       <c r="U38" s="6"/>
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B39" s="8">
         <v>46080.778288518515</v>
@@ -3637,16 +3644,16 @@
         <v>46149.197581886576</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="I39" s="8">
         <v>46100</v>
@@ -3664,13 +3671,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="O39" s="9" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="P39" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="Q39" s="10" t="s">
         <v>31</v>
@@ -3690,7 +3697,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B40" s="5">
         <v>46080.77828673611</v>
@@ -3702,16 +3709,16 @@
         <v>46121.8600697338</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="I40" s="5">
         <v>46100</v>
@@ -3729,29 +3736,29 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="Q40" s="11" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="R40" s="6">
         <v>0</v>
       </c>
       <c r="S40" s="10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="T40" s="6"/>
       <c r="U40" s="6"/>
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B41" s="8">
         <v>46080.77828702546</v>
@@ -3763,16 +3770,16 @@
         <v>46121.86006597222</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="I41" s="8">
         <v>46120</v>
@@ -3790,29 +3797,29 @@
         <v>26</v>
       </c>
       <c r="N41" s="9" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="O41" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="P41" s="9" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Q41" s="11" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="R41" s="9">
         <v>0</v>
       </c>
       <c r="S41" s="10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="T41" s="9"/>
       <c r="U41" s="9"/>
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B42" s="5">
         <v>46080.77828724537</v>
@@ -3824,16 +3831,16 @@
         <v>46210.17465634259</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="I42" s="5">
         <v>46100</v>
@@ -3851,13 +3858,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="Q42" s="10" t="s">
         <v>31</v>
@@ -3877,7 +3884,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B43" s="8">
         <v>46080.77828748843</v>
@@ -3889,16 +3896,16 @@
         <v>46114.76045094908</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="I43" s="8">
         <v>46100</v>
@@ -3916,29 +3923,29 @@
         <v>26</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O43" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="P43" s="9" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Q43" s="11" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="R43" s="9">
         <v>0</v>
       </c>
       <c r="S43" s="10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="T43" s="9"/>
       <c r="U43" s="9"/>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B44" s="5">
         <v>46080.77828770834</v>
@@ -3950,16 +3957,16 @@
         <v>46114.7604978125</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="I44" s="5">
         <v>46129</v>
@@ -3977,29 +3984,29 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q44" s="11" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="R44" s="6">
         <v>0</v>
       </c>
       <c r="S44" s="10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="T44" s="6"/>
       <c r="U44" s="6"/>
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B45" s="8">
         <v>46080.778287939815</v>
@@ -4011,7 +4018,7 @@
         <v>46141.772341724536</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>25</v>
@@ -4035,7 +4042,7 @@
         <v>26</v>
       </c>
       <c r="O45" s="9" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="P45" s="9" t="s">
         <v>26</v>
@@ -4048,7 +4055,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B46" s="5">
         <v>46080.778288182875</v>
@@ -4060,16 +4067,16 @@
         <v>46127.67810105324</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="I46" s="5">
         <v>46098</v>
@@ -4087,13 +4094,13 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O46" s="6" t="s">
         <v>67</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q46" s="10" t="s">
         <v>31</v>
@@ -4113,7 +4120,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B47" s="8">
         <v>46080.77828842592</v>
@@ -4125,16 +4132,16 @@
         <v>46158.16995894676</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="I47" s="8">
         <v>46140</v>
@@ -4152,13 +4159,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O47" s="9" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="P47" s="9" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q47" s="10" t="s">
         <v>31</v>
@@ -4178,7 +4185,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B48" s="5">
         <v>46087.53644159722</v>
@@ -4190,16 +4197,16 @@
         <v>46161.20788581019</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="I48" s="6"/>
       <c r="J48" s="5">
@@ -4215,13 +4222,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q48" s="10" t="s">
         <v>31</v>
@@ -4241,7 +4248,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B49" s="8">
         <v>46087.536521331014</v>
@@ -4253,16 +4260,16 @@
         <v>46141.771787060185</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="I49" s="8">
         <v>46233</v>
@@ -4280,16 +4287,16 @@
         <v>26</v>
       </c>
       <c r="N49" s="9" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="P49" s="9" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q49" s="11" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="R49" s="9">
         <v>1</v>
@@ -4306,7 +4313,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B50" s="5">
         <v>46080.77828866898</v>
@@ -4318,7 +4325,7 @@
         <v>46141.772585231476</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>25</v>
@@ -4342,7 +4349,7 @@
         <v>26</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>26</v>
@@ -4355,7 +4362,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B51" s="8">
         <v>46080.77828892361</v>
@@ -4367,16 +4374,16 @@
         <v>46151.18472762732</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I51" s="8">
         <v>46149</v>
@@ -4394,13 +4401,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="O51" s="9" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q51" s="10" t="s">
         <v>31</v>
@@ -4420,7 +4427,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B52" s="5">
         <v>46080.77828760417</v>
@@ -4432,16 +4439,16 @@
         <v>46155.20414789351</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="I52" s="5">
         <v>46153</v>
@@ -4459,13 +4466,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q52" s="10" t="s">
         <v>31</v>
@@ -4485,7 +4492,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B53" s="8">
         <v>46080.778288009256</v>
@@ -4497,7 +4504,7 @@
         <v>46141.77186175926</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>25</v>
@@ -4521,7 +4528,7 @@
         <v>26</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="P53" s="9" t="s">
         <v>26</v>
@@ -4534,7 +4541,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B54" s="5">
         <v>46080.77828832176</v>
@@ -4546,16 +4553,16 @@
         <v>46165.18131118055</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I54" s="5">
         <v>46155</v>
@@ -4573,13 +4580,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q54" s="10" t="s">
         <v>31</v>
@@ -4599,7 +4606,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B55" s="8">
         <v>46080.77828861111</v>
@@ -4611,16 +4618,16 @@
         <v>46170.185211909724</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H55" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I55" s="8">
         <v>46167</v>
@@ -4638,13 +4645,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="P55" s="9" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q55" s="10" t="s">
         <v>31</v>
@@ -4664,7 +4671,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B56" s="5">
         <v>46080.778288912035</v>
@@ -4676,16 +4683,16 @@
         <v>46172.2027446875</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="I56" s="5">
         <v>46170</v>
@@ -4703,13 +4710,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q56" s="10" t="s">
         <v>31</v>
@@ -4729,7 +4736,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B57" s="8">
         <v>46080.77828921296</v>
@@ -4741,7 +4748,7 @@
         <v>46141.77231675926</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>25</v>
@@ -4765,7 +4772,7 @@
         <v>26</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P57" s="9" t="s">
         <v>26</v>
@@ -4778,7 +4785,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B58" s="5">
         <v>46080.77828957176</v>
@@ -4790,16 +4797,16 @@
         <v>46156.16908381945</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I58" s="5">
         <v>46154</v>
@@ -4817,13 +4824,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q58" s="10" t="s">
         <v>31</v>
@@ -4843,7 +4850,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B59" s="8">
         <v>46080.77828986111</v>
@@ -4855,16 +4862,16 @@
         <v>46218.18543643519</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I59" s="8">
         <v>46216</v>
@@ -4882,13 +4889,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="P59" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q59" s="10" t="s">
         <v>31</v>
@@ -4908,7 +4915,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B60" s="5">
         <v>46080.778290138885</v>
@@ -4920,16 +4927,16 @@
         <v>46220.19441659722</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I60" s="5">
         <v>46226</v>
@@ -4947,16 +4954,16 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q60" s="12" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="R60" s="6">
         <v>1</v>
@@ -4973,7 +4980,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B61" s="8">
         <v>46080.778290393515</v>
@@ -4985,16 +4992,16 @@
         <v>46212.18789364584</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H61" s="9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I61" s="8">
         <v>46210</v>
@@ -5012,13 +5019,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P61" s="9" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q61" s="10" t="s">
         <v>31</v>
@@ -5038,7 +5045,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B62" s="5">
         <v>46080.7854796875</v>
@@ -5056,10 +5063,10 @@
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I62" s="5">
         <v>46199</v>
@@ -5077,13 +5084,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q62" s="10" t="s">
         <v>31</v>
@@ -5103,7 +5110,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B63" s="8">
         <v>46080.77828662037</v>
@@ -5115,7 +5122,7 @@
         <v>46141.71127789352</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>25</v>
@@ -5139,7 +5146,7 @@
         <v>26</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="P63" s="9" t="s">
         <v>26</v>
@@ -5152,7 +5159,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B64" s="5">
         <v>46080.77828694445</v>
@@ -5161,18 +5168,20 @@
         <v>46133.62079252314</v>
       </c>
       <c r="D64" s="5">
-        <v>46192.18706700232</v>
+        <v>46223.80691788194</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H64" s="6"/>
+        <v>84</v>
+      </c>
+      <c r="H64" s="6" t="s">
+        <v>84</v>
+      </c>
       <c r="I64" s="5">
         <v>46174</v>
       </c>
@@ -5189,13 +5198,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q64" s="10" t="s">
         <v>31</v>
@@ -5215,7 +5224,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B65" s="8">
         <v>46080.778287187495</v>
@@ -5224,18 +5233,20 @@
         <v>46133.620870451385</v>
       </c>
       <c r="D65" s="8">
-        <v>46133.62091327546</v>
+        <v>46223.8069141088</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H65" s="9"/>
+        <v>84</v>
+      </c>
+      <c r="H65" s="9" t="s">
+        <v>84</v>
+      </c>
       <c r="I65" s="8">
         <v>46230</v>
       </c>
@@ -5252,16 +5263,16 @@
         <v>26</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="O65" s="9" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="P65" s="9" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q65" s="11" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="R65" s="9">
         <v>1</v>
@@ -5278,7 +5289,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B66" s="5">
         <v>46080.77828746528</v>
@@ -5287,18 +5298,20 @@
         <v>46133.62178611111</v>
       </c>
       <c r="D66" s="5">
-        <v>46220.19710090278</v>
+        <v>46223.80691021991</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H66" s="6"/>
+        <v>84</v>
+      </c>
+      <c r="H66" s="6" t="s">
+        <v>84</v>
+      </c>
       <c r="I66" s="5">
         <v>46218</v>
       </c>
@@ -5315,13 +5328,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q66" s="10" t="s">
         <v>31</v>
@@ -5341,7 +5354,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B67" s="8">
         <v>46080.77828770834</v>
@@ -5350,18 +5363,20 @@
         <v>46133.62179804398</v>
       </c>
       <c r="D67" s="8">
-        <v>46216.19658863426</v>
+        <v>46223.80690626157</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H67" s="9"/>
+        <v>84</v>
+      </c>
+      <c r="H67" s="9" t="s">
+        <v>84</v>
+      </c>
       <c r="I67" s="8">
         <v>46220</v>
       </c>
@@ -5378,16 +5393,16 @@
         <v>26</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="P67" s="9" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q67" s="12" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="R67" s="9">
         <v>1</v>
@@ -5404,7 +5419,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B68" s="5">
         <v>46080.77828796297</v>
@@ -5413,18 +5428,20 @@
         <v>46133.62181768518</v>
       </c>
       <c r="D68" s="5">
-        <v>46214.19413130787</v>
+        <v>46223.80690207176</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H68" s="6"/>
+        <v>84</v>
+      </c>
+      <c r="H68" s="6" t="s">
+        <v>84</v>
+      </c>
       <c r="I68" s="5">
         <v>46212</v>
       </c>
@@ -5441,13 +5458,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q68" s="10" t="s">
         <v>31</v>
@@ -5467,7 +5484,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B69" s="8">
         <v>46080.778288217596</v>
@@ -5476,18 +5493,20 @@
         <v>46133.621873553246</v>
       </c>
       <c r="D69" s="8">
-        <v>46133.621889710645</v>
+        <v>46223.806898055554</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H69" s="9"/>
+        <v>84</v>
+      </c>
+      <c r="H69" s="9" t="s">
+        <v>84</v>
+      </c>
       <c r="I69" s="8">
         <v>46232</v>
       </c>
@@ -5504,16 +5523,16 @@
         <v>26</v>
       </c>
       <c r="N69" s="9" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="P69" s="9" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q69" s="11" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="R69" s="9">
         <v>1</v>
@@ -5530,7 +5549,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B70" s="5">
         <v>46080.77828846065</v>
@@ -5539,18 +5558,20 @@
         <v>46140.8390024074</v>
       </c>
       <c r="D70" s="5">
-        <v>46141.711773055555</v>
+        <v>46223.80689234954</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H70" s="6"/>
+        <v>84</v>
+      </c>
+      <c r="H70" s="6" t="s">
+        <v>84</v>
+      </c>
       <c r="I70" s="5">
         <v>46234</v>
       </c>
@@ -5567,22 +5588,22 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q70" s="11" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="R70" s="6">
         <v>1</v>
       </c>
       <c r="S70" s="10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="T70" s="5">
         <v>46234</v>
@@ -5593,7 +5614,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B71" s="8">
         <v>46080.7782887037</v>
@@ -5605,7 +5626,7 @@
         <v>46141.712052731484</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>25</v>
@@ -5629,7 +5650,7 @@
         <v>26</v>
       </c>
       <c r="O71" s="9" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="P71" s="9" t="s">
         <v>26</v>
@@ -5642,7 +5663,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B72" s="5">
         <v>46080.77828895833</v>
@@ -5654,16 +5675,16 @@
         <v>46141.711805625004</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="I72" s="5">
         <v>46237</v>
@@ -5681,22 +5702,22 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q72" s="11" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="R72" s="6">
         <v>1</v>
       </c>
       <c r="S72" s="10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="T72" s="5">
         <v>46237</v>
@@ -5707,7 +5728,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B73" s="8">
         <v>46080.778287152774</v>
@@ -5719,7 +5740,7 @@
         <v>46141.7118290162</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>26</v>
@@ -5744,22 +5765,22 @@
         <v>26</v>
       </c>
       <c r="N73" s="9" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="P73" s="9" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q73" s="11" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="R73" s="9">
         <v>1</v>
       </c>
       <c r="S73" s="10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="T73" s="8">
         <v>46238</v>
@@ -5770,7 +5791,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B74" s="5">
         <v>46080.77828751157</v>
@@ -5782,16 +5803,16 @@
         <v>46141.711917002314</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I74" s="5">
         <v>46239</v>
@@ -5809,22 +5830,22 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q74" s="11" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="R74" s="6">
         <v>1</v>
       </c>
       <c r="S74" s="10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="T74" s="5">
         <v>46239</v>
@@ -5835,7 +5856,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B75" s="8">
         <v>46080.77828782407</v>
@@ -5847,16 +5868,16 @@
         <v>46141.71196212963</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H75" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I75" s="8">
         <v>46240</v>
@@ -5874,22 +5895,22 @@
         <v>26</v>
       </c>
       <c r="N75" s="9" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="P75" s="9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q75" s="11" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="R75" s="9">
         <v>1</v>
       </c>
       <c r="S75" s="10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="T75" s="8">
         <v>46240</v>
@@ -5900,7 +5921,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B76" s="5">
         <v>46080.77828809028</v>
@@ -5910,7 +5931,7 @@
         <v>46090.61092975695</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>25</v>
@@ -5934,7 +5955,7 @@
         <v>26</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="P76" s="6" t="s">
         <v>26</v>
@@ -5947,7 +5968,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B77" s="8">
         <v>46080.77828868055</v>
@@ -5963,10 +5984,10 @@
         <v>26</v>
       </c>
       <c r="G77" s="9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H77" s="9" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="I77" s="8">
         <v>46241</v>
@@ -5984,22 +6005,22 @@
         <v>26</v>
       </c>
       <c r="N77" s="9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="P77" s="9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q77" s="11" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="R77" s="9">
         <v>0</v>
       </c>
       <c r="S77" s="10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="T77" s="8">
         <v>46241</v>
@@ -6010,7 +6031,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B78" s="5">
         <v>46080.77828835648</v>
@@ -6020,16 +6041,16 @@
         <v>46141.711970648146</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="I78" s="5">
         <v>46241</v>
@@ -6047,22 +6068,22 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q78" s="11" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="R78" s="6">
         <v>0</v>
       </c>
       <c r="S78" s="10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="T78" s="5">
         <v>46241</v>
@@ -6073,7 +6094,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B79" s="8">
         <v>46090.61171577546</v>
@@ -6083,7 +6104,7 @@
         <v>46090.614530335646</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>25</v>
@@ -6107,26 +6128,26 @@
         <v>26</v>
       </c>
       <c r="O79" s="9" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="P79" s="9" t="s">
         <v>26</v>
       </c>
       <c r="Q79" s="11" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="R79" s="9">
         <v>0</v>
       </c>
       <c r="S79" s="10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="T79" s="9"/>
       <c r="U79" s="9"/>
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B80" s="5">
         <v>46090.61199928241</v>
@@ -6136,7 +6157,7 @@
         <v>46141.711971944445</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
@@ -6163,22 +6184,22 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q80" s="11" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="R80" s="6">
         <v>0</v>
       </c>
       <c r="S80" s="10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="T80" s="5">
         <v>46241</v>
@@ -6189,7 +6210,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B81" s="8">
         <v>46090.61208010417</v>
@@ -6199,7 +6220,7 @@
         <v>46090.61869820602</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>26</v>
@@ -6226,22 +6247,22 @@
         <v>26</v>
       </c>
       <c r="N81" s="9" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="P81" s="9" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q81" s="11" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="R81" s="9">
         <v>0</v>
       </c>
       <c r="S81" s="10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="T81" s="8">
         <v>46252</v>

--- a/data/50001524 - ATACAMA KOZAN.xlsx
+++ b/data/50001524 - ATACAMA KOZAN.xlsx
@@ -5233,7 +5233,7 @@
         <v>46133.620870451385</v>
       </c>
       <c r="D65" s="8">
-        <v>46223.8069141088</v>
+        <v>46224.18165298611</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>233</v>
@@ -5271,8 +5271,8 @@
       <c r="P65" s="9" t="s">
         <v>235</v>
       </c>
-      <c r="Q65" s="11" t="s">
-        <v>106</v>
+      <c r="Q65" s="12" t="s">
+        <v>131</v>
       </c>
       <c r="R65" s="9">
         <v>1</v>
@@ -5363,7 +5363,7 @@
         <v>46133.62179804398</v>
       </c>
       <c r="D67" s="8">
-        <v>46223.80690626157</v>
+        <v>46224.20544344907</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>240</v>
@@ -5401,8 +5401,8 @@
       <c r="P67" s="9" t="s">
         <v>235</v>
       </c>
-      <c r="Q67" s="12" t="s">
-        <v>131</v>
+      <c r="Q67" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="R67" s="9">
         <v>1</v>

--- a/data/50001524 - ATACAMA KOZAN.xlsx
+++ b/data/50001524 - ATACAMA KOZAN.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="997" uniqueCount="285">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="998" uniqueCount="285">
   <si>
     <t>50001524 - ATACAMA KOZAN</t>
   </si>
@@ -5737,7 +5737,7 @@
         <v>46141.711726180554</v>
       </c>
       <c r="D73" s="8">
-        <v>46141.7118290162</v>
+        <v>46224.575120925925</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>259</v>
@@ -5746,9 +5746,11 @@
         <v>26</v>
       </c>
       <c r="G73" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H73" s="9"/>
+        <v>84</v>
+      </c>
+      <c r="H73" s="9" t="s">
+        <v>84</v>
+      </c>
       <c r="I73" s="8">
         <v>46238</v>
       </c>

--- a/data/50001524 - ATACAMA KOZAN.xlsx
+++ b/data/50001524 - ATACAMA KOZAN.xlsx
@@ -5493,7 +5493,7 @@
         <v>46133.621873553246</v>
       </c>
       <c r="D69" s="8">
-        <v>46223.806898055554</v>
+        <v>46225.18881381945</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>179</v>
@@ -5531,8 +5531,8 @@
       <c r="P69" s="9" t="s">
         <v>247</v>
       </c>
-      <c r="Q69" s="11" t="s">
-        <v>106</v>
+      <c r="Q69" s="12" t="s">
+        <v>131</v>
       </c>
       <c r="R69" s="9">
         <v>1</v>

--- a/data/50001524 - ATACAMA KOZAN.xlsx
+++ b/data/50001524 - ATACAMA KOZAN.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="998" uniqueCount="285">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="998" uniqueCount="286">
   <si>
     <t>50001524 - ATACAMA KOZAN</t>
   </si>
@@ -263,6 +263,9 @@
   </si>
   <si>
     <t>propuesta nucleo rodete</t>
+  </si>
+  <si>
+    <t>NATALYA ESPINOZA</t>
   </si>
   <si>
     <t>nespinoza@zitron.com</t>
@@ -2547,7 +2550,7 @@
         <v>84</v>
       </c>
       <c r="H21" s="9" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I21" s="8">
         <v>46098</v>
@@ -2571,7 +2574,7 @@
         <v>64</v>
       </c>
       <c r="P21" s="9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="Q21" s="10" t="s">
         <v>31</v>
@@ -2591,7 +2594,7 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B22" s="5">
         <v>46080.78405931713</v>
@@ -2603,7 +2606,7 @@
         <v>46114.51309576389</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>26</v>
@@ -2636,7 +2639,7 @@
         <v>48</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="Q22" s="10" t="s">
         <v>31</v>
@@ -2656,7 +2659,7 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B23" s="8">
         <v>46080.778288113426</v>
@@ -2668,7 +2671,7 @@
         <v>46114.51327625</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F23" s="9" t="s">
         <v>26</v>
@@ -2701,7 +2704,7 @@
         <v>67</v>
       </c>
       <c r="P23" s="9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="Q23" s="10" t="s">
         <v>31</v>
@@ -2721,7 +2724,7 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B24" s="5">
         <v>46080.77828840278</v>
@@ -2733,7 +2736,7 @@
         <v>46223.80697344907</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
@@ -2742,7 +2745,7 @@
         <v>84</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I24" s="5">
         <v>46098</v>
@@ -2766,7 +2769,7 @@
         <v>67</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="Q24" s="10" t="s">
         <v>31</v>
@@ -2786,7 +2789,7 @@
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B25" s="8">
         <v>46080.778288692134</v>
@@ -2798,7 +2801,7 @@
         <v>46140.838952673614</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F25" s="9" t="s">
         <v>25</v>
@@ -2822,7 +2825,7 @@
         <v>26</v>
       </c>
       <c r="O25" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="P25" s="9" t="s">
         <v>26</v>
@@ -2835,7 +2838,7 @@
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B26" s="5">
         <v>46080.778288981484</v>
@@ -2847,16 +2850,16 @@
         <v>46214.19413398148</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I26" s="5">
         <v>46100</v>
@@ -2874,13 +2877,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="Q26" s="10" t="s">
         <v>31</v>
@@ -2900,7 +2903,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B27" s="8">
         <v>46080.77828601852</v>
@@ -2912,16 +2915,16 @@
         <v>46139.78108450232</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I27" s="8">
         <v>46100</v>
@@ -2939,29 +2942,29 @@
         <v>26</v>
       </c>
       <c r="N27" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="O27" s="9" t="s">
         <v>80</v>
       </c>
       <c r="P27" s="9" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="Q27" s="11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="R27" s="9">
         <v>0</v>
       </c>
       <c r="S27" s="10" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="T27" s="9"/>
       <c r="U27" s="9"/>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B28" s="5">
         <v>46080.778286388886</v>
@@ -2973,16 +2976,16 @@
         <v>46139.78118329861</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I28" s="5">
         <v>46101</v>
@@ -3000,29 +3003,29 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="Q28" s="11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="R28" s="6">
         <v>0</v>
       </c>
       <c r="S28" s="10" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="T28" s="6"/>
       <c r="U28" s="6"/>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B29" s="8">
         <v>46080.78421460648</v>
@@ -3034,16 +3037,16 @@
         <v>46199.207547604165</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I29" s="8">
         <v>46092</v>
@@ -3061,13 +3064,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="O29" s="9" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="P29" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="Q29" s="10" t="s">
         <v>31</v>
@@ -3076,7 +3079,7 @@
         <v>1</v>
       </c>
       <c r="S29" s="10" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="T29" s="8">
         <v>46092</v>
@@ -3087,7 +3090,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B30" s="5">
         <v>46080.78464398148</v>
@@ -3099,16 +3102,16 @@
         <v>46114.761801307875</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I30" s="5">
         <v>46092</v>
@@ -3126,13 +3129,13 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
@@ -3142,7 +3145,7 @@
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B31" s="8">
         <v>46080.78472030093</v>
@@ -3154,16 +3157,16 @@
         <v>46140.80895233796</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I31" s="8">
         <v>46101</v>
@@ -3181,13 +3184,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="9" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="O31" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="P31" s="9" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="Q31" s="9"/>
       <c r="R31" s="9"/>
@@ -3197,7 +3200,7 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B32" s="5">
         <v>46080.77828665509</v>
@@ -3209,16 +3212,16 @@
         <v>46154.1920628125</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I32" s="5">
         <v>46100</v>
@@ -3236,13 +3239,13 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="Q32" s="10" t="s">
         <v>31</v>
@@ -3262,7 +3265,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B33" s="8">
         <v>46080.7782869213</v>
@@ -3274,16 +3277,16 @@
         <v>46133.62086326389</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I33" s="8">
         <v>46100</v>
@@ -3301,29 +3304,29 @@
         <v>26</v>
       </c>
       <c r="N33" s="9" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O33" s="9" t="s">
         <v>83</v>
       </c>
       <c r="P33" s="9" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="Q33" s="11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="R33" s="9">
         <v>0</v>
       </c>
       <c r="S33" s="10" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="T33" s="9"/>
       <c r="U33" s="9"/>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B34" s="5">
         <v>46080.778287187495</v>
@@ -3335,16 +3338,16 @@
         <v>46133.62090126157</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I34" s="5">
         <v>46104</v>
@@ -3362,29 +3365,29 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="Q34" s="11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="R34" s="6">
         <v>0</v>
       </c>
       <c r="S34" s="10" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="T34" s="6"/>
       <c r="U34" s="6"/>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B35" s="8">
         <v>46080.77828746528</v>
@@ -3396,16 +3399,16 @@
         <v>46218.1834093287</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I35" s="8">
         <v>46091</v>
@@ -3423,16 +3426,16 @@
         <v>26</v>
       </c>
       <c r="N35" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="O35" s="9" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="P35" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="Q35" s="12" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="R35" s="9">
         <v>1</v>
@@ -3449,7 +3452,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B36" s="5">
         <v>46080.77828773148</v>
@@ -3461,16 +3464,16 @@
         <v>46114.76319354167</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I36" s="5">
         <v>46091</v>
@@ -3488,29 +3491,29 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="O36" s="6" t="s">
         <v>77</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="Q36" s="11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="R36" s="6">
         <v>0</v>
       </c>
       <c r="S36" s="10" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="T36" s="6"/>
       <c r="U36" s="6"/>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B37" s="8">
         <v>46080.77828799769</v>
@@ -3522,16 +3525,16 @@
         <v>46114.763248877316</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I37" s="8">
         <v>46100</v>
@@ -3549,29 +3552,29 @@
         <v>26</v>
       </c>
       <c r="N37" s="9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="O37" s="9" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="P37" s="9" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="Q37" s="11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="R37" s="9">
         <v>0</v>
       </c>
       <c r="S37" s="10" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="T37" s="9"/>
       <c r="U37" s="9"/>
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B38" s="5">
         <v>46080.77828825232</v>
@@ -3583,16 +3586,16 @@
         <v>46114.7632599537</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I38" s="5">
         <v>46100</v>
@@ -3610,29 +3613,29 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="Q38" s="11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="R38" s="6">
         <v>0</v>
       </c>
       <c r="S38" s="10" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="T38" s="6"/>
       <c r="U38" s="6"/>
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B39" s="8">
         <v>46080.778288518515</v>
@@ -3644,16 +3647,16 @@
         <v>46149.197581886576</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I39" s="8">
         <v>46100</v>
@@ -3671,13 +3674,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="O39" s="9" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="P39" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="Q39" s="10" t="s">
         <v>31</v>
@@ -3697,7 +3700,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B40" s="5">
         <v>46080.77828673611</v>
@@ -3709,16 +3712,16 @@
         <v>46121.8600697338</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I40" s="5">
         <v>46100</v>
@@ -3736,29 +3739,29 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="Q40" s="11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="R40" s="6">
         <v>0</v>
       </c>
       <c r="S40" s="10" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="T40" s="6"/>
       <c r="U40" s="6"/>
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B41" s="8">
         <v>46080.77828702546</v>
@@ -3770,16 +3773,16 @@
         <v>46121.86006597222</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I41" s="8">
         <v>46120</v>
@@ -3797,29 +3800,29 @@
         <v>26</v>
       </c>
       <c r="N41" s="9" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O41" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="P41" s="9" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Q41" s="11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="R41" s="9">
         <v>0</v>
       </c>
       <c r="S41" s="10" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="T41" s="9"/>
       <c r="U41" s="9"/>
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B42" s="5">
         <v>46080.77828724537</v>
@@ -3831,16 +3834,16 @@
         <v>46210.17465634259</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I42" s="5">
         <v>46100</v>
@@ -3858,13 +3861,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="Q42" s="10" t="s">
         <v>31</v>
@@ -3884,7 +3887,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B43" s="8">
         <v>46080.77828748843</v>
@@ -3896,16 +3899,16 @@
         <v>46114.76045094908</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I43" s="8">
         <v>46100</v>
@@ -3923,29 +3926,29 @@
         <v>26</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="O43" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="P43" s="9" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Q43" s="11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="R43" s="9">
         <v>0</v>
       </c>
       <c r="S43" s="10" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="T43" s="9"/>
       <c r="U43" s="9"/>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B44" s="5">
         <v>46080.77828770834</v>
@@ -3957,16 +3960,16 @@
         <v>46114.7604978125</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I44" s="5">
         <v>46129</v>
@@ -3984,29 +3987,29 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Q44" s="11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="R44" s="6">
         <v>0</v>
       </c>
       <c r="S44" s="10" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="T44" s="6"/>
       <c r="U44" s="6"/>
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B45" s="8">
         <v>46080.778287939815</v>
@@ -4018,7 +4021,7 @@
         <v>46141.772341724536</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>25</v>
@@ -4042,7 +4045,7 @@
         <v>26</v>
       </c>
       <c r="O45" s="9" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="P45" s="9" t="s">
         <v>26</v>
@@ -4055,7 +4058,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B46" s="5">
         <v>46080.778288182875</v>
@@ -4067,16 +4070,16 @@
         <v>46127.67810105324</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="I46" s="5">
         <v>46098</v>
@@ -4094,13 +4097,13 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="O46" s="6" t="s">
         <v>67</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q46" s="10" t="s">
         <v>31</v>
@@ -4120,7 +4123,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B47" s="8">
         <v>46080.77828842592</v>
@@ -4132,16 +4135,16 @@
         <v>46158.16995894676</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="I47" s="8">
         <v>46140</v>
@@ -4159,13 +4162,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="O47" s="9" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="P47" s="9" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q47" s="10" t="s">
         <v>31</v>
@@ -4185,7 +4188,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B48" s="5">
         <v>46087.53644159722</v>
@@ -4197,16 +4200,16 @@
         <v>46161.20788581019</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="I48" s="6"/>
       <c r="J48" s="5">
@@ -4222,13 +4225,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q48" s="10" t="s">
         <v>31</v>
@@ -4248,7 +4251,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B49" s="8">
         <v>46087.536521331014</v>
@@ -4260,16 +4263,16 @@
         <v>46141.771787060185</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="I49" s="8">
         <v>46233</v>
@@ -4287,16 +4290,16 @@
         <v>26</v>
       </c>
       <c r="N49" s="9" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="P49" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q49" s="11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="R49" s="9">
         <v>1</v>
@@ -4313,7 +4316,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B50" s="5">
         <v>46080.77828866898</v>
@@ -4325,7 +4328,7 @@
         <v>46141.772585231476</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>25</v>
@@ -4349,7 +4352,7 @@
         <v>26</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>26</v>
@@ -4362,7 +4365,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B51" s="8">
         <v>46080.77828892361</v>
@@ -4374,16 +4377,16 @@
         <v>46151.18472762732</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I51" s="8">
         <v>46149</v>
@@ -4401,13 +4404,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="O51" s="9" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q51" s="10" t="s">
         <v>31</v>
@@ -4427,7 +4430,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B52" s="5">
         <v>46080.77828760417</v>
@@ -4439,16 +4442,16 @@
         <v>46155.20414789351</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="I52" s="5">
         <v>46153</v>
@@ -4466,13 +4469,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q52" s="10" t="s">
         <v>31</v>
@@ -4492,7 +4495,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B53" s="8">
         <v>46080.778288009256</v>
@@ -4504,7 +4507,7 @@
         <v>46141.77186175926</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>25</v>
@@ -4528,7 +4531,7 @@
         <v>26</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="P53" s="9" t="s">
         <v>26</v>
@@ -4541,7 +4544,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B54" s="5">
         <v>46080.77828832176</v>
@@ -4553,16 +4556,16 @@
         <v>46165.18131118055</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="I54" s="5">
         <v>46155</v>
@@ -4580,13 +4583,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q54" s="10" t="s">
         <v>31</v>
@@ -4606,7 +4609,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B55" s="8">
         <v>46080.77828861111</v>
@@ -4618,16 +4621,16 @@
         <v>46170.185211909724</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H55" s="9" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="I55" s="8">
         <v>46167</v>
@@ -4645,13 +4648,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="P55" s="9" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q55" s="10" t="s">
         <v>31</v>
@@ -4671,7 +4674,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B56" s="5">
         <v>46080.778288912035</v>
@@ -4683,16 +4686,16 @@
         <v>46172.2027446875</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="I56" s="5">
         <v>46170</v>
@@ -4710,13 +4713,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q56" s="10" t="s">
         <v>31</v>
@@ -4736,7 +4739,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B57" s="8">
         <v>46080.77828921296</v>
@@ -4748,7 +4751,7 @@
         <v>46141.77231675926</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>25</v>
@@ -4772,7 +4775,7 @@
         <v>26</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P57" s="9" t="s">
         <v>26</v>
@@ -4785,7 +4788,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B58" s="5">
         <v>46080.77828957176</v>
@@ -4797,16 +4800,16 @@
         <v>46156.16908381945</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I58" s="5">
         <v>46154</v>
@@ -4824,13 +4827,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q58" s="10" t="s">
         <v>31</v>
@@ -4850,7 +4853,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B59" s="8">
         <v>46080.77828986111</v>
@@ -4862,16 +4865,16 @@
         <v>46218.18543643519</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I59" s="8">
         <v>46216</v>
@@ -4889,13 +4892,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="P59" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q59" s="10" t="s">
         <v>31</v>
@@ -4915,7 +4918,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B60" s="5">
         <v>46080.778290138885</v>
@@ -4927,16 +4930,16 @@
         <v>46220.19441659722</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I60" s="5">
         <v>46226</v>
@@ -4954,16 +4957,16 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q60" s="12" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="R60" s="6">
         <v>1</v>
@@ -4980,7 +4983,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B61" s="8">
         <v>46080.778290393515</v>
@@ -4992,16 +4995,16 @@
         <v>46212.18789364584</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H61" s="9" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I61" s="8">
         <v>46210</v>
@@ -5019,13 +5022,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="P61" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q61" s="10" t="s">
         <v>31</v>
@@ -5045,7 +5048,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B62" s="5">
         <v>46080.7854796875</v>
@@ -5063,10 +5066,10 @@
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I62" s="5">
         <v>46199</v>
@@ -5084,13 +5087,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q62" s="10" t="s">
         <v>31</v>
@@ -5110,7 +5113,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B63" s="8">
         <v>46080.77828662037</v>
@@ -5122,7 +5125,7 @@
         <v>46141.71127789352</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>25</v>
@@ -5146,7 +5149,7 @@
         <v>26</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="P63" s="9" t="s">
         <v>26</v>
@@ -5159,7 +5162,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B64" s="5">
         <v>46080.77828694445</v>
@@ -5171,7 +5174,7 @@
         <v>46223.80691788194</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
@@ -5180,7 +5183,7 @@
         <v>84</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I64" s="5">
         <v>46174</v>
@@ -5198,13 +5201,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q64" s="10" t="s">
         <v>31</v>
@@ -5224,7 +5227,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B65" s="8">
         <v>46080.778287187495</v>
@@ -5236,7 +5239,7 @@
         <v>46224.18165298611</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>26</v>
@@ -5245,7 +5248,7 @@
         <v>84</v>
       </c>
       <c r="H65" s="9" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I65" s="8">
         <v>46230</v>
@@ -5263,16 +5266,16 @@
         <v>26</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="O65" s="9" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="P65" s="9" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q65" s="12" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="R65" s="9">
         <v>1</v>
@@ -5289,7 +5292,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B66" s="5">
         <v>46080.77828746528</v>
@@ -5301,7 +5304,7 @@
         <v>46223.80691021991</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
@@ -5310,7 +5313,7 @@
         <v>84</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I66" s="5">
         <v>46218</v>
@@ -5328,13 +5331,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q66" s="10" t="s">
         <v>31</v>
@@ -5354,7 +5357,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B67" s="8">
         <v>46080.77828770834</v>
@@ -5366,7 +5369,7 @@
         <v>46224.20544344907</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>26</v>
@@ -5375,7 +5378,7 @@
         <v>84</v>
       </c>
       <c r="H67" s="9" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I67" s="8">
         <v>46220</v>
@@ -5393,13 +5396,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="P67" s="9" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q67" s="10" t="s">
         <v>31</v>
@@ -5419,7 +5422,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B68" s="5">
         <v>46080.77828796297</v>
@@ -5431,7 +5434,7 @@
         <v>46223.80690207176</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
@@ -5440,7 +5443,7 @@
         <v>84</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I68" s="5">
         <v>46212</v>
@@ -5458,13 +5461,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q68" s="10" t="s">
         <v>31</v>
@@ -5484,7 +5487,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B69" s="8">
         <v>46080.778288217596</v>
@@ -5496,7 +5499,7 @@
         <v>46225.18881381945</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>26</v>
@@ -5505,7 +5508,7 @@
         <v>84</v>
       </c>
       <c r="H69" s="9" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I69" s="8">
         <v>46232</v>
@@ -5523,16 +5526,16 @@
         <v>26</v>
       </c>
       <c r="N69" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="P69" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q69" s="12" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="R69" s="9">
         <v>1</v>
@@ -5549,7 +5552,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B70" s="5">
         <v>46080.77828846065</v>
@@ -5561,7 +5564,7 @@
         <v>46223.80689234954</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
@@ -5570,7 +5573,7 @@
         <v>84</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I70" s="5">
         <v>46234</v>
@@ -5588,22 +5591,22 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q70" s="11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="R70" s="6">
         <v>1</v>
       </c>
       <c r="S70" s="10" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="T70" s="5">
         <v>46234</v>
@@ -5614,7 +5617,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B71" s="8">
         <v>46080.7782887037</v>
@@ -5626,7 +5629,7 @@
         <v>46141.712052731484</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>25</v>
@@ -5650,7 +5653,7 @@
         <v>26</v>
       </c>
       <c r="O71" s="9" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="P71" s="9" t="s">
         <v>26</v>
@@ -5663,7 +5666,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B72" s="5">
         <v>46080.77828895833</v>
@@ -5675,16 +5678,16 @@
         <v>46141.711805625004</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="I72" s="5">
         <v>46237</v>
@@ -5702,22 +5705,22 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q72" s="11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="R72" s="6">
         <v>1</v>
       </c>
       <c r="S72" s="10" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="T72" s="5">
         <v>46237</v>
@@ -5728,7 +5731,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B73" s="8">
         <v>46080.778287152774</v>
@@ -5740,7 +5743,7 @@
         <v>46224.575120925925</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>26</v>
@@ -5749,7 +5752,7 @@
         <v>84</v>
       </c>
       <c r="H73" s="9" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I73" s="8">
         <v>46238</v>
@@ -5767,22 +5770,22 @@
         <v>26</v>
       </c>
       <c r="N73" s="9" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="P73" s="9" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q73" s="11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="R73" s="9">
         <v>1</v>
       </c>
       <c r="S73" s="10" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="T73" s="8">
         <v>46238</v>
@@ -5793,7 +5796,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B74" s="5">
         <v>46080.77828751157</v>
@@ -5805,16 +5808,16 @@
         <v>46141.711917002314</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="I74" s="5">
         <v>46239</v>
@@ -5832,22 +5835,22 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q74" s="11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="R74" s="6">
         <v>1</v>
       </c>
       <c r="S74" s="10" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="T74" s="5">
         <v>46239</v>
@@ -5858,7 +5861,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B75" s="8">
         <v>46080.77828782407</v>
@@ -5870,16 +5873,16 @@
         <v>46141.71196212963</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H75" s="9" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="I75" s="8">
         <v>46240</v>
@@ -5897,22 +5900,22 @@
         <v>26</v>
       </c>
       <c r="N75" s="9" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="P75" s="9" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q75" s="11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="R75" s="9">
         <v>1</v>
       </c>
       <c r="S75" s="10" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="T75" s="8">
         <v>46240</v>
@@ -5923,7 +5926,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B76" s="5">
         <v>46080.77828809028</v>
@@ -5933,7 +5936,7 @@
         <v>46090.61092975695</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>25</v>
@@ -5957,7 +5960,7 @@
         <v>26</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="P76" s="6" t="s">
         <v>26</v>
@@ -5970,7 +5973,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B77" s="8">
         <v>46080.77828868055</v>
@@ -5986,10 +5989,10 @@
         <v>26</v>
       </c>
       <c r="G77" s="9" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H77" s="9" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="I77" s="8">
         <v>46241</v>
@@ -6007,22 +6010,22 @@
         <v>26</v>
       </c>
       <c r="N77" s="9" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="P77" s="9" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q77" s="11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="R77" s="9">
         <v>0</v>
       </c>
       <c r="S77" s="10" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="T77" s="8">
         <v>46241</v>
@@ -6033,7 +6036,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B78" s="5">
         <v>46080.77828835648</v>
@@ -6043,16 +6046,16 @@
         <v>46141.711970648146</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="I78" s="5">
         <v>46241</v>
@@ -6070,22 +6073,22 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q78" s="11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="R78" s="6">
         <v>0</v>
       </c>
       <c r="S78" s="10" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="T78" s="5">
         <v>46241</v>
@@ -6096,7 +6099,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B79" s="8">
         <v>46090.61171577546</v>
@@ -6106,7 +6109,7 @@
         <v>46090.614530335646</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>25</v>
@@ -6130,26 +6133,26 @@
         <v>26</v>
       </c>
       <c r="O79" s="9" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="P79" s="9" t="s">
         <v>26</v>
       </c>
       <c r="Q79" s="11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="R79" s="9">
         <v>0</v>
       </c>
       <c r="S79" s="10" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="T79" s="9"/>
       <c r="U79" s="9"/>
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B80" s="5">
         <v>46090.61199928241</v>
@@ -6159,7 +6162,7 @@
         <v>46141.711971944445</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
@@ -6186,22 +6189,22 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q80" s="11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="R80" s="6">
         <v>0</v>
       </c>
       <c r="S80" s="10" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="T80" s="5">
         <v>46241</v>
@@ -6212,7 +6215,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B81" s="8">
         <v>46090.61208010417</v>
@@ -6222,7 +6225,7 @@
         <v>46090.61869820602</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>26</v>
@@ -6249,22 +6252,22 @@
         <v>26</v>
       </c>
       <c r="N81" s="9" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="P81" s="9" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q81" s="11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="R81" s="9">
         <v>0</v>
       </c>
       <c r="S81" s="10" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="T81" s="8">
         <v>46252</v>

--- a/data/50001524 - ATACAMA KOZAN.xlsx
+++ b/data/50001524 - ATACAMA KOZAN.xlsx
@@ -409,154 +409,154 @@
     <t>Generación OC motor,Fabricación motor,Planos motor proveedor</t>
   </si>
   <si>
+    <t>1213470416901260</t>
+  </si>
+  <si>
+    <t>Generación OC motor</t>
+  </si>
+  <si>
+    <t>Fabricación motor,Planos motor proveedor,Motor</t>
+  </si>
+  <si>
+    <t>1213470416901261</t>
+  </si>
+  <si>
+    <t>Fabricación motor</t>
+  </si>
+  <si>
+    <t>Motor,Recepcion  motor</t>
+  </si>
+  <si>
+    <t>1213470416901262</t>
+  </si>
+  <si>
+    <t>Planos motor proveedor</t>
+  </si>
+  <si>
+    <t>Motor,Planos Definitivos</t>
+  </si>
+  <si>
+    <t>1213470416901263</t>
+  </si>
+  <si>
+    <t>Materiales a codigo // compras locales aprovisionamientomiento:</t>
+  </si>
+  <si>
+    <t>Yerlia Ayleen Castillo Diaz</t>
+  </si>
+  <si>
+    <t>yerlia.castillo@zitron.com</t>
+  </si>
+  <si>
+    <t>Generación OC materiales,Fabricacion a codigo y compras locales</t>
+  </si>
+  <si>
+    <t>1213470416901264</t>
+  </si>
+  <si>
+    <t>Generación OC materiales</t>
+  </si>
+  <si>
+    <t>Fabricacion a codigo y compras locales</t>
+  </si>
+  <si>
+    <t>1213470416901265</t>
+  </si>
+  <si>
+    <t>Generación OC materiales,Materiales a codigo // compras locales aprovisionamientomiento:,Recepcion materiales a codigos // compras locales aprovisionamiento</t>
+  </si>
+  <si>
+    <t>1213470416901266</t>
+  </si>
+  <si>
+    <t>Sensores</t>
+  </si>
+  <si>
+    <t>Generación Oc sensores,Fabricación Sensores</t>
+  </si>
+  <si>
+    <t>1213470416901267</t>
+  </si>
+  <si>
+    <t>Generación Oc sensores</t>
+  </si>
+  <si>
+    <t>Fabricación Sensores,Sensores</t>
+  </si>
+  <si>
+    <t>1213470416901268</t>
+  </si>
+  <si>
+    <t>Fabricación Sensores</t>
+  </si>
+  <si>
+    <t>Sensores,Recepcion sensores</t>
+  </si>
+  <si>
+    <t>1213470416901269</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseño:</t>
+  </si>
+  <si>
+    <t>Planos Preliminar,Planos Definitivos</t>
+  </si>
+  <si>
+    <t>1213470416901270</t>
+  </si>
+  <si>
+    <t>Planos Preliminar</t>
+  </si>
+  <si>
+    <t>Francisca González Cornejo</t>
+  </si>
+  <si>
+    <t>francisca.gonzalez@zitron.com</t>
+  </si>
+  <si>
+    <t>Planos Definitivos,Ingenieria y diseño:</t>
+  </si>
+  <si>
+    <t>1213470416901271</t>
+  </si>
+  <si>
+    <t>Planos Definitivos</t>
+  </si>
+  <si>
+    <t>Hernan Roberto Gutierrez Barrientos</t>
+  </si>
+  <si>
+    <t>hgutierrez@zitron.com</t>
+  </si>
+  <si>
+    <t>Planos motor proveedor,Planos Preliminar</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseño:,Check planos</t>
+  </si>
+  <si>
+    <t>1213561126963324</t>
+  </si>
+  <si>
+    <t>Check planos</t>
+  </si>
+  <si>
+    <t>Armado,Control de calidad Armado,Montaje motor,Montaje Alabe,Montaje Rodete,Montaje Sensor</t>
+  </si>
+  <si>
+    <t>1213561126963325</t>
+  </si>
+  <si>
+    <t>Check pruebas FAT</t>
+  </si>
+  <si>
+    <t>Pruebas FAT</t>
+  </si>
+  <si>
+    <t>RE-PINTADO</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1213470416901260</t>
-  </si>
-  <si>
-    <t>Generación OC motor</t>
-  </si>
-  <si>
-    <t>Fabricación motor,Planos motor proveedor,Motor</t>
-  </si>
-  <si>
-    <t>1213470416901261</t>
-  </si>
-  <si>
-    <t>Fabricación motor</t>
-  </si>
-  <si>
-    <t>Motor,Recepcion  motor</t>
-  </si>
-  <si>
-    <t>1213470416901262</t>
-  </si>
-  <si>
-    <t>Planos motor proveedor</t>
-  </si>
-  <si>
-    <t>Motor,Planos Definitivos</t>
-  </si>
-  <si>
-    <t>1213470416901263</t>
-  </si>
-  <si>
-    <t>Materiales a codigo // compras locales aprovisionamientomiento:</t>
-  </si>
-  <si>
-    <t>Yerlia Ayleen Castillo Diaz</t>
-  </si>
-  <si>
-    <t>yerlia.castillo@zitron.com</t>
-  </si>
-  <si>
-    <t>Generación OC materiales,Fabricacion a codigo y compras locales</t>
-  </si>
-  <si>
-    <t>1213470416901264</t>
-  </si>
-  <si>
-    <t>Generación OC materiales</t>
-  </si>
-  <si>
-    <t>Fabricacion a codigo y compras locales</t>
-  </si>
-  <si>
-    <t>1213470416901265</t>
-  </si>
-  <si>
-    <t>Generación OC materiales,Materiales a codigo // compras locales aprovisionamientomiento:,Recepcion materiales a codigos // compras locales aprovisionamiento</t>
-  </si>
-  <si>
-    <t>1213470416901266</t>
-  </si>
-  <si>
-    <t>Sensores</t>
-  </si>
-  <si>
-    <t>Generación Oc sensores,Fabricación Sensores</t>
-  </si>
-  <si>
-    <t>1213470416901267</t>
-  </si>
-  <si>
-    <t>Generación Oc sensores</t>
-  </si>
-  <si>
-    <t>Fabricación Sensores,Sensores</t>
-  </si>
-  <si>
-    <t>1213470416901268</t>
-  </si>
-  <si>
-    <t>Fabricación Sensores</t>
-  </si>
-  <si>
-    <t>Sensores,Recepcion sensores</t>
-  </si>
-  <si>
-    <t>1213470416901269</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseño:</t>
-  </si>
-  <si>
-    <t>Planos Preliminar,Planos Definitivos</t>
-  </si>
-  <si>
-    <t>1213470416901270</t>
-  </si>
-  <si>
-    <t>Planos Preliminar</t>
-  </si>
-  <si>
-    <t>Francisca González Cornejo</t>
-  </si>
-  <si>
-    <t>francisca.gonzalez@zitron.com</t>
-  </si>
-  <si>
-    <t>Planos Definitivos,Ingenieria y diseño:</t>
-  </si>
-  <si>
-    <t>1213470416901271</t>
-  </si>
-  <si>
-    <t>Planos Definitivos</t>
-  </si>
-  <si>
-    <t>Hernan Roberto Gutierrez Barrientos</t>
-  </si>
-  <si>
-    <t>hgutierrez@zitron.com</t>
-  </si>
-  <si>
-    <t>Planos motor proveedor,Planos Preliminar</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseño:,Check planos</t>
-  </si>
-  <si>
-    <t>1213561126963324</t>
-  </si>
-  <si>
-    <t>Check planos</t>
-  </si>
-  <si>
-    <t>Armado,Control de calidad Armado,Montaje motor,Montaje Alabe,Montaje Rodete,Montaje Sensor</t>
-  </si>
-  <si>
-    <t>1213561126963325</t>
-  </si>
-  <si>
-    <t>Check pruebas FAT</t>
-  </si>
-  <si>
-    <t>Pruebas FAT</t>
-  </si>
-  <si>
-    <t>RE-PINTADO</t>
   </si>
   <si>
     <t>1213470416901272</t>
@@ -3396,7 +3396,7 @@
         <v>46114.76327634259</v>
       </c>
       <c r="D35" s="8">
-        <v>46218.1834093287</v>
+        <v>46226.18144005787</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>130</v>
@@ -3434,8 +3434,8 @@
       <c r="P35" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="Q35" s="12" t="s">
-        <v>132</v>
+      <c r="Q35" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="R35" s="9">
         <v>1</v>
@@ -3452,7 +3452,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B36" s="5">
         <v>46080.77828773148</v>
@@ -3464,7 +3464,7 @@
         <v>46114.76319354167</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
@@ -3497,7 +3497,7 @@
         <v>77</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Q36" s="11" t="s">
         <v>107</v>
@@ -3513,7 +3513,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B37" s="8">
         <v>46080.77828799769</v>
@@ -3525,7 +3525,7 @@
         <v>46114.763248877316</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>26</v>
@@ -3555,10 +3555,10 @@
         <v>130</v>
       </c>
       <c r="O37" s="9" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="P37" s="9" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="Q37" s="11" t="s">
         <v>107</v>
@@ -3574,7 +3574,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B38" s="5">
         <v>46080.77828825232</v>
@@ -3586,7 +3586,7 @@
         <v>46114.7632599537</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
@@ -3616,10 +3616,10 @@
         <v>130</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="Q38" s="11" t="s">
         <v>107</v>
@@ -3635,7 +3635,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B39" s="8">
         <v>46080.778288518515</v>
@@ -3647,16 +3647,16 @@
         <v>46149.197581886576</v>
       </c>
       <c r="E39" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="F39" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G39" s="9" t="s">
         <v>143</v>
       </c>
-      <c r="F39" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G39" s="9" t="s">
+      <c r="H39" s="9" t="s">
         <v>144</v>
-      </c>
-      <c r="H39" s="9" t="s">
-        <v>145</v>
       </c>
       <c r="I39" s="8">
         <v>46100</v>
@@ -3677,7 +3677,7 @@
         <v>97</v>
       </c>
       <c r="O39" s="9" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="P39" s="9" t="s">
         <v>97</v>
@@ -3700,7 +3700,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B40" s="5">
         <v>46080.77828673611</v>
@@ -3712,16 +3712,16 @@
         <v>46121.8600697338</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="H40" s="6" t="s">
         <v>144</v>
-      </c>
-      <c r="H40" s="6" t="s">
-        <v>145</v>
       </c>
       <c r="I40" s="5">
         <v>46100</v>
@@ -3739,13 +3739,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="Q40" s="11" t="s">
         <v>107</v>
@@ -3761,7 +3761,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B41" s="8">
         <v>46080.77828702546</v>
@@ -3773,16 +3773,16 @@
         <v>46121.86006597222</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="H41" s="9" t="s">
         <v>144</v>
-      </c>
-      <c r="H41" s="9" t="s">
-        <v>145</v>
       </c>
       <c r="I41" s="8">
         <v>46120</v>
@@ -3800,13 +3800,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="9" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="O41" s="9" t="s">
         <v>94</v>
       </c>
       <c r="P41" s="9" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="Q41" s="11" t="s">
         <v>107</v>
@@ -3822,7 +3822,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B42" s="5">
         <v>46080.77828724537</v>
@@ -3834,16 +3834,16 @@
         <v>46210.17465634259</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="H42" s="6" t="s">
         <v>144</v>
-      </c>
-      <c r="H42" s="6" t="s">
-        <v>145</v>
       </c>
       <c r="I42" s="5">
         <v>46100</v>
@@ -3864,7 +3864,7 @@
         <v>97</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>97</v>
@@ -3887,7 +3887,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B43" s="8">
         <v>46080.77828748843</v>
@@ -3899,16 +3899,16 @@
         <v>46114.76045094908</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="H43" s="9" t="s">
         <v>144</v>
-      </c>
-      <c r="H43" s="9" t="s">
-        <v>145</v>
       </c>
       <c r="I43" s="8">
         <v>46100</v>
@@ -3926,13 +3926,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="O43" s="9" t="s">
         <v>91</v>
       </c>
       <c r="P43" s="9" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="Q43" s="11" t="s">
         <v>107</v>
@@ -3948,7 +3948,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B44" s="5">
         <v>46080.77828770834</v>
@@ -3960,16 +3960,16 @@
         <v>46114.7604978125</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="H44" s="6" t="s">
         <v>144</v>
-      </c>
-      <c r="H44" s="6" t="s">
-        <v>145</v>
       </c>
       <c r="I44" s="5">
         <v>46129</v>
@@ -3987,13 +3987,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="Q44" s="11" t="s">
         <v>107</v>
@@ -4009,7 +4009,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B45" s="8">
         <v>46080.778287939815</v>
@@ -4021,7 +4021,7 @@
         <v>46141.772341724536</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>25</v>
@@ -4045,7 +4045,7 @@
         <v>26</v>
       </c>
       <c r="O45" s="9" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="P45" s="9" t="s">
         <v>26</v>
@@ -4058,7 +4058,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B46" s="5">
         <v>46080.778288182875</v>
@@ -4070,16 +4070,16 @@
         <v>46127.67810105324</v>
       </c>
       <c r="E46" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="F46" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G46" s="6" t="s">
         <v>165</v>
       </c>
-      <c r="F46" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G46" s="6" t="s">
+      <c r="H46" s="6" t="s">
         <v>166</v>
-      </c>
-      <c r="H46" s="6" t="s">
-        <v>167</v>
       </c>
       <c r="I46" s="5">
         <v>46098</v>
@@ -4097,13 +4097,13 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="O46" s="6" t="s">
         <v>67</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="Q46" s="10" t="s">
         <v>31</v>
@@ -4123,7 +4123,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B47" s="8">
         <v>46080.77828842592</v>
@@ -4135,16 +4135,16 @@
         <v>46158.16995894676</v>
       </c>
       <c r="E47" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="F47" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G47" s="9" t="s">
         <v>170</v>
       </c>
-      <c r="F47" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G47" s="9" t="s">
+      <c r="H47" s="9" t="s">
         <v>171</v>
-      </c>
-      <c r="H47" s="9" t="s">
-        <v>172</v>
       </c>
       <c r="I47" s="8">
         <v>46140</v>
@@ -4162,13 +4162,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="O47" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="P47" s="9" t="s">
         <v>173</v>
-      </c>
-      <c r="P47" s="9" t="s">
-        <v>174</v>
       </c>
       <c r="Q47" s="10" t="s">
         <v>31</v>
@@ -4188,7 +4188,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B48" s="5">
         <v>46087.53644159722</v>
@@ -4200,16 +4200,16 @@
         <v>46161.20788581019</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="H48" s="6" t="s">
         <v>171</v>
-      </c>
-      <c r="H48" s="6" t="s">
-        <v>172</v>
       </c>
       <c r="I48" s="6"/>
       <c r="J48" s="5">
@@ -4225,13 +4225,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q48" s="10" t="s">
         <v>31</v>
@@ -4251,7 +4251,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B49" s="8">
         <v>46087.536521331014</v>
@@ -4260,19 +4260,19 @@
         <v>46140.83887265046</v>
       </c>
       <c r="D49" s="8">
-        <v>46141.771787060185</v>
+        <v>46226.177547245374</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="H49" s="9" t="s">
         <v>166</v>
-      </c>
-      <c r="H49" s="9" t="s">
-        <v>167</v>
       </c>
       <c r="I49" s="8">
         <v>46233</v>
@@ -4290,16 +4290,16 @@
         <v>26</v>
       </c>
       <c r="N49" s="9" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="O49" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="P49" s="9" t="s">
         <v>180</v>
       </c>
-      <c r="P49" s="9" t="s">
+      <c r="Q49" s="12" t="s">
         <v>181</v>
-      </c>
-      <c r="Q49" s="11" t="s">
-        <v>107</v>
       </c>
       <c r="R49" s="9">
         <v>1</v>
@@ -4407,7 +4407,7 @@
         <v>183</v>
       </c>
       <c r="O51" s="9" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="P51" s="9" t="s">
         <v>189</v>
@@ -4960,13 +4960,13 @@
         <v>183</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="P60" s="6" t="s">
         <v>221</v>
       </c>
       <c r="Q60" s="12" t="s">
-        <v>132</v>
+        <v>181</v>
       </c>
       <c r="R60" s="6">
         <v>1</v>
@@ -5025,7 +5025,7 @@
         <v>183</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="P61" s="9" t="s">
         <v>224</v>
@@ -5275,7 +5275,7 @@
         <v>236</v>
       </c>
       <c r="Q65" s="12" t="s">
-        <v>132</v>
+        <v>181</v>
       </c>
       <c r="R65" s="9">
         <v>1</v>
@@ -5499,7 +5499,7 @@
         <v>46225.18881381945</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>26</v>
@@ -5535,7 +5535,7 @@
         <v>248</v>
       </c>
       <c r="Q69" s="12" t="s">
-        <v>132</v>
+        <v>181</v>
       </c>
       <c r="R69" s="9">
         <v>1</v>
@@ -5564,7 +5564,7 @@
         <v>46223.80689234954</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
@@ -5594,7 +5594,7 @@
         <v>228</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="P70" s="6" t="s">
         <v>250</v>
@@ -5708,7 +5708,7 @@
         <v>252</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="P72" s="6" t="s">
         <v>258</v>

--- a/data/50001524 - ATACAMA KOZAN.xlsx
+++ b/data/50001524 - ATACAMA KOZAN.xlsx
@@ -4927,7 +4927,7 @@
         <v>46121.8679578125</v>
       </c>
       <c r="D60" s="5">
-        <v>46220.19441659722</v>
+        <v>46228.20468340278</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>220</v>
@@ -4965,8 +4965,8 @@
       <c r="P60" s="6" t="s">
         <v>221</v>
       </c>
-      <c r="Q60" s="12" t="s">
-        <v>181</v>
+      <c r="Q60" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="R60" s="6">
         <v>1</v>
@@ -5561,7 +5561,7 @@
         <v>46140.8390024074</v>
       </c>
       <c r="D70" s="5">
-        <v>46223.80689234954</v>
+        <v>46227.19814736111</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>180</v>
@@ -5599,8 +5599,8 @@
       <c r="P70" s="6" t="s">
         <v>250</v>
       </c>
-      <c r="Q70" s="11" t="s">
-        <v>107</v>
+      <c r="Q70" s="12" t="s">
+        <v>181</v>
       </c>
       <c r="R70" s="6">
         <v>1</v>
@@ -5675,7 +5675,7 @@
         <v>46140.83904666667</v>
       </c>
       <c r="D72" s="5">
-        <v>46141.711805625004</v>
+        <v>46230.16861260417</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>255</v>
@@ -5713,8 +5713,8 @@
       <c r="P72" s="6" t="s">
         <v>258</v>
       </c>
-      <c r="Q72" s="11" t="s">
-        <v>107</v>
+      <c r="Q72" s="12" t="s">
+        <v>181</v>
       </c>
       <c r="R72" s="6">
         <v>1</v>

--- a/data/50001524 - ATACAMA KOZAN.xlsx
+++ b/data/50001524 - ATACAMA KOZAN.xlsx
@@ -5740,7 +5740,7 @@
         <v>46141.711726180554</v>
       </c>
       <c r="D73" s="8">
-        <v>46224.575120925925</v>
+        <v>46231.1834590625</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>260</v>
@@ -5778,8 +5778,8 @@
       <c r="P73" s="9" t="s">
         <v>262</v>
       </c>
-      <c r="Q73" s="11" t="s">
-        <v>107</v>
+      <c r="Q73" s="12" t="s">
+        <v>181</v>
       </c>
       <c r="R73" s="9">
         <v>1</v>

--- a/data/50001524 - ATACAMA KOZAN.xlsx
+++ b/data/50001524 - ATACAMA KOZAN.xlsx
@@ -5236,7 +5236,7 @@
         <v>46133.620870451385</v>
       </c>
       <c r="D65" s="8">
-        <v>46224.18165298611</v>
+        <v>46232.187510625</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>234</v>
@@ -5274,8 +5274,8 @@
       <c r="P65" s="9" t="s">
         <v>236</v>
       </c>
-      <c r="Q65" s="12" t="s">
-        <v>181</v>
+      <c r="Q65" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="R65" s="9">
         <v>1</v>
@@ -5805,7 +5805,7 @@
         <v>46141.7119153588</v>
       </c>
       <c r="D74" s="5">
-        <v>46141.711917002314</v>
+        <v>46232.186334178245</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>264</v>
@@ -5843,8 +5843,8 @@
       <c r="P74" s="6" t="s">
         <v>265</v>
       </c>
-      <c r="Q74" s="11" t="s">
-        <v>107</v>
+      <c r="Q74" s="12" t="s">
+        <v>181</v>
       </c>
       <c r="R74" s="6">
         <v>1</v>

--- a/data/50001524 - ATACAMA KOZAN.xlsx
+++ b/data/50001524 - ATACAMA KOZAN.xlsx
@@ -5496,7 +5496,7 @@
         <v>46133.621873553246</v>
       </c>
       <c r="D69" s="8">
-        <v>46225.18881381945</v>
+        <v>46233.18282159722</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>179</v>
@@ -5534,8 +5534,8 @@
       <c r="P69" s="9" t="s">
         <v>248</v>
       </c>
-      <c r="Q69" s="12" t="s">
-        <v>181</v>
+      <c r="Q69" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="R69" s="9">
         <v>1</v>
@@ -5870,7 +5870,7 @@
         <v>46141.71196090278</v>
       </c>
       <c r="D75" s="8">
-        <v>46141.71196212963</v>
+        <v>46233.174222974536</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>267</v>
@@ -5908,8 +5908,8 @@
       <c r="P75" s="9" t="s">
         <v>268</v>
       </c>
-      <c r="Q75" s="11" t="s">
-        <v>107</v>
+      <c r="Q75" s="12" t="s">
+        <v>181</v>
       </c>
       <c r="R75" s="9">
         <v>1</v>

--- a/data/50001524 - ATACAMA KOZAN.xlsx
+++ b/data/50001524 - ATACAMA KOZAN.xlsx
@@ -556,214 +556,214 @@
     <t>RE-PINTADO</t>
   </si>
   <si>
+    <t>1213470416901272</t>
+  </si>
+  <si>
+    <t>Bodega:</t>
+  </si>
+  <si>
+    <t>Recepcion materiales a codigos // compras locales aprovisionamiento,Control de calidad compras materiales a codigo // compras locale aprovisionamiento</t>
+  </si>
+  <si>
+    <t>1213470416901273</t>
+  </si>
+  <si>
+    <t>Recepcion materiales a codigos // compras locales aprovisionamiento</t>
+  </si>
+  <si>
+    <t>Victor Muñoz</t>
+  </si>
+  <si>
+    <t>victor.munoz@zitron.com</t>
+  </si>
+  <si>
+    <t>Control de calidad compras materiales a codigo // compras locale aprovisionamiento,Bodega:</t>
+  </si>
+  <si>
+    <t>1213470416901274</t>
+  </si>
+  <si>
+    <t>Control de calidad compras materiales a codigo // compras locale aprovisionamiento</t>
+  </si>
+  <si>
+    <t>Nicolás López</t>
+  </si>
+  <si>
+    <t>nicolas.lopez@zitron.com</t>
+  </si>
+  <si>
+    <t>Bodega:,Preparación Materiales</t>
+  </si>
+  <si>
+    <t>1213470416901275</t>
+  </si>
+  <si>
+    <t>Caldereria:</t>
+  </si>
+  <si>
+    <t>Preparación Materiales,Armado,Control de calidad Armado</t>
+  </si>
+  <si>
+    <t>1213470416901276</t>
+  </si>
+  <si>
+    <t>Preparación Materiales</t>
+  </si>
+  <si>
+    <t>Nicolás Mol</t>
+  </si>
+  <si>
+    <t>nicolas.mol@zitron.com</t>
+  </si>
+  <si>
+    <t>Armado,Caldereria:</t>
+  </si>
+  <si>
+    <t>1213470416901277</t>
+  </si>
+  <si>
+    <t>Armado</t>
+  </si>
+  <si>
+    <t>Preparación Materiales,Check planos</t>
+  </si>
+  <si>
+    <t>Control de calidad Armado,Caldereria:</t>
+  </si>
+  <si>
+    <t>1213470416901278</t>
+  </si>
+  <si>
+    <t>Control de calidad Armado</t>
+  </si>
+  <si>
+    <t>Armado,Check planos</t>
+  </si>
+  <si>
+    <t>Caldereria:,Revestimiento</t>
+  </si>
+  <si>
+    <t>1213470416901279</t>
+  </si>
+  <si>
+    <t>Recepcion Rodete,Recepcion Alabe,Recepcion  motor,Recepcion sensores,Recepcion Tableros</t>
+  </si>
+  <si>
+    <t>1213470416901280</t>
+  </si>
+  <si>
+    <t>Recepcion Rodete</t>
+  </si>
+  <si>
+    <t>Bodega:,Montaje Rodete</t>
+  </si>
+  <si>
+    <t>1213470416901281</t>
+  </si>
+  <si>
+    <t>Recepcion Alabe</t>
+  </si>
+  <si>
+    <t>Bodega:,Montaje Alabe</t>
+  </si>
+  <si>
+    <t>1213470416901282</t>
+  </si>
+  <si>
+    <t>Recepcion  motor</t>
+  </si>
+  <si>
+    <t>Bodega:,Montaje motor</t>
+  </si>
+  <si>
+    <t>1213470416901283</t>
+  </si>
+  <si>
+    <t>Recepcion sensores</t>
+  </si>
+  <si>
+    <t>Bodega:,Montaje Sensor</t>
+  </si>
+  <si>
+    <t>1213458788103573</t>
+  </si>
+  <si>
+    <t>Bodega:,Revision Tableros</t>
+  </si>
+  <si>
+    <t>1213470416901284</t>
+  </si>
+  <si>
+    <t>Montaje:</t>
+  </si>
+  <si>
+    <t>Revestimiento,Montaje motor,Montaje Alabe,Montaje Rodete,Montaje Sensor,RE-PINTADO,Pruebas FAT</t>
+  </si>
+  <si>
+    <t>1213470416901285</t>
+  </si>
+  <si>
+    <t>Revestimiento</t>
+  </si>
+  <si>
+    <t>Montaje motor,Montaje Alabe,Montaje Rodete,Montaje Sensor,Montaje:</t>
+  </si>
+  <si>
+    <t>1213470416901286</t>
+  </si>
+  <si>
+    <t>Montaje motor</t>
+  </si>
+  <si>
+    <t>Revestimiento,Recepcion  motor,Check planos</t>
+  </si>
+  <si>
+    <t>Montaje:,Pruebas FAT</t>
+  </si>
+  <si>
+    <t>1213470416901287</t>
+  </si>
+  <si>
+    <t>Montaje Alabe</t>
+  </si>
+  <si>
+    <t>Revestimiento,Recepcion Alabe,Check planos</t>
+  </si>
+  <si>
+    <t>1213470416901288</t>
+  </si>
+  <si>
+    <t>Montaje Rodete</t>
+  </si>
+  <si>
+    <t>Revestimiento,Recepcion Rodete,Check planos</t>
+  </si>
+  <si>
+    <t>1213470416901289</t>
+  </si>
+  <si>
+    <t>Montaje Sensor</t>
+  </si>
+  <si>
+    <t>Revestimiento,Recepcion sensores,Check planos</t>
+  </si>
+  <si>
+    <t>1213470416901290</t>
+  </si>
+  <si>
+    <t>Montaje Sensor,Montaje motor,Montaje Alabe,Montaje Rodete</t>
+  </si>
+  <si>
+    <t>Montaje:,Check pruebas FAT</t>
+  </si>
+  <si>
+    <t>1213470414925601</t>
+  </si>
+  <si>
+    <t>Montaje:,Coordinacion Entrega con Cliente</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1213470416901272</t>
-  </si>
-  <si>
-    <t>Bodega:</t>
-  </si>
-  <si>
-    <t>Recepcion materiales a codigos // compras locales aprovisionamiento,Control de calidad compras materiales a codigo // compras locale aprovisionamiento</t>
-  </si>
-  <si>
-    <t>1213470416901273</t>
-  </si>
-  <si>
-    <t>Recepcion materiales a codigos // compras locales aprovisionamiento</t>
-  </si>
-  <si>
-    <t>Victor Muñoz</t>
-  </si>
-  <si>
-    <t>victor.munoz@zitron.com</t>
-  </si>
-  <si>
-    <t>Control de calidad compras materiales a codigo // compras locale aprovisionamiento,Bodega:</t>
-  </si>
-  <si>
-    <t>1213470416901274</t>
-  </si>
-  <si>
-    <t>Control de calidad compras materiales a codigo // compras locale aprovisionamiento</t>
-  </si>
-  <si>
-    <t>Nicolás López</t>
-  </si>
-  <si>
-    <t>nicolas.lopez@zitron.com</t>
-  </si>
-  <si>
-    <t>Bodega:,Preparación Materiales</t>
-  </si>
-  <si>
-    <t>1213470416901275</t>
-  </si>
-  <si>
-    <t>Caldereria:</t>
-  </si>
-  <si>
-    <t>Preparación Materiales,Armado,Control de calidad Armado</t>
-  </si>
-  <si>
-    <t>1213470416901276</t>
-  </si>
-  <si>
-    <t>Preparación Materiales</t>
-  </si>
-  <si>
-    <t>Nicolás Mol</t>
-  </si>
-  <si>
-    <t>nicolas.mol@zitron.com</t>
-  </si>
-  <si>
-    <t>Armado,Caldereria:</t>
-  </si>
-  <si>
-    <t>1213470416901277</t>
-  </si>
-  <si>
-    <t>Armado</t>
-  </si>
-  <si>
-    <t>Preparación Materiales,Check planos</t>
-  </si>
-  <si>
-    <t>Control de calidad Armado,Caldereria:</t>
-  </si>
-  <si>
-    <t>1213470416901278</t>
-  </si>
-  <si>
-    <t>Control de calidad Armado</t>
-  </si>
-  <si>
-    <t>Armado,Check planos</t>
-  </si>
-  <si>
-    <t>Caldereria:,Revestimiento</t>
-  </si>
-  <si>
-    <t>1213470416901279</t>
-  </si>
-  <si>
-    <t>Recepcion Rodete,Recepcion Alabe,Recepcion  motor,Recepcion sensores,Recepcion Tableros</t>
-  </si>
-  <si>
-    <t>1213470416901280</t>
-  </si>
-  <si>
-    <t>Recepcion Rodete</t>
-  </si>
-  <si>
-    <t>Bodega:,Montaje Rodete</t>
-  </si>
-  <si>
-    <t>1213470416901281</t>
-  </si>
-  <si>
-    <t>Recepcion Alabe</t>
-  </si>
-  <si>
-    <t>Bodega:,Montaje Alabe</t>
-  </si>
-  <si>
-    <t>1213470416901282</t>
-  </si>
-  <si>
-    <t>Recepcion  motor</t>
-  </si>
-  <si>
-    <t>Bodega:,Montaje motor</t>
-  </si>
-  <si>
-    <t>1213470416901283</t>
-  </si>
-  <si>
-    <t>Recepcion sensores</t>
-  </si>
-  <si>
-    <t>Bodega:,Montaje Sensor</t>
-  </si>
-  <si>
-    <t>1213458788103573</t>
-  </si>
-  <si>
-    <t>Bodega:,Revision Tableros</t>
-  </si>
-  <si>
-    <t>1213470416901284</t>
-  </si>
-  <si>
-    <t>Montaje:</t>
-  </si>
-  <si>
-    <t>Revestimiento,Montaje motor,Montaje Alabe,Montaje Rodete,Montaje Sensor,RE-PINTADO,Pruebas FAT</t>
-  </si>
-  <si>
-    <t>1213470416901285</t>
-  </si>
-  <si>
-    <t>Revestimiento</t>
-  </si>
-  <si>
-    <t>Montaje motor,Montaje Alabe,Montaje Rodete,Montaje Sensor,Montaje:</t>
-  </si>
-  <si>
-    <t>1213470416901286</t>
-  </si>
-  <si>
-    <t>Montaje motor</t>
-  </si>
-  <si>
-    <t>Revestimiento,Recepcion  motor,Check planos</t>
-  </si>
-  <si>
-    <t>Montaje:,Pruebas FAT</t>
-  </si>
-  <si>
-    <t>1213470416901287</t>
-  </si>
-  <si>
-    <t>Montaje Alabe</t>
-  </si>
-  <si>
-    <t>Revestimiento,Recepcion Alabe,Check planos</t>
-  </si>
-  <si>
-    <t>1213470416901288</t>
-  </si>
-  <si>
-    <t>Montaje Rodete</t>
-  </si>
-  <si>
-    <t>Revestimiento,Recepcion Rodete,Check planos</t>
-  </si>
-  <si>
-    <t>1213470416901289</t>
-  </si>
-  <si>
-    <t>Montaje Sensor</t>
-  </si>
-  <si>
-    <t>Revestimiento,Recepcion sensores,Check planos</t>
-  </si>
-  <si>
-    <t>1213470416901290</t>
-  </si>
-  <si>
-    <t>Montaje Sensor,Montaje motor,Montaje Alabe,Montaje Rodete</t>
-  </si>
-  <si>
-    <t>Montaje:,Check pruebas FAT</t>
-  </si>
-  <si>
-    <t>1213470414925601</t>
-  </si>
-  <si>
-    <t>Montaje:,Coordinacion Entrega con Cliente</t>
   </si>
   <si>
     <t>1213470414925602</t>
@@ -4260,7 +4260,7 @@
         <v>46140.83887265046</v>
       </c>
       <c r="D49" s="8">
-        <v>46226.177547245374</v>
+        <v>46234.1840334375</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>178</v>
@@ -4298,8 +4298,8 @@
       <c r="P49" s="9" t="s">
         <v>180</v>
       </c>
-      <c r="Q49" s="12" t="s">
-        <v>181</v>
+      <c r="Q49" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="R49" s="9">
         <v>1</v>
@@ -4316,7 +4316,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B50" s="5">
         <v>46080.77828866898</v>
@@ -4328,7 +4328,7 @@
         <v>46141.772585231476</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>25</v>
@@ -4352,7 +4352,7 @@
         <v>26</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>26</v>
@@ -4365,7 +4365,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B51" s="8">
         <v>46080.77828892361</v>
@@ -4377,16 +4377,16 @@
         <v>46151.18472762732</v>
       </c>
       <c r="E51" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="F51" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G51" s="9" t="s">
         <v>186</v>
       </c>
-      <c r="F51" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G51" s="9" t="s">
+      <c r="H51" s="9" t="s">
         <v>187</v>
-      </c>
-      <c r="H51" s="9" t="s">
-        <v>188</v>
       </c>
       <c r="I51" s="8">
         <v>46149</v>
@@ -4404,13 +4404,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="O51" s="9" t="s">
         <v>148</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="Q51" s="10" t="s">
         <v>31</v>
@@ -4430,7 +4430,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B52" s="5">
         <v>46080.77828760417</v>
@@ -4442,16 +4442,16 @@
         <v>46155.20414789351</v>
       </c>
       <c r="E52" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="F52" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G52" s="6" t="s">
         <v>191</v>
       </c>
-      <c r="F52" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G52" s="6" t="s">
+      <c r="H52" s="6" t="s">
         <v>192</v>
-      </c>
-      <c r="H52" s="6" t="s">
-        <v>193</v>
       </c>
       <c r="I52" s="5">
         <v>46153</v>
@@ -4469,13 +4469,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="Q52" s="10" t="s">
         <v>31</v>
@@ -4495,7 +4495,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B53" s="8">
         <v>46080.778288009256</v>
@@ -4507,7 +4507,7 @@
         <v>46141.77186175926</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>25</v>
@@ -4531,7 +4531,7 @@
         <v>26</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P53" s="9" t="s">
         <v>26</v>
@@ -4544,7 +4544,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B54" s="5">
         <v>46080.77828832176</v>
@@ -4556,16 +4556,16 @@
         <v>46165.18131118055</v>
       </c>
       <c r="E54" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="F54" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G54" s="6" t="s">
         <v>199</v>
       </c>
-      <c r="F54" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G54" s="6" t="s">
+      <c r="H54" s="6" t="s">
         <v>200</v>
-      </c>
-      <c r="H54" s="6" t="s">
-        <v>201</v>
       </c>
       <c r="I54" s="5">
         <v>46155</v>
@@ -4583,13 +4583,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="Q54" s="10" t="s">
         <v>31</v>
@@ -4609,7 +4609,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B55" s="8">
         <v>46080.77828861111</v>
@@ -4621,16 +4621,16 @@
         <v>46170.185211909724</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="9" t="s">
+        <v>199</v>
+      </c>
+      <c r="H55" s="9" t="s">
         <v>200</v>
-      </c>
-      <c r="H55" s="9" t="s">
-        <v>201</v>
       </c>
       <c r="I55" s="8">
         <v>46167</v>
@@ -4648,13 +4648,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="9" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="O55" s="9" t="s">
+        <v>204</v>
+      </c>
+      <c r="P55" s="9" t="s">
         <v>205</v>
-      </c>
-      <c r="P55" s="9" t="s">
-        <v>206</v>
       </c>
       <c r="Q55" s="10" t="s">
         <v>31</v>
@@ -4674,7 +4674,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B56" s="5">
         <v>46080.778288912035</v>
@@ -4686,16 +4686,16 @@
         <v>46172.2027446875</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="H56" s="6" t="s">
         <v>192</v>
-      </c>
-      <c r="H56" s="6" t="s">
-        <v>193</v>
       </c>
       <c r="I56" s="5">
         <v>46170</v>
@@ -4713,13 +4713,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="O56" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="P56" s="6" t="s">
         <v>209</v>
-      </c>
-      <c r="P56" s="6" t="s">
-        <v>210</v>
       </c>
       <c r="Q56" s="10" t="s">
         <v>31</v>
@@ -4739,7 +4739,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B57" s="8">
         <v>46080.77828921296</v>
@@ -4751,7 +4751,7 @@
         <v>46141.77231675926</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>25</v>
@@ -4775,7 +4775,7 @@
         <v>26</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="P57" s="9" t="s">
         <v>26</v>
@@ -4788,7 +4788,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B58" s="5">
         <v>46080.77828957176</v>
@@ -4800,16 +4800,16 @@
         <v>46156.16908381945</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="H58" s="6" t="s">
         <v>187</v>
-      </c>
-      <c r="H58" s="6" t="s">
-        <v>188</v>
       </c>
       <c r="I58" s="5">
         <v>46154</v>
@@ -4827,13 +4827,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="O58" s="6" t="s">
         <v>127</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="Q58" s="10" t="s">
         <v>31</v>
@@ -4853,7 +4853,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B59" s="8">
         <v>46080.77828986111</v>
@@ -4865,16 +4865,16 @@
         <v>46218.18543643519</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="H59" s="9" t="s">
         <v>187</v>
-      </c>
-      <c r="H59" s="9" t="s">
-        <v>188</v>
       </c>
       <c r="I59" s="8">
         <v>46216</v>
@@ -4892,13 +4892,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="O59" s="9" t="s">
         <v>127</v>
       </c>
       <c r="P59" s="9" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="Q59" s="10" t="s">
         <v>31</v>
@@ -4918,7 +4918,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B60" s="5">
         <v>46080.778290138885</v>
@@ -4930,16 +4930,16 @@
         <v>46228.20468340278</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="H60" s="6" t="s">
         <v>187</v>
-      </c>
-      <c r="H60" s="6" t="s">
-        <v>188</v>
       </c>
       <c r="I60" s="5">
         <v>46226</v>
@@ -4957,13 +4957,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="O60" s="6" t="s">
         <v>136</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="Q60" s="10" t="s">
         <v>31</v>
@@ -4983,7 +4983,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B61" s="8">
         <v>46080.778290393515</v>
@@ -4995,16 +4995,16 @@
         <v>46212.18789364584</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="H61" s="9" t="s">
         <v>187</v>
-      </c>
-      <c r="H61" s="9" t="s">
-        <v>188</v>
       </c>
       <c r="I61" s="8">
         <v>46210</v>
@@ -5022,13 +5022,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="O61" s="9" t="s">
         <v>158</v>
       </c>
       <c r="P61" s="9" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="Q61" s="10" t="s">
         <v>31</v>
@@ -5048,7 +5048,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B62" s="5">
         <v>46080.7854796875</v>
@@ -5066,10 +5066,10 @@
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="H62" s="6" t="s">
         <v>187</v>
-      </c>
-      <c r="H62" s="6" t="s">
-        <v>188</v>
       </c>
       <c r="I62" s="5">
         <v>46199</v>
@@ -5087,13 +5087,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="O62" s="6" t="s">
         <v>118</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="Q62" s="10" t="s">
         <v>31</v>
@@ -5113,7 +5113,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B63" s="8">
         <v>46080.77828662037</v>
@@ -5125,7 +5125,7 @@
         <v>46141.71127789352</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>25</v>
@@ -5149,7 +5149,7 @@
         <v>26</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="P63" s="9" t="s">
         <v>26</v>
@@ -5162,7 +5162,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B64" s="5">
         <v>46080.77828694445</v>
@@ -5174,7 +5174,7 @@
         <v>46223.80691788194</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
@@ -5201,13 +5201,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="Q64" s="10" t="s">
         <v>31</v>
@@ -5227,7 +5227,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B65" s="8">
         <v>46080.778287187495</v>
@@ -5239,7 +5239,7 @@
         <v>46232.187510625</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>26</v>
@@ -5266,13 +5266,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="O65" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="P65" s="9" t="s">
         <v>235</v>
-      </c>
-      <c r="P65" s="9" t="s">
-        <v>236</v>
       </c>
       <c r="Q65" s="10" t="s">
         <v>31</v>
@@ -5292,7 +5292,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B66" s="5">
         <v>46080.77828746528</v>
@@ -5304,7 +5304,7 @@
         <v>46223.80691021991</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
@@ -5331,13 +5331,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="Q66" s="10" t="s">
         <v>31</v>
@@ -5357,7 +5357,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B67" s="8">
         <v>46080.77828770834</v>
@@ -5369,7 +5369,7 @@
         <v>46224.20544344907</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>26</v>
@@ -5396,13 +5396,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="P67" s="9" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="Q67" s="10" t="s">
         <v>31</v>
@@ -5422,7 +5422,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B68" s="5">
         <v>46080.77828796297</v>
@@ -5434,7 +5434,7 @@
         <v>46223.80690207176</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
@@ -5461,13 +5461,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="Q68" s="10" t="s">
         <v>31</v>
@@ -5487,7 +5487,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B69" s="8">
         <v>46080.778288217596</v>
@@ -5526,13 +5526,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="9" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="O69" s="9" t="s">
+        <v>246</v>
+      </c>
+      <c r="P69" s="9" t="s">
         <v>247</v>
-      </c>
-      <c r="P69" s="9" t="s">
-        <v>248</v>
       </c>
       <c r="Q69" s="10" t="s">
         <v>31</v>
@@ -5552,7 +5552,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B70" s="5">
         <v>46080.77828846065</v>
@@ -5591,16 +5591,16 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="O70" s="6" t="s">
         <v>178</v>
       </c>
       <c r="P70" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="Q70" s="12" t="s">
         <v>250</v>
-      </c>
-      <c r="Q70" s="12" t="s">
-        <v>181</v>
       </c>
       <c r="R70" s="6">
         <v>1</v>
@@ -5714,7 +5714,7 @@
         <v>258</v>
       </c>
       <c r="Q72" s="12" t="s">
-        <v>181</v>
+        <v>250</v>
       </c>
       <c r="R72" s="6">
         <v>1</v>
@@ -5779,7 +5779,7 @@
         <v>262</v>
       </c>
       <c r="Q73" s="12" t="s">
-        <v>181</v>
+        <v>250</v>
       </c>
       <c r="R73" s="9">
         <v>1</v>
@@ -5814,10 +5814,10 @@
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="H74" s="6" t="s">
         <v>200</v>
-      </c>
-      <c r="H74" s="6" t="s">
-        <v>201</v>
       </c>
       <c r="I74" s="5">
         <v>46239</v>
@@ -5844,7 +5844,7 @@
         <v>265</v>
       </c>
       <c r="Q74" s="12" t="s">
-        <v>181</v>
+        <v>250</v>
       </c>
       <c r="R74" s="6">
         <v>1</v>
@@ -5879,10 +5879,10 @@
         <v>26</v>
       </c>
       <c r="G75" s="9" t="s">
+        <v>199</v>
+      </c>
+      <c r="H75" s="9" t="s">
         <v>200</v>
-      </c>
-      <c r="H75" s="9" t="s">
-        <v>201</v>
       </c>
       <c r="I75" s="8">
         <v>46240</v>
@@ -5909,7 +5909,7 @@
         <v>268</v>
       </c>
       <c r="Q75" s="12" t="s">
-        <v>181</v>
+        <v>250</v>
       </c>
       <c r="R75" s="9">
         <v>1</v>

--- a/data/50001524 - ATACAMA KOZAN.xlsx
+++ b/data/50001524 - ATACAMA KOZAN.xlsx
@@ -763,31 +763,31 @@
     <t>Montaje:,Coordinacion Entrega con Cliente</t>
   </si>
   <si>
+    <t>1213470414925602</t>
+  </si>
+  <si>
+    <t>Logistica:</t>
+  </si>
+  <si>
+    <t>Coordinacion Entrega con Cliente,Embalaje,PACKING LIST,Despacho</t>
+  </si>
+  <si>
+    <t>1213470414925603</t>
+  </si>
+  <si>
+    <t>Coordinacion Entrega con Cliente</t>
+  </si>
+  <si>
+    <t>Karin Pinto</t>
+  </si>
+  <si>
+    <t>kpinto@zitron.com</t>
+  </si>
+  <si>
+    <t>Embalaje,Logistica:</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1213470414925602</t>
-  </si>
-  <si>
-    <t>Logistica:</t>
-  </si>
-  <si>
-    <t>Coordinacion Entrega con Cliente,Embalaje,PACKING LIST,Despacho</t>
-  </si>
-  <si>
-    <t>1213470414925603</t>
-  </si>
-  <si>
-    <t>Coordinacion Entrega con Cliente</t>
-  </si>
-  <si>
-    <t>Karin Pinto</t>
-  </si>
-  <si>
-    <t>kpinto@zitron.com</t>
-  </si>
-  <si>
-    <t>Embalaje,Logistica:</t>
   </si>
   <si>
     <t>1213470414925604</t>
@@ -5561,7 +5561,7 @@
         <v>46140.8390024074</v>
       </c>
       <c r="D70" s="5">
-        <v>46227.19814736111</v>
+        <v>46235.19700590278</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>180</v>
@@ -5599,8 +5599,8 @@
       <c r="P70" s="6" t="s">
         <v>249</v>
       </c>
-      <c r="Q70" s="12" t="s">
-        <v>250</v>
+      <c r="Q70" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="R70" s="6">
         <v>1</v>
@@ -5617,7 +5617,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B71" s="8">
         <v>46080.7782887037</v>
@@ -5629,7 +5629,7 @@
         <v>46141.712052731484</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>25</v>
@@ -5653,7 +5653,7 @@
         <v>26</v>
       </c>
       <c r="O71" s="9" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="P71" s="9" t="s">
         <v>26</v>
@@ -5666,7 +5666,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B72" s="5">
         <v>46080.77828895833</v>
@@ -5678,16 +5678,16 @@
         <v>46230.16861260417</v>
       </c>
       <c r="E72" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="F72" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G72" s="6" t="s">
         <v>255</v>
       </c>
-      <c r="F72" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G72" s="6" t="s">
+      <c r="H72" s="6" t="s">
         <v>256</v>
-      </c>
-      <c r="H72" s="6" t="s">
-        <v>257</v>
       </c>
       <c r="I72" s="5">
         <v>46237</v>
@@ -5705,16 +5705,16 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="O72" s="6" t="s">
         <v>180</v>
       </c>
       <c r="P72" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="Q72" s="12" t="s">
         <v>258</v>
-      </c>
-      <c r="Q72" s="12" t="s">
-        <v>250</v>
       </c>
       <c r="R72" s="6">
         <v>1</v>
@@ -5770,7 +5770,7 @@
         <v>26</v>
       </c>
       <c r="N73" s="9" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="O73" s="9" t="s">
         <v>261</v>
@@ -5779,7 +5779,7 @@
         <v>262</v>
       </c>
       <c r="Q73" s="12" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="R73" s="9">
         <v>1</v>
@@ -5835,7 +5835,7 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="O74" s="6" t="s">
         <v>260</v>
@@ -5844,7 +5844,7 @@
         <v>265</v>
       </c>
       <c r="Q74" s="12" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="R74" s="6">
         <v>1</v>
@@ -5900,7 +5900,7 @@
         <v>26</v>
       </c>
       <c r="N75" s="9" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="O75" s="9" t="s">
         <v>264</v>
@@ -5909,7 +5909,7 @@
         <v>268</v>
       </c>
       <c r="Q75" s="12" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="R75" s="9">
         <v>1</v>

--- a/data/50001524 - ATACAMA KOZAN.xlsx
+++ b/data/50001524 - ATACAMA KOZAN.xlsx
@@ -787,19 +787,19 @@
     <t>Embalaje,Logistica:</t>
   </si>
   <si>
+    <t>1213470414925604</t>
+  </si>
+  <si>
+    <t>Embalaje</t>
+  </si>
+  <si>
+    <t>Coordinacion Entrega con Cliente,Revision Tableros</t>
+  </si>
+  <si>
+    <t>PACKING LIST,Logistica:</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1213470414925604</t>
-  </si>
-  <si>
-    <t>Embalaje</t>
-  </si>
-  <si>
-    <t>Coordinacion Entrega con Cliente,Revision Tableros</t>
-  </si>
-  <si>
-    <t>PACKING LIST,Logistica:</t>
   </si>
   <si>
     <t>1213470414925605</t>
@@ -5675,7 +5675,7 @@
         <v>46140.83904666667</v>
       </c>
       <c r="D72" s="5">
-        <v>46230.16861260417</v>
+        <v>46238.16738209491</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>254</v>
@@ -5713,8 +5713,8 @@
       <c r="P72" s="6" t="s">
         <v>257</v>
       </c>
-      <c r="Q72" s="12" t="s">
-        <v>258</v>
+      <c r="Q72" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="R72" s="6">
         <v>1</v>
@@ -5731,7 +5731,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B73" s="8">
         <v>46080.778287152774</v>
@@ -5743,7 +5743,7 @@
         <v>46231.1834590625</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>26</v>
@@ -5773,13 +5773,13 @@
         <v>251</v>
       </c>
       <c r="O73" s="9" t="s">
+        <v>260</v>
+      </c>
+      <c r="P73" s="9" t="s">
         <v>261</v>
       </c>
-      <c r="P73" s="9" t="s">
+      <c r="Q73" s="12" t="s">
         <v>262</v>
-      </c>
-      <c r="Q73" s="12" t="s">
-        <v>258</v>
       </c>
       <c r="R73" s="9">
         <v>1</v>
@@ -5838,13 +5838,13 @@
         <v>251</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="P74" s="6" t="s">
         <v>265</v>
       </c>
       <c r="Q74" s="12" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="R74" s="6">
         <v>1</v>
@@ -5909,7 +5909,7 @@
         <v>268</v>
       </c>
       <c r="Q75" s="12" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="R75" s="9">
         <v>1</v>

--- a/data/50001524 - ATACAMA KOZAN.xlsx
+++ b/data/50001524 - ATACAMA KOZAN.xlsx
@@ -799,16 +799,16 @@
     <t>PACKING LIST,Logistica:</t>
   </si>
   <si>
+    <t>1213470414925605</t>
+  </si>
+  <si>
+    <t>PACKING LIST</t>
+  </si>
+  <si>
+    <t>Despacho,Logistica:</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1213470414925605</t>
-  </si>
-  <si>
-    <t>PACKING LIST</t>
-  </si>
-  <si>
-    <t>Despacho,Logistica:</t>
   </si>
   <si>
     <t>1213470414925606</t>
@@ -5740,7 +5740,7 @@
         <v>46141.711726180554</v>
       </c>
       <c r="D73" s="8">
-        <v>46231.1834590625</v>
+        <v>46239.17956423611</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>259</v>
@@ -5778,8 +5778,8 @@
       <c r="P73" s="9" t="s">
         <v>261</v>
       </c>
-      <c r="Q73" s="12" t="s">
-        <v>262</v>
+      <c r="Q73" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="R73" s="9">
         <v>1</v>
@@ -5796,7 +5796,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B74" s="5">
         <v>46080.77828751157</v>
@@ -5808,7 +5808,7 @@
         <v>46232.186334178245</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
@@ -5841,10 +5841,10 @@
         <v>259</v>
       </c>
       <c r="P74" s="6" t="s">
+        <v>264</v>
+      </c>
+      <c r="Q74" s="12" t="s">
         <v>265</v>
-      </c>
-      <c r="Q74" s="12" t="s">
-        <v>262</v>
       </c>
       <c r="R74" s="6">
         <v>1</v>
@@ -5903,13 +5903,13 @@
         <v>251</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="P75" s="9" t="s">
         <v>268</v>
       </c>
       <c r="Q75" s="12" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="R75" s="9">
         <v>1</v>

--- a/data/50001524 - ATACAMA KOZAN.xlsx
+++ b/data/50001524 - ATACAMA KOZAN.xlsx
@@ -808,16 +808,16 @@
     <t>Despacho,Logistica:</t>
   </si>
   <si>
+    <t>1213470414925606</t>
+  </si>
+  <si>
+    <t>Despacho</t>
+  </si>
+  <si>
+    <t>Logistica:,Costos,Gestion,instalación de componentes</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1213470414925606</t>
-  </si>
-  <si>
-    <t>Despacho</t>
-  </si>
-  <si>
-    <t>Logistica:,Costos,Gestion,instalación de componentes</t>
   </si>
   <si>
     <t>1213470414925607</t>
@@ -5805,7 +5805,7 @@
         <v>46141.7119153588</v>
       </c>
       <c r="D74" s="5">
-        <v>46232.186334178245</v>
+        <v>46240.187568333335</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>263</v>
@@ -5843,8 +5843,8 @@
       <c r="P74" s="6" t="s">
         <v>264</v>
       </c>
-      <c r="Q74" s="12" t="s">
-        <v>265</v>
+      <c r="Q74" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="R74" s="6">
         <v>1</v>
@@ -5861,7 +5861,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B75" s="8">
         <v>46080.77828782407</v>
@@ -5873,7 +5873,7 @@
         <v>46233.174222974536</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>26</v>
@@ -5906,10 +5906,10 @@
         <v>263</v>
       </c>
       <c r="P75" s="9" t="s">
+        <v>267</v>
+      </c>
+      <c r="Q75" s="12" t="s">
         <v>268</v>
-      </c>
-      <c r="Q75" s="12" t="s">
-        <v>265</v>
       </c>
       <c r="R75" s="9">
         <v>1</v>
@@ -6076,7 +6076,7 @@
         <v>270</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P78" s="6" t="s">
         <v>270</v>
@@ -6192,7 +6192,7 @@
         <v>279</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P80" s="6" t="s">
         <v>283</v>

--- a/data/50001524 - ATACAMA KOZAN.xlsx
+++ b/data/50001524 - ATACAMA KOZAN.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="998" uniqueCount="286">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="960" uniqueCount="278">
   <si>
     <t>50001524 - ATACAMA KOZAN</t>
   </si>
@@ -814,7 +814,7 @@
     <t>Despacho</t>
   </si>
   <si>
-    <t>Logistica:,Costos,Gestion,instalación de componentes</t>
+    <t>Logistica:,Costos,Gestion</t>
   </si>
   <si>
     <t>Media</t>
@@ -845,30 +845,6 @@
   </si>
   <si>
     <t>Gestion</t>
-  </si>
-  <si>
-    <t>1213575386156156</t>
-  </si>
-  <si>
-    <t>Puesta en marcha Servicios</t>
-  </si>
-  <si>
-    <t>instalación de componentes,Pruebas de instalación de componentes</t>
-  </si>
-  <si>
-    <t>1213575386156158</t>
-  </si>
-  <si>
-    <t>instalación de componentes</t>
-  </si>
-  <si>
-    <t>Pruebas de instalación de componentes,Puesta en marcha Servicios</t>
-  </si>
-  <si>
-    <t>1213575386156160</t>
-  </si>
-  <si>
-    <t>Pruebas de instalación de componentes</t>
   </si>
 </sst>
 </file>
@@ -1392,7 +1368,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:U81"/>
+  <dimension ref="A1:U78"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10.4" customWidth="1"/>
@@ -5870,7 +5846,7 @@
         <v>46141.71196090278</v>
       </c>
       <c r="D75" s="8">
-        <v>46233.174222974536</v>
+        <v>46240.71927141203</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>266</v>
@@ -6095,185 +6071,6 @@
       </c>
       <c r="U78" s="5">
         <v>46251</v>
-      </c>
-    </row>
-    <row r="79" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A79" s="7" t="s">
-        <v>278</v>
-      </c>
-      <c r="B79" s="8">
-        <v>46090.61171577546</v>
-      </c>
-      <c r="C79" s="9"/>
-      <c r="D79" s="8">
-        <v>46090.614530335646</v>
-      </c>
-      <c r="E79" s="9" t="s">
-        <v>279</v>
-      </c>
-      <c r="F79" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="G79" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H79" s="9"/>
-      <c r="I79" s="9"/>
-      <c r="J79" s="9"/>
-      <c r="K79" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L79" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M79" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="N79" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="O79" s="9" t="s">
-        <v>280</v>
-      </c>
-      <c r="P79" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q79" s="11" t="s">
-        <v>107</v>
-      </c>
-      <c r="R79" s="9">
-        <v>0</v>
-      </c>
-      <c r="S79" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="T79" s="9"/>
-      <c r="U79" s="9"/>
-    </row>
-    <row r="80" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A80" s="4" t="s">
-        <v>281</v>
-      </c>
-      <c r="B80" s="5">
-        <v>46090.61199928241</v>
-      </c>
-      <c r="C80" s="6"/>
-      <c r="D80" s="5">
-        <v>46141.711971944445</v>
-      </c>
-      <c r="E80" s="6" t="s">
-        <v>282</v>
-      </c>
-      <c r="F80" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G80" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="H80" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="I80" s="5">
-        <v>46241</v>
-      </c>
-      <c r="J80" s="5">
-        <v>46251</v>
-      </c>
-      <c r="K80" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L80" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M80" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N80" s="6" t="s">
-        <v>279</v>
-      </c>
-      <c r="O80" s="6" t="s">
-        <v>266</v>
-      </c>
-      <c r="P80" s="6" t="s">
-        <v>283</v>
-      </c>
-      <c r="Q80" s="11" t="s">
-        <v>107</v>
-      </c>
-      <c r="R80" s="6">
-        <v>0</v>
-      </c>
-      <c r="S80" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="T80" s="5">
-        <v>46241</v>
-      </c>
-      <c r="U80" s="5">
-        <v>46251</v>
-      </c>
-    </row>
-    <row r="81" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A81" s="7" t="s">
-        <v>284</v>
-      </c>
-      <c r="B81" s="8">
-        <v>46090.61208010417</v>
-      </c>
-      <c r="C81" s="9"/>
-      <c r="D81" s="8">
-        <v>46090.61869820602</v>
-      </c>
-      <c r="E81" s="9" t="s">
-        <v>285</v>
-      </c>
-      <c r="F81" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G81" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="H81" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="I81" s="8">
-        <v>46252</v>
-      </c>
-      <c r="J81" s="8">
-        <v>46260</v>
-      </c>
-      <c r="K81" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L81" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M81" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N81" s="9" t="s">
-        <v>279</v>
-      </c>
-      <c r="O81" s="9" t="s">
-        <v>282</v>
-      </c>
-      <c r="P81" s="9" t="s">
-        <v>279</v>
-      </c>
-      <c r="Q81" s="11" t="s">
-        <v>107</v>
-      </c>
-      <c r="R81" s="9">
-        <v>0</v>
-      </c>
-      <c r="S81" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="T81" s="8">
-        <v>46252</v>
-      </c>
-      <c r="U81" s="8">
-        <v>46260</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001524 - ATACAMA KOZAN.xlsx
+++ b/data/50001524 - ATACAMA KOZAN.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="960" uniqueCount="278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="961" uniqueCount="278">
   <si>
     <t>50001524 - ATACAMA KOZAN</t>
   </si>
@@ -5907,9 +5907,11 @@
       <c r="B76" s="5">
         <v>46080.77828809028</v>
       </c>
-      <c r="C76" s="6"/>
+      <c r="C76" s="5">
+        <v>46240.815848865735</v>
+      </c>
       <c r="D76" s="5">
-        <v>46090.61092975695</v>
+        <v>46240.815850011575</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>270</v>
@@ -5942,8 +5944,12 @@
         <v>26</v>
       </c>
       <c r="Q76" s="6"/>
-      <c r="R76" s="6"/>
-      <c r="S76" s="6"/>
+      <c r="R76" s="6">
+        <v>1</v>
+      </c>
+      <c r="S76" s="11" t="s">
+        <v>32</v>
+      </c>
       <c r="T76" s="6"/>
       <c r="U76" s="6"/>
     </row>
@@ -5954,9 +5960,11 @@
       <c r="B77" s="8">
         <v>46080.77828868055</v>
       </c>
-      <c r="C77" s="9"/>
+      <c r="C77" s="8">
+        <v>46240.815745381944</v>
+      </c>
       <c r="D77" s="8">
-        <v>46141.711969386575</v>
+        <v>46240.81576049769</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>72</v>
@@ -5998,10 +6006,10 @@
         <v>107</v>
       </c>
       <c r="R77" s="9">
-        <v>0</v>
-      </c>
-      <c r="S77" s="10" t="s">
-        <v>108</v>
+        <v>1</v>
+      </c>
+      <c r="S77" s="11" t="s">
+        <v>32</v>
       </c>
       <c r="T77" s="8">
         <v>46241</v>
@@ -6017,9 +6025,11 @@
       <c r="B78" s="5">
         <v>46080.77828835648</v>
       </c>
-      <c r="C78" s="6"/>
+      <c r="C78" s="5">
+        <v>46240.81575891204</v>
+      </c>
       <c r="D78" s="5">
-        <v>46141.711970648146</v>
+        <v>46240.81577349537</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>277</v>
@@ -6061,10 +6071,10 @@
         <v>107</v>
       </c>
       <c r="R78" s="6">
-        <v>0</v>
-      </c>
-      <c r="S78" s="10" t="s">
-        <v>108</v>
+        <v>1</v>
+      </c>
+      <c r="S78" s="11" t="s">
+        <v>32</v>
       </c>
       <c r="T78" s="5">
         <v>46241</v>

--- a/data/50001524 - ATACAMA KOZAN.xlsx
+++ b/data/50001524 - ATACAMA KOZAN.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="961" uniqueCount="278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="961" uniqueCount="277">
   <si>
     <t>50001524 - ATACAMA KOZAN</t>
   </si>
@@ -815,9 +815,6 @@
   </si>
   <si>
     <t>Logistica:,Costos,Gestion</t>
-  </si>
-  <si>
-    <t>Media</t>
   </si>
   <si>
     <t>1213470414925607</t>
@@ -5846,7 +5843,7 @@
         <v>46141.71196090278</v>
       </c>
       <c r="D75" s="8">
-        <v>46240.71927141203</v>
+        <v>46241.18253277778</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>266</v>
@@ -5884,8 +5881,8 @@
       <c r="P75" s="9" t="s">
         <v>267</v>
       </c>
-      <c r="Q75" s="12" t="s">
-        <v>268</v>
+      <c r="Q75" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="R75" s="9">
         <v>1</v>
@@ -5902,7 +5899,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B76" s="5">
         <v>46080.77828809028</v>
@@ -5914,7 +5911,7 @@
         <v>46240.815850011575</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>25</v>
@@ -5938,7 +5935,7 @@
         <v>26</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="P76" s="6" t="s">
         <v>26</v>
@@ -5955,7 +5952,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B77" s="8">
         <v>46080.77828868055</v>
@@ -5973,10 +5970,10 @@
         <v>26</v>
       </c>
       <c r="G77" s="9" t="s">
+        <v>272</v>
+      </c>
+      <c r="H77" s="9" t="s">
         <v>273</v>
-      </c>
-      <c r="H77" s="9" t="s">
-        <v>274</v>
       </c>
       <c r="I77" s="8">
         <v>46241</v>
@@ -5994,13 +5991,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="9" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="P77" s="9" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="Q77" s="11" t="s">
         <v>107</v>
@@ -6020,7 +6017,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B78" s="5">
         <v>46080.77828835648</v>
@@ -6032,16 +6029,16 @@
         <v>46240.81577349537</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
+        <v>272</v>
+      </c>
+      <c r="H78" s="6" t="s">
         <v>273</v>
-      </c>
-      <c r="H78" s="6" t="s">
-        <v>274</v>
       </c>
       <c r="I78" s="5">
         <v>46241</v>
@@ -6059,13 +6056,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="O78" s="6" t="s">
         <v>266</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="Q78" s="11" t="s">
         <v>107</v>

--- a/data/50001524 - ATACAMA KOZAN.xlsx
+++ b/data/50001524 - ATACAMA KOZAN.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="961" uniqueCount="277">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="961" uniqueCount="278">
   <si>
     <t>50001524 - ATACAMA KOZAN</t>
   </si>
@@ -836,6 +836,9 @@
   </si>
   <si>
     <t>Despacho,Analisis de costeo</t>
+  </si>
+  <si>
+    <t>Media</t>
   </si>
   <si>
     <t>1213470414925608</t>
@@ -5961,7 +5964,7 @@
         <v>46240.815745381944</v>
       </c>
       <c r="D77" s="8">
-        <v>46240.81576049769</v>
+        <v>46244.191082060184</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>72</v>
@@ -5999,8 +6002,8 @@
       <c r="P77" s="9" t="s">
         <v>269</v>
       </c>
-      <c r="Q77" s="11" t="s">
-        <v>107</v>
+      <c r="Q77" s="12" t="s">
+        <v>275</v>
       </c>
       <c r="R77" s="9">
         <v>1</v>
@@ -6017,7 +6020,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B78" s="5">
         <v>46080.77828835648</v>
@@ -6026,10 +6029,10 @@
         <v>46240.81575891204</v>
       </c>
       <c r="D78" s="5">
-        <v>46240.81577349537</v>
+        <v>46244.19108202546</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
@@ -6064,8 +6067,8 @@
       <c r="P78" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="Q78" s="11" t="s">
-        <v>107</v>
+      <c r="Q78" s="12" t="s">
+        <v>275</v>
       </c>
       <c r="R78" s="6">
         <v>1</v>

--- a/data/50001524 - ATACAMA KOZAN.xlsx
+++ b/data/50001524 - ATACAMA KOZAN.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="961" uniqueCount="278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="961" uniqueCount="277">
   <si>
     <t>50001524 - ATACAMA KOZAN</t>
   </si>
@@ -836,9 +836,6 @@
   </si>
   <si>
     <t>Despacho,Analisis de costeo</t>
-  </si>
-  <si>
-    <t>Media</t>
   </si>
   <si>
     <t>1213470414925608</t>
@@ -5964,7 +5961,7 @@
         <v>46240.815745381944</v>
       </c>
       <c r="D77" s="8">
-        <v>46244.191082060184</v>
+        <v>46252.18359792824</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>72</v>
@@ -6002,8 +5999,8 @@
       <c r="P77" s="9" t="s">
         <v>269</v>
       </c>
-      <c r="Q77" s="12" t="s">
-        <v>275</v>
+      <c r="Q77" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="R77" s="9">
         <v>1</v>
@@ -6020,7 +6017,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B78" s="5">
         <v>46080.77828835648</v>
@@ -6029,10 +6026,10 @@
         <v>46240.81575891204</v>
       </c>
       <c r="D78" s="5">
-        <v>46244.19108202546</v>
+        <v>46252.18359729167</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
@@ -6067,8 +6064,8 @@
       <c r="P78" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="Q78" s="12" t="s">
-        <v>275</v>
+      <c r="Q78" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="R78" s="6">
         <v>1</v>
